--- a/lists.xlsx
+++ b/lists.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/StatsAutomator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A238B7-64BD-DB45-8EED-205A97B176C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B1CB04-19C4-EE4D-A186-3C611368B863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" xr2:uid="{98AF27AA-E156-FB4B-94CA-68D339A0B8C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" concurrentCalc="0"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4595,7 +4595,7 @@
     <col min="2" max="2" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="59" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="41.83203125" style="1" bestFit="1" customWidth="1"/>
@@ -4604,17 +4604,17 @@
     <col min="11" max="11" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="2.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.5" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="2.6640625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="59.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="59.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11.5" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="2.6640625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="59.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="59.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="2.6640625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="69.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="65.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="2.6640625" style="1" customWidth="1"/>
     <col min="26" max="16384" width="27.83203125" style="1"/>
   </cols>

--- a/lists.xlsx
+++ b/lists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/StatsAutomator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B1CB04-19C4-EE4D-A186-3C611368B863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B65318D-006E-8947-85B1-69098BDA2F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" xr2:uid="{98AF27AA-E156-FB4B-94CA-68D339A0B8C2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2265" uniqueCount="1281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="1282">
   <si>
     <t>Avatar</t>
   </si>
@@ -2315,9 +2315,6 @@
     <t>How to Lose a Guy in 10 Days</t>
   </si>
   <si>
-    <t>Kwaidan</t>
-  </si>
-  <si>
     <t>Neon Genesis Evangelion: The End of Evangelion</t>
   </si>
   <si>
@@ -2327,12 +2324,6 @@
     <t>Talk to Me</t>
   </si>
   <si>
-    <t>Demon Slayer -Kimetsu no Yaiba- The Movie: Mugen Train</t>
-  </si>
-  <si>
-    <t>Gangs of Wasseypur</t>
-  </si>
-  <si>
     <t>How to Make Millions Before Grandma Dies</t>
   </si>
   <si>
@@ -3879,6 +3870,18 @@
   </si>
   <si>
     <t>Most Watched Title</t>
+  </si>
+  <si>
+    <t>Terminator 2: Judgement Day</t>
+  </si>
+  <si>
+    <t>Scent of a Woman</t>
+  </si>
+  <si>
+    <t>Drishyam</t>
+  </si>
+  <si>
+    <t>An Autumn Afternoon</t>
   </si>
 </sst>
 </file>
@@ -4673,10 +4676,10 @@
       </c>
       <c r="V1" s="7"/>
       <c r="W1" s="35" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="X1" s="35" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="Y1" s="7"/>
     </row>
@@ -4692,10 +4695,10 @@
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="25" t="s">
-        <v>762</v>
+        <v>1278</v>
       </c>
       <c r="F2" s="19">
-        <v>2022</v>
+        <v>1991</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="10" t="s">
@@ -4753,10 +4756,10 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="25" t="s">
-        <v>758</v>
+        <v>487</v>
       </c>
       <c r="F3" s="19">
-        <v>2003</v>
+        <v>1982</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="10" t="s">
@@ -4814,10 +4817,10 @@
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="25" t="s">
-        <v>59</v>
+        <v>764</v>
       </c>
       <c r="F4" s="19">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="10" t="s">
@@ -4875,10 +4878,10 @@
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="25" t="s">
-        <v>100</v>
+        <v>761</v>
       </c>
       <c r="F5" s="19">
-        <v>1987</v>
+        <v>2022</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="10" t="s">
@@ -4936,10 +4939,10 @@
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="25" t="s">
-        <v>101</v>
+        <v>758</v>
       </c>
       <c r="F6" s="19">
-        <v>1989</v>
+        <v>2003</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="10" t="s">
@@ -4993,10 +4996,10 @@
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="25" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="F7" s="19">
-        <v>1989</v>
+        <v>2013</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="10" t="s">
@@ -5048,10 +5051,10 @@
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="25" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F8" s="19">
-        <v>2015</v>
+        <v>1987</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="10" t="s">
@@ -5103,10 +5106,10 @@
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="25" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F9" s="19">
-        <v>2007</v>
+        <v>1989</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="10" t="s">
@@ -5158,10 +5161,10 @@
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="25" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F10" s="19">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="10" t="s">
@@ -5213,10 +5216,10 @@
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="25" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F11" s="19">
-        <v>1957</v>
+        <v>2015</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="10" t="s">
@@ -5268,10 +5271,10 @@
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="25" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F12" s="19">
-        <v>1993</v>
+        <v>2007</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="10" t="s">
@@ -5323,10 +5326,10 @@
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="25" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F13" s="19">
-        <v>2009</v>
+        <v>1990</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="10" t="s">
@@ -5378,10 +5381,10 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="25" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F14" s="19">
-        <v>2013</v>
+        <v>1957</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="10" t="s">
@@ -5433,10 +5436,10 @@
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="25" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F15" s="19">
-        <v>2011</v>
+        <v>1993</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="10" t="s">
@@ -5488,10 +5491,10 @@
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F16" s="19">
-        <v>1999</v>
+        <v>2009</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="10" t="s">
@@ -5543,10 +5546,10 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="25" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="F17" s="19">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="10" t="s">
@@ -5598,10 +5601,10 @@
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F18" s="19">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="10" t="s">
@@ -5653,10 +5656,10 @@
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="25" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F19" s="19">
-        <v>1994</v>
+        <v>1999</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="10" t="s">
@@ -5708,10 +5711,10 @@
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="25" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="F20" s="19">
-        <v>2011</v>
+        <v>2024</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="10" t="s">
@@ -5763,10 +5766,10 @@
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="25" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F21" s="19">
-        <v>2018</v>
+        <v>2009</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="10" t="s">
@@ -5818,10 +5821,10 @@
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="25" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F22" s="19">
-        <v>2013</v>
+        <v>1994</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="10" t="s">
@@ -5873,10 +5876,10 @@
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="25" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F23" s="19">
-        <v>1973</v>
+        <v>2011</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="10" t="s">
@@ -5928,10 +5931,10 @@
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="25" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F24" s="19">
-        <v>2004</v>
+        <v>2018</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="10" t="s">
@@ -5957,10 +5960,10 @@
       </c>
       <c r="S24" s="4"/>
       <c r="T24" s="13" t="s">
-        <v>759</v>
+        <v>1281</v>
       </c>
       <c r="U24" s="12">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="36" t="s">
@@ -5983,10 +5986,10 @@
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="25" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F25" s="19">
-        <v>2004</v>
+        <v>2013</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="10" t="s">
@@ -6038,10 +6041,10 @@
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="25" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F26" s="19">
-        <v>2020</v>
+        <v>1973</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="10" t="s">
@@ -6093,10 +6096,10 @@
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="25" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F27" s="19">
-        <v>1984</v>
+        <v>2004</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="10" t="s">
@@ -6148,10 +6151,10 @@
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="25" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F28" s="19">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="10" t="s">
@@ -6203,10 +6206,10 @@
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="25" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F29" s="19">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="10" t="s">
@@ -6258,10 +6261,10 @@
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="25" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F30" s="19">
-        <v>2022</v>
+        <v>1984</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="10" t="s">
@@ -6313,10 +6316,10 @@
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="25" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
       <c r="F31" s="19">
-        <v>2024</v>
+        <v>2008</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="10" t="s">
@@ -6368,10 +6371,10 @@
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F32" s="19">
-        <v>2002</v>
+        <v>2022</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="10" t="s">
@@ -6381,8 +6384,12 @@
         <v>1980</v>
       </c>
       <c r="J32" s="2"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
+      <c r="K32" s="33" t="s">
+        <v>362</v>
+      </c>
+      <c r="L32" s="34">
+        <v>2000</v>
+      </c>
       <c r="M32" s="3"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="18" t="s">
@@ -6419,10 +6426,10 @@
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="25" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F33" s="19">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="10" t="s">
@@ -6432,6 +6439,9 @@
         <v>1995</v>
       </c>
       <c r="J33" s="2"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
       <c r="P33" s="3"/>
       <c r="Q33" s="18" t="s">
         <v>125</v>
@@ -6467,10 +6477,10 @@
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="25" t="s">
-        <v>127</v>
+        <v>9</v>
       </c>
       <c r="F34" s="19">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="10" t="s">
@@ -6515,10 +6525,10 @@
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="25" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F35" s="19">
-        <v>2019</v>
+        <v>2002</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="10" t="s">
@@ -6563,10 +6573,10 @@
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="25" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F36" s="19">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="10" t="s">
@@ -6611,10 +6621,10 @@
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="25" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F37" s="19">
-        <v>2003</v>
+        <v>2023</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="10" t="s">
@@ -6659,10 +6669,10 @@
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="25" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F38" s="19">
-        <v>1995</v>
+        <v>2019</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="10" t="s">
@@ -6707,10 +6717,10 @@
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="25" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F39" s="19">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="10" t="s">
@@ -6755,10 +6765,10 @@
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="25" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F40" s="19">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="10" t="s">
@@ -6803,7 +6813,7 @@
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="25" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F41" s="19">
         <v>1995</v>
@@ -6851,10 +6861,10 @@
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="25" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F42" s="19">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="10" t="s">
@@ -6899,10 +6909,10 @@
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F43" s="19">
-        <v>1999</v>
+        <v>2007</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="10" t="s">
@@ -6947,10 +6957,10 @@
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="25" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F44" s="19">
-        <v>2023</v>
+        <v>1995</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="10" t="s">
@@ -6995,10 +7005,10 @@
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="25" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F45" s="19">
-        <v>1986</v>
+        <v>2022</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="10" t="s">
@@ -7043,10 +7053,10 @@
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="25" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F46" s="19">
-        <v>2005</v>
+        <v>1999</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="10" t="s">
@@ -7091,10 +7101,10 @@
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="25" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F47" s="19">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="10" t="s">
@@ -7139,10 +7149,10 @@
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="25" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F48" s="19">
-        <v>1997</v>
+        <v>1986</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="10" t="s">
@@ -7187,10 +7197,10 @@
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="25" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F49" s="19">
-        <v>2024</v>
+        <v>2005</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="10" t="s">
@@ -7235,10 +7245,10 @@
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="25" t="s">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="F50" s="19">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="10" t="s">
@@ -7283,10 +7293,10 @@
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="25" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F51" s="19">
-        <v>2005</v>
+        <v>1997</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="10" t="s">
@@ -7331,10 +7341,10 @@
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="25" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F52" s="19">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="10" t="s">
@@ -7379,10 +7389,10 @@
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="25" t="s">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="F53" s="19">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="10" t="s">
@@ -7427,10 +7437,10 @@
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="25" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F54" s="19">
-        <v>2023</v>
+        <v>2005</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="10" t="s">
@@ -7475,10 +7485,10 @@
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="25" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F55" s="19">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="10" t="s">
@@ -7523,7 +7533,7 @@
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="25" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F56" s="19">
         <v>2023</v>
@@ -7571,10 +7581,10 @@
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="25" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F57" s="19">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="10" t="s">
@@ -7619,10 +7629,10 @@
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="25" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F58" s="19">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="10" t="s">
@@ -7667,10 +7677,10 @@
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="25" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F59" s="19">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="10" t="s">
@@ -7715,10 +7725,10 @@
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="25" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F60" s="19">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="10" t="s">
@@ -7763,10 +7773,10 @@
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="25" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F61" s="19">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="10" t="s">
@@ -7811,10 +7821,10 @@
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="25" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F62" s="19">
-        <v>2009</v>
+        <v>2020</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="10" t="s">
@@ -7859,10 +7869,10 @@
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="25" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F63" s="19">
-        <v>1996</v>
+        <v>2007</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="10" t="s">
@@ -7907,10 +7917,10 @@
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="25" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F64" s="19">
-        <v>1998</v>
+        <v>2021</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="10" t="s">
@@ -7955,10 +7965,10 @@
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="25" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F65" s="19">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="10" t="s">
@@ -8003,10 +8013,10 @@
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="25" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F66" s="19">
-        <v>2022</v>
+        <v>1996</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="10" t="s">
@@ -8051,10 +8061,10 @@
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="25" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F67" s="19">
-        <v>2023</v>
+        <v>1998</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="10" t="s">
@@ -8099,10 +8109,10 @@
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="25" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F68" s="19">
-        <v>1978</v>
+        <v>2014</v>
       </c>
       <c r="G68" s="4"/>
       <c r="H68" s="10" t="s">
@@ -8147,10 +8157,10 @@
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="25" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F69" s="19">
-        <v>2000</v>
+        <v>2022</v>
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="10" t="s">
@@ -8195,10 +8205,10 @@
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="25" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F70" s="19">
-        <v>2003</v>
+        <v>2023</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="10" t="s">
@@ -8243,10 +8253,10 @@
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="25" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F71" s="19">
-        <v>1989</v>
+        <v>1978</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="10" t="s">
@@ -8291,10 +8301,10 @@
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="25" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F72" s="19">
-        <v>2015</v>
+        <v>2000</v>
       </c>
       <c r="G72" s="4"/>
       <c r="H72" s="10" t="s">
@@ -8339,10 +8349,10 @@
       </c>
       <c r="D73" s="3"/>
       <c r="E73" s="25" t="s">
-        <v>87</v>
+        <v>162</v>
       </c>
       <c r="F73" s="19">
-        <v>2022</v>
+        <v>2003</v>
       </c>
       <c r="G73" s="4"/>
       <c r="H73" s="10" t="s">
@@ -8387,10 +8397,10 @@
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="25" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F74" s="19">
-        <v>2024</v>
+        <v>1989</v>
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="10" t="s">
@@ -8435,10 +8445,10 @@
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="25" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F75" s="19">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="G75" s="4"/>
       <c r="H75" s="10" t="s">
@@ -8483,10 +8493,10 @@
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="25" t="s">
-        <v>167</v>
+        <v>87</v>
       </c>
       <c r="F76" s="19">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="10" t="s">
@@ -8531,10 +8541,10 @@
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="25" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F77" s="19">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="10" t="s">
@@ -8579,10 +8589,10 @@
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="25" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F78" s="19">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="10" t="s">
@@ -8627,10 +8637,10 @@
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="25" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F79" s="19">
-        <v>1996</v>
+        <v>2006</v>
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="10" t="s">
@@ -8675,10 +8685,10 @@
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="25" t="s">
-        <v>58</v>
+        <v>168</v>
       </c>
       <c r="F80" s="19">
-        <v>2007</v>
+        <v>2021</v>
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="10" t="s">
@@ -8723,10 +8733,10 @@
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="25" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F81" s="19">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="10" t="s">
@@ -8771,10 +8781,10 @@
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F82" s="19">
-        <v>2022</v>
+        <v>1996</v>
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="10" t="s">
@@ -8819,10 +8829,10 @@
       </c>
       <c r="D83" s="2"/>
       <c r="E83" s="25" t="s">
-        <v>173</v>
+        <v>58</v>
       </c>
       <c r="F83" s="19">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="G83" s="4"/>
       <c r="H83" s="10" t="s">
@@ -8867,10 +8877,10 @@
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="25" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F84" s="19">
-        <v>2001</v>
+        <v>2021</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="10" t="s">
@@ -8915,10 +8925,10 @@
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="25" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F85" s="19">
-        <v>2005</v>
+        <v>2022</v>
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="10" t="s">
@@ -8963,10 +8973,10 @@
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="25" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F86" s="19">
-        <v>2023</v>
+        <v>2011</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="10" t="s">
@@ -9011,10 +9021,10 @@
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="25" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F87" s="19">
-        <v>2017</v>
+        <v>2001</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="10" t="s">
@@ -9059,10 +9069,10 @@
       </c>
       <c r="D88" s="2"/>
       <c r="E88" s="25" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F88" s="19">
-        <v>1988</v>
+        <v>2005</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="10" t="s">
@@ -9107,10 +9117,10 @@
       </c>
       <c r="D89" s="2"/>
       <c r="E89" s="25" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F89" s="19">
-        <v>2002</v>
+        <v>2023</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="10" t="s">
@@ -9155,10 +9165,10 @@
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="25" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F90" s="19">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="10" t="s">
@@ -9203,10 +9213,10 @@
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="25" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F91" s="19">
-        <v>2008</v>
+        <v>1988</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="10" t="s">
@@ -9251,10 +9261,10 @@
       </c>
       <c r="D92" s="2"/>
       <c r="E92" s="25" t="s">
-        <v>57</v>
+        <v>179</v>
       </c>
       <c r="F92" s="19">
-        <v>2017</v>
+        <v>2002</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="10" t="s">
@@ -9299,10 +9309,10 @@
       </c>
       <c r="D93" s="2"/>
       <c r="E93" s="25" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F93" s="19">
-        <v>1998</v>
+        <v>2016</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="10" t="s">
@@ -9347,10 +9357,10 @@
       </c>
       <c r="D94" s="2"/>
       <c r="E94" s="25" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F94" s="19">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="10" t="s">
@@ -9395,10 +9405,10 @@
       </c>
       <c r="D95" s="2"/>
       <c r="E95" s="25" t="s">
-        <v>184</v>
+        <v>57</v>
       </c>
       <c r="F95" s="19">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="G95" s="4"/>
       <c r="H95" s="10" t="s">
@@ -9443,10 +9453,10 @@
       </c>
       <c r="D96" s="2"/>
       <c r="E96" s="25" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F96" s="19">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="10" t="s">
@@ -9491,10 +9501,10 @@
       </c>
       <c r="D97" s="2"/>
       <c r="E97" s="25" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F97" s="19">
-        <v>2014</v>
+        <v>2004</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="10" t="s">
@@ -9539,10 +9549,10 @@
       </c>
       <c r="D98" s="2"/>
       <c r="E98" s="25" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F98" s="19">
-        <v>1978</v>
+        <v>2010</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="10" t="s">
@@ -9587,10 +9597,10 @@
       </c>
       <c r="D99" s="2"/>
       <c r="E99" s="25" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F99" s="19">
-        <v>2005</v>
+        <v>2000</v>
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="10" t="s">
@@ -9635,10 +9645,10 @@
       </c>
       <c r="D100" s="2"/>
       <c r="E100" s="25" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F100" s="19">
-        <v>1974</v>
+        <v>2014</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="10" t="s">
@@ -9683,10 +9693,10 @@
       </c>
       <c r="D101" s="2"/>
       <c r="E101" s="25" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F101" s="19">
-        <v>2003</v>
+        <v>1978</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="10" t="s">
@@ -9725,10 +9735,10 @@
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="25" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F102" s="19">
-        <v>1983</v>
+        <v>2005</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="10" t="s">
@@ -9763,11 +9773,11 @@
     </row>
     <row r="103" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D103" s="3"/>
-      <c r="E103" s="18" t="s">
-        <v>192</v>
+      <c r="E103" s="25" t="s">
+        <v>189</v>
       </c>
       <c r="F103" s="19">
-        <v>1992</v>
+        <v>1974</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="10" t="s">
@@ -9802,11 +9812,11 @@
     </row>
     <row r="104" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D104" s="3"/>
-      <c r="E104" s="18" t="s">
-        <v>193</v>
+      <c r="E104" s="25" t="s">
+        <v>190</v>
       </c>
       <c r="F104" s="19">
-        <v>2012</v>
+        <v>2003</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="10" t="s">
@@ -9841,11 +9851,11 @@
     </row>
     <row r="105" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D105" s="3"/>
-      <c r="E105" s="18" t="s">
-        <v>194</v>
+      <c r="E105" s="25" t="s">
+        <v>191</v>
       </c>
       <c r="F105" s="19">
-        <v>2017</v>
+        <v>1983</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="10" t="s">
@@ -9881,10 +9891,10 @@
     <row r="106" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D106" s="3"/>
       <c r="E106" s="18" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F106" s="19">
-        <v>2022</v>
+        <v>1992</v>
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="10" t="s">
@@ -9920,10 +9930,10 @@
     <row r="107" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D107" s="3"/>
       <c r="E107" s="18" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F107" s="19">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="10" t="s">
@@ -9959,10 +9969,10 @@
     <row r="108" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D108" s="3"/>
       <c r="E108" s="18" t="s">
-        <v>16</v>
+        <v>194</v>
       </c>
       <c r="F108" s="19">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="10" t="s">
@@ -9998,10 +10008,10 @@
     <row r="109" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D109" s="3"/>
       <c r="E109" s="18" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F109" s="19">
-        <v>1988</v>
+        <v>2022</v>
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="10" t="s">
@@ -10037,10 +10047,10 @@
     <row r="110" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D110" s="3"/>
       <c r="E110" s="18" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F110" s="19">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="10" t="s">
@@ -10076,10 +10086,10 @@
     <row r="111" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D111" s="3"/>
       <c r="E111" s="18" t="s">
-        <v>199</v>
+        <v>16</v>
       </c>
       <c r="F111" s="19">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="10" t="s">
@@ -10115,10 +10125,10 @@
     <row r="112" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D112" s="3"/>
       <c r="E112" s="18" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F112" s="19">
-        <v>1996</v>
+        <v>1988</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="10" t="s">
@@ -10154,10 +10164,10 @@
     <row r="113" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D113" s="3"/>
       <c r="E113" s="18" t="s">
-        <v>22</v>
+        <v>198</v>
       </c>
       <c r="F113" s="19">
-        <v>1991</v>
+        <v>2013</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="10" t="s">
@@ -10193,10 +10203,10 @@
     <row r="114" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D114" s="3"/>
       <c r="E114" s="18" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F114" s="19">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="10" t="s">
@@ -10232,10 +10242,10 @@
     <row r="115" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D115" s="3"/>
       <c r="E115" s="18" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F115" s="19">
-        <v>2023</v>
+        <v>1996</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="10" t="s">
@@ -10271,10 +10281,10 @@
     <row r="116" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D116" s="3"/>
       <c r="E116" s="18" t="s">
-        <v>203</v>
+        <v>22</v>
       </c>
       <c r="F116" s="19">
-        <v>1999</v>
+        <v>1991</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="10" t="s">
@@ -10310,10 +10320,10 @@
     <row r="117" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D117" s="3"/>
       <c r="E117" s="18" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F117" s="19">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="10" t="s">
@@ -10349,10 +10359,10 @@
     <row r="118" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D118" s="3"/>
       <c r="E118" s="18" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F118" s="19">
-        <v>1984</v>
+        <v>2023</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="10" t="s">
@@ -10388,10 +10398,10 @@
     <row r="119" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D119" s="3"/>
       <c r="E119" s="18" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F119" s="19">
-        <v>2004</v>
+        <v>1999</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="10" t="s">
@@ -10427,10 +10437,10 @@
     <row r="120" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D120" s="3"/>
       <c r="E120" s="18" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F120" s="19">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="10" t="s">
@@ -10466,10 +10476,10 @@
     <row r="121" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D121" s="3"/>
       <c r="E121" s="18" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F121" s="19">
-        <v>2001</v>
+        <v>1984</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="10" t="s">
@@ -10505,10 +10515,10 @@
     <row r="122" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D122" s="3"/>
       <c r="E122" s="18" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F122" s="19">
-        <v>2019</v>
+        <v>2004</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="10" t="s">
@@ -10544,10 +10554,10 @@
     <row r="123" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D123" s="3"/>
       <c r="E123" s="18" t="s">
-        <v>34</v>
+        <v>207</v>
       </c>
       <c r="F123" s="19">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="10" t="s">
@@ -10583,10 +10593,10 @@
     <row r="124" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D124" s="3"/>
       <c r="E124" s="18" t="s">
-        <v>50</v>
+        <v>208</v>
       </c>
       <c r="F124" s="19">
-        <v>2012</v>
+        <v>2001</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="10" t="s">
@@ -10622,10 +10632,10 @@
     <row r="125" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D125" s="3"/>
       <c r="E125" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F125" s="19">
-        <v>2005</v>
+        <v>2019</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="10" t="s">
@@ -10661,10 +10671,10 @@
     <row r="126" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D126" s="3"/>
       <c r="E126" s="18" t="s">
-        <v>211</v>
+        <v>34</v>
       </c>
       <c r="F126" s="19">
-        <v>1997</v>
+        <v>2012</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="10" t="s">
@@ -10700,10 +10710,10 @@
     <row r="127" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D127" s="3"/>
       <c r="E127" s="18" t="s">
-        <v>212</v>
+        <v>50</v>
       </c>
       <c r="F127" s="19">
-        <v>1997</v>
+        <v>2012</v>
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="1" t="s">
@@ -10739,10 +10749,10 @@
     <row r="128" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D128" s="3"/>
       <c r="E128" s="18" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F128" s="19">
-        <v>2022</v>
+        <v>2005</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="1" t="s">
@@ -10778,14 +10788,14 @@
     <row r="129" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D129" s="3"/>
       <c r="E129" s="18" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F129" s="19">
-        <v>1989</v>
+        <v>1997</v>
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="I129" s="1">
         <v>2003</v>
@@ -10817,10 +10827,10 @@
     <row r="130" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D130" s="3"/>
       <c r="E130" s="18" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F130" s="19">
-        <v>2018</v>
+        <v>1997</v>
       </c>
       <c r="G130" s="2"/>
       <c r="H130" s="1" t="s">
@@ -10856,10 +10866,10 @@
     <row r="131" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D131" s="3"/>
       <c r="E131" s="18" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F131" s="19">
-        <v>2001</v>
+        <v>2022</v>
       </c>
       <c r="G131" s="2"/>
       <c r="H131" s="3"/>
@@ -10891,10 +10901,10 @@
     <row r="132" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D132" s="3"/>
       <c r="E132" s="18" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F132" s="19">
-        <v>2001</v>
+        <v>1989</v>
       </c>
       <c r="G132" s="2"/>
       <c r="P132" s="3"/>
@@ -10923,10 +10933,10 @@
     <row r="133" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D133" s="3"/>
       <c r="E133" s="18" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F133" s="19">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="G133" s="2"/>
       <c r="P133" s="3"/>
@@ -10955,10 +10965,10 @@
     <row r="134" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D134" s="3"/>
       <c r="E134" s="18" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F134" s="19">
-        <v>2012</v>
+        <v>2001</v>
       </c>
       <c r="G134" s="2"/>
       <c r="P134" s="3"/>
@@ -10987,10 +10997,10 @@
     <row r="135" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D135" s="3"/>
       <c r="E135" s="18" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F135" s="19">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="G135" s="2"/>
       <c r="P135" s="3"/>
@@ -11019,10 +11029,10 @@
     <row r="136" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D136" s="3"/>
       <c r="E136" s="18" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F136" s="19">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="G136" s="2"/>
       <c r="P136" s="3"/>
@@ -11051,10 +11061,10 @@
     <row r="137" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D137" s="3"/>
       <c r="E137" s="18" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F137" s="19">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="G137" s="2"/>
       <c r="P137" s="3"/>
@@ -11083,10 +11093,10 @@
     <row r="138" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D138" s="3"/>
       <c r="E138" s="18" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F138" s="19">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="G138" s="2"/>
       <c r="P138" s="3"/>
@@ -11115,10 +11125,10 @@
     <row r="139" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D139" s="3"/>
       <c r="E139" s="18" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F139" s="19">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="G139" s="2"/>
       <c r="P139" s="3"/>
@@ -11147,10 +11157,10 @@
     <row r="140" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D140" s="3"/>
       <c r="E140" s="18" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F140" s="19">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="G140" s="2"/>
       <c r="P140" s="3"/>
@@ -11179,10 +11189,10 @@
     <row r="141" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D141" s="3"/>
       <c r="E141" s="18" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F141" s="19">
-        <v>2015</v>
+        <v>2000</v>
       </c>
       <c r="G141" s="2"/>
       <c r="P141" s="3"/>
@@ -11211,10 +11221,10 @@
     <row r="142" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D142" s="3"/>
       <c r="E142" s="18" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F142" s="19">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="G142" s="2"/>
       <c r="P142" s="3"/>
@@ -11243,10 +11253,10 @@
     <row r="143" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D143" s="3"/>
       <c r="E143" s="18" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F143" s="19">
-        <v>2000</v>
+        <v>2014</v>
       </c>
       <c r="G143" s="2"/>
       <c r="P143" s="3"/>
@@ -11275,10 +11285,10 @@
     <row r="144" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D144" s="3"/>
       <c r="E144" s="18" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F144" s="19">
-        <v>1993</v>
+        <v>2015</v>
       </c>
       <c r="G144" s="2"/>
       <c r="P144" s="3"/>
@@ -11307,10 +11317,10 @@
     <row r="145" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D145" s="3"/>
       <c r="E145" s="18" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F145" s="19">
-        <v>2004</v>
+        <v>2012</v>
       </c>
       <c r="G145" s="2"/>
       <c r="P145" s="3"/>
@@ -11339,10 +11349,10 @@
     <row r="146" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D146" s="3"/>
       <c r="E146" s="18" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F146" s="19">
-        <v>2015</v>
+        <v>2000</v>
       </c>
       <c r="G146" s="2"/>
       <c r="P146" s="3"/>
@@ -11371,10 +11381,10 @@
     <row r="147" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D147" s="3"/>
       <c r="E147" s="18" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F147" s="19">
-        <v>2013</v>
+        <v>1993</v>
       </c>
       <c r="G147" s="2"/>
       <c r="P147" s="3"/>
@@ -11403,10 +11413,10 @@
     <row r="148" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D148" s="3"/>
       <c r="E148" s="18" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F148" s="19">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="G148" s="2"/>
       <c r="P148" s="3"/>
@@ -11435,10 +11445,10 @@
     <row r="149" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D149" s="3"/>
       <c r="E149" s="18" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F149" s="19">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="G149" s="2"/>
       <c r="P149" s="3"/>
@@ -11467,10 +11477,10 @@
     <row r="150" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D150" s="3"/>
       <c r="E150" s="18" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F150" s="19">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="G150" s="2"/>
       <c r="P150" s="3"/>
@@ -11499,10 +11509,10 @@
     <row r="151" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D151" s="3"/>
       <c r="E151" s="18" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F151" s="19">
-        <v>2018</v>
+        <v>2005</v>
       </c>
       <c r="G151" s="2"/>
       <c r="P151" s="3"/>
@@ -11531,10 +11541,10 @@
     <row r="152" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D152" s="3"/>
       <c r="E152" s="18" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F152" s="19">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="G152" s="2"/>
       <c r="P152" s="3"/>
@@ -11563,10 +11573,10 @@
     <row r="153" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D153" s="3"/>
       <c r="E153" s="18" t="s">
-        <v>91</v>
+        <v>235</v>
       </c>
       <c r="F153" s="19">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="G153" s="2"/>
       <c r="P153" s="3"/>
@@ -11595,10 +11605,10 @@
     <row r="154" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D154" s="3"/>
       <c r="E154" s="18" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F154" s="19">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="G154" s="2"/>
       <c r="P154" s="3"/>
@@ -11627,10 +11637,10 @@
     <row r="155" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D155" s="3"/>
       <c r="E155" s="18" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F155" s="19">
-        <v>1960</v>
+        <v>2017</v>
       </c>
       <c r="G155" s="2"/>
       <c r="P155" s="3"/>
@@ -11659,10 +11669,10 @@
     <row r="156" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D156" s="3"/>
       <c r="E156" s="18" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F156" s="19">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="G156" s="2"/>
       <c r="P156" s="3"/>
@@ -11691,10 +11701,10 @@
     <row r="157" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D157" s="3"/>
       <c r="E157" s="18" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F157" s="19">
-        <v>2008</v>
+        <v>2015</v>
       </c>
       <c r="G157" s="2"/>
       <c r="P157" s="3"/>
@@ -11723,10 +11733,10 @@
     <row r="158" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D158" s="3"/>
       <c r="E158" s="18" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F158" s="19">
-        <v>1998</v>
+        <v>1960</v>
       </c>
       <c r="G158" s="2"/>
       <c r="P158" s="3"/>
@@ -11755,10 +11765,10 @@
     <row r="159" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D159" s="3"/>
       <c r="E159" s="18" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="F159" s="19">
-        <v>2006</v>
+        <v>2018</v>
       </c>
       <c r="G159" s="2"/>
       <c r="P159" s="3"/>
@@ -11787,10 +11797,10 @@
     <row r="160" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D160" s="3"/>
       <c r="E160" s="18" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F160" s="19">
-        <v>1994</v>
+        <v>2008</v>
       </c>
       <c r="G160" s="2"/>
       <c r="P160" s="3"/>
@@ -11819,10 +11829,10 @@
     <row r="161" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D161" s="3"/>
       <c r="E161" s="18" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F161" s="19">
-        <v>2014</v>
+        <v>1998</v>
       </c>
       <c r="G161" s="2"/>
       <c r="P161" s="3"/>
@@ -11851,7 +11861,7 @@
     <row r="162" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D162" s="3"/>
       <c r="E162" s="18" t="s">
-        <v>244</v>
+        <v>40</v>
       </c>
       <c r="F162" s="19">
         <v>2006</v>
@@ -11883,10 +11893,10 @@
     <row r="163" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D163" s="3"/>
       <c r="E163" s="18" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F163" s="19">
-        <v>1999</v>
+        <v>1994</v>
       </c>
       <c r="G163" s="2"/>
       <c r="P163" s="3"/>
@@ -11915,10 +11925,10 @@
     <row r="164" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D164" s="3"/>
       <c r="E164" s="18" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F164" s="19">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="G164" s="2"/>
       <c r="P164" s="3"/>
@@ -11947,10 +11957,10 @@
     <row r="165" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D165" s="3"/>
       <c r="E165" s="18" t="s">
-        <v>44</v>
+        <v>244</v>
       </c>
       <c r="F165" s="19">
-        <v>1992</v>
+        <v>2006</v>
       </c>
       <c r="G165" s="2"/>
       <c r="P165" s="3"/>
@@ -11979,10 +11989,10 @@
     <row r="166" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D166" s="3"/>
       <c r="E166" s="18" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F166" s="19">
-        <v>2014</v>
+        <v>1999</v>
       </c>
       <c r="G166" s="2"/>
       <c r="P166" s="3"/>
@@ -12011,10 +12021,10 @@
     <row r="167" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D167" s="3"/>
       <c r="E167" s="18" t="s">
-        <v>48</v>
+        <v>246</v>
       </c>
       <c r="F167" s="19">
-        <v>2010</v>
+        <v>2021</v>
       </c>
       <c r="G167" s="2"/>
       <c r="P167" s="3"/>
@@ -12043,10 +12053,10 @@
     <row r="168" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D168" s="3"/>
       <c r="E168" s="18" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F168" s="19">
-        <v>2023</v>
+        <v>1992</v>
       </c>
       <c r="G168" s="2"/>
       <c r="P168" s="3"/>
@@ -12075,10 +12085,10 @@
     <row r="169" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D169" s="3"/>
       <c r="E169" s="18" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F169" s="19">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="G169" s="2"/>
       <c r="P169" s="3"/>
@@ -12107,10 +12117,10 @@
     <row r="170" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D170" s="3"/>
       <c r="E170" s="18" t="s">
-        <v>249</v>
+        <v>48</v>
       </c>
       <c r="F170" s="19">
-        <v>2021</v>
+        <v>2010</v>
       </c>
       <c r="G170" s="2"/>
       <c r="P170" s="3"/>
@@ -12139,10 +12149,10 @@
     <row r="171" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D171" s="3"/>
       <c r="E171" s="18" t="s">
-        <v>250</v>
+        <v>54</v>
       </c>
       <c r="F171" s="19">
-        <v>2010</v>
+        <v>2023</v>
       </c>
       <c r="G171" s="2"/>
       <c r="P171" s="3"/>
@@ -12171,10 +12181,10 @@
     <row r="172" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D172" s="3"/>
       <c r="E172" s="18" t="s">
-        <v>37</v>
+        <v>248</v>
       </c>
       <c r="F172" s="19">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="G172" s="2"/>
       <c r="P172" s="3"/>
@@ -12203,10 +12213,10 @@
     <row r="173" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D173" s="3"/>
       <c r="E173" s="18" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F173" s="19">
-        <v>1968</v>
+        <v>2021</v>
       </c>
       <c r="G173" s="2"/>
       <c r="P173" s="3"/>
@@ -12235,10 +12245,10 @@
     <row r="174" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D174" s="3"/>
       <c r="E174" s="18" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F174" s="19">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="G174" s="2"/>
       <c r="P174" s="3"/>
@@ -12267,10 +12277,10 @@
     <row r="175" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D175" s="3"/>
       <c r="E175" s="18" t="s">
-        <v>253</v>
+        <v>37</v>
       </c>
       <c r="F175" s="19">
-        <v>1998</v>
+        <v>2019</v>
       </c>
       <c r="G175" s="2"/>
       <c r="P175" s="3"/>
@@ -12299,10 +12309,10 @@
     <row r="176" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D176" s="3"/>
       <c r="E176" s="18" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F176" s="19">
-        <v>2002</v>
+        <v>1968</v>
       </c>
       <c r="G176" s="2"/>
       <c r="P176" s="3"/>
@@ -12331,10 +12341,10 @@
     <row r="177" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D177" s="3"/>
       <c r="E177" s="18" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F177" s="19">
-        <v>2021</v>
+        <v>2009</v>
       </c>
       <c r="G177" s="2"/>
       <c r="P177" s="3"/>
@@ -12363,10 +12373,10 @@
     <row r="178" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D178" s="3"/>
       <c r="E178" s="18" t="s">
-        <v>14</v>
+        <v>253</v>
       </c>
       <c r="F178" s="19">
-        <v>2023</v>
+        <v>1998</v>
       </c>
       <c r="G178" s="2"/>
       <c r="P178" s="3"/>
@@ -12395,10 +12405,10 @@
     <row r="179" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D179" s="3"/>
       <c r="E179" s="18" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F179" s="19">
-        <v>1998</v>
+        <v>2002</v>
       </c>
       <c r="G179" s="2"/>
       <c r="P179" s="3"/>
@@ -12427,10 +12437,10 @@
     <row r="180" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D180" s="3"/>
       <c r="E180" s="18" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F180" s="19">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="G180" s="2"/>
       <c r="P180" s="3"/>
@@ -12459,10 +12469,10 @@
     <row r="181" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D181" s="3"/>
       <c r="E181" s="18" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F181" s="19">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="G181" s="2"/>
       <c r="P181" s="3"/>
@@ -12491,10 +12501,10 @@
     <row r="182" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D182" s="3"/>
       <c r="E182" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F182" s="19">
-        <v>2012</v>
+        <v>1998</v>
       </c>
       <c r="G182" s="2"/>
       <c r="P182" s="3"/>
@@ -12523,10 +12533,10 @@
     <row r="183" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D183" s="3"/>
       <c r="E183" s="18" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F183" s="19">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="G183" s="2"/>
       <c r="P183" s="3"/>
@@ -12555,10 +12565,10 @@
     <row r="184" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D184" s="3"/>
       <c r="E184" s="18" t="s">
-        <v>260</v>
+        <v>49</v>
       </c>
       <c r="F184" s="19">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="G184" s="2"/>
       <c r="P184" s="3"/>
@@ -12587,10 +12597,10 @@
     <row r="185" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D185" s="3"/>
       <c r="E185" s="18" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F185" s="19">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="G185" s="2"/>
       <c r="P185" s="3"/>
@@ -12619,10 +12629,10 @@
     <row r="186" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D186" s="3"/>
       <c r="E186" s="18" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F186" s="19">
-        <v>2003</v>
+        <v>2013</v>
       </c>
       <c r="G186" s="2"/>
       <c r="P186" s="3"/>
@@ -12651,10 +12661,10 @@
     <row r="187" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D187" s="3"/>
       <c r="E187" s="18" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F187" s="19">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="G187" s="2"/>
       <c r="P187" s="3"/>
@@ -12683,10 +12693,10 @@
     <row r="188" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D188" s="3"/>
       <c r="E188" s="18" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F188" s="19">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="G188" s="2"/>
       <c r="P188" s="3"/>
@@ -12715,10 +12725,10 @@
     <row r="189" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D189" s="3"/>
       <c r="E189" s="18" t="s">
-        <v>12</v>
+        <v>262</v>
       </c>
       <c r="F189" s="19">
-        <v>2022</v>
+        <v>2003</v>
       </c>
       <c r="G189" s="2"/>
       <c r="P189" s="3"/>
@@ -12747,10 +12757,10 @@
     <row r="190" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D190" s="3"/>
       <c r="E190" s="18" t="s">
-        <v>2</v>
+        <v>263</v>
       </c>
       <c r="F190" s="19">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="G190" s="2"/>
       <c r="P190" s="3"/>
@@ -12779,10 +12789,10 @@
     <row r="191" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D191" s="3"/>
       <c r="E191" s="18" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F191" s="19">
-        <v>1981</v>
+        <v>2012</v>
       </c>
       <c r="G191" s="2"/>
       <c r="P191" s="3"/>
@@ -12811,10 +12821,10 @@
     <row r="192" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D192" s="3"/>
       <c r="E192" s="18" t="s">
-        <v>266</v>
+        <v>12</v>
       </c>
       <c r="F192" s="19">
-        <v>1996</v>
+        <v>2022</v>
       </c>
       <c r="G192" s="2"/>
       <c r="P192" s="3"/>
@@ -12843,10 +12853,10 @@
     <row r="193" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D193" s="3"/>
       <c r="E193" s="18" t="s">
-        <v>267</v>
+        <v>2</v>
       </c>
       <c r="F193" s="19">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G193" s="2"/>
       <c r="P193" s="3"/>
@@ -12875,10 +12885,10 @@
     <row r="194" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D194" s="3"/>
       <c r="E194" s="18" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F194" s="19">
-        <v>2018</v>
+        <v>1981</v>
       </c>
       <c r="G194" s="2"/>
       <c r="P194" s="3"/>
@@ -12907,10 +12917,10 @@
     <row r="195" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D195" s="3"/>
       <c r="E195" s="18" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F195" s="19">
-        <v>2016</v>
+        <v>1996</v>
       </c>
       <c r="G195" s="2"/>
       <c r="P195" s="3"/>
@@ -12939,10 +12949,10 @@
     <row r="196" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D196" s="3"/>
       <c r="E196" s="18" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F196" s="19">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="G196" s="2"/>
       <c r="P196" s="3"/>
@@ -12971,10 +12981,10 @@
     <row r="197" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D197" s="3"/>
       <c r="E197" s="18" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F197" s="19">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="G197" s="2"/>
       <c r="P197" s="3"/>
@@ -13003,10 +13013,10 @@
     <row r="198" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D198" s="3"/>
       <c r="E198" s="18" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F198" s="19">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="G198" s="2"/>
       <c r="P198" s="3"/>
@@ -13035,10 +13045,10 @@
     <row r="199" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D199" s="3"/>
       <c r="E199" s="18" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F199" s="19">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="G199" s="2"/>
       <c r="P199" s="3"/>
@@ -13067,10 +13077,10 @@
     <row r="200" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D200" s="3"/>
       <c r="E200" s="18" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F200" s="19">
-        <v>2004</v>
+        <v>2020</v>
       </c>
       <c r="G200" s="2"/>
       <c r="P200" s="3"/>
@@ -13099,10 +13109,10 @@
     <row r="201" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D201" s="3"/>
       <c r="E201" s="18" t="s">
-        <v>7</v>
+        <v>272</v>
       </c>
       <c r="F201" s="19">
-        <v>2015</v>
+        <v>2008</v>
       </c>
       <c r="G201" s="2"/>
       <c r="P201" s="3"/>
@@ -13131,10 +13141,10 @@
     <row r="202" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D202" s="3"/>
       <c r="E202" s="18" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F202" s="19">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="G202" s="2"/>
       <c r="P202" s="3"/>
@@ -13163,10 +13173,10 @@
     <row r="203" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D203" s="3"/>
       <c r="E203" s="18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F203" s="19">
-        <v>1995</v>
+        <v>2004</v>
       </c>
       <c r="G203" s="2"/>
       <c r="P203" s="3"/>
@@ -13195,10 +13205,10 @@
     <row r="204" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D204" s="3"/>
       <c r="E204" s="18" t="s">
-        <v>277</v>
+        <v>7</v>
       </c>
       <c r="F204" s="19">
-        <v>1971</v>
+        <v>2015</v>
       </c>
       <c r="G204" s="2"/>
       <c r="P204" s="3"/>
@@ -13227,10 +13237,10 @@
     <row r="205" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D205" s="3"/>
       <c r="E205" s="18" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F205" s="19">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="G205" s="2"/>
       <c r="P205" s="3"/>
@@ -13259,10 +13269,10 @@
     <row r="206" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D206" s="3"/>
       <c r="E206" s="18" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F206" s="19">
-        <v>2013</v>
+        <v>1995</v>
       </c>
       <c r="G206" s="2"/>
       <c r="P206" s="3"/>
@@ -13291,10 +13301,10 @@
     <row r="207" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D207" s="3"/>
       <c r="E207" s="18" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F207" s="19">
-        <v>1988</v>
+        <v>1971</v>
       </c>
       <c r="G207" s="2"/>
       <c r="P207" s="3"/>
@@ -13323,10 +13333,10 @@
     <row r="208" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D208" s="3"/>
       <c r="E208" s="18" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F208" s="19">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="G208" s="2"/>
       <c r="P208" s="3"/>
@@ -13355,10 +13365,10 @@
     <row r="209" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D209" s="3"/>
       <c r="E209" s="18" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F209" s="19">
-        <v>1982</v>
+        <v>2013</v>
       </c>
       <c r="G209" s="2"/>
       <c r="P209" s="3"/>
@@ -13387,10 +13397,10 @@
     <row r="210" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D210" s="3"/>
       <c r="E210" s="18" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F210" s="19">
-        <v>2006</v>
+        <v>1988</v>
       </c>
       <c r="G210" s="2"/>
       <c r="P210" s="3"/>
@@ -13419,10 +13429,10 @@
     <row r="211" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D211" s="3"/>
       <c r="E211" s="18" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F211" s="19">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="G211" s="2"/>
       <c r="P211" s="3"/>
@@ -13451,10 +13461,10 @@
     <row r="212" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D212" s="3"/>
       <c r="E212" s="18" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F212" s="19">
-        <v>2015</v>
+        <v>1982</v>
       </c>
       <c r="G212" s="2"/>
       <c r="P212" s="3"/>
@@ -13483,10 +13493,10 @@
     <row r="213" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D213" s="3"/>
       <c r="E213" s="18" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F213" s="19">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="G213" s="2"/>
       <c r="P213" s="3"/>
@@ -13515,10 +13525,10 @@
     <row r="214" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D214" s="3"/>
       <c r="E214" s="18" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F214" s="19">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="G214" s="2"/>
       <c r="P214" s="3"/>
@@ -13547,7 +13557,7 @@
     <row r="215" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D215" s="3"/>
       <c r="E215" s="18" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F215" s="19">
         <v>2015</v>
@@ -13579,10 +13589,10 @@
     <row r="216" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D216" s="3"/>
       <c r="E216" s="18" t="s">
-        <v>38</v>
+        <v>286</v>
       </c>
       <c r="F216" s="19">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="G216" s="2"/>
       <c r="P216" s="3"/>
@@ -13611,10 +13621,10 @@
     <row r="217" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D217" s="3"/>
       <c r="E217" s="18" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F217" s="19">
-        <v>1990</v>
+        <v>2006</v>
       </c>
       <c r="G217" s="2"/>
       <c r="P217" s="3"/>
@@ -13643,10 +13653,10 @@
     <row r="218" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D218" s="3"/>
       <c r="E218" s="18" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F218" s="19">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="G218" s="2"/>
       <c r="P218" s="3"/>
@@ -13675,10 +13685,10 @@
     <row r="219" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D219" s="3"/>
       <c r="E219" s="18" t="s">
-        <v>291</v>
+        <v>38</v>
       </c>
       <c r="F219" s="19">
-        <v>2006</v>
+        <v>2019</v>
       </c>
       <c r="G219" s="2"/>
       <c r="P219" s="3"/>
@@ -13707,10 +13717,10 @@
     <row r="220" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D220" s="3"/>
       <c r="E220" s="18" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F220" s="19">
-        <v>2016</v>
+        <v>1990</v>
       </c>
       <c r="G220" s="2"/>
       <c r="P220" s="3"/>
@@ -13739,10 +13749,10 @@
     <row r="221" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D221" s="3"/>
       <c r="E221" s="18" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F221" s="19">
-        <v>1979</v>
+        <v>2022</v>
       </c>
       <c r="G221" s="2"/>
       <c r="P221" s="3"/>
@@ -13771,10 +13781,10 @@
     <row r="222" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D222" s="3"/>
       <c r="E222" s="18" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F222" s="19">
-        <v>2000</v>
+        <v>2006</v>
       </c>
       <c r="G222" s="2"/>
       <c r="P222" s="3"/>
@@ -13803,10 +13813,10 @@
     <row r="223" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D223" s="3"/>
       <c r="E223" s="18" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F223" s="19">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="G223" s="2"/>
       <c r="P223" s="3"/>
@@ -13835,10 +13845,10 @@
     <row r="224" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D224" s="3"/>
       <c r="E224" s="18" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F224" s="19">
-        <v>1986</v>
+        <v>1979</v>
       </c>
       <c r="G224" s="2"/>
       <c r="P224" s="3"/>
@@ -13867,10 +13877,10 @@
     <row r="225" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D225" s="3"/>
       <c r="E225" s="18" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F225" s="19">
-        <v>2022</v>
+        <v>2000</v>
       </c>
       <c r="G225" s="2"/>
       <c r="P225" s="3"/>
@@ -13899,10 +13909,10 @@
     <row r="226" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D226" s="3"/>
       <c r="E226" s="18" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F226" s="19">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="G226" s="2"/>
       <c r="P226" s="3"/>
@@ -13931,10 +13941,10 @@
     <row r="227" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D227" s="3"/>
       <c r="E227" s="18" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F227" s="19">
-        <v>2007</v>
+        <v>1986</v>
       </c>
       <c r="G227" s="2"/>
       <c r="P227" s="3"/>
@@ -13963,10 +13973,10 @@
     <row r="228" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D228" s="3"/>
       <c r="E228" s="18" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F228" s="19">
-        <v>1992</v>
+        <v>2022</v>
       </c>
       <c r="G228" s="2"/>
       <c r="P228" s="3"/>
@@ -13995,10 +14005,10 @@
     <row r="229" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D229" s="3"/>
       <c r="E229" s="18" t="s">
-        <v>71</v>
+        <v>298</v>
       </c>
       <c r="F229" s="19">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="G229" s="2"/>
       <c r="P229" s="3"/>
@@ -14027,10 +14037,10 @@
     <row r="230" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D230" s="3"/>
       <c r="E230" s="18" t="s">
-        <v>60</v>
+        <v>299</v>
       </c>
       <c r="F230" s="19">
-        <v>2022</v>
+        <v>2007</v>
       </c>
       <c r="G230" s="2"/>
       <c r="P230" s="3"/>
@@ -14059,10 +14069,10 @@
     <row r="231" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D231" s="3"/>
       <c r="E231" s="18" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F231" s="19">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="G231" s="2"/>
       <c r="P231" s="3"/>
@@ -14091,10 +14101,10 @@
     <row r="232" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D232" s="3"/>
       <c r="E232" s="18" t="s">
-        <v>302</v>
+        <v>71</v>
       </c>
       <c r="F232" s="19">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="G232" s="2"/>
       <c r="P232" s="3"/>
@@ -14123,10 +14133,10 @@
     <row r="233" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D233" s="3"/>
       <c r="E233" s="18" t="s">
-        <v>303</v>
+        <v>60</v>
       </c>
       <c r="F233" s="19">
-        <v>1982</v>
+        <v>2022</v>
       </c>
       <c r="G233" s="2"/>
       <c r="P233" s="3"/>
@@ -14155,10 +14165,10 @@
     <row r="234" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D234" s="3"/>
       <c r="E234" s="18" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F234" s="19">
-        <v>2009</v>
+        <v>1990</v>
       </c>
       <c r="G234" s="2"/>
       <c r="P234" s="3"/>
@@ -14187,10 +14197,10 @@
     <row r="235" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D235" s="3"/>
       <c r="E235" s="18" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F235" s="19">
-        <v>1975</v>
+        <v>2002</v>
       </c>
       <c r="G235" s="2"/>
       <c r="P235" s="3"/>
@@ -14219,10 +14229,10 @@
     <row r="236" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D236" s="3"/>
       <c r="E236" s="18" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F236" s="19">
-        <v>2019</v>
+        <v>1982</v>
       </c>
       <c r="G236" s="2"/>
       <c r="P236" s="3"/>
@@ -14251,7 +14261,7 @@
     <row r="237" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D237" s="3"/>
       <c r="E237" s="18" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F237" s="19">
         <v>2009</v>
@@ -14283,10 +14293,10 @@
     <row r="238" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D238" s="3"/>
       <c r="E238" s="18" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F238" s="19">
-        <v>1989</v>
+        <v>1975</v>
       </c>
       <c r="G238" s="2"/>
       <c r="P238" s="3"/>
@@ -14315,10 +14325,10 @@
     <row r="239" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D239" s="3"/>
       <c r="E239" s="18" t="s">
-        <v>85</v>
+        <v>306</v>
       </c>
       <c r="F239" s="19">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="G239" s="2"/>
       <c r="P239" s="3"/>
@@ -14347,10 +14357,10 @@
     <row r="240" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D240" s="3"/>
       <c r="E240" s="18" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F240" s="19">
-        <v>1993</v>
+        <v>2009</v>
       </c>
       <c r="G240" s="2"/>
       <c r="P240" s="3"/>
@@ -14379,10 +14389,10 @@
     <row r="241" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D241" s="3"/>
       <c r="E241" s="18" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F241" s="19">
-        <v>2019</v>
+        <v>1989</v>
       </c>
       <c r="G241" s="2"/>
       <c r="P241" s="3"/>
@@ -14411,10 +14421,10 @@
     <row r="242" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D242" s="3"/>
       <c r="E242" s="18" t="s">
-        <v>311</v>
+        <v>85</v>
       </c>
       <c r="F242" s="19">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="G242" s="2"/>
       <c r="P242" s="3"/>
@@ -14443,10 +14453,10 @@
     <row r="243" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D243" s="3"/>
       <c r="E243" s="18" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F243" s="19">
-        <v>2009</v>
+        <v>1993</v>
       </c>
       <c r="G243" s="2"/>
       <c r="P243" s="3"/>
@@ -14475,10 +14485,10 @@
     <row r="244" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D244" s="3"/>
       <c r="E244" s="18" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F244" s="19">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="G244" s="2"/>
       <c r="P244" s="3"/>
@@ -14507,10 +14517,10 @@
     <row r="245" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D245" s="3"/>
       <c r="E245" s="18" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F245" s="19">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="G245" s="2"/>
       <c r="P245" s="3"/>
@@ -14539,10 +14549,10 @@
     <row r="246" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D246" s="3"/>
       <c r="E246" s="18" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F246" s="19">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="G246" s="2"/>
       <c r="P246" s="3"/>
@@ -14571,10 +14581,10 @@
     <row r="247" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D247" s="3"/>
       <c r="E247" s="18" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F247" s="19">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="G247" s="2"/>
       <c r="P247" s="3"/>
@@ -14603,10 +14613,10 @@
     <row r="248" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D248" s="3"/>
       <c r="E248" s="18" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F248" s="19">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="G248" s="2"/>
       <c r="P248" s="3"/>
@@ -14635,7 +14645,7 @@
     <row r="249" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D249" s="3"/>
       <c r="E249" s="18" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F249" s="19">
         <v>2016</v>
@@ -14643,14 +14653,14 @@
       <c r="G249" s="2"/>
       <c r="P249" s="3"/>
       <c r="Q249" s="18" t="s">
-        <v>763</v>
+        <v>1279</v>
       </c>
       <c r="R249" s="19">
-        <v>2020</v>
+        <v>1992</v>
       </c>
       <c r="S249" s="4"/>
       <c r="T249" s="13" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="U249" s="12">
         <v>1997</v>
@@ -14667,7 +14677,7 @@
     <row r="250" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D250" s="3"/>
       <c r="E250" s="18" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F250" s="19">
         <v>2007</v>
@@ -14682,7 +14692,7 @@
       </c>
       <c r="S250" s="4"/>
       <c r="T250" s="13" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="U250" s="12">
         <v>2024</v>
@@ -14699,22 +14709,22 @@
     <row r="251" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D251" s="3"/>
       <c r="E251" s="18" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F251" s="19">
-        <v>1997</v>
+        <v>2018</v>
       </c>
       <c r="G251" s="2"/>
       <c r="P251" s="3"/>
       <c r="Q251" s="18" t="s">
-        <v>764</v>
+        <v>1280</v>
       </c>
       <c r="R251" s="19">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="S251" s="4"/>
       <c r="T251" s="13" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="U251" s="12">
         <v>2004</v>
@@ -14731,10 +14741,10 @@
     <row r="252" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D252" s="3"/>
       <c r="E252" s="18" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F252" s="19">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="G252" s="2"/>
       <c r="P252" s="3"/>
@@ -14755,10 +14765,10 @@
     <row r="253" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D253" s="3"/>
       <c r="E253" s="18" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F253" s="19">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="G253" s="2"/>
       <c r="V253" s="3"/>
@@ -14773,10 +14783,10 @@
     <row r="254" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D254" s="3"/>
       <c r="E254" s="18" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F254" s="19">
-        <v>2017</v>
+        <v>1997</v>
       </c>
       <c r="G254" s="2"/>
       <c r="V254" s="3"/>
@@ -14791,10 +14801,10 @@
     <row r="255" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D255" s="3"/>
       <c r="E255" s="18" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F255" s="19">
-        <v>2002</v>
+        <v>2014</v>
       </c>
       <c r="G255" s="2"/>
       <c r="V255" s="3"/>
@@ -14809,10 +14819,10 @@
     <row r="256" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D256" s="3"/>
       <c r="E256" s="18" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F256" s="19">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="G256" s="2"/>
       <c r="V256" s="3"/>
@@ -14827,10 +14837,10 @@
     <row r="257" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D257" s="3"/>
       <c r="E257" s="18" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F257" s="19">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="G257" s="2"/>
       <c r="V257" s="3"/>
@@ -14845,10 +14855,10 @@
     <row r="258" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D258" s="3"/>
       <c r="E258" s="18" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F258" s="19">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="G258" s="2"/>
       <c r="V258" s="3"/>
@@ -14863,10 +14873,10 @@
     <row r="259" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D259" s="3"/>
       <c r="E259" s="18" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F259" s="19">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="G259" s="2"/>
       <c r="V259" s="3"/>
@@ -14881,10 +14891,10 @@
     <row r="260" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D260" s="3"/>
       <c r="E260" s="18" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F260" s="19">
-        <v>1999</v>
+        <v>2010</v>
       </c>
       <c r="G260" s="2"/>
       <c r="V260" s="3"/>
@@ -14899,10 +14909,10 @@
     <row r="261" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D261" s="3"/>
       <c r="E261" s="18" t="s">
-        <v>46</v>
+        <v>327</v>
       </c>
       <c r="F261" s="19">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="G261" s="2"/>
       <c r="V261" s="3"/>
@@ -14916,11 +14926,11 @@
     </row>
     <row r="262" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D262" s="3"/>
-      <c r="E262" s="26">
-        <v>1917</v>
+      <c r="E262" s="18" t="s">
+        <v>328</v>
       </c>
       <c r="F262" s="19">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="G262" s="2"/>
       <c r="V262" s="3"/>
@@ -14935,10 +14945,10 @@
     <row r="263" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D263" s="3"/>
       <c r="E263" s="18" t="s">
-        <v>97</v>
+        <v>329</v>
       </c>
       <c r="F263" s="19">
-        <v>2017</v>
+        <v>1999</v>
       </c>
       <c r="G263" s="2"/>
       <c r="V263" s="3"/>
@@ -14953,10 +14963,10 @@
     <row r="264" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D264" s="3"/>
       <c r="E264" s="18" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="F264" s="19">
-        <v>2005</v>
+        <v>1999</v>
       </c>
       <c r="G264" s="2"/>
       <c r="V264" s="3"/>
@@ -14970,8 +14980,8 @@
     </row>
     <row r="265" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D265" s="3"/>
-      <c r="E265" s="18" t="s">
-        <v>330</v>
+      <c r="E265" s="26">
+        <v>1917</v>
       </c>
       <c r="F265" s="19">
         <v>2019</v>
@@ -14989,10 +14999,10 @@
     <row r="266" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D266" s="3"/>
       <c r="E266" s="18" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="F266" s="19">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="G266" s="2"/>
       <c r="V266" s="3"/>
@@ -15007,10 +15017,10 @@
     <row r="267" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D267" s="3"/>
       <c r="E267" s="18" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F267" s="19">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="G267" s="2"/>
       <c r="V267" s="3"/>
@@ -15025,10 +15035,10 @@
     <row r="268" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D268" s="3"/>
       <c r="E268" s="18" t="s">
-        <v>43</v>
+        <v>330</v>
       </c>
       <c r="F268" s="19">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="G268" s="2"/>
       <c r="V268" s="3"/>
@@ -15043,10 +15053,10 @@
     <row r="269" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D269" s="3"/>
       <c r="E269" s="18" t="s">
-        <v>331</v>
+        <v>23</v>
       </c>
       <c r="F269" s="19">
-        <v>2005</v>
+        <v>2018</v>
       </c>
       <c r="G269" s="2"/>
       <c r="V269" s="3"/>
@@ -15061,10 +15071,10 @@
     <row r="270" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D270" s="3"/>
       <c r="E270" s="18" t="s">
-        <v>332</v>
+        <v>67</v>
       </c>
       <c r="F270" s="19">
-        <v>2020</v>
+        <v>2004</v>
       </c>
       <c r="G270" s="2"/>
       <c r="V270" s="3"/>
@@ -15079,7 +15089,7 @@
     <row r="271" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D271" s="3"/>
       <c r="E271" s="18" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F271" s="19">
         <v>2016</v>
@@ -15097,10 +15107,10 @@
     <row r="272" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D272" s="3"/>
       <c r="E272" s="18" t="s">
-        <v>21</v>
+        <v>331</v>
       </c>
       <c r="F272" s="19">
-        <v>2013</v>
+        <v>2005</v>
       </c>
       <c r="G272" s="2"/>
       <c r="V272" s="3"/>
@@ -15115,10 +15125,10 @@
     <row r="273" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D273" s="3"/>
       <c r="E273" s="18" t="s">
-        <v>78</v>
+        <v>332</v>
       </c>
       <c r="F273" s="19">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="G273" s="2"/>
       <c r="V273" s="3"/>
@@ -15133,10 +15143,10 @@
     <row r="274" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D274" s="3"/>
       <c r="E274" s="18" t="s">
-        <v>333</v>
+        <v>53</v>
       </c>
       <c r="F274" s="19">
-        <v>2003</v>
+        <v>2016</v>
       </c>
       <c r="G274" s="2"/>
       <c r="V274" s="3"/>
@@ -15151,10 +15161,10 @@
     <row r="275" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D275" s="3"/>
       <c r="E275" s="18" t="s">
-        <v>334</v>
+        <v>21</v>
       </c>
       <c r="F275" s="19">
-        <v>1976</v>
+        <v>2013</v>
       </c>
       <c r="G275" s="2"/>
       <c r="V275" s="3"/>
@@ -15169,10 +15179,10 @@
     <row r="276" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D276" s="3"/>
       <c r="E276" s="18" t="s">
-        <v>335</v>
+        <v>78</v>
       </c>
       <c r="F276" s="19">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="G276" s="2"/>
       <c r="V276" s="3"/>
@@ -15187,10 +15197,10 @@
     <row r="277" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D277" s="3"/>
       <c r="E277" s="18" t="s">
-        <v>31</v>
+        <v>333</v>
       </c>
       <c r="F277" s="19">
-        <v>2019</v>
+        <v>2003</v>
       </c>
       <c r="G277" s="2"/>
       <c r="V277" s="3"/>
@@ -15205,10 +15215,10 @@
     <row r="278" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D278" s="3"/>
       <c r="E278" s="18" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F278" s="19">
-        <v>2016</v>
+        <v>1976</v>
       </c>
       <c r="G278" s="2"/>
       <c r="V278" s="3"/>
@@ -15223,10 +15233,10 @@
     <row r="279" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D279" s="3"/>
       <c r="E279" s="18" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F279" s="19">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="G279" s="2"/>
       <c r="V279" s="3"/>
@@ -15241,10 +15251,10 @@
     <row r="280" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D280" s="3"/>
       <c r="E280" s="18" t="s">
-        <v>338</v>
+        <v>31</v>
       </c>
       <c r="F280" s="19">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G280" s="2"/>
       <c r="V280" s="3"/>
@@ -15259,10 +15269,10 @@
     <row r="281" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D281" s="3"/>
       <c r="E281" s="18" t="s">
-        <v>26</v>
+        <v>336</v>
       </c>
       <c r="F281" s="19">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="G281" s="2"/>
       <c r="V281" s="3"/>
@@ -15277,10 +15287,10 @@
     <row r="282" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D282" s="3"/>
       <c r="E282" s="18" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F282" s="19">
-        <v>2010</v>
+        <v>2019</v>
       </c>
       <c r="G282" s="2"/>
       <c r="V282" s="3"/>
@@ -15295,10 +15305,10 @@
     <row r="283" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D283" s="3"/>
       <c r="E283" s="18" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F283" s="19">
-        <v>2004</v>
+        <v>2018</v>
       </c>
       <c r="G283" s="2"/>
       <c r="V283" s="3"/>
@@ -15313,10 +15323,10 @@
     <row r="284" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D284" s="3"/>
       <c r="E284" s="18" t="s">
-        <v>341</v>
+        <v>26</v>
       </c>
       <c r="F284" s="19">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="G284" s="2"/>
       <c r="V284" s="3"/>
@@ -15331,10 +15341,10 @@
     <row r="285" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D285" s="3"/>
       <c r="E285" s="18" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F285" s="19">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="G285" s="2"/>
       <c r="V285" s="3"/>
@@ -15349,10 +15359,10 @@
     <row r="286" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D286" s="3"/>
       <c r="E286" s="18" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F286" s="19">
-        <v>1983</v>
+        <v>2004</v>
       </c>
       <c r="G286" s="2"/>
       <c r="V286" s="3"/>
@@ -15367,10 +15377,10 @@
     <row r="287" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D287" s="3"/>
       <c r="E287" s="18" t="s">
-        <v>68</v>
+        <v>341</v>
       </c>
       <c r="F287" s="19">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="G287" s="2"/>
       <c r="V287" s="3"/>
@@ -15385,10 +15395,10 @@
     <row r="288" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D288" s="3"/>
       <c r="E288" s="18" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F288" s="19">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="G288" s="2"/>
       <c r="V288" s="3"/>
@@ -15403,10 +15413,10 @@
     <row r="289" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D289" s="3"/>
       <c r="E289" s="18" t="s">
-        <v>69</v>
+        <v>343</v>
       </c>
       <c r="F289" s="19">
-        <v>2002</v>
+        <v>1983</v>
       </c>
       <c r="G289" s="2"/>
       <c r="V289" s="3"/>
@@ -15421,10 +15431,10 @@
     <row r="290" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D290" s="3"/>
       <c r="E290" s="18" t="s">
-        <v>345</v>
+        <v>68</v>
       </c>
       <c r="F290" s="19">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="G290" s="2"/>
       <c r="V290" s="3"/>
@@ -15439,10 +15449,10 @@
     <row r="291" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D291" s="3"/>
       <c r="E291" s="18" t="s">
-        <v>62</v>
+        <v>344</v>
       </c>
       <c r="F291" s="19">
-        <v>2010</v>
+        <v>2021</v>
       </c>
       <c r="G291" s="2"/>
       <c r="V291" s="3"/>
@@ -15457,10 +15467,10 @@
     <row r="292" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D292" s="3"/>
       <c r="E292" s="18" t="s">
-        <v>346</v>
+        <v>69</v>
       </c>
       <c r="F292" s="19">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="G292" s="2"/>
       <c r="V292" s="3"/>
@@ -15475,10 +15485,10 @@
     <row r="293" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D293" s="3"/>
       <c r="E293" s="18" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F293" s="19">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="G293" s="2"/>
       <c r="V293" s="3"/>
@@ -15493,10 +15503,10 @@
     <row r="294" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D294" s="3"/>
       <c r="E294" s="18" t="s">
-        <v>348</v>
+        <v>62</v>
       </c>
       <c r="F294" s="19">
-        <v>1985</v>
+        <v>2010</v>
       </c>
       <c r="G294" s="2"/>
       <c r="V294" s="3"/>
@@ -15511,10 +15521,10 @@
     <row r="295" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D295" s="3"/>
       <c r="E295" s="18" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F295" s="19">
-        <v>2005</v>
+        <v>1999</v>
       </c>
       <c r="G295" s="2"/>
       <c r="V295" s="3"/>
@@ -15529,10 +15539,10 @@
     <row r="296" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D296" s="3"/>
       <c r="E296" s="18" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F296" s="19">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="G296" s="2"/>
       <c r="V296" s="3"/>
@@ -15547,10 +15557,10 @@
     <row r="297" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D297" s="3"/>
       <c r="E297" s="18" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F297" s="19">
-        <v>2017</v>
+        <v>1985</v>
       </c>
       <c r="G297" s="2"/>
       <c r="V297" s="3"/>
@@ -15565,10 +15575,10 @@
     <row r="298" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D298" s="3"/>
       <c r="E298" s="18" t="s">
-        <v>32</v>
+        <v>349</v>
       </c>
       <c r="F298" s="19">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="G298" s="2"/>
       <c r="V298" s="3"/>
@@ -15583,10 +15593,10 @@
     <row r="299" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D299" s="3"/>
       <c r="E299" s="18" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F299" s="19">
-        <v>1972</v>
+        <v>2015</v>
       </c>
       <c r="G299" s="2"/>
       <c r="V299" s="3"/>
@@ -15601,10 +15611,10 @@
     <row r="300" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D300" s="3"/>
       <c r="E300" s="18" t="s">
-        <v>65</v>
+        <v>351</v>
       </c>
       <c r="F300" s="19">
-        <v>2007</v>
+        <v>2017</v>
       </c>
       <c r="G300" s="2"/>
       <c r="V300" s="3"/>
@@ -15619,10 +15629,10 @@
     <row r="301" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D301" s="3"/>
       <c r="E301" s="18" t="s">
-        <v>353</v>
+        <v>32</v>
       </c>
       <c r="F301" s="19">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="G301" s="2"/>
       <c r="V301" s="3"/>
@@ -15637,10 +15647,10 @@
     <row r="302" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D302" s="3"/>
       <c r="E302" s="18" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F302" s="19">
-        <v>2022</v>
+        <v>1972</v>
       </c>
       <c r="G302" s="2"/>
       <c r="V302" s="3"/>
@@ -15655,10 +15665,10 @@
     <row r="303" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D303" s="3"/>
       <c r="E303" s="18" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="F303" s="19">
-        <v>2017</v>
+        <v>2007</v>
       </c>
       <c r="G303" s="2"/>
       <c r="V303" s="3"/>
@@ -15673,10 +15683,10 @@
     <row r="304" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D304" s="3"/>
       <c r="E304" s="18" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F304" s="19">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="G304" s="2"/>
       <c r="V304" s="3"/>
@@ -15691,10 +15701,10 @@
     <row r="305" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D305" s="3"/>
       <c r="E305" s="18" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F305" s="19">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="G305" s="2"/>
       <c r="V305" s="3"/>
@@ -15709,10 +15719,10 @@
     <row r="306" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D306" s="3"/>
       <c r="E306" s="18" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F306" s="19">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="G306" s="2"/>
       <c r="V306" s="3"/>
@@ -15727,10 +15737,10 @@
     <row r="307" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D307" s="3"/>
       <c r="E307" s="18" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F307" s="19">
-        <v>2004</v>
+        <v>2017</v>
       </c>
       <c r="G307" s="2"/>
       <c r="V307" s="3"/>
@@ -15745,10 +15755,10 @@
     <row r="308" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D308" s="3"/>
       <c r="E308" s="18" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F308" s="19">
-        <v>1994</v>
+        <v>2018</v>
       </c>
       <c r="G308" s="2"/>
       <c r="V308" s="3"/>
@@ -15763,10 +15773,10 @@
     <row r="309" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D309" s="3"/>
       <c r="E309" s="18" t="s">
-        <v>359</v>
+        <v>39</v>
       </c>
       <c r="F309" s="19">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="G309" s="2"/>
       <c r="V309" s="3"/>
@@ -15781,10 +15791,10 @@
     <row r="310" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D310" s="3"/>
       <c r="E310" s="18" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F310" s="19">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="G310" s="2"/>
       <c r="V310" s="3"/>
@@ -15799,10 +15809,10 @@
     <row r="311" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D311" s="3"/>
       <c r="E311" s="18" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F311" s="19">
-        <v>1990</v>
+        <v>1994</v>
       </c>
       <c r="G311" s="2"/>
       <c r="V311" s="3"/>
@@ -15817,10 +15827,10 @@
     <row r="312" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D312" s="3"/>
       <c r="E312" s="18" t="s">
-        <v>6</v>
+        <v>359</v>
       </c>
       <c r="F312" s="19">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="G312" s="2"/>
       <c r="V312" s="3"/>
@@ -15835,10 +15845,10 @@
     <row r="313" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D313" s="3"/>
       <c r="E313" s="18" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F313" s="19">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="G313" s="2"/>
       <c r="V313" s="3"/>
@@ -15853,10 +15863,10 @@
     <row r="314" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D314" s="3"/>
       <c r="E314" s="18" t="s">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="F314" s="19">
-        <v>2011</v>
+        <v>1990</v>
       </c>
       <c r="G314" s="2"/>
       <c r="V314" s="3"/>
@@ -15871,10 +15881,10 @@
     <row r="315" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D315" s="3"/>
       <c r="E315" s="18" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="F315" s="19">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="G315" s="2"/>
       <c r="V315" s="3"/>
@@ -15889,10 +15899,10 @@
     <row r="316" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D316" s="3"/>
       <c r="E316" s="18" t="s">
-        <v>76</v>
+        <v>362</v>
       </c>
       <c r="F316" s="19">
-        <v>2005</v>
+        <v>2000</v>
       </c>
       <c r="G316" s="2"/>
       <c r="V316" s="3"/>
@@ -15907,10 +15917,10 @@
     <row r="317" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D317" s="3"/>
       <c r="E317" s="18" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F317" s="19">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="G317" s="2"/>
       <c r="V317" s="3"/>
@@ -15925,10 +15935,10 @@
     <row r="318" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D318" s="3"/>
       <c r="E318" s="18" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="F318" s="19">
-        <v>2002</v>
+        <v>2019</v>
       </c>
       <c r="G318" s="2"/>
       <c r="V318" s="3"/>
@@ -15943,10 +15953,10 @@
     <row r="319" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D319" s="3"/>
       <c r="E319" s="18" t="s">
-        <v>363</v>
+        <v>76</v>
       </c>
       <c r="F319" s="19">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="G319" s="2"/>
       <c r="V319" s="3"/>
@@ -15961,10 +15971,10 @@
     <row r="320" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D320" s="3"/>
       <c r="E320" s="18" t="s">
-        <v>364</v>
+        <v>36</v>
       </c>
       <c r="F320" s="19">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G320" s="2"/>
       <c r="V320" s="3"/>
@@ -15979,10 +15989,10 @@
     <row r="321" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D321" s="3"/>
       <c r="E321" s="18" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="F321" s="19">
-        <v>2015</v>
+        <v>2002</v>
       </c>
       <c r="G321" s="2"/>
       <c r="V321" s="3"/>
@@ -15997,10 +16007,10 @@
     <row r="322" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D322" s="3"/>
       <c r="E322" s="18" t="s">
-        <v>0</v>
+        <v>363</v>
       </c>
       <c r="F322" s="19">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="G322" s="2"/>
       <c r="V322" s="3"/>
@@ -16015,10 +16025,10 @@
     <row r="323" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D323" s="3"/>
       <c r="E323" s="18" t="s">
-        <v>96</v>
+        <v>364</v>
       </c>
       <c r="F323" s="19">
-        <v>2002</v>
+        <v>2017</v>
       </c>
       <c r="G323" s="2"/>
       <c r="V323" s="3"/>
@@ -16033,10 +16043,10 @@
     <row r="324" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D324" s="3"/>
       <c r="E324" s="18" t="s">
-        <v>365</v>
+        <v>15</v>
       </c>
       <c r="F324" s="19">
-        <v>2001</v>
+        <v>2015</v>
       </c>
       <c r="G324" s="2"/>
       <c r="V324" s="3"/>
@@ -16051,10 +16061,10 @@
     <row r="325" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D325" s="3"/>
       <c r="E325" s="18" t="s">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="F325" s="19">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="G325" s="2"/>
       <c r="V325" s="3"/>
@@ -16069,10 +16079,10 @@
     <row r="326" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D326" s="3"/>
       <c r="E326" s="18" t="s">
-        <v>367</v>
+        <v>96</v>
       </c>
       <c r="F326" s="19">
-        <v>2017</v>
+        <v>2002</v>
       </c>
       <c r="G326" s="2"/>
       <c r="V326" s="3"/>
@@ -16087,10 +16097,10 @@
     <row r="327" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D327" s="3"/>
       <c r="E327" s="18" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F327" s="19">
-        <v>2014</v>
+        <v>2001</v>
       </c>
       <c r="G327" s="2"/>
       <c r="V327" s="3"/>
@@ -16105,10 +16115,10 @@
     <row r="328" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D328" s="3"/>
       <c r="E328" s="18" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F328" s="19">
-        <v>1980</v>
+        <v>2013</v>
       </c>
       <c r="G328" s="2"/>
       <c r="V328" s="3"/>
@@ -16123,10 +16133,10 @@
     <row r="329" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D329" s="3"/>
       <c r="E329" s="18" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F329" s="19">
-        <v>1995</v>
+        <v>2017</v>
       </c>
       <c r="G329" s="2"/>
       <c r="V329" s="3"/>
@@ -16141,10 +16151,10 @@
     <row r="330" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D330" s="3"/>
       <c r="E330" s="18" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F330" s="19">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="G330" s="2"/>
       <c r="V330" s="3"/>
@@ -16159,10 +16169,10 @@
     <row r="331" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D331" s="3"/>
       <c r="E331" s="18" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F331" s="19">
-        <v>2004</v>
+        <v>1980</v>
       </c>
       <c r="G331" s="2"/>
       <c r="V331" s="3"/>
@@ -16177,10 +16187,10 @@
     <row r="332" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D332" s="3"/>
       <c r="E332" s="18" t="s">
-        <v>42</v>
+        <v>370</v>
       </c>
       <c r="F332" s="19">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="G332" s="2"/>
       <c r="V332" s="3"/>
@@ -16195,10 +16205,10 @@
     <row r="333" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D333" s="3"/>
       <c r="E333" s="18" t="s">
-        <v>84</v>
+        <v>371</v>
       </c>
       <c r="F333" s="19">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="G333" s="2"/>
       <c r="V333" s="3"/>
@@ -16213,10 +16223,10 @@
     <row r="334" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D334" s="3"/>
       <c r="E334" s="18" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F334" s="19">
-        <v>2014</v>
+        <v>2004</v>
       </c>
       <c r="G334" s="2"/>
       <c r="V334" s="3"/>
@@ -16231,10 +16241,10 @@
     <row r="335" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D335" s="3"/>
       <c r="E335" s="18" t="s">
-        <v>374</v>
+        <v>42</v>
       </c>
       <c r="F335" s="19">
-        <v>2010</v>
+        <v>1993</v>
       </c>
       <c r="G335" s="2"/>
       <c r="V335" s="3"/>
@@ -16249,10 +16259,10 @@
     <row r="336" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D336" s="3"/>
       <c r="E336" s="18" t="s">
-        <v>375</v>
+        <v>84</v>
       </c>
       <c r="F336" s="19">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="G336" s="2"/>
       <c r="V336" s="3"/>
@@ -16267,10 +16277,10 @@
     <row r="337" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D337" s="3"/>
       <c r="E337" s="18" t="s">
-        <v>28</v>
+        <v>373</v>
       </c>
       <c r="F337" s="19">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="G337" s="2"/>
       <c r="V337" s="3"/>
@@ -16285,10 +16295,10 @@
     <row r="338" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D338" s="3"/>
       <c r="E338" s="18" t="s">
-        <v>8</v>
+        <v>374</v>
       </c>
       <c r="F338" s="19">
-        <v>1994</v>
+        <v>2010</v>
       </c>
       <c r="G338" s="2"/>
       <c r="V338" s="3"/>
@@ -16303,10 +16313,10 @@
     <row r="339" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D339" s="3"/>
       <c r="E339" s="18" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F339" s="19">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="G339" s="2"/>
       <c r="V339" s="3"/>
@@ -16321,10 +16331,10 @@
     <row r="340" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D340" s="3"/>
       <c r="E340" s="18" t="s">
-        <v>377</v>
+        <v>28</v>
       </c>
       <c r="F340" s="19">
-        <v>1991</v>
+        <v>2016</v>
       </c>
       <c r="G340" s="2"/>
       <c r="V340" s="3"/>
@@ -16339,10 +16349,10 @@
     <row r="341" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D341" s="3"/>
       <c r="E341" s="18" t="s">
-        <v>378</v>
+        <v>8</v>
       </c>
       <c r="F341" s="19">
-        <v>2019</v>
+        <v>1994</v>
       </c>
       <c r="G341" s="2"/>
       <c r="V341" s="3"/>
@@ -16357,10 +16367,10 @@
     <row r="342" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D342" s="3"/>
       <c r="E342" s="18" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F342" s="19">
-        <v>2001</v>
+        <v>2015</v>
       </c>
       <c r="G342" s="2"/>
       <c r="V342" s="3"/>
@@ -16375,10 +16385,10 @@
     <row r="343" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D343" s="3"/>
       <c r="E343" s="18" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F343" s="19">
-        <v>2004</v>
+        <v>1991</v>
       </c>
       <c r="G343" s="2"/>
       <c r="V343" s="3"/>
@@ -16393,10 +16403,10 @@
     <row r="344" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D344" s="3"/>
       <c r="E344" s="18" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F344" s="19">
-        <v>2001</v>
+        <v>2019</v>
       </c>
       <c r="G344" s="2"/>
       <c r="V344" s="3"/>
@@ -16411,7 +16421,7 @@
     <row r="345" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D345" s="3"/>
       <c r="E345" s="18" t="s">
-        <v>56</v>
+        <v>379</v>
       </c>
       <c r="F345" s="19">
         <v>2001</v>
@@ -16429,10 +16439,10 @@
     <row r="346" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D346" s="3"/>
       <c r="E346" s="18" t="s">
-        <v>88</v>
+        <v>380</v>
       </c>
       <c r="F346" s="19">
-        <v>2017</v>
+        <v>2004</v>
       </c>
       <c r="G346" s="2"/>
       <c r="V346" s="3"/>
@@ -16447,10 +16457,10 @@
     <row r="347" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D347" s="3"/>
       <c r="E347" s="18" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F347" s="19">
-        <v>1985</v>
+        <v>2001</v>
       </c>
       <c r="G347" s="2"/>
       <c r="V347" s="3"/>
@@ -16465,7 +16475,7 @@
     <row r="348" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D348" s="3"/>
       <c r="E348" s="18" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="F348" s="19">
         <v>2001</v>
@@ -16483,10 +16493,10 @@
     <row r="349" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D349" s="3"/>
       <c r="E349" s="18" t="s">
-        <v>383</v>
+        <v>88</v>
       </c>
       <c r="F349" s="19">
-        <v>2003</v>
+        <v>2017</v>
       </c>
       <c r="G349" s="2"/>
       <c r="V349" s="3"/>
@@ -16501,10 +16511,10 @@
     <row r="350" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D350" s="3"/>
       <c r="E350" s="18" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F350" s="19">
-        <v>2008</v>
+        <v>1985</v>
       </c>
       <c r="G350" s="2"/>
       <c r="V350" s="3"/>
@@ -16519,10 +16529,10 @@
     <row r="351" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D351" s="3"/>
       <c r="E351" s="18" t="s">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="F351" s="19">
-        <v>1997</v>
+        <v>2001</v>
       </c>
       <c r="G351" s="2"/>
       <c r="V351" s="3"/>
@@ -16537,10 +16547,10 @@
     <row r="352" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D352" s="3"/>
       <c r="E352" s="18" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F352" s="19">
-        <v>2019</v>
+        <v>2003</v>
       </c>
       <c r="G352" s="2"/>
       <c r="V352" s="3"/>
@@ -16555,10 +16565,10 @@
     <row r="353" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D353" s="3"/>
       <c r="E353" s="18" t="s">
-        <v>80</v>
+        <v>384</v>
       </c>
       <c r="F353" s="19">
-        <v>2017</v>
+        <v>2008</v>
       </c>
       <c r="G353" s="2"/>
       <c r="V353" s="3"/>
@@ -16573,10 +16583,10 @@
     <row r="354" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D354" s="3"/>
       <c r="E354" s="18" t="s">
-        <v>386</v>
+        <v>3</v>
       </c>
       <c r="F354" s="19">
-        <v>1977</v>
+        <v>1997</v>
       </c>
       <c r="G354" s="2"/>
       <c r="V354" s="3"/>
@@ -16591,10 +16601,10 @@
     <row r="355" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D355" s="3"/>
       <c r="E355" s="18" t="s">
-        <v>4</v>
+        <v>385</v>
       </c>
       <c r="F355" s="19">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="G355" s="2"/>
       <c r="V355" s="3"/>
@@ -16609,10 +16619,10 @@
     <row r="356" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D356" s="3"/>
       <c r="E356" s="18" t="s">
-        <v>387</v>
+        <v>80</v>
       </c>
       <c r="F356" s="19">
-        <v>1999</v>
+        <v>2017</v>
       </c>
       <c r="G356" s="2"/>
       <c r="V356" s="3"/>
@@ -16627,10 +16637,10 @@
     <row r="357" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D357" s="3"/>
       <c r="E357" s="18" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F357" s="19">
-        <v>2014</v>
+        <v>1977</v>
       </c>
       <c r="G357" s="2"/>
       <c r="V357" s="3"/>
@@ -16645,10 +16655,10 @@
     <row r="358" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D358" s="3"/>
       <c r="E358" s="18" t="s">
-        <v>389</v>
+        <v>4</v>
       </c>
       <c r="F358" s="19">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="G358" s="2"/>
       <c r="V358" s="3"/>
@@ -16663,10 +16673,10 @@
     <row r="359" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D359" s="3"/>
       <c r="E359" s="18" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F359" s="19">
-        <v>2014</v>
+        <v>1999</v>
       </c>
       <c r="G359" s="2"/>
       <c r="V359" s="3"/>
@@ -16681,10 +16691,10 @@
     <row r="360" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D360" s="3"/>
       <c r="E360" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F360" s="19">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="G360" s="2"/>
       <c r="V360" s="3"/>
@@ -16699,10 +16709,10 @@
     <row r="361" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D361" s="3"/>
       <c r="E361" s="18" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F361" s="19">
-        <v>1998</v>
+        <v>2010</v>
       </c>
       <c r="G361" s="2"/>
       <c r="V361" s="3"/>
@@ -16717,10 +16727,10 @@
     <row r="362" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D362" s="3"/>
       <c r="E362" s="18" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F362" s="19">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="G362" s="2"/>
       <c r="V362" s="3"/>
@@ -16735,10 +16745,10 @@
     <row r="363" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D363" s="3"/>
       <c r="E363" s="18" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F363" s="19">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="G363" s="2"/>
       <c r="V363" s="3"/>
@@ -16753,10 +16763,10 @@
     <row r="364" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D364" s="3"/>
       <c r="E364" s="18" t="s">
-        <v>66</v>
+        <v>392</v>
       </c>
       <c r="F364" s="19">
-        <v>2003</v>
+        <v>1998</v>
       </c>
       <c r="G364" s="2"/>
       <c r="V364" s="3"/>
@@ -16771,10 +16781,10 @@
     <row r="365" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D365" s="3"/>
       <c r="E365" s="18" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F365" s="19">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="G365" s="2"/>
       <c r="V365" s="3"/>
@@ -16789,10 +16799,10 @@
     <row r="366" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D366" s="3"/>
       <c r="E366" s="18" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F366" s="19">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="G366" s="2"/>
       <c r="V366" s="3"/>
@@ -16807,10 +16817,10 @@
     <row r="367" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D367" s="3"/>
       <c r="E367" s="18" t="s">
-        <v>397</v>
+        <v>66</v>
       </c>
       <c r="F367" s="19">
-        <v>2017</v>
+        <v>2003</v>
       </c>
       <c r="G367" s="2"/>
       <c r="V367" s="3"/>
@@ -16825,10 +16835,10 @@
     <row r="368" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D368" s="3"/>
       <c r="E368" s="18" t="s">
-        <v>1</v>
+        <v>395</v>
       </c>
       <c r="F368" s="19">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="G368" s="2"/>
       <c r="V368" s="3"/>
@@ -16843,10 +16853,10 @@
     <row r="369" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D369" s="3"/>
       <c r="E369" s="18" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F369" s="19">
-        <v>1995</v>
+        <v>2007</v>
       </c>
       <c r="G369" s="2"/>
       <c r="V369" s="3"/>
@@ -16861,10 +16871,10 @@
     <row r="370" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D370" s="3"/>
       <c r="E370" s="18" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F370" s="19">
-        <v>1980</v>
+        <v>2017</v>
       </c>
       <c r="G370" s="2"/>
       <c r="V370" s="3"/>
@@ -16879,10 +16889,10 @@
     <row r="371" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D371" s="3"/>
       <c r="E371" s="18" t="s">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="F371" s="19">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G371" s="2"/>
       <c r="V371" s="3"/>
@@ -16897,10 +16907,10 @@
     <row r="372" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D372" s="3"/>
       <c r="E372" s="18" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="F372" s="19">
-        <v>2016</v>
+        <v>1995</v>
       </c>
       <c r="G372" s="2"/>
       <c r="V372" s="3"/>
@@ -16915,10 +16925,10 @@
     <row r="373" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D373" s="3"/>
       <c r="E373" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F373" s="19">
-        <v>2009</v>
+        <v>1980</v>
       </c>
       <c r="G373" s="2"/>
       <c r="V373" s="3"/>
@@ -16933,10 +16943,10 @@
     <row r="374" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D374" s="3"/>
       <c r="E374" s="18" t="s">
-        <v>89</v>
+        <v>400</v>
       </c>
       <c r="F374" s="19">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="G374" s="2"/>
       <c r="V374" s="3"/>
@@ -16951,7 +16961,7 @@
     <row r="375" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D375" s="3"/>
       <c r="E375" s="18" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F375" s="19">
         <v>2016</v>
@@ -16969,10 +16979,10 @@
     <row r="376" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D376" s="3"/>
       <c r="E376" s="18" t="s">
-        <v>10</v>
+        <v>402</v>
       </c>
       <c r="F376" s="19">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="G376" s="2"/>
       <c r="V376" s="3"/>
@@ -16987,10 +16997,10 @@
     <row r="377" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D377" s="3"/>
       <c r="E377" s="18" t="s">
-        <v>404</v>
+        <v>89</v>
       </c>
       <c r="F377" s="19">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="G377" s="2"/>
       <c r="V377" s="3"/>
@@ -17005,10 +17015,10 @@
     <row r="378" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D378" s="3"/>
       <c r="E378" s="18" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F378" s="19">
-        <v>2009</v>
+        <v>2016</v>
       </c>
       <c r="G378" s="2"/>
       <c r="V378" s="3"/>
@@ -17023,10 +17033,10 @@
     <row r="379" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D379" s="3"/>
       <c r="E379" s="18" t="s">
-        <v>406</v>
+        <v>10</v>
       </c>
       <c r="F379" s="19">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="G379" s="2"/>
       <c r="V379" s="3"/>
@@ -17041,10 +17051,10 @@
     <row r="380" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D380" s="3"/>
       <c r="E380" s="18" t="s">
-        <v>17</v>
+        <v>404</v>
       </c>
       <c r="F380" s="19">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G380" s="2"/>
       <c r="V380" s="3"/>
@@ -17059,10 +17069,10 @@
     <row r="381" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D381" s="3"/>
       <c r="E381" s="18" t="s">
-        <v>5</v>
+        <v>405</v>
       </c>
       <c r="F381" s="19">
-        <v>2018</v>
+        <v>2009</v>
       </c>
       <c r="G381" s="2"/>
       <c r="V381" s="3"/>
@@ -17077,10 +17087,10 @@
     <row r="382" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D382" s="3"/>
       <c r="E382" s="18" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F382" s="19">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="G382" s="2"/>
       <c r="V382" s="3"/>
@@ -17095,10 +17105,10 @@
     <row r="383" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D383" s="3"/>
       <c r="E383" s="18" t="s">
-        <v>408</v>
+        <v>17</v>
       </c>
       <c r="F383" s="19">
-        <v>1994</v>
+        <v>2018</v>
       </c>
       <c r="G383" s="2"/>
       <c r="V383" s="3"/>
@@ -17113,10 +17123,10 @@
     <row r="384" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D384" s="3"/>
       <c r="E384" s="18" t="s">
-        <v>409</v>
+        <v>5</v>
       </c>
       <c r="F384" s="19">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="G384" s="2"/>
       <c r="V384" s="3"/>
@@ -17131,10 +17141,10 @@
     <row r="385" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D385" s="3"/>
       <c r="E385" s="18" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="F385" s="19">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="G385" s="2"/>
       <c r="V385" s="3"/>
@@ -17149,10 +17159,10 @@
     <row r="386" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D386" s="3"/>
       <c r="E386" s="18" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F386" s="19">
-        <v>1999</v>
+        <v>1994</v>
       </c>
       <c r="G386" s="2"/>
       <c r="V386" s="3"/>
@@ -17167,10 +17177,10 @@
     <row r="387" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D387" s="3"/>
       <c r="E387" s="18" t="s">
-        <v>41</v>
+        <v>409</v>
       </c>
       <c r="F387" s="19">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="G387" s="2"/>
       <c r="V387" s="3"/>
@@ -17185,10 +17195,10 @@
     <row r="388" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D388" s="3"/>
       <c r="E388" s="18" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F388" s="19">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="G388" s="2"/>
       <c r="V388" s="3"/>
@@ -17203,10 +17213,10 @@
     <row r="389" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D389" s="3"/>
       <c r="E389" s="18" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F389" s="19">
-        <v>1994</v>
+        <v>1999</v>
       </c>
       <c r="G389" s="2"/>
       <c r="V389" s="3"/>
@@ -17221,15 +17231,15 @@
     <row r="390" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D390" s="3"/>
       <c r="E390" s="18" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F390" s="19">
-        <v>2008</v>
+        <v>2019</v>
       </c>
       <c r="G390" s="2"/>
       <c r="V390" s="3"/>
       <c r="W390" s="36" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="X390" s="36">
         <v>2022</v>
@@ -17239,15 +17249,15 @@
     <row r="391" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D391" s="3"/>
       <c r="E391" s="18" t="s">
-        <v>95</v>
+        <v>412</v>
       </c>
       <c r="F391" s="19">
-        <v>2010</v>
+        <v>2019</v>
       </c>
       <c r="G391" s="3"/>
       <c r="V391" s="3"/>
       <c r="W391" s="36" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="X391" s="36">
         <v>2014</v>
@@ -17256,12 +17266,16 @@
     </row>
     <row r="392" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D392" s="3"/>
-      <c r="E392" s="3"/>
-      <c r="F392" s="3"/>
+      <c r="E392" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="F392" s="19">
+        <v>1994</v>
+      </c>
       <c r="G392" s="3"/>
       <c r="V392" s="3"/>
       <c r="W392" s="36" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="X392" s="36">
         <v>2021</v>
@@ -17269,6 +17283,14 @@
       <c r="Y392" s="3"/>
     </row>
     <row r="393" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D393" s="3"/>
+      <c r="E393" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F393" s="19">
+        <v>2008</v>
+      </c>
+      <c r="G393" s="3"/>
       <c r="V393" s="3"/>
       <c r="W393" s="36" t="s">
         <v>424</v>
@@ -17279,6 +17301,14 @@
       <c r="Y393" s="3"/>
     </row>
     <row r="394" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D394" s="3"/>
+      <c r="E394" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F394" s="19">
+        <v>2010</v>
+      </c>
+      <c r="G394" s="3"/>
       <c r="V394" s="3"/>
       <c r="W394" s="36" t="s">
         <v>487</v>
@@ -17289,9 +17319,13 @@
       <c r="Y394" s="3"/>
     </row>
     <row r="395" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D395" s="3"/>
+      <c r="E395" s="3"/>
+      <c r="F395" s="3"/>
+      <c r="G395" s="3"/>
       <c r="V395" s="3"/>
       <c r="W395" s="36" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="X395" s="36">
         <v>2018</v>
@@ -17301,7 +17335,7 @@
     <row r="396" spans="4:25" x14ac:dyDescent="0.2">
       <c r="V396" s="3"/>
       <c r="W396" s="36" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="X396" s="36">
         <v>2010</v>
@@ -17331,7 +17365,7 @@
     <row r="399" spans="4:25" x14ac:dyDescent="0.2">
       <c r="V399" s="3"/>
       <c r="W399" s="36" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="X399" s="36">
         <v>2007</v>
@@ -17341,7 +17375,7 @@
     <row r="400" spans="4:25" x14ac:dyDescent="0.2">
       <c r="V400" s="3"/>
       <c r="W400" s="36" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="X400" s="36">
         <v>2018</v>
@@ -17351,7 +17385,7 @@
     <row r="401" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V401" s="3"/>
       <c r="W401" s="36" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="X401" s="36">
         <v>2019</v>
@@ -17361,7 +17395,7 @@
     <row r="402" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V402" s="3"/>
       <c r="W402" s="36" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="X402" s="36">
         <v>2018</v>
@@ -17371,7 +17405,7 @@
     <row r="403" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V403" s="3"/>
       <c r="W403" s="36" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="X403" s="36">
         <v>2018</v>
@@ -17381,7 +17415,7 @@
     <row r="404" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V404" s="3"/>
       <c r="W404" s="36" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="X404" s="36">
         <v>2006</v>
@@ -17391,7 +17425,7 @@
     <row r="405" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V405" s="3"/>
       <c r="W405" s="36" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="X405" s="36">
         <v>2016</v>
@@ -17411,7 +17445,7 @@
     <row r="407" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V407" s="3"/>
       <c r="W407" s="36" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="X407" s="36">
         <v>2018</v>
@@ -17421,7 +17455,7 @@
     <row r="408" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V408" s="3"/>
       <c r="W408" s="36" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="X408" s="36">
         <v>2011</v>
@@ -17431,7 +17465,7 @@
     <row r="409" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V409" s="3"/>
       <c r="W409" s="36" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="X409" s="36">
         <v>2009</v>
@@ -17441,7 +17475,7 @@
     <row r="410" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V410" s="3"/>
       <c r="W410" s="36" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="X410" s="36">
         <v>2008</v>
@@ -17451,7 +17485,7 @@
     <row r="411" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V411" s="3"/>
       <c r="W411" s="36" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="X411" s="36">
         <v>2011</v>
@@ -17471,7 +17505,7 @@
     <row r="413" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V413" s="3"/>
       <c r="W413" s="36" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="X413" s="36">
         <v>2000</v>
@@ -17491,7 +17525,7 @@
     <row r="415" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V415" s="3"/>
       <c r="W415" s="36" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="X415" s="36">
         <v>1999</v>
@@ -17501,7 +17535,7 @@
     <row r="416" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V416" s="3"/>
       <c r="W416" s="36" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="X416" s="36">
         <v>2011</v>
@@ -17511,7 +17545,7 @@
     <row r="417" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V417" s="3"/>
       <c r="W417" s="36" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="X417" s="36">
         <v>2007</v>
@@ -17521,7 +17555,7 @@
     <row r="418" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V418" s="3"/>
       <c r="W418" s="36" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="X418" s="36">
         <v>1984</v>
@@ -17531,7 +17565,7 @@
     <row r="419" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V419" s="3"/>
       <c r="W419" s="36" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="X419" s="36">
         <v>2019</v>
@@ -17551,7 +17585,7 @@
     <row r="421" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V421" s="3"/>
       <c r="W421" s="36" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="X421" s="36">
         <v>2006</v>
@@ -17571,7 +17605,7 @@
     <row r="423" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V423" s="3"/>
       <c r="W423" s="36" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="X423" s="36">
         <v>2022</v>
@@ -17581,7 +17615,7 @@
     <row r="424" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V424" s="3"/>
       <c r="W424" s="36" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="X424" s="36">
         <v>2023</v>
@@ -17591,7 +17625,7 @@
     <row r="425" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V425" s="3"/>
       <c r="W425" s="36" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="X425" s="36">
         <v>2001</v>
@@ -17601,7 +17635,7 @@
     <row r="426" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V426" s="3"/>
       <c r="W426" s="36" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="X426" s="36">
         <v>2018</v>
@@ -17621,7 +17655,7 @@
     <row r="428" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V428" s="3"/>
       <c r="W428" s="36" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="X428" s="36">
         <v>2003</v>
@@ -17631,7 +17665,7 @@
     <row r="429" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V429" s="3"/>
       <c r="W429" s="36" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="X429" s="36">
         <v>2013</v>
@@ -17651,7 +17685,7 @@
     <row r="431" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V431" s="3"/>
       <c r="W431" s="36" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="X431" s="36">
         <v>2020</v>
@@ -17661,7 +17695,7 @@
     <row r="432" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V432" s="3"/>
       <c r="W432" s="36" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="X432" s="36">
         <v>2006</v>
@@ -17671,7 +17705,7 @@
     <row r="433" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V433" s="3"/>
       <c r="W433" s="36" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="X433" s="36">
         <v>2016</v>
@@ -17691,7 +17725,7 @@
     <row r="435" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V435" s="3"/>
       <c r="W435" s="36" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="X435" s="36">
         <v>1999</v>
@@ -17711,7 +17745,7 @@
     <row r="437" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V437" s="3"/>
       <c r="W437" s="36" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="X437" s="36">
         <v>1990</v>
@@ -17731,7 +17765,7 @@
     <row r="439" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V439" s="3"/>
       <c r="W439" s="36" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="X439" s="36">
         <v>2014</v>
@@ -17741,7 +17775,7 @@
     <row r="440" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V440" s="3"/>
       <c r="W440" s="36" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="X440" s="36">
         <v>2019</v>
@@ -17761,7 +17795,7 @@
     <row r="442" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V442" s="3"/>
       <c r="W442" s="36" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="X442" s="36">
         <v>2021</v>
@@ -17791,7 +17825,7 @@
     <row r="445" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V445" s="3"/>
       <c r="W445" s="36" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="X445" s="36">
         <v>2010</v>
@@ -17801,7 +17835,7 @@
     <row r="446" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V446" s="3"/>
       <c r="W446" s="36" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="X446" s="36">
         <v>2021</v>
@@ -17811,7 +17845,7 @@
     <row r="447" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V447" s="3"/>
       <c r="W447" s="36" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="X447" s="36">
         <v>2021</v>
@@ -17821,7 +17855,7 @@
     <row r="448" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V448" s="3"/>
       <c r="W448" s="36" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="X448" s="36">
         <v>2006</v>
@@ -17831,7 +17865,7 @@
     <row r="449" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V449" s="3"/>
       <c r="W449" s="36" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="X449" s="36">
         <v>2023</v>
@@ -17841,7 +17875,7 @@
     <row r="450" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V450" s="3"/>
       <c r="W450" s="36" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="X450" s="36">
         <v>2000</v>
@@ -17861,7 +17895,7 @@
     <row r="452" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V452" s="3"/>
       <c r="W452" s="36" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="X452" s="36">
         <v>2011</v>
@@ -17871,7 +17905,7 @@
     <row r="453" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V453" s="3"/>
       <c r="W453" s="36" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="X453" s="36">
         <v>2014</v>
@@ -17881,7 +17915,7 @@
     <row r="454" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V454" s="3"/>
       <c r="W454" s="36" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="X454" s="36">
         <v>2014</v>
@@ -17901,7 +17935,7 @@
     <row r="456" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V456" s="3"/>
       <c r="W456" s="36" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="X456" s="36">
         <v>2011</v>
@@ -17911,7 +17945,7 @@
     <row r="457" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V457" s="3"/>
       <c r="W457" s="36" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="X457" s="36">
         <v>2022</v>
@@ -17921,7 +17955,7 @@
     <row r="458" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V458" s="3"/>
       <c r="W458" s="36" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="X458" s="36">
         <v>2014</v>
@@ -17931,7 +17965,7 @@
     <row r="459" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V459" s="3"/>
       <c r="W459" s="36" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="X459" s="36">
         <v>2023</v>
@@ -17941,7 +17975,7 @@
     <row r="460" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V460" s="3"/>
       <c r="W460" s="36" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="X460" s="36">
         <v>2022</v>
@@ -17951,7 +17985,7 @@
     <row r="461" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V461" s="3"/>
       <c r="W461" s="36" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="X461" s="36">
         <v>1999</v>
@@ -17961,7 +17995,7 @@
     <row r="462" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V462" s="3"/>
       <c r="W462" s="36" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="X462" s="36">
         <v>1999</v>
@@ -17971,7 +18005,7 @@
     <row r="463" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V463" s="3"/>
       <c r="W463" s="36" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="X463" s="36">
         <v>2007</v>
@@ -17981,7 +18015,7 @@
     <row r="464" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V464" s="3"/>
       <c r="W464" s="36" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="X464" s="36">
         <v>1989</v>
@@ -17991,7 +18025,7 @@
     <row r="465" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V465" s="3"/>
       <c r="W465" s="36" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="X465" s="36">
         <v>2018</v>
@@ -18001,7 +18035,7 @@
     <row r="466" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V466" s="3"/>
       <c r="W466" s="36" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="X466" s="36">
         <v>2017</v>
@@ -18011,7 +18045,7 @@
     <row r="467" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V467" s="3"/>
       <c r="W467" s="36" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="X467" s="36">
         <v>2002</v>
@@ -18021,7 +18055,7 @@
     <row r="468" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V468" s="3"/>
       <c r="W468" s="36" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="X468" s="36">
         <v>2004</v>
@@ -18031,7 +18065,7 @@
     <row r="469" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V469" s="3"/>
       <c r="W469" s="36" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="X469" s="36">
         <v>2009</v>
@@ -18051,7 +18085,7 @@
     <row r="471" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V471" s="3"/>
       <c r="W471" s="36" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="X471" s="36">
         <v>2014</v>
@@ -18061,7 +18095,7 @@
     <row r="472" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V472" s="3"/>
       <c r="W472" s="36" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="X472" s="36">
         <v>1999</v>
@@ -18071,7 +18105,7 @@
     <row r="473" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V473" s="3"/>
       <c r="W473" s="36" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="X473" s="36">
         <v>2001</v>
@@ -18081,7 +18115,7 @@
     <row r="474" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V474" s="3"/>
       <c r="W474" s="36" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="X474" s="36">
         <v>2004</v>
@@ -18101,7 +18135,7 @@
     <row r="476" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V476" s="3"/>
       <c r="W476" s="36" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="X476" s="36">
         <v>2008</v>
@@ -18111,7 +18145,7 @@
     <row r="477" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V477" s="3"/>
       <c r="W477" s="36" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="X477" s="36">
         <v>1937</v>
@@ -18121,7 +18155,7 @@
     <row r="478" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V478" s="3"/>
       <c r="W478" s="36" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="X478" s="36">
         <v>2014</v>
@@ -18141,7 +18175,7 @@
     <row r="480" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V480" s="3"/>
       <c r="W480" s="36" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="X480" s="36">
         <v>2016</v>
@@ -18161,7 +18195,7 @@
     <row r="482" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V482" s="3"/>
       <c r="W482" s="36" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="X482" s="36">
         <v>2017</v>
@@ -18171,7 +18205,7 @@
     <row r="483" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V483" s="3"/>
       <c r="W483" s="36" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="X483" s="36">
         <v>2014</v>
@@ -18181,7 +18215,7 @@
     <row r="484" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V484" s="3"/>
       <c r="W484" s="36" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="X484" s="36">
         <v>2003</v>
@@ -18191,7 +18225,7 @@
     <row r="485" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V485" s="3"/>
       <c r="W485" s="36" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="X485" s="36">
         <v>2008</v>
@@ -18201,7 +18235,7 @@
     <row r="486" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V486" s="3"/>
       <c r="W486" s="36" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="X486" s="36">
         <v>2021</v>
@@ -18211,7 +18245,7 @@
     <row r="487" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V487" s="3"/>
       <c r="W487" s="36" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="X487" s="36">
         <v>2014</v>
@@ -18231,7 +18265,7 @@
     <row r="489" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V489" s="3"/>
       <c r="W489" s="36" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="X489" s="36">
         <v>1971</v>
@@ -18241,7 +18275,7 @@
     <row r="490" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V490" s="3"/>
       <c r="W490" s="36" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="X490" s="36">
         <v>2014</v>
@@ -18261,7 +18295,7 @@
     <row r="492" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V492" s="3"/>
       <c r="W492" s="36" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="X492" s="36">
         <v>2014</v>
@@ -18271,7 +18305,7 @@
     <row r="493" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V493" s="3"/>
       <c r="W493" s="36" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="X493" s="36">
         <v>2009</v>
@@ -18281,7 +18315,7 @@
     <row r="494" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V494" s="3"/>
       <c r="W494" s="36" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="X494" s="36">
         <v>2023</v>
@@ -18291,7 +18325,7 @@
     <row r="495" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V495" s="3"/>
       <c r="W495" s="36" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="X495" s="36">
         <v>2013</v>
@@ -18301,7 +18335,7 @@
     <row r="496" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V496" s="3"/>
       <c r="W496" s="36" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="X496" s="36">
         <v>2007</v>
@@ -18321,7 +18355,7 @@
     <row r="498" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V498" s="3"/>
       <c r="W498" s="36" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="X498" s="36">
         <v>2011</v>
@@ -18331,7 +18365,7 @@
     <row r="499" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V499" s="3"/>
       <c r="W499" s="36" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="X499" s="36">
         <v>2021</v>
@@ -18351,7 +18385,7 @@
     <row r="501" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V501" s="3"/>
       <c r="W501" s="36" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="X501" s="36">
         <v>2017</v>
@@ -18361,7 +18395,7 @@
     <row r="502" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V502" s="3"/>
       <c r="W502" s="36" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="X502" s="36">
         <v>1996</v>
@@ -18371,7 +18405,7 @@
     <row r="503" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V503" s="3"/>
       <c r="W503" s="36" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="X503" s="36">
         <v>1976</v>
@@ -18381,7 +18415,7 @@
     <row r="504" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V504" s="3"/>
       <c r="W504" s="36" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="X504" s="36">
         <v>2023</v>
@@ -18391,7 +18425,7 @@
     <row r="505" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V505" s="3"/>
       <c r="W505" s="36" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="X505" s="36">
         <v>2024</v>
@@ -18401,7 +18435,7 @@
     <row r="506" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V506" s="3"/>
       <c r="W506" s="36" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="X506" s="36">
         <v>2020</v>
@@ -18411,7 +18445,7 @@
     <row r="507" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V507" s="3"/>
       <c r="W507" s="36" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="X507" s="36">
         <v>2017</v>
@@ -18421,7 +18455,7 @@
     <row r="508" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V508" s="3"/>
       <c r="W508" s="36" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="X508" s="36">
         <v>2005</v>
@@ -18431,7 +18465,7 @@
     <row r="509" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V509" s="3"/>
       <c r="W509" s="36" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="X509" s="36">
         <v>2022</v>
@@ -18441,7 +18475,7 @@
     <row r="510" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V510" s="3"/>
       <c r="W510" s="36" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="X510" s="36">
         <v>2008</v>
@@ -18461,7 +18495,7 @@
     <row r="512" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V512" s="3"/>
       <c r="W512" s="36" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="X512" s="36">
         <v>1987</v>
@@ -18471,7 +18505,7 @@
     <row r="513" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V513" s="3"/>
       <c r="W513" s="36" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="X513" s="36">
         <v>2007</v>
@@ -18481,7 +18515,7 @@
     <row r="514" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V514" s="3"/>
       <c r="W514" s="36" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="X514" s="36">
         <v>2015</v>
@@ -18501,7 +18535,7 @@
     <row r="516" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V516" s="3"/>
       <c r="W516" s="36" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="X516" s="36">
         <v>2023</v>
@@ -18511,7 +18545,7 @@
     <row r="517" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V517" s="3"/>
       <c r="W517" s="36" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="X517" s="36">
         <v>2020</v>
@@ -18521,7 +18555,7 @@
     <row r="518" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V518" s="3"/>
       <c r="W518" s="36" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="X518" s="36">
         <v>2004</v>
@@ -18531,7 +18565,7 @@
     <row r="519" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V519" s="3"/>
       <c r="W519" s="36" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="X519" s="36">
         <v>2023</v>
@@ -18541,7 +18575,7 @@
     <row r="520" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V520" s="3"/>
       <c r="W520" s="36" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="X520" s="36">
         <v>2006</v>
@@ -18551,7 +18585,7 @@
     <row r="521" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V521" s="3"/>
       <c r="W521" s="36" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="X521" s="36">
         <v>2018</v>
@@ -18571,7 +18605,7 @@
     <row r="523" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V523" s="3"/>
       <c r="W523" s="36" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="X523" s="36">
         <v>2017</v>
@@ -18581,7 +18615,7 @@
     <row r="524" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V524" s="3"/>
       <c r="W524" s="36" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="X524" s="36">
         <v>2012</v>
@@ -18601,7 +18635,7 @@
     <row r="526" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V526" s="3"/>
       <c r="W526" s="36" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="X526" s="36">
         <v>2010</v>
@@ -18621,7 +18655,7 @@
     <row r="528" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V528" s="3"/>
       <c r="W528" s="36" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="X528" s="36">
         <v>1999</v>
@@ -18631,7 +18665,7 @@
     <row r="529" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V529" s="3"/>
       <c r="W529" s="36" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="X529" s="36">
         <v>2022</v>
@@ -18641,7 +18675,7 @@
     <row r="530" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V530" s="3"/>
       <c r="W530" s="36" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="X530" s="36">
         <v>2006</v>
@@ -18661,7 +18695,7 @@
     <row r="532" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V532" s="3"/>
       <c r="W532" s="36" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="X532" s="36">
         <v>1995</v>
@@ -18671,7 +18705,7 @@
     <row r="533" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V533" s="3"/>
       <c r="W533" s="36" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="X533" s="36">
         <v>2014</v>
@@ -18691,7 +18725,7 @@
     <row r="535" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V535" s="3"/>
       <c r="W535" s="36" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="X535" s="36">
         <v>2022</v>
@@ -18701,7 +18735,7 @@
     <row r="536" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V536" s="3"/>
       <c r="W536" s="36" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="X536" s="36">
         <v>2020</v>
@@ -18711,7 +18745,7 @@
     <row r="537" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V537" s="3"/>
       <c r="W537" s="36" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="X537" s="36">
         <v>2022</v>
@@ -18731,7 +18765,7 @@
     <row r="539" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V539" s="3"/>
       <c r="W539" s="36" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="X539" s="36">
         <v>2011</v>
@@ -18761,7 +18795,7 @@
     <row r="542" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V542" s="3"/>
       <c r="W542" s="36" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="X542" s="36">
         <v>2019</v>
@@ -18781,7 +18815,7 @@
     <row r="544" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V544" s="3"/>
       <c r="W544" s="36" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="X544" s="36">
         <v>2016</v>
@@ -18791,7 +18825,7 @@
     <row r="545" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V545" s="3"/>
       <c r="W545" s="36" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="X545" s="36">
         <v>2008</v>
@@ -18801,7 +18835,7 @@
     <row r="546" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V546" s="3"/>
       <c r="W546" s="36" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="X546" s="36">
         <v>2017</v>
@@ -18811,7 +18845,7 @@
     <row r="547" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V547" s="3"/>
       <c r="W547" s="36" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="X547" s="36">
         <v>1996</v>
@@ -18831,7 +18865,7 @@
     <row r="549" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V549" s="3"/>
       <c r="W549" s="36" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="X549" s="36">
         <v>2003</v>
@@ -18841,7 +18875,7 @@
     <row r="550" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V550" s="3"/>
       <c r="W550" s="36" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="X550" s="36">
         <v>2006</v>
@@ -18851,7 +18885,7 @@
     <row r="551" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V551" s="3"/>
       <c r="W551" s="36" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="X551" s="36">
         <v>2000</v>
@@ -18861,7 +18895,7 @@
     <row r="552" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V552" s="3"/>
       <c r="W552" s="36" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="X552" s="36">
         <v>2020</v>
@@ -18871,7 +18905,7 @@
     <row r="553" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V553" s="3"/>
       <c r="W553" s="36" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="X553" s="36">
         <v>1975</v>
@@ -18881,7 +18915,7 @@
     <row r="554" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V554" s="3"/>
       <c r="W554" s="36" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="X554" s="36">
         <v>2016</v>
@@ -18891,7 +18925,7 @@
     <row r="555" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V555" s="3"/>
       <c r="W555" s="36" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="X555" s="36">
         <v>2001</v>
@@ -18901,7 +18935,7 @@
     <row r="556" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V556" s="3"/>
       <c r="W556" s="36" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="X556" s="36">
         <v>2016</v>
@@ -18911,7 +18945,7 @@
     <row r="557" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V557" s="3"/>
       <c r="W557" s="36" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="X557" s="36">
         <v>2023</v>
@@ -18921,7 +18955,7 @@
     <row r="558" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V558" s="3"/>
       <c r="W558" s="36" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="X558" s="36">
         <v>1974</v>
@@ -18931,7 +18965,7 @@
     <row r="559" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V559" s="3"/>
       <c r="W559" s="36" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="X559" s="36">
         <v>2021</v>
@@ -18941,7 +18975,7 @@
     <row r="560" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V560" s="3"/>
       <c r="W560" s="36" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="X560" s="36">
         <v>2013</v>
@@ -18951,7 +18985,7 @@
     <row r="561" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V561" s="3"/>
       <c r="W561" s="36" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="X561" s="36">
         <v>2023</v>
@@ -18961,7 +18995,7 @@
     <row r="562" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V562" s="3"/>
       <c r="W562" s="36" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="X562" s="36">
         <v>1984</v>
@@ -18981,7 +19015,7 @@
     <row r="564" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V564" s="3"/>
       <c r="W564" s="36" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="X564" s="36">
         <v>2021</v>
@@ -19001,7 +19035,7 @@
     <row r="566" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V566" s="3"/>
       <c r="W566" s="36" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="X566" s="36">
         <v>2019</v>
@@ -19011,7 +19045,7 @@
     <row r="567" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V567" s="3"/>
       <c r="W567" s="36" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="X567" s="36">
         <v>2022</v>
@@ -19031,7 +19065,7 @@
     <row r="569" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V569" s="3"/>
       <c r="W569" s="36" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="X569" s="36">
         <v>1989</v>
@@ -19041,7 +19075,7 @@
     <row r="570" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V570" s="3"/>
       <c r="W570" s="36" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="X570" s="36">
         <v>2005</v>
@@ -19051,7 +19085,7 @@
     <row r="571" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V571" s="3"/>
       <c r="W571" s="36" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="X571" s="36">
         <v>2010</v>
@@ -19071,7 +19105,7 @@
     <row r="573" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V573" s="3"/>
       <c r="W573" s="36" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="X573" s="36">
         <v>2014</v>
@@ -19081,7 +19115,7 @@
     <row r="574" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V574" s="3"/>
       <c r="W574" s="36" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="X574" s="36">
         <v>2018</v>
@@ -19091,7 +19125,7 @@
     <row r="575" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V575" s="3"/>
       <c r="W575" s="36" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="X575" s="36">
         <v>2018</v>
@@ -19101,7 +19135,7 @@
     <row r="576" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V576" s="3"/>
       <c r="W576" s="36" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="X576" s="36">
         <v>2023</v>
@@ -19111,7 +19145,7 @@
     <row r="577" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V577" s="3"/>
       <c r="W577" s="36" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="X577" s="36">
         <v>2010</v>
@@ -19121,7 +19155,7 @@
     <row r="578" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V578" s="3"/>
       <c r="W578" s="36" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="X578" s="36">
         <v>2006</v>
@@ -19141,7 +19175,7 @@
     <row r="580" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V580" s="3"/>
       <c r="W580" s="36" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="X580" s="36">
         <v>2016</v>
@@ -19151,7 +19185,7 @@
     <row r="581" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V581" s="3"/>
       <c r="W581" s="36" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="X581" s="36">
         <v>2008</v>
@@ -19161,7 +19195,7 @@
     <row r="582" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V582" s="3"/>
       <c r="W582" s="36" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="X582" s="36">
         <v>2013</v>
@@ -19171,7 +19205,7 @@
     <row r="583" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V583" s="3"/>
       <c r="W583" s="36" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="X583" s="36">
         <v>2021</v>
@@ -19181,7 +19215,7 @@
     <row r="584" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V584" s="3"/>
       <c r="W584" s="36" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="X584" s="36">
         <v>2011</v>
@@ -19191,7 +19225,7 @@
     <row r="585" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V585" s="3"/>
       <c r="W585" s="36" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="X585" s="36">
         <v>2009</v>
@@ -19201,7 +19235,7 @@
     <row r="586" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V586" s="3"/>
       <c r="W586" s="36" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="X586" s="36">
         <v>2013</v>
@@ -19211,7 +19245,7 @@
     <row r="587" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V587" s="3"/>
       <c r="W587" s="36" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="X587" s="36">
         <v>2000</v>
@@ -19221,7 +19255,7 @@
     <row r="588" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V588" s="3"/>
       <c r="W588" s="36" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="X588" s="36">
         <v>1989</v>
@@ -19241,7 +19275,7 @@
     <row r="590" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V590" s="3"/>
       <c r="W590" s="36" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="X590" s="36">
         <v>2019</v>
@@ -19251,7 +19285,7 @@
     <row r="591" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V591" s="3"/>
       <c r="W591" s="36" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="X591" s="36">
         <v>2017</v>
@@ -19271,7 +19305,7 @@
     <row r="593" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V593" s="3"/>
       <c r="W593" s="36" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="X593" s="36">
         <v>2011</v>
@@ -19281,7 +19315,7 @@
     <row r="594" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V594" s="3"/>
       <c r="W594" s="36" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="X594" s="36">
         <v>2018</v>
@@ -19291,7 +19325,7 @@
     <row r="595" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V595" s="3"/>
       <c r="W595" s="36" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="X595" s="36">
         <v>2003</v>
@@ -19301,7 +19335,7 @@
     <row r="596" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V596" s="3"/>
       <c r="W596" s="36" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="X596" s="36">
         <v>2018</v>
@@ -19311,7 +19345,7 @@
     <row r="597" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V597" s="3"/>
       <c r="W597" s="36" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="X597" s="36">
         <v>2011</v>
@@ -19321,7 +19355,7 @@
     <row r="598" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V598" s="3"/>
       <c r="W598" s="36" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="X598" s="36">
         <v>2017</v>
@@ -19341,7 +19375,7 @@
     <row r="600" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V600" s="3"/>
       <c r="W600" s="36" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="X600" s="36">
         <v>2004</v>
@@ -19351,7 +19385,7 @@
     <row r="601" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V601" s="3"/>
       <c r="W601" s="36" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="X601" s="36">
         <v>2016</v>
@@ -19361,7 +19395,7 @@
     <row r="602" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V602" s="3"/>
       <c r="W602" s="36" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="X602" s="36">
         <v>2024</v>
@@ -19371,7 +19405,7 @@
     <row r="603" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V603" s="3"/>
       <c r="W603" s="36" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="X603" s="36">
         <v>2009</v>
@@ -19381,7 +19415,7 @@
     <row r="604" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V604" s="3"/>
       <c r="W604" s="36" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="X604" s="36">
         <v>2006</v>
@@ -19401,7 +19435,7 @@
     <row r="606" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V606" s="3"/>
       <c r="W606" s="36" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="X606" s="36">
         <v>2005</v>
@@ -19411,7 +19445,7 @@
     <row r="607" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V607" s="3"/>
       <c r="W607" s="36" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="X607" s="36">
         <v>1997</v>
@@ -19421,7 +19455,7 @@
     <row r="608" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V608" s="3"/>
       <c r="W608" s="36" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="X608" s="36">
         <v>2012</v>
@@ -19431,7 +19465,7 @@
     <row r="609" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V609" s="3"/>
       <c r="W609" s="36" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="X609" s="36">
         <v>2004</v>
@@ -19441,7 +19475,7 @@
     <row r="610" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V610" s="3"/>
       <c r="W610" s="36" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="X610" s="36">
         <v>2011</v>
@@ -19451,7 +19485,7 @@
     <row r="611" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V611" s="3"/>
       <c r="W611" s="36" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="X611" s="36">
         <v>2013</v>
@@ -19461,7 +19495,7 @@
     <row r="612" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V612" s="3"/>
       <c r="W612" s="36" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="X612" s="36">
         <v>2023</v>
@@ -19491,7 +19525,7 @@
     <row r="615" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V615" s="3"/>
       <c r="W615" s="36" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="X615" s="36">
         <v>2020</v>
@@ -19511,7 +19545,7 @@
     <row r="617" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V617" s="3"/>
       <c r="W617" s="36" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="X617" s="36">
         <v>1985</v>
@@ -19521,7 +19555,7 @@
     <row r="618" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V618" s="3"/>
       <c r="W618" s="36" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="X618" s="36">
         <v>2017</v>
@@ -19531,7 +19565,7 @@
     <row r="619" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V619" s="3"/>
       <c r="W619" s="36" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="X619" s="36">
         <v>2007</v>
@@ -19541,7 +19575,7 @@
     <row r="620" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V620" s="3"/>
       <c r="W620" s="36" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="X620" s="36">
         <v>2006</v>
@@ -19551,7 +19585,7 @@
     <row r="621" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V621" s="3"/>
       <c r="W621" s="36" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="X621" s="36">
         <v>1984</v>
@@ -19561,7 +19595,7 @@
     <row r="622" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V622" s="3"/>
       <c r="W622" s="36" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="X622" s="36">
         <v>2011</v>
@@ -19571,7 +19605,7 @@
     <row r="623" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V623" s="3"/>
       <c r="W623" s="36" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="X623" s="36">
         <v>2013</v>
@@ -19581,7 +19615,7 @@
     <row r="624" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V624" s="3"/>
       <c r="W624" s="36" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="X624" s="36">
         <v>1996</v>
@@ -19611,7 +19645,7 @@
     <row r="627" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V627" s="3"/>
       <c r="W627" s="36" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="X627" s="36">
         <v>2014</v>
@@ -19621,7 +19655,7 @@
     <row r="628" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V628" s="3"/>
       <c r="W628" s="36" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="X628" s="36">
         <v>1942</v>
@@ -19631,7 +19665,7 @@
     <row r="629" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V629" s="3"/>
       <c r="W629" s="36" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="X629" s="36">
         <v>2017</v>
@@ -19641,7 +19675,7 @@
     <row r="630" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V630" s="3"/>
       <c r="W630" s="36" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="X630" s="36">
         <v>2008</v>
@@ -19651,7 +19685,7 @@
     <row r="631" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V631" s="3"/>
       <c r="W631" s="36" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="X631" s="36">
         <v>2021</v>
@@ -19661,7 +19695,7 @@
     <row r="632" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V632" s="3"/>
       <c r="W632" s="36" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="X632" s="36">
         <v>2018</v>
@@ -19671,7 +19705,7 @@
     <row r="633" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V633" s="3"/>
       <c r="W633" s="36" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="X633" s="36">
         <v>2005</v>
@@ -19681,7 +19715,7 @@
     <row r="634" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V634" s="3"/>
       <c r="W634" s="36" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="X634" s="36">
         <v>2022</v>
@@ -19691,7 +19725,7 @@
     <row r="635" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V635" s="3"/>
       <c r="W635" s="36" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="X635" s="36">
         <v>2006</v>
@@ -19711,7 +19745,7 @@
     <row r="637" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V637" s="3"/>
       <c r="W637" s="36" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="X637" s="36">
         <v>2016</v>
@@ -19721,7 +19755,7 @@
     <row r="638" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V638" s="3"/>
       <c r="W638" s="36" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="X638" s="36">
         <v>2019</v>
@@ -19731,7 +19765,7 @@
     <row r="639" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V639" s="3"/>
       <c r="W639" s="36" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="X639" s="36">
         <v>2023</v>
@@ -19741,7 +19775,7 @@
     <row r="640" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V640" s="3"/>
       <c r="W640" s="36" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="X640" s="36">
         <v>2019</v>
@@ -19751,7 +19785,7 @@
     <row r="641" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V641" s="3"/>
       <c r="W641" s="36" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="X641" s="36">
         <v>2015</v>
@@ -19761,7 +19795,7 @@
     <row r="642" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V642" s="3"/>
       <c r="W642" s="36" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="X642" s="36">
         <v>2023</v>
@@ -19781,7 +19815,7 @@
     <row r="644" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V644" s="3"/>
       <c r="W644" s="36" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="X644" s="36">
         <v>2016</v>
@@ -19791,7 +19825,7 @@
     <row r="645" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V645" s="3"/>
       <c r="W645" s="36" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="X645" s="36">
         <v>1997</v>
@@ -19801,7 +19835,7 @@
     <row r="646" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V646" s="3"/>
       <c r="W646" s="36" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="X646" s="36">
         <v>2003</v>
@@ -19821,7 +19855,7 @@
     <row r="648" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V648" s="3"/>
       <c r="W648" s="36" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="X648" s="36">
         <v>1993</v>
@@ -19831,7 +19865,7 @@
     <row r="649" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V649" s="3"/>
       <c r="W649" s="36" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="X649" s="36">
         <v>2013</v>
@@ -19841,7 +19875,7 @@
     <row r="650" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V650" s="3"/>
       <c r="W650" s="36" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="X650" s="36">
         <v>2001</v>
@@ -19851,7 +19885,7 @@
     <row r="651" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V651" s="3"/>
       <c r="W651" s="36" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="X651" s="36">
         <v>2016</v>
@@ -19861,7 +19895,7 @@
     <row r="652" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V652" s="3"/>
       <c r="W652" s="36" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="X652" s="36">
         <v>1950</v>
@@ -19871,7 +19905,7 @@
     <row r="653" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V653" s="3"/>
       <c r="W653" s="36" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="X653" s="36">
         <v>2024</v>
@@ -19881,7 +19915,7 @@
     <row r="654" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V654" s="3"/>
       <c r="W654" s="36" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="X654" s="36">
         <v>2004</v>
@@ -19891,7 +19925,7 @@
     <row r="655" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V655" s="3"/>
       <c r="W655" s="36" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="X655" s="36">
         <v>2020</v>
@@ -19901,7 +19935,7 @@
     <row r="656" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V656" s="3"/>
       <c r="W656" s="36" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="X656" s="36">
         <v>2019</v>
@@ -19911,7 +19945,7 @@
     <row r="657" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V657" s="3"/>
       <c r="W657" s="36" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="X657" s="36">
         <v>1940</v>
@@ -19921,7 +19955,7 @@
     <row r="658" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V658" s="3"/>
       <c r="W658" s="36" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="X658" s="36">
         <v>2008</v>
@@ -19931,7 +19965,7 @@
     <row r="659" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V659" s="3"/>
       <c r="W659" s="36" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="X659" s="36">
         <v>2011</v>
@@ -19941,7 +19975,7 @@
     <row r="660" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V660" s="3"/>
       <c r="W660" s="36" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="X660" s="36">
         <v>2016</v>
@@ -19961,7 +19995,7 @@
     <row r="662" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V662" s="3"/>
       <c r="W662" s="36" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="X662" s="36">
         <v>2023</v>
@@ -19971,7 +20005,7 @@
     <row r="663" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V663" s="3"/>
       <c r="W663" s="36" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="X663" s="36">
         <v>2007</v>
@@ -19981,7 +20015,7 @@
     <row r="664" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V664" s="3"/>
       <c r="W664" s="36" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="X664" s="36">
         <v>2006</v>
@@ -20001,7 +20035,7 @@
     <row r="666" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V666" s="3"/>
       <c r="W666" s="36" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="X666" s="36">
         <v>2010</v>
@@ -20011,7 +20045,7 @@
     <row r="667" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V667" s="3"/>
       <c r="W667" s="36" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="X667" s="36">
         <v>1993</v>
@@ -20021,7 +20055,7 @@
     <row r="668" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V668" s="3"/>
       <c r="W668" s="36" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="X668" s="36">
         <v>2002</v>
@@ -20041,7 +20075,7 @@
     <row r="670" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V670" s="3"/>
       <c r="W670" s="36" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="X670" s="36">
         <v>2022</v>
@@ -20071,7 +20105,7 @@
     <row r="673" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V673" s="3"/>
       <c r="W673" s="36" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="X673" s="36">
         <v>2009</v>
@@ -20081,7 +20115,7 @@
     <row r="674" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V674" s="3"/>
       <c r="W674" s="36" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="X674" s="36">
         <v>2002</v>
@@ -20091,7 +20125,7 @@
     <row r="675" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V675" s="3"/>
       <c r="W675" s="36" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="X675" s="36">
         <v>1999</v>
@@ -20101,7 +20135,7 @@
     <row r="676" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V676" s="3"/>
       <c r="W676" s="36" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="X676" s="36">
         <v>2003</v>
@@ -20111,7 +20145,7 @@
     <row r="677" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V677" s="3"/>
       <c r="W677" s="36" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="X677" s="36">
         <v>2021</v>
@@ -20121,7 +20155,7 @@
     <row r="678" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V678" s="3"/>
       <c r="W678" s="36" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="X678" s="36">
         <v>2012</v>
@@ -20131,7 +20165,7 @@
     <row r="679" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V679" s="3"/>
       <c r="W679" s="36" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="X679" s="36">
         <v>2016</v>
@@ -20151,7 +20185,7 @@
     <row r="681" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V681" s="3"/>
       <c r="W681" s="36" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="X681" s="36">
         <v>2004</v>
@@ -20161,7 +20195,7 @@
     <row r="682" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V682" s="3"/>
       <c r="W682" s="36" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="X682" s="36">
         <v>2023</v>
@@ -20171,7 +20205,7 @@
     <row r="683" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V683" s="3"/>
       <c r="W683" s="36" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="X683" s="36">
         <v>1961</v>
@@ -20181,7 +20215,7 @@
     <row r="684" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V684" s="3"/>
       <c r="W684" s="36" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="X684" s="36">
         <v>2023</v>
@@ -20191,7 +20225,7 @@
     <row r="685" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V685" s="3"/>
       <c r="W685" s="36" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="X685" s="36">
         <v>2002</v>
@@ -20201,7 +20235,7 @@
     <row r="686" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V686" s="3"/>
       <c r="W686" s="36" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="X686" s="36">
         <v>2000</v>
@@ -20211,7 +20245,7 @@
     <row r="687" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V687" s="3"/>
       <c r="W687" s="36" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="X687" s="36">
         <v>2023</v>
@@ -20221,7 +20255,7 @@
     <row r="688" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V688" s="3"/>
       <c r="W688" s="36" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="X688" s="36">
         <v>2017</v>
@@ -20241,7 +20275,7 @@
     <row r="690" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V690" s="3"/>
       <c r="W690" s="36" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="X690" s="36">
         <v>2022</v>
@@ -20251,7 +20285,7 @@
     <row r="691" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V691" s="3"/>
       <c r="W691" s="36" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="X691" s="36">
         <v>2017</v>
@@ -20261,7 +20295,7 @@
     <row r="692" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V692" s="3"/>
       <c r="W692" s="36" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="X692" s="36">
         <v>2021</v>
@@ -20271,7 +20305,7 @@
     <row r="693" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V693" s="3"/>
       <c r="W693" s="36" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="X693" s="36">
         <v>2012</v>
@@ -20281,7 +20315,7 @@
     <row r="694" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V694" s="3"/>
       <c r="W694" s="36" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="X694" s="36">
         <v>2014</v>
@@ -20291,7 +20325,7 @@
     <row r="695" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V695" s="3"/>
       <c r="W695" s="36" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="X695" s="36">
         <v>1980</v>
@@ -20301,7 +20335,7 @@
     <row r="696" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V696" s="3"/>
       <c r="W696" s="36" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="X696" s="36">
         <v>2012</v>
@@ -20311,7 +20345,7 @@
     <row r="697" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V697" s="3"/>
       <c r="W697" s="36" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="X697" s="36">
         <v>2010</v>
@@ -20321,7 +20355,7 @@
     <row r="698" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V698" s="3"/>
       <c r="W698" s="36" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="X698" s="36">
         <v>1984</v>
@@ -20341,7 +20375,7 @@
     <row r="700" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V700" s="3"/>
       <c r="W700" s="36" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="X700" s="36">
         <v>2019</v>
@@ -20351,7 +20385,7 @@
     <row r="701" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V701" s="3"/>
       <c r="W701" s="36" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="X701" s="36">
         <v>2014</v>
@@ -20361,7 +20395,7 @@
     <row r="702" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V702" s="3"/>
       <c r="W702" s="36" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="X702" s="36">
         <v>2005</v>
@@ -20371,7 +20405,7 @@
     <row r="703" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V703" s="3"/>
       <c r="W703" s="36" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="X703" s="36">
         <v>2007</v>
@@ -20381,7 +20415,7 @@
     <row r="704" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V704" s="3"/>
       <c r="W704" s="36" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="X704" s="36">
         <v>2008</v>
@@ -20391,7 +20425,7 @@
     <row r="705" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V705" s="3"/>
       <c r="W705" s="36" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="X705" s="36">
         <v>2021</v>
@@ -20401,7 +20435,7 @@
     <row r="706" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V706" s="3"/>
       <c r="W706" s="36" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="X706" s="36">
         <v>2012</v>
@@ -20411,7 +20445,7 @@
     <row r="707" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V707" s="3"/>
       <c r="W707" s="36" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="X707" s="36">
         <v>1991</v>
@@ -20451,7 +20485,7 @@
     <row r="711" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V711" s="3"/>
       <c r="W711" s="36" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="X711" s="36">
         <v>1992</v>
@@ -20461,7 +20495,7 @@
     <row r="712" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V712" s="3"/>
       <c r="W712" s="36" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="X712" s="36">
         <v>2023</v>
@@ -20471,7 +20505,7 @@
     <row r="713" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V713" s="3"/>
       <c r="W713" s="36" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="X713" s="36">
         <v>2007</v>
@@ -20481,7 +20515,7 @@
     <row r="714" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V714" s="3"/>
       <c r="W714" s="36" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="X714" s="36">
         <v>2004</v>
@@ -20491,7 +20525,7 @@
     <row r="715" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V715" s="3"/>
       <c r="W715" s="36" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="X715" s="36">
         <v>2003</v>
@@ -20501,7 +20535,7 @@
     <row r="716" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V716" s="3"/>
       <c r="W716" s="36" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="X716" s="36">
         <v>2012</v>
@@ -20511,7 +20545,7 @@
     <row r="717" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V717" s="3"/>
       <c r="W717" s="36" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="X717" s="36">
         <v>2021</v>
@@ -20521,7 +20555,7 @@
     <row r="718" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V718" s="3"/>
       <c r="W718" s="36" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="X718" s="36">
         <v>2022</v>
@@ -20531,7 +20565,7 @@
     <row r="719" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V719" s="3"/>
       <c r="W719" s="36" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="X719" s="36">
         <v>2014</v>
@@ -20551,7 +20585,7 @@
     <row r="721" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V721" s="3"/>
       <c r="W721" s="36" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="X721" s="36">
         <v>2015</v>
@@ -20561,7 +20595,7 @@
     <row r="722" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V722" s="3"/>
       <c r="W722" s="36" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="X722" s="36">
         <v>2001</v>
@@ -20571,7 +20605,7 @@
     <row r="723" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V723" s="3"/>
       <c r="W723" s="36" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="X723" s="36">
         <v>2019</v>
@@ -20581,7 +20615,7 @@
     <row r="724" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V724" s="3"/>
       <c r="W724" s="36" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="X724" s="36">
         <v>1953</v>
@@ -20591,7 +20625,7 @@
     <row r="725" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V725" s="3"/>
       <c r="W725" s="36" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="X725" s="36">
         <v>2024</v>
@@ -20601,7 +20635,7 @@
     <row r="726" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V726" s="3"/>
       <c r="W726" s="36" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="X726" s="36">
         <v>1959</v>
@@ -20611,7 +20645,7 @@
     <row r="727" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V727" s="3"/>
       <c r="W727" s="36" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="X727" s="36">
         <v>2021</v>
@@ -20621,7 +20655,7 @@
     <row r="728" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V728" s="3"/>
       <c r="W728" s="36" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="X728" s="36">
         <v>2021</v>
@@ -20641,7 +20675,7 @@
     <row r="730" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V730" s="3"/>
       <c r="W730" s="36" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="X730" s="36">
         <v>2009</v>
@@ -20651,7 +20685,7 @@
     <row r="731" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V731" s="3"/>
       <c r="W731" s="36" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="X731" s="36">
         <v>1999</v>
@@ -20661,7 +20695,7 @@
     <row r="732" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V732" s="3"/>
       <c r="W732" s="36" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="X732" s="36">
         <v>1994</v>
@@ -20671,7 +20705,7 @@
     <row r="733" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V733" s="3"/>
       <c r="W733" s="36" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="X733" s="36">
         <v>1997</v>
@@ -20691,7 +20725,7 @@
     <row r="735" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V735" s="3"/>
       <c r="W735" s="36" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="X735" s="36">
         <v>2019</v>
@@ -20701,7 +20735,7 @@
     <row r="736" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V736" s="3"/>
       <c r="W736" s="36" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="X736" s="36">
         <v>2014</v>
@@ -20711,7 +20745,7 @@
     <row r="737" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V737" s="3"/>
       <c r="W737" s="36" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="X737" s="36">
         <v>2010</v>
@@ -20721,7 +20755,7 @@
     <row r="738" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V738" s="3"/>
       <c r="W738" s="36" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="X738" s="36">
         <v>2020</v>
@@ -20731,7 +20765,7 @@
     <row r="739" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V739" s="3"/>
       <c r="W739" s="36" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="X739" s="36">
         <v>2009</v>
@@ -20751,7 +20785,7 @@
     <row r="741" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V741" s="3"/>
       <c r="W741" s="36" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="X741" s="36">
         <v>2012</v>
@@ -20761,7 +20795,7 @@
     <row r="742" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V742" s="3"/>
       <c r="W742" s="36" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="X742" s="36">
         <v>2015</v>
@@ -20771,7 +20805,7 @@
     <row r="743" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V743" s="3"/>
       <c r="W743" s="36" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="X743" s="36">
         <v>2009</v>
@@ -20781,7 +20815,7 @@
     <row r="744" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V744" s="3"/>
       <c r="W744" s="36" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="X744" s="36">
         <v>2015</v>
@@ -20791,7 +20825,7 @@
     <row r="745" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V745" s="3"/>
       <c r="W745" s="36" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="X745" s="36">
         <v>1986</v>
@@ -20801,7 +20835,7 @@
     <row r="746" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V746" s="3"/>
       <c r="W746" s="36" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="X746" s="36">
         <v>2017</v>
@@ -20811,7 +20845,7 @@
     <row r="747" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V747" s="3"/>
       <c r="W747" s="36" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="X747" s="36">
         <v>2000</v>
@@ -20821,7 +20855,7 @@
     <row r="748" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V748" s="3"/>
       <c r="W748" s="36" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="X748" s="36">
         <v>1997</v>
@@ -20841,7 +20875,7 @@
     <row r="750" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V750" s="3"/>
       <c r="W750" s="36" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="X750" s="36">
         <v>2002</v>
@@ -20851,7 +20885,7 @@
     <row r="751" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V751" s="3"/>
       <c r="W751" s="36" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="X751" s="36">
         <v>2016</v>
@@ -20861,7 +20895,7 @@
     <row r="752" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V752" s="3"/>
       <c r="W752" s="36" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="X752" s="36">
         <v>2011</v>
@@ -20871,7 +20905,7 @@
     <row r="753" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V753" s="3"/>
       <c r="W753" s="36" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="X753" s="36">
         <v>2002</v>
@@ -20881,7 +20915,7 @@
     <row r="754" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V754" s="3"/>
       <c r="W754" s="36" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="X754" s="36">
         <v>2017</v>
@@ -20891,7 +20925,7 @@
     <row r="755" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V755" s="3"/>
       <c r="W755" s="36" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="X755" s="36">
         <v>1964</v>
@@ -20901,7 +20935,7 @@
     <row r="756" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V756" s="3"/>
       <c r="W756" s="36" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="X756" s="36">
         <v>1955</v>
@@ -20911,7 +20945,7 @@
     <row r="757" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V757" s="3"/>
       <c r="W757" s="36" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="X757" s="36">
         <v>1997</v>
@@ -20921,7 +20955,7 @@
     <row r="758" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V758" s="3"/>
       <c r="W758" s="36" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="X758" s="36">
         <v>2020</v>
@@ -20931,7 +20965,7 @@
     <row r="759" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V759" s="3"/>
       <c r="W759" s="36" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="X759" s="36">
         <v>2009</v>
@@ -20941,7 +20975,7 @@
     <row r="760" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V760" s="3"/>
       <c r="W760" s="36" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="X760" s="36">
         <v>2022</v>
@@ -20951,7 +20985,7 @@
     <row r="761" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V761" s="3"/>
       <c r="W761" s="36" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="X761" s="36">
         <v>2016</v>
@@ -20961,7 +20995,7 @@
     <row r="762" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V762" s="3"/>
       <c r="W762" s="36" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="X762" s="36">
         <v>2018</v>
@@ -20971,7 +21005,7 @@
     <row r="763" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V763" s="3"/>
       <c r="W763" s="36" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="X763" s="36">
         <v>2018</v>
@@ -20991,7 +21025,7 @@
     <row r="765" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V765" s="3"/>
       <c r="W765" s="36" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="X765" s="36">
         <v>1981</v>
@@ -21001,7 +21035,7 @@
     <row r="766" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V766" s="3"/>
       <c r="W766" s="36" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="X766" s="36">
         <v>2004</v>
@@ -21011,7 +21045,7 @@
     <row r="767" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V767" s="3"/>
       <c r="W767" s="36" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="X767" s="36">
         <v>2012</v>
@@ -21021,7 +21055,7 @@
     <row r="768" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V768" s="3"/>
       <c r="W768" s="36" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="X768" s="36">
         <v>1999</v>
@@ -21041,7 +21075,7 @@
     <row r="770" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V770" s="3"/>
       <c r="W770" s="36" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="X770" s="36">
         <v>2021</v>
@@ -21051,7 +21085,7 @@
     <row r="771" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V771" s="3"/>
       <c r="W771" s="36" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="X771" s="36">
         <v>2006</v>
@@ -21061,7 +21095,7 @@
     <row r="772" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V772" s="3"/>
       <c r="W772" s="36" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="X772" s="36">
         <v>2012</v>
@@ -21071,7 +21105,7 @@
     <row r="773" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V773" s="3"/>
       <c r="W773" s="36" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="X773" s="36">
         <v>1968</v>
@@ -21081,7 +21115,7 @@
     <row r="774" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V774" s="3"/>
       <c r="W774" s="36" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="X774" s="36">
         <v>2002</v>
@@ -21091,7 +21125,7 @@
     <row r="775" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V775" s="3"/>
       <c r="W775" s="36" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="X775" s="36">
         <v>2006</v>
@@ -21101,7 +21135,7 @@
     <row r="776" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V776" s="3"/>
       <c r="W776" s="36" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="X776" s="36">
         <v>1961</v>
@@ -21111,7 +21145,7 @@
     <row r="777" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V777" s="3"/>
       <c r="W777" s="36" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="X777" s="36">
         <v>2004</v>
@@ -21121,7 +21155,7 @@
     <row r="778" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V778" s="3"/>
       <c r="W778" s="36" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="X778" s="36">
         <v>2008</v>
@@ -21131,7 +21165,7 @@
     <row r="779" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V779" s="3"/>
       <c r="W779" s="36" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="X779" s="36">
         <v>2010</v>
@@ -21141,7 +21175,7 @@
     <row r="780" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V780" s="3"/>
       <c r="W780" s="36" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="X780" s="36">
         <v>2017</v>
@@ -21151,7 +21185,7 @@
     <row r="781" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V781" s="3"/>
       <c r="W781" s="36" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="X781" s="36">
         <v>2006</v>
@@ -21161,7 +21195,7 @@
     <row r="782" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V782" s="3"/>
       <c r="W782" s="36" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="X782" s="36">
         <v>2007</v>
@@ -21171,7 +21205,7 @@
     <row r="783" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V783" s="3"/>
       <c r="W783" s="36" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="X783" s="36">
         <v>2020</v>
@@ -21181,7 +21215,7 @@
     <row r="784" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V784" s="3"/>
       <c r="W784" s="36" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="X784" s="36">
         <v>2017</v>
@@ -21191,7 +21225,7 @@
     <row r="785" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V785" s="3"/>
       <c r="W785" s="36" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="X785" s="36">
         <v>2021</v>
@@ -21201,7 +21235,7 @@
     <row r="786" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V786" s="3"/>
       <c r="W786" s="36" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="X786" s="36">
         <v>1988</v>
@@ -21211,7 +21245,7 @@
     <row r="787" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V787" s="3"/>
       <c r="W787" s="36" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="X787" s="36">
         <v>2007</v>
@@ -21221,7 +21255,7 @@
     <row r="788" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V788" s="3"/>
       <c r="W788" s="36" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="X788" s="36">
         <v>2000</v>
@@ -21231,7 +21265,7 @@
     <row r="789" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V789" s="3"/>
       <c r="W789" s="36" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="X789" s="36">
         <v>2018</v>
@@ -21241,7 +21275,7 @@
     <row r="790" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V790" s="3"/>
       <c r="W790" s="36" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="X790" s="36">
         <v>1987</v>
@@ -21251,7 +21285,7 @@
     <row r="791" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V791" s="3"/>
       <c r="W791" s="36" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="X791" s="36">
         <v>2018</v>
@@ -21261,7 +21295,7 @@
     <row r="792" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V792" s="3"/>
       <c r="W792" s="36" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="X792" s="36">
         <v>1996</v>
@@ -21271,7 +21305,7 @@
     <row r="793" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V793" s="3"/>
       <c r="W793" s="36" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="X793" s="36">
         <v>2013</v>
@@ -21281,7 +21315,7 @@
     <row r="794" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V794" s="3"/>
       <c r="W794" s="36" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="X794" s="36">
         <v>2015</v>
@@ -21291,7 +21325,7 @@
     <row r="795" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V795" s="3"/>
       <c r="W795" s="36" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="X795" s="36">
         <v>2004</v>
@@ -21301,7 +21335,7 @@
     <row r="796" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V796" s="3"/>
       <c r="W796" s="36" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="X796" s="36">
         <v>1999</v>
@@ -21311,7 +21345,7 @@
     <row r="797" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V797" s="3"/>
       <c r="W797" s="36" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="X797" s="36">
         <v>2001</v>
@@ -21321,7 +21355,7 @@
     <row r="798" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V798" s="3"/>
       <c r="W798" s="36" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="X798" s="36">
         <v>1993</v>
@@ -21331,7 +21365,7 @@
     <row r="799" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V799" s="3"/>
       <c r="W799" s="36" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="X799" s="36">
         <v>2002</v>
@@ -21341,7 +21375,7 @@
     <row r="800" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V800" s="3"/>
       <c r="W800" s="36" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="X800" s="36">
         <v>2021</v>
@@ -21351,7 +21385,7 @@
     <row r="801" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V801" s="3"/>
       <c r="W801" s="36" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="X801" s="36">
         <v>2011</v>
@@ -21361,7 +21395,7 @@
     <row r="802" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V802" s="3"/>
       <c r="W802" s="36" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="X802" s="36">
         <v>2021</v>
@@ -21371,7 +21405,7 @@
     <row r="803" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V803" s="3"/>
       <c r="W803" s="36" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="X803" s="36">
         <v>2022</v>
@@ -21381,7 +21415,7 @@
     <row r="804" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V804" s="3"/>
       <c r="W804" s="36" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="X804" s="36">
         <v>2017</v>
@@ -21391,7 +21425,7 @@
     <row r="805" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V805" s="3"/>
       <c r="W805" s="36" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="X805" s="36">
         <v>2014</v>
@@ -21411,7 +21445,7 @@
     <row r="807" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V807" s="3"/>
       <c r="W807" s="36" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="X807" s="36">
         <v>2016</v>
@@ -21421,7 +21455,7 @@
     <row r="808" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V808" s="3"/>
       <c r="W808" s="36" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="X808" s="36">
         <v>2016</v>
@@ -21431,7 +21465,7 @@
     <row r="809" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V809" s="3"/>
       <c r="W809" s="36" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="X809" s="36">
         <v>2019</v>
@@ -21441,7 +21475,7 @@
     <row r="810" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V810" s="3"/>
       <c r="W810" s="36" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="X810" s="36">
         <v>2007</v>
@@ -21451,7 +21485,7 @@
     <row r="811" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V811" s="3"/>
       <c r="W811" s="36" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="X811" s="36">
         <v>1999</v>
@@ -21461,7 +21495,7 @@
     <row r="812" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V812" s="3"/>
       <c r="W812" s="36" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="X812" s="36">
         <v>2024</v>
@@ -21471,7 +21505,7 @@
     <row r="813" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V813" s="3"/>
       <c r="W813" s="36" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="X813" s="36">
         <v>2019</v>
@@ -21481,7 +21515,7 @@
     <row r="814" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V814" s="3"/>
       <c r="W814" s="36" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="X814" s="36">
         <v>2020</v>
@@ -21491,7 +21525,7 @@
     <row r="815" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V815" s="3"/>
       <c r="W815" s="36" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="X815" s="36">
         <v>2019</v>
@@ -21501,7 +21535,7 @@
     <row r="816" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V816" s="3"/>
       <c r="W816" s="36" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="X816" s="36">
         <v>2002</v>
@@ -21511,7 +21545,7 @@
     <row r="817" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V817" s="3"/>
       <c r="W817" s="36" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="X817" s="36">
         <v>1998</v>
@@ -21521,7 +21555,7 @@
     <row r="818" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V818" s="3"/>
       <c r="W818" s="36" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="X818" s="36">
         <v>2020</v>
@@ -21531,7 +21565,7 @@
     <row r="819" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V819" s="3"/>
       <c r="W819" s="36" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="X819" s="36">
         <v>2000</v>
@@ -21541,7 +21575,7 @@
     <row r="820" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V820" s="3"/>
       <c r="W820" s="36" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="X820" s="36">
         <v>2022</v>
@@ -21551,7 +21585,7 @@
     <row r="821" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V821" s="3"/>
       <c r="W821" s="36" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="X821" s="36">
         <v>1986</v>
@@ -21561,7 +21595,7 @@
     <row r="822" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V822" s="3"/>
       <c r="W822" s="36" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="X822" s="36">
         <v>2023</v>
@@ -21581,7 +21615,7 @@
     <row r="824" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V824" s="3"/>
       <c r="W824" s="36" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="X824" s="36">
         <v>1997</v>
@@ -21591,7 +21625,7 @@
     <row r="825" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V825" s="3"/>
       <c r="W825" s="36" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="X825" s="36">
         <v>2008</v>
@@ -21601,7 +21635,7 @@
     <row r="826" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V826" s="3"/>
       <c r="W826" s="36" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="X826" s="36">
         <v>2017</v>
@@ -21611,7 +21645,7 @@
     <row r="827" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V827" s="3"/>
       <c r="W827" s="36" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="X827" s="36">
         <v>2008</v>
@@ -21621,7 +21655,7 @@
     <row r="828" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V828" s="3"/>
       <c r="W828" s="36" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="X828" s="36">
         <v>2000</v>
@@ -21631,7 +21665,7 @@
     <row r="829" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V829" s="3"/>
       <c r="W829" s="36" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="X829" s="36">
         <v>2018</v>
@@ -21641,7 +21675,7 @@
     <row r="830" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V830" s="3"/>
       <c r="W830" s="36" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="X830" s="36">
         <v>1941</v>
@@ -21651,7 +21685,7 @@
     <row r="831" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V831" s="3"/>
       <c r="W831" s="36" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="X831" s="36">
         <v>2013</v>
@@ -21661,7 +21695,7 @@
     <row r="832" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V832" s="3"/>
       <c r="W832" s="36" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="X832" s="36">
         <v>2007</v>
@@ -21671,7 +21705,7 @@
     <row r="833" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V833" s="3"/>
       <c r="W833" s="36" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="X833" s="36">
         <v>1998</v>
@@ -21681,7 +21715,7 @@
     <row r="834" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V834" s="3"/>
       <c r="W834" s="36" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="X834" s="36">
         <v>2013</v>
@@ -21691,7 +21725,7 @@
     <row r="835" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V835" s="3"/>
       <c r="W835" s="36" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="X835" s="36">
         <v>2014</v>
@@ -21701,7 +21735,7 @@
     <row r="836" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V836" s="3"/>
       <c r="W836" s="36" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="X836" s="36">
         <v>2005</v>
@@ -21711,7 +21745,7 @@
     <row r="837" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V837" s="3"/>
       <c r="W837" s="36" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="X837" s="36">
         <v>2004</v>
@@ -21721,7 +21755,7 @@
     <row r="838" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V838" s="3"/>
       <c r="W838" s="36" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="X838" s="36">
         <v>2021</v>
@@ -21731,7 +21765,7 @@
     <row r="839" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V839" s="3"/>
       <c r="W839" s="36" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="X839" s="36">
         <v>2015</v>
@@ -21741,7 +21775,7 @@
     <row r="840" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V840" s="3"/>
       <c r="W840" s="36" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="X840" s="36">
         <v>2008</v>
@@ -21751,7 +21785,7 @@
     <row r="841" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V841" s="3"/>
       <c r="W841" s="36" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="X841" s="36">
         <v>2019</v>
@@ -21761,7 +21795,7 @@
     <row r="842" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V842" s="3"/>
       <c r="W842" s="36" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="X842" s="36">
         <v>2021</v>
@@ -21771,7 +21805,7 @@
     <row r="843" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V843" s="3"/>
       <c r="W843" s="36" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="X843" s="36">
         <v>1988</v>
@@ -21791,7 +21825,7 @@
     <row r="845" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V845" s="3"/>
       <c r="W845" s="36" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="X845" s="36">
         <v>2008</v>
@@ -21801,7 +21835,7 @@
     <row r="846" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V846" s="3"/>
       <c r="W846" s="36" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="X846" s="36">
         <v>2001</v>
@@ -21811,7 +21845,7 @@
     <row r="847" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V847" s="3"/>
       <c r="W847" s="36" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="X847" s="36">
         <v>1967</v>
@@ -21821,7 +21855,7 @@
     <row r="848" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V848" s="3"/>
       <c r="W848" s="36" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="X848" s="36">
         <v>2023</v>
@@ -21831,7 +21865,7 @@
     <row r="849" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V849" s="3"/>
       <c r="W849" s="36" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="X849" s="36">
         <v>2023</v>
@@ -21841,7 +21875,7 @@
     <row r="850" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V850" s="3"/>
       <c r="W850" s="36" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="X850" s="36">
         <v>2004</v>
@@ -21851,7 +21885,7 @@
     <row r="851" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V851" s="3"/>
       <c r="W851" s="36" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="X851" s="36">
         <v>2021</v>
@@ -21861,7 +21895,7 @@
     <row r="852" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V852" s="3"/>
       <c r="W852" s="36" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="X852" s="36">
         <v>2024</v>
@@ -21871,7 +21905,7 @@
     <row r="853" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V853" s="3"/>
       <c r="W853" s="36" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="X853" s="36">
         <v>2009</v>
@@ -21881,7 +21915,7 @@
     <row r="854" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V854" s="3"/>
       <c r="W854" s="36" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="X854" s="36">
         <v>2018</v>
@@ -21891,7 +21925,7 @@
     <row r="855" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V855" s="3"/>
       <c r="W855" s="36" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="X855" s="36">
         <v>2023</v>
@@ -21901,7 +21935,7 @@
     <row r="856" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V856" s="3"/>
       <c r="W856" s="36" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="X856" s="36">
         <v>2020</v>
@@ -21911,7 +21945,7 @@
     <row r="857" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V857" s="3"/>
       <c r="W857" s="36" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="X857" s="36">
         <v>2011</v>
@@ -21941,7 +21975,7 @@
     <row r="860" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V860" s="3"/>
       <c r="W860" s="36" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="X860" s="36">
         <v>2011</v>
@@ -21951,7 +21985,7 @@
     <row r="861" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V861" s="3"/>
       <c r="W861" s="36" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="X861" s="36">
         <v>2004</v>
@@ -21961,7 +21995,7 @@
     <row r="862" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V862" s="3"/>
       <c r="W862" s="36" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="X862" s="36">
         <v>2020</v>
@@ -21971,7 +22005,7 @@
     <row r="863" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V863" s="3"/>
       <c r="W863" s="36" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="X863" s="36">
         <v>2012</v>
@@ -21981,7 +22015,7 @@
     <row r="864" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V864" s="3"/>
       <c r="W864" s="36" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="X864" s="36">
         <v>2006</v>
@@ -21991,7 +22025,7 @@
     <row r="865" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V865" s="3"/>
       <c r="W865" s="36" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="X865" s="36">
         <v>1991</v>
@@ -22001,7 +22035,7 @@
     <row r="866" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V866" s="3"/>
       <c r="W866" s="36" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="X866" s="36">
         <v>2024</v>
@@ -22011,7 +22045,7 @@
     <row r="867" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V867" s="3"/>
       <c r="W867" s="36" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="X867" s="36">
         <v>2021</v>
@@ -22021,7 +22055,7 @@
     <row r="868" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V868" s="3"/>
       <c r="W868" s="36" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="X868" s="36">
         <v>1977</v>
@@ -22031,7 +22065,7 @@
     <row r="869" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V869" s="3"/>
       <c r="W869" s="36" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="X869" s="36">
         <v>2000</v>
@@ -22041,7 +22075,7 @@
     <row r="870" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V870" s="3"/>
       <c r="W870" s="36" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="X870" s="36">
         <v>2007</v>
@@ -22051,7 +22085,7 @@
     <row r="871" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V871" s="3"/>
       <c r="W871" s="36" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="X871" s="36">
         <v>2004</v>
@@ -22061,7 +22095,7 @@
     <row r="872" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V872" s="3"/>
       <c r="W872" s="36" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="X872" s="36">
         <v>2024</v>
@@ -22071,7 +22105,7 @@
     <row r="873" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V873" s="3"/>
       <c r="W873" s="36" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="X873" s="36">
         <v>2003</v>
@@ -22081,7 +22115,7 @@
     <row r="874" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V874" s="3"/>
       <c r="W874" s="36" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="X874" s="36">
         <v>2015</v>
@@ -22091,7 +22125,7 @@
     <row r="875" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V875" s="3"/>
       <c r="W875" s="36" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="X875" s="36">
         <v>2008</v>
@@ -22121,7 +22155,7 @@
     <row r="878" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V878" s="3"/>
       <c r="W878" s="36" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="X878" s="36">
         <v>2000</v>
@@ -22131,7 +22165,7 @@
     <row r="879" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V879" s="3"/>
       <c r="W879" s="36" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="X879" s="36">
         <v>2008</v>
@@ -22141,7 +22175,7 @@
     <row r="880" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V880" s="3"/>
       <c r="W880" s="36" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="X880" s="36">
         <v>2018</v>
@@ -22161,7 +22195,7 @@
     <row r="882" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V882" s="3"/>
       <c r="W882" s="36" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="X882" s="36">
         <v>1990</v>
@@ -22171,7 +22205,7 @@
     <row r="883" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V883" s="3"/>
       <c r="W883" s="36" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="X883" s="36">
         <v>2023</v>
@@ -22181,7 +22215,7 @@
     <row r="884" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V884" s="3"/>
       <c r="W884" s="36" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="X884" s="36">
         <v>1994</v>
@@ -22191,7 +22225,7 @@
     <row r="885" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V885" s="3"/>
       <c r="W885" s="36" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="X885" s="36">
         <v>2011</v>
@@ -22201,7 +22235,7 @@
     <row r="886" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V886" s="3"/>
       <c r="W886" s="36" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="X886" s="36">
         <v>2002</v>
@@ -22211,7 +22245,7 @@
     <row r="887" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V887" s="3"/>
       <c r="W887" s="36" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="X887" s="36">
         <v>2010</v>
@@ -22221,7 +22255,7 @@
     <row r="888" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V888" s="3"/>
       <c r="W888" s="36" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="X888" s="36">
         <v>2020</v>
@@ -22241,7 +22275,7 @@
     <row r="890" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V890" s="3"/>
       <c r="W890" s="36" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="X890" s="36">
         <v>1998</v>
@@ -22251,7 +22285,7 @@
     <row r="891" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V891" s="3"/>
       <c r="W891" s="36" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="X891" s="36">
         <v>1995</v>
@@ -22261,7 +22295,7 @@
     <row r="892" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V892" s="3"/>
       <c r="W892" s="36" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="X892" s="36">
         <v>2016</v>
@@ -22281,7 +22315,7 @@
     <row r="894" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V894" s="3"/>
       <c r="W894" s="36" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="X894" s="36">
         <v>2009</v>
@@ -22291,7 +22325,7 @@
     <row r="895" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V895" s="3"/>
       <c r="W895" s="36" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="X895" s="36">
         <v>1994</v>
@@ -22301,7 +22335,7 @@
     <row r="896" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V896" s="3"/>
       <c r="W896" s="36" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="X896" s="36">
         <v>2013</v>
@@ -22311,7 +22345,7 @@
     <row r="897" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V897" s="3"/>
       <c r="W897" s="36" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="X897" s="36">
         <v>2018</v>
@@ -22321,7 +22355,7 @@
     <row r="898" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V898" s="3"/>
       <c r="W898" s="36" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="X898" s="36">
         <v>2007</v>
@@ -22331,7 +22365,7 @@
     <row r="899" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V899" s="3"/>
       <c r="W899" s="36" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="X899" s="36">
         <v>2004</v>
@@ -22341,7 +22375,7 @@
     <row r="900" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V900" s="3"/>
       <c r="W900" s="36" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="X900" s="36">
         <v>2023</v>
@@ -22351,7 +22385,7 @@
     <row r="901" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V901" s="3"/>
       <c r="W901" s="36" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="X901" s="36">
         <v>2011</v>
@@ -22361,7 +22395,7 @@
     <row r="902" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V902" s="3"/>
       <c r="W902" s="36" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="X902" s="36">
         <v>2017</v>
@@ -22371,7 +22405,7 @@
     <row r="903" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V903" s="3"/>
       <c r="W903" s="36" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="X903" s="36">
         <v>2008</v>
@@ -22381,7 +22415,7 @@
     <row r="904" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V904" s="3"/>
       <c r="W904" s="36" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="X904" s="36">
         <v>1980</v>
@@ -22391,7 +22425,7 @@
     <row r="905" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V905" s="3"/>
       <c r="W905" s="36" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="X905" s="36">
         <v>2001</v>
@@ -22411,7 +22445,7 @@
     <row r="907" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V907" s="3"/>
       <c r="W907" s="36" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="X907" s="36">
         <v>2013</v>
@@ -22421,7 +22455,7 @@
     <row r="908" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V908" s="3"/>
       <c r="W908" s="36" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="X908" s="36">
         <v>2013</v>
@@ -22441,7 +22475,7 @@
     <row r="910" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V910" s="3"/>
       <c r="W910" s="36" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="X910" s="36">
         <v>1995</v>
@@ -22451,7 +22485,7 @@
     <row r="911" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V911" s="3"/>
       <c r="W911" s="36" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="X911" s="36">
         <v>2011</v>
@@ -22471,7 +22505,7 @@
     <row r="913" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V913" s="3"/>
       <c r="W913" s="36" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="X913" s="36">
         <v>1940</v>
@@ -22481,7 +22515,7 @@
     <row r="914" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V914" s="3"/>
       <c r="W914" s="36" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="X914" s="36">
         <v>2012</v>
@@ -22491,7 +22525,7 @@
     <row r="915" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V915" s="3"/>
       <c r="W915" s="36" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="X915" s="36">
         <v>2006</v>
@@ -22501,7 +22535,7 @@
     <row r="916" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V916" s="3"/>
       <c r="W916" s="36" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="X916" s="36">
         <v>2011</v>
@@ -22511,7 +22545,7 @@
     <row r="917" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V917" s="3"/>
       <c r="W917" s="36" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="X917" s="36">
         <v>1963</v>
@@ -22521,7 +22555,7 @@
     <row r="918" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V918" s="3"/>
       <c r="W918" s="36" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="X918" s="36">
         <v>2000</v>
@@ -22531,7 +22565,7 @@
     <row r="919" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V919" s="3"/>
       <c r="W919" s="36" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="X919" s="36">
         <v>2019</v>
@@ -22541,7 +22575,7 @@
     <row r="920" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V920" s="3"/>
       <c r="W920" s="36" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="X920" s="36">
         <v>2022</v>
@@ -22551,7 +22585,7 @@
     <row r="921" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V921" s="3"/>
       <c r="W921" s="36" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="X921" s="36">
         <v>1979</v>
@@ -22561,7 +22595,7 @@
     <row r="922" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V922" s="3"/>
       <c r="W922" s="36" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="X922" s="36">
         <v>2011</v>
@@ -22571,7 +22605,7 @@
     <row r="923" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V923" s="3"/>
       <c r="W923" s="36" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="X923" s="36">
         <v>2008</v>
@@ -22581,7 +22615,7 @@
     <row r="924" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V924" s="3"/>
       <c r="W924" s="36" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="X924" s="36">
         <v>2011</v>
@@ -22591,7 +22625,7 @@
     <row r="925" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V925" s="3"/>
       <c r="W925" s="36" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="X925" s="36">
         <v>1994</v>
@@ -22601,7 +22635,7 @@
     <row r="926" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V926" s="3"/>
       <c r="W926" s="36" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="X926" s="36">
         <v>2021</v>
@@ -22611,7 +22645,7 @@
     <row r="927" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V927" s="3"/>
       <c r="W927" s="36" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="X927" s="36">
         <v>1997</v>
@@ -22621,7 +22655,7 @@
     <row r="928" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V928" s="3"/>
       <c r="W928" s="36" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="X928" s="36">
         <v>1986</v>
@@ -22631,7 +22665,7 @@
     <row r="929" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V929" s="3"/>
       <c r="W929" s="36" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="X929" s="36">
         <v>2000</v>
@@ -22641,7 +22675,7 @@
     <row r="930" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V930" s="3"/>
       <c r="W930" s="36" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="X930" s="36">
         <v>1999</v>
@@ -22651,7 +22685,7 @@
     <row r="931" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V931" s="3"/>
       <c r="W931" s="36" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="X931" s="36">
         <v>2012</v>
@@ -22671,7 +22705,7 @@
     <row r="933" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V933" s="3"/>
       <c r="W933" s="36" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="X933" s="36">
         <v>2019</v>
@@ -22681,7 +22715,7 @@
     <row r="934" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V934" s="3"/>
       <c r="W934" s="36" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="X934" s="36">
         <v>2005</v>
@@ -22691,7 +22725,7 @@
     <row r="935" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V935" s="3"/>
       <c r="W935" s="36" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="X935" s="36">
         <v>2023</v>
@@ -22701,7 +22735,7 @@
     <row r="936" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V936" s="3"/>
       <c r="W936" s="36" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="X936" s="36">
         <v>2012</v>
@@ -22711,7 +22745,7 @@
     <row r="937" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V937" s="3"/>
       <c r="W937" s="36" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="X937" s="36">
         <v>2015</v>
@@ -22721,7 +22755,7 @@
     <row r="938" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V938" s="3"/>
       <c r="W938" s="36" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="X938" s="36">
         <v>2020</v>
@@ -22731,7 +22765,7 @@
     <row r="939" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V939" s="3"/>
       <c r="W939" s="36" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="X939" s="36">
         <v>2023</v>
@@ -22741,7 +22775,7 @@
     <row r="940" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V940" s="3"/>
       <c r="W940" s="36" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="X940" s="36">
         <v>2021</v>
@@ -22751,7 +22785,7 @@
     <row r="941" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V941" s="3"/>
       <c r="W941" s="36" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="X941" s="36">
         <v>2019</v>
@@ -22761,7 +22795,7 @@
     <row r="942" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V942" s="3"/>
       <c r="W942" s="36" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="X942" s="36">
         <v>1996</v>
@@ -22771,7 +22805,7 @@
     <row r="943" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V943" s="3"/>
       <c r="W943" s="36" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="X943" s="36">
         <v>2019</v>
@@ -22781,7 +22815,7 @@
     <row r="944" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V944" s="3"/>
       <c r="W944" s="36" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="X944" s="36">
         <v>2022</v>
@@ -22791,7 +22825,7 @@
     <row r="945" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V945" s="3"/>
       <c r="W945" s="36" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="X945" s="36">
         <v>1997</v>
@@ -22801,7 +22835,7 @@
     <row r="946" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V946" s="3"/>
       <c r="W946" s="36" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="X946" s="36">
         <v>2023</v>
@@ -22811,7 +22845,7 @@
     <row r="947" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V947" s="3"/>
       <c r="W947" s="36" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="X947" s="36">
         <v>2021</v>
@@ -22831,7 +22865,7 @@
     <row r="949" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V949" s="3"/>
       <c r="W949" s="36" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="X949" s="36">
         <v>2001</v>
@@ -22841,7 +22875,7 @@
     <row r="950" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V950" s="3"/>
       <c r="W950" s="36" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="X950" s="36">
         <v>2010</v>
@@ -22861,7 +22895,7 @@
     <row r="952" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V952" s="3"/>
       <c r="W952" s="36" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="X952" s="36">
         <v>1970</v>
@@ -22871,7 +22905,7 @@
     <row r="953" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V953" s="3"/>
       <c r="W953" s="36" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="X953" s="36">
         <v>2016</v>
@@ -22881,7 +22915,7 @@
     <row r="954" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V954" s="3"/>
       <c r="W954" s="36" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="X954" s="36">
         <v>2020</v>
@@ -22891,7 +22925,7 @@
     <row r="955" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V955" s="3"/>
       <c r="W955" s="36" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="X955" s="36">
         <v>2023</v>
@@ -22901,7 +22935,7 @@
     <row r="956" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V956" s="3"/>
       <c r="W956" s="36" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="X956" s="36">
         <v>1987</v>
@@ -22911,7 +22945,7 @@
     <row r="957" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V957" s="3"/>
       <c r="W957" s="36" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="X957" s="36">
         <v>2018</v>
@@ -22931,7 +22965,7 @@
     <row r="959" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V959" s="3"/>
       <c r="W959" s="36" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="X959" s="36">
         <v>2018</v>
@@ -22941,7 +22975,7 @@
     <row r="960" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V960" s="3"/>
       <c r="W960" s="36" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="X960" s="36">
         <v>1991</v>
@@ -22951,7 +22985,7 @@
     <row r="961" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V961" s="3"/>
       <c r="W961" s="36" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="X961" s="36">
         <v>2016</v>
@@ -22961,7 +22995,7 @@
     <row r="962" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V962" s="3"/>
       <c r="W962" s="36" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="X962" s="36">
         <v>2024</v>
@@ -22971,7 +23005,7 @@
     <row r="963" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V963" s="3"/>
       <c r="W963" s="36" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="X963" s="36">
         <v>2006</v>
@@ -22981,7 +23015,7 @@
     <row r="964" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V964" s="3"/>
       <c r="W964" s="36" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="X964" s="36">
         <v>2004</v>
@@ -22991,7 +23025,7 @@
     <row r="965" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V965" s="3"/>
       <c r="W965" s="36" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="X965" s="36">
         <v>2001</v>
@@ -23001,7 +23035,7 @@
     <row r="966" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V966" s="3"/>
       <c r="W966" s="36" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="X966" s="36">
         <v>1977</v>
@@ -23011,7 +23045,7 @@
     <row r="967" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V967" s="3"/>
       <c r="W967" s="36" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="X967" s="36">
         <v>2022</v>
@@ -23031,7 +23065,7 @@
     <row r="969" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V969" s="3"/>
       <c r="W969" s="36" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="X969" s="36">
         <v>2016</v>
@@ -23041,7 +23075,7 @@
     <row r="970" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V970" s="3"/>
       <c r="W970" s="36" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="X970" s="36">
         <v>1996</v>
@@ -23061,7 +23095,7 @@
     <row r="972" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V972" s="3"/>
       <c r="W972" s="36" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="X972" s="36">
         <v>2016</v>
@@ -23071,7 +23105,7 @@
     <row r="973" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V973" s="3"/>
       <c r="W973" s="36" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="X973" s="36">
         <v>2022</v>
@@ -23081,7 +23115,7 @@
     <row r="974" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V974" s="3"/>
       <c r="W974" s="36" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="X974" s="36">
         <v>2024</v>
@@ -23101,7 +23135,7 @@
     <row r="976" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V976" s="3"/>
       <c r="W976" s="36" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="X976" s="36">
         <v>2004</v>
@@ -23111,7 +23145,7 @@
     <row r="977" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V977" s="3"/>
       <c r="W977" s="36" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="X977" s="36">
         <v>2007</v>
@@ -23121,7 +23155,7 @@
     <row r="978" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V978" s="3"/>
       <c r="W978" s="36" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="X978" s="36">
         <v>2019</v>
@@ -23131,7 +23165,7 @@
     <row r="979" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V979" s="3"/>
       <c r="W979" s="36" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="X979" s="36">
         <v>2014</v>
@@ -23141,7 +23175,7 @@
     <row r="980" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V980" s="3"/>
       <c r="W980" s="36" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="X980" s="36">
         <v>2022</v>
@@ -23151,7 +23185,7 @@
     <row r="981" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V981" s="3"/>
       <c r="W981" s="36" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="X981" s="36">
         <v>2007</v>
@@ -23161,7 +23195,7 @@
     <row r="982" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V982" s="3"/>
       <c r="W982" s="36" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="X982" s="36">
         <v>2007</v>
@@ -23171,7 +23205,7 @@
     <row r="983" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V983" s="3"/>
       <c r="W983" s="36" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="X983" s="36">
         <v>2024</v>
@@ -23181,7 +23215,7 @@
     <row r="984" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V984" s="3"/>
       <c r="W984" s="36" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="X984" s="36">
         <v>2023</v>
@@ -23191,7 +23225,7 @@
     <row r="985" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V985" s="3"/>
       <c r="W985" s="36" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="X985" s="36">
         <v>2023</v>
@@ -23211,7 +23245,7 @@
     <row r="987" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V987" s="3"/>
       <c r="W987" s="36" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="X987" s="36">
         <v>2021</v>
@@ -23221,7 +23255,7 @@
     <row r="988" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V988" s="3"/>
       <c r="W988" s="36" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="X988" s="36">
         <v>2015</v>
@@ -23241,7 +23275,7 @@
     <row r="990" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V990" s="3"/>
       <c r="W990" s="36" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="X990" s="36">
         <v>2002</v>
@@ -23251,7 +23285,7 @@
     <row r="991" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V991" s="3"/>
       <c r="W991" s="36" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="X991" s="36">
         <v>2004</v>
@@ -23261,7 +23295,7 @@
     <row r="992" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V992" s="3"/>
       <c r="W992" s="36" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="X992" s="36">
         <v>2003</v>
@@ -23271,7 +23305,7 @@
     <row r="993" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V993" s="3"/>
       <c r="W993" s="36" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="X993" s="36">
         <v>1982</v>
@@ -23281,7 +23315,7 @@
     <row r="994" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V994" s="3"/>
       <c r="W994" s="36" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="X994" s="36">
         <v>2024</v>
@@ -23291,7 +23325,7 @@
     <row r="995" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V995" s="3"/>
       <c r="W995" s="36" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="X995" s="36">
         <v>2021</v>
@@ -23301,7 +23335,7 @@
     <row r="996" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V996" s="3"/>
       <c r="W996" s="36" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="X996" s="36">
         <v>2011</v>
@@ -23311,7 +23345,7 @@
     <row r="997" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V997" s="3"/>
       <c r="W997" s="36" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="X997" s="36">
         <v>2011</v>
@@ -23321,7 +23355,7 @@
     <row r="998" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V998" s="3"/>
       <c r="W998" s="36" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="X998" s="36">
         <v>2024</v>
@@ -23331,7 +23365,7 @@
     <row r="999" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V999" s="3"/>
       <c r="W999" s="36" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="X999" s="36">
         <v>1993</v>
@@ -23341,7 +23375,7 @@
     <row r="1000" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V1000" s="3"/>
       <c r="W1000" s="36" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="X1000" s="36">
         <v>1988</v>
@@ -23351,7 +23385,7 @@
     <row r="1001" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V1001" s="3"/>
       <c r="W1001" s="36" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="X1001" s="36">
         <v>2003</v>

--- a/lists.xlsx
+++ b/lists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/StatsAutomator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B65318D-006E-8947-85B1-69098BDA2F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2936E4F1-1A5F-9B47-A06D-0BAC3590D57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" xr2:uid="{98AF27AA-E156-FB4B-94CA-68D339A0B8C2}"/>
   </bookViews>
@@ -3848,9 +3848,6 @@
     <t>Malignant</t>
   </si>
   <si>
-    <t>Horrible Bosses</t>
-  </si>
-  <si>
     <t>Super 8</t>
   </si>
   <si>
@@ -3863,9 +3860,6 @@
     <t>Big</t>
   </si>
   <si>
-    <t>Holes</t>
-  </si>
-  <si>
     <t>Most Watched Year</t>
   </si>
   <si>
@@ -3875,20 +3869,26 @@
     <t>Terminator 2: Judgement Day</t>
   </si>
   <si>
-    <t>Scent of a Woman</t>
-  </si>
-  <si>
     <t>Drishyam</t>
   </si>
   <si>
-    <t>An Autumn Afternoon</t>
+    <t>The Wild Robot</t>
+  </si>
+  <si>
+    <t>Look Back</t>
+  </si>
+  <si>
+    <t>Beetlejuice Beetlejuice</t>
+  </si>
+  <si>
+    <t>Trap</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3931,12 +3931,6 @@
       <color theme="1"/>
       <name val="Aptos Display"/>
       <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -4143,8 +4137,8 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4676,10 +4670,10 @@
       </c>
       <c r="V1" s="7"/>
       <c r="W1" s="35" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="X1" s="35" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="Y1" s="7"/>
     </row>
@@ -4695,7 +4689,7 @@
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="25" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="F2" s="19">
         <v>1991</v>
@@ -4737,10 +4731,10 @@
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="36" t="s">
-        <v>411</v>
+        <v>41</v>
       </c>
       <c r="X2" s="36">
-        <v>1999</v>
+        <v>2019</v>
       </c>
       <c r="Y2" s="3"/>
     </row>
@@ -4798,10 +4792,10 @@
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="36" t="s">
-        <v>41</v>
+        <v>411</v>
       </c>
       <c r="X3" s="36">
-        <v>2019</v>
+        <v>1999</v>
       </c>
       <c r="Y3" s="3"/>
     </row>
@@ -5142,10 +5136,10 @@
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="36" t="s">
-        <v>95</v>
+        <v>410</v>
       </c>
       <c r="X9" s="36">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="Y9" s="3"/>
     </row>
@@ -5197,10 +5191,10 @@
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="36" t="s">
-        <v>410</v>
+        <v>95</v>
       </c>
       <c r="X10" s="36">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="Y10" s="3"/>
     </row>
@@ -5362,10 +5356,10 @@
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="36" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="X13" s="36">
-        <v>2019</v>
+        <v>1998</v>
       </c>
       <c r="Y13" s="3"/>
     </row>
@@ -5417,10 +5411,10 @@
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="36" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="X14" s="36">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="Y14" s="3"/>
     </row>
@@ -5472,10 +5466,10 @@
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="36" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="X15" s="36">
-        <v>1998</v>
+        <v>2007</v>
       </c>
       <c r="Y15" s="3"/>
     </row>
@@ -5857,7 +5851,7 @@
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="36" t="s">
-        <v>409</v>
+        <v>373</v>
       </c>
       <c r="X22" s="36">
         <v>2014</v>
@@ -5912,10 +5906,10 @@
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="36" t="s">
-        <v>328</v>
+        <v>409</v>
       </c>
       <c r="X23" s="36">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="Y23" s="3"/>
     </row>
@@ -5960,17 +5954,17 @@
       </c>
       <c r="S24" s="4"/>
       <c r="T24" s="13" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="U24" s="12">
-        <v>1962</v>
+        <v>2024</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="36" t="s">
-        <v>373</v>
+        <v>328</v>
       </c>
       <c r="X24" s="36">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="Y24" s="3"/>
     </row>
@@ -6554,10 +6548,10 @@
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="36" t="s">
-        <v>405</v>
+        <v>56</v>
       </c>
       <c r="X35" s="36">
-        <v>2009</v>
+        <v>2001</v>
       </c>
       <c r="Y35" s="3"/>
     </row>
@@ -6602,10 +6596,10 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="36" t="s">
-        <v>56</v>
+        <v>380</v>
       </c>
       <c r="X36" s="36">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="Y36" s="3"/>
     </row>
@@ -6650,10 +6644,10 @@
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="36" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="X37" s="36">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="Y37" s="3"/>
     </row>
@@ -6698,10 +6692,10 @@
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="36" t="s">
-        <v>66</v>
+        <v>391</v>
       </c>
       <c r="X38" s="36">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="Y38" s="3"/>
     </row>
@@ -6746,10 +6740,10 @@
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="36" t="s">
-        <v>380</v>
+        <v>66</v>
       </c>
       <c r="X39" s="36">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="Y39" s="3"/>
     </row>
@@ -6842,10 +6836,10 @@
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="36" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="X41" s="36">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="Y41" s="3"/>
     </row>
@@ -6890,10 +6884,10 @@
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="36" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="X42" s="36">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="Y42" s="3"/>
     </row>
@@ -6938,10 +6932,10 @@
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="36" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="X43" s="36">
-        <v>2017</v>
+        <v>1980</v>
       </c>
       <c r="Y43" s="3"/>
     </row>
@@ -6986,10 +6980,10 @@
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="36" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="X44" s="36">
-        <v>1980</v>
+        <v>2017</v>
       </c>
       <c r="Y44" s="3"/>
     </row>
@@ -7226,10 +7220,10 @@
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="36" t="s">
-        <v>394</v>
+        <v>365</v>
       </c>
       <c r="X49" s="36">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="Y49" s="3"/>
     </row>
@@ -7274,10 +7268,10 @@
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="36" t="s">
-        <v>365</v>
+        <v>394</v>
       </c>
       <c r="X50" s="36">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="Y50" s="3"/>
     </row>
@@ -7418,10 +7412,10 @@
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="36" t="s">
-        <v>390</v>
+        <v>363</v>
       </c>
       <c r="X53" s="36">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="Y53" s="3"/>
     </row>
@@ -7514,10 +7508,10 @@
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="36" t="s">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="X55" s="36">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="Y55" s="3"/>
     </row>
@@ -7610,10 +7604,10 @@
       </c>
       <c r="V57" s="3"/>
       <c r="W57" s="36" t="s">
-        <v>385</v>
+        <v>340</v>
       </c>
       <c r="X57" s="36">
-        <v>2019</v>
+        <v>2004</v>
       </c>
       <c r="Y57" s="3"/>
     </row>
@@ -7658,10 +7652,10 @@
       </c>
       <c r="V58" s="3"/>
       <c r="W58" s="36" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="X58" s="36">
-        <v>2010</v>
+        <v>2019</v>
       </c>
       <c r="Y58" s="3"/>
     </row>
@@ -7706,10 +7700,10 @@
       </c>
       <c r="V59" s="3"/>
       <c r="W59" s="36" t="s">
-        <v>340</v>
+        <v>389</v>
       </c>
       <c r="X59" s="36">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="Y59" s="3"/>
     </row>
@@ -7754,10 +7748,10 @@
       </c>
       <c r="V60" s="3"/>
       <c r="W60" s="36" t="s">
-        <v>382</v>
+        <v>72</v>
       </c>
       <c r="X60" s="36">
-        <v>1985</v>
+        <v>2001</v>
       </c>
       <c r="Y60" s="3"/>
     </row>
@@ -7802,10 +7796,10 @@
       </c>
       <c r="V61" s="3"/>
       <c r="W61" s="36" t="s">
-        <v>72</v>
+        <v>382</v>
       </c>
       <c r="X61" s="36">
-        <v>2001</v>
+        <v>1985</v>
       </c>
       <c r="Y61" s="3"/>
     </row>
@@ -7946,10 +7940,10 @@
       </c>
       <c r="V64" s="3"/>
       <c r="W64" s="36" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X64" s="36">
-        <v>1977</v>
+        <v>2003</v>
       </c>
       <c r="Y64" s="3"/>
     </row>
@@ -7994,10 +7988,10 @@
       </c>
       <c r="V65" s="3"/>
       <c r="W65" s="36" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="X65" s="36">
-        <v>2003</v>
+        <v>1977</v>
       </c>
       <c r="Y65" s="3"/>
     </row>
@@ -8042,10 +8036,10 @@
       </c>
       <c r="V66" s="3"/>
       <c r="W66" s="36" t="s">
-        <v>96</v>
+        <v>377</v>
       </c>
       <c r="X66" s="36">
-        <v>2002</v>
+        <v>1991</v>
       </c>
       <c r="Y66" s="3"/>
     </row>
@@ -8090,10 +8084,10 @@
       </c>
       <c r="V67" s="3"/>
       <c r="W67" s="36" t="s">
-        <v>384</v>
+        <v>329</v>
       </c>
       <c r="X67" s="36">
-        <v>2008</v>
+        <v>1999</v>
       </c>
       <c r="Y67" s="3"/>
     </row>
@@ -8138,10 +8132,10 @@
       </c>
       <c r="V68" s="3"/>
       <c r="W68" s="36" t="s">
-        <v>361</v>
+        <v>96</v>
       </c>
       <c r="X68" s="36">
-        <v>1990</v>
+        <v>2002</v>
       </c>
       <c r="Y68" s="3"/>
     </row>
@@ -8186,10 +8180,10 @@
       </c>
       <c r="V69" s="3"/>
       <c r="W69" s="36" t="s">
-        <v>329</v>
+        <v>384</v>
       </c>
       <c r="X69" s="36">
-        <v>1999</v>
+        <v>2008</v>
       </c>
       <c r="Y69" s="3"/>
     </row>
@@ -8234,10 +8228,10 @@
       </c>
       <c r="V70" s="3"/>
       <c r="W70" s="36" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="X70" s="36">
-        <v>1991</v>
+        <v>2010</v>
       </c>
       <c r="Y70" s="3"/>
     </row>
@@ -8282,10 +8276,10 @@
       </c>
       <c r="V71" s="3"/>
       <c r="W71" s="36" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="X71" s="36">
-        <v>2010</v>
+        <v>1990</v>
       </c>
       <c r="Y71" s="3"/>
     </row>
@@ -8330,10 +8324,10 @@
       </c>
       <c r="V72" s="3"/>
       <c r="W72" s="36" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="X72" s="36">
-        <v>2017</v>
+        <v>1994</v>
       </c>
       <c r="Y72" s="3"/>
     </row>
@@ -8378,10 +8372,10 @@
       </c>
       <c r="V73" s="3"/>
       <c r="W73" s="36" t="s">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="X73" s="36">
-        <v>1994</v>
+        <v>2017</v>
       </c>
       <c r="Y73" s="3"/>
     </row>
@@ -8858,10 +8852,10 @@
       </c>
       <c r="V83" s="3"/>
       <c r="W83" s="36" t="s">
-        <v>28</v>
+        <v>314</v>
       </c>
       <c r="X83" s="36">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="Y83" s="3"/>
     </row>
@@ -8906,10 +8900,10 @@
       </c>
       <c r="V84" s="3"/>
       <c r="W84" s="36" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="X84" s="36">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y84" s="3"/>
     </row>
@@ -8954,10 +8948,10 @@
       </c>
       <c r="V85" s="3"/>
       <c r="W85" s="36" t="s">
-        <v>314</v>
+        <v>84</v>
       </c>
       <c r="X85" s="36">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="Y85" s="3"/>
     </row>
@@ -9626,10 +9620,10 @@
       </c>
       <c r="V99" s="3"/>
       <c r="W99" s="36" t="s">
-        <v>368</v>
+        <v>307</v>
       </c>
       <c r="X99" s="36">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="Y99" s="3"/>
     </row>
@@ -9674,10 +9668,10 @@
       </c>
       <c r="V100" s="3"/>
       <c r="W100" s="36" t="s">
-        <v>4</v>
+        <v>368</v>
       </c>
       <c r="X100" s="36">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="Y100" s="3"/>
     </row>
@@ -9722,10 +9716,10 @@
       </c>
       <c r="V101" s="3"/>
       <c r="W101" s="36" t="s">
-        <v>15</v>
+        <v>326</v>
       </c>
       <c r="X101" s="36">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="Y101" s="3"/>
     </row>
@@ -9764,7 +9758,7 @@
       </c>
       <c r="V102" s="3"/>
       <c r="W102" s="36" t="s">
-        <v>376</v>
+        <v>4</v>
       </c>
       <c r="X102" s="36">
         <v>2015</v>
@@ -9803,10 +9797,10 @@
       </c>
       <c r="V103" s="3"/>
       <c r="W103" s="36" t="s">
-        <v>326</v>
+        <v>15</v>
       </c>
       <c r="X103" s="36">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="Y103" s="3"/>
     </row>
@@ -9920,10 +9914,10 @@
       </c>
       <c r="V106" s="3"/>
       <c r="W106" s="36" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="X106" s="36">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="Y106" s="3"/>
     </row>
@@ -9998,10 +9992,10 @@
       </c>
       <c r="V108" s="3"/>
       <c r="W108" s="36" t="s">
-        <v>307</v>
+        <v>366</v>
       </c>
       <c r="X108" s="36">
-        <v>2009</v>
+        <v>2013</v>
       </c>
       <c r="Y108" s="3"/>
     </row>
@@ -10115,10 +10109,10 @@
       </c>
       <c r="V111" s="3"/>
       <c r="W111" s="36" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="X111" s="36">
-        <v>2009</v>
+        <v>1997</v>
       </c>
       <c r="Y111" s="3"/>
     </row>
@@ -10154,10 +10148,10 @@
       </c>
       <c r="V112" s="3"/>
       <c r="W112" s="36" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="X112" s="36">
-        <v>1997</v>
+        <v>2009</v>
       </c>
       <c r="Y112" s="3"/>
     </row>
@@ -10193,10 +10187,10 @@
       </c>
       <c r="V113" s="3"/>
       <c r="W113" s="36" t="s">
-        <v>85</v>
+        <v>283</v>
       </c>
       <c r="X113" s="36">
-        <v>2013</v>
+        <v>2006</v>
       </c>
       <c r="Y113" s="3"/>
     </row>
@@ -10232,10 +10226,10 @@
       </c>
       <c r="V114" s="3"/>
       <c r="W114" s="36" t="s">
-        <v>356</v>
+        <v>85</v>
       </c>
       <c r="X114" s="36">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="Y114" s="3"/>
     </row>
@@ -10271,10 +10265,10 @@
       </c>
       <c r="V115" s="3"/>
       <c r="W115" s="36" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="X115" s="36">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="Y115" s="3"/>
     </row>
@@ -10349,10 +10343,10 @@
       </c>
       <c r="V117" s="3"/>
       <c r="W117" s="36" t="s">
-        <v>39</v>
+        <v>356</v>
       </c>
       <c r="X117" s="36">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="Y117" s="3"/>
     </row>
@@ -10388,10 +10382,10 @@
       </c>
       <c r="V118" s="3"/>
       <c r="W118" s="36" t="s">
-        <v>36</v>
+        <v>308</v>
       </c>
       <c r="X118" s="36">
-        <v>2012</v>
+        <v>1989</v>
       </c>
       <c r="Y118" s="3"/>
     </row>
@@ -10427,10 +10421,10 @@
       </c>
       <c r="V119" s="3"/>
       <c r="W119" s="36" t="s">
-        <v>347</v>
+        <v>39</v>
       </c>
       <c r="X119" s="36">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="Y119" s="3"/>
     </row>
@@ -10466,10 +10460,10 @@
       </c>
       <c r="V120" s="3"/>
       <c r="W120" s="36" t="s">
-        <v>304</v>
+        <v>36</v>
       </c>
       <c r="X120" s="36">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="Y120" s="3"/>
     </row>
@@ -10505,10 +10499,10 @@
       </c>
       <c r="V121" s="3"/>
       <c r="W121" s="36" t="s">
-        <v>308</v>
+        <v>347</v>
       </c>
       <c r="X121" s="36">
-        <v>1989</v>
+        <v>2019</v>
       </c>
       <c r="Y121" s="3"/>
     </row>
@@ -10544,10 +10538,10 @@
       </c>
       <c r="V122" s="3"/>
       <c r="W122" s="36" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="X122" s="36">
-        <v>2019</v>
+        <v>2005</v>
       </c>
       <c r="Y122" s="3"/>
     </row>
@@ -10583,10 +10577,10 @@
       </c>
       <c r="V123" s="3"/>
       <c r="W123" s="36" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="X123" s="36">
-        <v>2005</v>
+        <v>2019</v>
       </c>
       <c r="Y123" s="3"/>
     </row>
@@ -10622,10 +10616,10 @@
       </c>
       <c r="V124" s="3"/>
       <c r="W124" s="36" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="X124" s="36">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="Y124" s="3"/>
     </row>
@@ -10661,7 +10655,7 @@
       </c>
       <c r="V125" s="3"/>
       <c r="W125" s="36" t="s">
-        <v>324</v>
+        <v>69</v>
       </c>
       <c r="X125" s="36">
         <v>2002</v>
@@ -10700,10 +10694,10 @@
       </c>
       <c r="V126" s="3"/>
       <c r="W126" s="36" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="X126" s="36">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="Y126" s="3"/>
     </row>
@@ -10739,10 +10733,10 @@
       </c>
       <c r="V127" s="3"/>
       <c r="W127" s="36" t="s">
-        <v>165</v>
+        <v>346</v>
       </c>
       <c r="X127" s="36">
-        <v>2024</v>
+        <v>1999</v>
       </c>
       <c r="Y127" s="3"/>
     </row>
@@ -10778,10 +10772,10 @@
       </c>
       <c r="V128" s="3"/>
       <c r="W128" s="36" t="s">
-        <v>21</v>
+        <v>333</v>
       </c>
       <c r="X128" s="36">
-        <v>2013</v>
+        <v>2003</v>
       </c>
       <c r="Y128" s="3"/>
     </row>
@@ -10817,10 +10811,10 @@
       </c>
       <c r="V129" s="3"/>
       <c r="W129" s="36" t="s">
-        <v>349</v>
+        <v>21</v>
       </c>
       <c r="X129" s="36">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="Y129" s="3"/>
     </row>
@@ -10856,10 +10850,10 @@
       </c>
       <c r="V130" s="3"/>
       <c r="W130" s="36" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="X130" s="36">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="Y130" s="3"/>
     </row>
@@ -10955,10 +10949,10 @@
       </c>
       <c r="V133" s="3"/>
       <c r="W133" s="36" t="s">
-        <v>350</v>
+        <v>176</v>
       </c>
       <c r="X133" s="36">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="Y133" s="3"/>
     </row>
@@ -10987,10 +10981,10 @@
       </c>
       <c r="V134" s="3"/>
       <c r="W134" s="36" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="X134" s="36">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="Y134" s="3"/>
     </row>
@@ -11019,10 +11013,10 @@
       </c>
       <c r="V135" s="3"/>
       <c r="W135" s="36" t="s">
-        <v>176</v>
+        <v>281</v>
       </c>
       <c r="X135" s="36">
-        <v>2023</v>
+        <v>2004</v>
       </c>
       <c r="Y135" s="3"/>
     </row>
@@ -11051,10 +11045,10 @@
       </c>
       <c r="V136" s="3"/>
       <c r="W136" s="36" t="s">
-        <v>60</v>
+        <v>355</v>
       </c>
       <c r="X136" s="36">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="Y136" s="3"/>
     </row>
@@ -11083,10 +11077,10 @@
       </c>
       <c r="V137" s="3"/>
       <c r="W137" s="36" t="s">
-        <v>281</v>
+        <v>60</v>
       </c>
       <c r="X137" s="36">
-        <v>2004</v>
+        <v>2022</v>
       </c>
       <c r="Y137" s="3"/>
     </row>
@@ -11115,10 +11109,10 @@
       </c>
       <c r="V138" s="3"/>
       <c r="W138" s="36" t="s">
-        <v>53</v>
+        <v>323</v>
       </c>
       <c r="X138" s="36">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="Y138" s="3"/>
     </row>
@@ -11147,10 +11141,10 @@
       </c>
       <c r="V139" s="3"/>
       <c r="W139" s="36" t="s">
-        <v>323</v>
+        <v>53</v>
       </c>
       <c r="X139" s="36">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y139" s="3"/>
     </row>
@@ -11179,10 +11173,10 @@
       </c>
       <c r="V140" s="3"/>
       <c r="W140" s="36" t="s">
-        <v>78</v>
+        <v>343</v>
       </c>
       <c r="X140" s="36">
-        <v>2018</v>
+        <v>1983</v>
       </c>
       <c r="Y140" s="3"/>
     </row>
@@ -11211,10 +11205,10 @@
       </c>
       <c r="V141" s="3"/>
       <c r="W141" s="36" t="s">
-        <v>343</v>
+        <v>299</v>
       </c>
       <c r="X141" s="36">
-        <v>1983</v>
+        <v>2007</v>
       </c>
       <c r="Y141" s="3"/>
     </row>
@@ -11243,10 +11237,10 @@
       </c>
       <c r="V142" s="3"/>
       <c r="W142" s="36" t="s">
-        <v>299</v>
+        <v>78</v>
       </c>
       <c r="X142" s="36">
-        <v>2007</v>
+        <v>2018</v>
       </c>
       <c r="Y142" s="3"/>
     </row>
@@ -11339,10 +11333,10 @@
       </c>
       <c r="V145" s="3"/>
       <c r="W145" s="36" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="X145" s="36">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="Y145" s="3"/>
     </row>
@@ -11371,10 +11365,10 @@
       </c>
       <c r="V146" s="3"/>
       <c r="W146" s="36" t="s">
-        <v>327</v>
+        <v>284</v>
       </c>
       <c r="X146" s="36">
-        <v>2001</v>
+        <v>2008</v>
       </c>
       <c r="Y146" s="3"/>
     </row>
@@ -11403,10 +11397,10 @@
       </c>
       <c r="V147" s="3"/>
       <c r="W147" s="36" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="X147" s="36">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="Y147" s="3"/>
     </row>
@@ -11435,10 +11429,10 @@
       </c>
       <c r="V148" s="3"/>
       <c r="W148" s="36" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="X148" s="36">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="Y148" s="3"/>
     </row>
@@ -11467,10 +11461,10 @@
       </c>
       <c r="V149" s="3"/>
       <c r="W149" s="36" t="s">
-        <v>284</v>
+        <v>342</v>
       </c>
       <c r="X149" s="36">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="Y149" s="3"/>
     </row>
@@ -11499,10 +11493,10 @@
       </c>
       <c r="V150" s="3"/>
       <c r="W150" s="36" t="s">
-        <v>336</v>
+        <v>290</v>
       </c>
       <c r="X150" s="36">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="Y150" s="3"/>
     </row>
@@ -11531,10 +11525,10 @@
       </c>
       <c r="V151" s="3"/>
       <c r="W151" s="36" t="s">
-        <v>18</v>
+        <v>336</v>
       </c>
       <c r="X151" s="36">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y151" s="3"/>
     </row>
@@ -11563,10 +11557,10 @@
       </c>
       <c r="V152" s="3"/>
       <c r="W152" s="36" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="X152" s="36">
-        <v>2022</v>
+        <v>1993</v>
       </c>
       <c r="Y152" s="3"/>
     </row>
@@ -11595,10 +11589,10 @@
       </c>
       <c r="V153" s="3"/>
       <c r="W153" s="36" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="X153" s="36">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="Y153" s="3"/>
     </row>
@@ -11627,10 +11621,10 @@
       </c>
       <c r="V154" s="3"/>
       <c r="W154" s="36" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="X154" s="36">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="Y154" s="3"/>
     </row>
@@ -11691,10 +11685,10 @@
       </c>
       <c r="V156" s="3"/>
       <c r="W156" s="36" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="X156" s="36">
-        <v>1999</v>
+        <v>2017</v>
       </c>
       <c r="Y156" s="3"/>
     </row>
@@ -11723,10 +11717,10 @@
       </c>
       <c r="V157" s="3"/>
       <c r="W157" s="36" t="s">
-        <v>309</v>
+        <v>46</v>
       </c>
       <c r="X157" s="36">
-        <v>1993</v>
+        <v>1999</v>
       </c>
       <c r="Y157" s="3"/>
     </row>
@@ -11819,10 +11813,10 @@
       </c>
       <c r="V160" s="3"/>
       <c r="W160" s="36" t="s">
-        <v>23</v>
+        <v>315</v>
       </c>
       <c r="X160" s="36">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="Y160" s="3"/>
     </row>
@@ -11851,10 +11845,10 @@
       </c>
       <c r="V161" s="3"/>
       <c r="W161" s="36" t="s">
-        <v>315</v>
+        <v>23</v>
       </c>
       <c r="X161" s="36">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="Y161" s="3"/>
     </row>
@@ -11946,11 +11940,11 @@
         <v>2006</v>
       </c>
       <c r="V164" s="3"/>
-      <c r="W164" s="36">
-        <v>1917</v>
+      <c r="W164" s="36" t="s">
+        <v>318</v>
       </c>
       <c r="X164" s="36">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="Y164" s="3"/>
     </row>
@@ -11978,11 +11972,11 @@
         <v>1960</v>
       </c>
       <c r="V165" s="3"/>
-      <c r="W165" s="36" t="s">
-        <v>318</v>
+      <c r="W165" s="36">
+        <v>1917</v>
       </c>
       <c r="X165" s="36">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="Y165" s="3"/>
     </row>
@@ -12011,10 +12005,10 @@
       </c>
       <c r="V166" s="3"/>
       <c r="W166" s="36" t="s">
-        <v>12</v>
+        <v>291</v>
       </c>
       <c r="X166" s="36">
-        <v>2022</v>
+        <v>2006</v>
       </c>
       <c r="Y166" s="3"/>
     </row>
@@ -12043,10 +12037,10 @@
       </c>
       <c r="V167" s="3"/>
       <c r="W167" s="36" t="s">
-        <v>291</v>
+        <v>12</v>
       </c>
       <c r="X167" s="36">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="Y167" s="3"/>
     </row>
@@ -12139,10 +12133,10 @@
       </c>
       <c r="V170" s="3"/>
       <c r="W170" s="36" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="X170" s="36">
-        <v>2008</v>
+        <v>1988</v>
       </c>
       <c r="Y170" s="3"/>
     </row>
@@ -12171,10 +12165,10 @@
       </c>
       <c r="V171" s="3"/>
       <c r="W171" s="36" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="X171" s="36">
-        <v>1988</v>
+        <v>2008</v>
       </c>
       <c r="Y171" s="3"/>
     </row>
@@ -12235,10 +12229,10 @@
       </c>
       <c r="V173" s="3"/>
       <c r="W173" s="36" t="s">
-        <v>319</v>
+        <v>293</v>
       </c>
       <c r="X173" s="36">
-        <v>2007</v>
+        <v>1979</v>
       </c>
       <c r="Y173" s="3"/>
     </row>
@@ -12267,10 +12261,10 @@
       </c>
       <c r="V174" s="3"/>
       <c r="W174" s="36" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="X174" s="36">
-        <v>1990</v>
+        <v>2007</v>
       </c>
       <c r="Y174" s="3"/>
     </row>
@@ -12299,10 +12293,10 @@
       </c>
       <c r="V175" s="3"/>
       <c r="W175" s="36" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="X175" s="36">
-        <v>1979</v>
+        <v>1990</v>
       </c>
       <c r="Y175" s="3"/>
     </row>
@@ -12395,10 +12389,10 @@
       </c>
       <c r="V178" s="3"/>
       <c r="W178" s="36" t="s">
-        <v>302</v>
+        <v>240</v>
       </c>
       <c r="X178" s="36">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="Y178" s="3"/>
     </row>
@@ -12427,10 +12421,10 @@
       </c>
       <c r="V179" s="3"/>
       <c r="W179" s="36" t="s">
-        <v>91</v>
+        <v>266</v>
       </c>
       <c r="X179" s="36">
-        <v>2023</v>
+        <v>1996</v>
       </c>
       <c r="Y179" s="3"/>
     </row>
@@ -12459,10 +12453,10 @@
       </c>
       <c r="V180" s="3"/>
       <c r="W180" s="36" t="s">
-        <v>275</v>
+        <v>91</v>
       </c>
       <c r="X180" s="36">
-        <v>2009</v>
+        <v>2023</v>
       </c>
       <c r="Y180" s="3"/>
     </row>
@@ -12491,10 +12485,10 @@
       </c>
       <c r="V181" s="3"/>
       <c r="W181" s="36" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="X181" s="36">
-        <v>1996</v>
+        <v>2009</v>
       </c>
       <c r="Y181" s="3"/>
     </row>
@@ -12523,10 +12517,10 @@
       </c>
       <c r="V182" s="3"/>
       <c r="W182" s="36" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="X182" s="36">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="Y182" s="3"/>
     </row>
@@ -12555,10 +12549,10 @@
       </c>
       <c r="V183" s="3"/>
       <c r="W183" s="36" t="s">
-        <v>240</v>
+        <v>289</v>
       </c>
       <c r="X183" s="36">
-        <v>2008</v>
+        <v>1990</v>
       </c>
       <c r="Y183" s="3"/>
     </row>
@@ -12587,10 +12581,10 @@
       </c>
       <c r="V184" s="3"/>
       <c r="W184" s="36" t="s">
-        <v>43</v>
+        <v>316</v>
       </c>
       <c r="X184" s="36">
-        <v>2016</v>
+        <v>2007</v>
       </c>
       <c r="Y184" s="3"/>
     </row>
@@ -12619,10 +12613,10 @@
       </c>
       <c r="V185" s="3"/>
       <c r="W185" s="36" t="s">
-        <v>289</v>
+        <v>43</v>
       </c>
       <c r="X185" s="36">
-        <v>1990</v>
+        <v>2016</v>
       </c>
       <c r="Y185" s="3"/>
     </row>
@@ -12715,10 +12709,10 @@
       </c>
       <c r="V188" s="3"/>
       <c r="W188" s="36" t="s">
-        <v>303</v>
+        <v>234</v>
       </c>
       <c r="X188" s="36">
-        <v>1982</v>
+        <v>2022</v>
       </c>
       <c r="Y188" s="3"/>
     </row>
@@ -12779,10 +12773,10 @@
       </c>
       <c r="V190" s="3"/>
       <c r="W190" s="36" t="s">
-        <v>234</v>
+        <v>303</v>
       </c>
       <c r="X190" s="36">
-        <v>2022</v>
+        <v>1982</v>
       </c>
       <c r="Y190" s="3"/>
     </row>
@@ -12907,10 +12901,10 @@
       </c>
       <c r="V194" s="3"/>
       <c r="W194" s="36" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="X194" s="36">
-        <v>1986</v>
+        <v>2013</v>
       </c>
       <c r="Y194" s="3"/>
     </row>
@@ -12939,10 +12933,10 @@
       </c>
       <c r="V195" s="3"/>
       <c r="W195" s="36" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="X195" s="36">
-        <v>2013</v>
+        <v>1986</v>
       </c>
       <c r="Y195" s="3"/>
     </row>
@@ -13003,10 +12997,10 @@
       </c>
       <c r="V197" s="3"/>
       <c r="W197" s="36" t="s">
-        <v>300</v>
+        <v>206</v>
       </c>
       <c r="X197" s="36">
-        <v>1992</v>
+        <v>2004</v>
       </c>
       <c r="Y197" s="3"/>
     </row>
@@ -13035,10 +13029,10 @@
       </c>
       <c r="V198" s="3"/>
       <c r="W198" s="36" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="X198" s="36">
-        <v>2019</v>
+        <v>1992</v>
       </c>
       <c r="Y198" s="3"/>
     </row>
@@ -13067,10 +13061,10 @@
       </c>
       <c r="V199" s="3"/>
       <c r="W199" s="36" t="s">
-        <v>97</v>
+        <v>306</v>
       </c>
       <c r="X199" s="36">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="Y199" s="3"/>
     </row>
@@ -13099,10 +13093,10 @@
       </c>
       <c r="V200" s="3"/>
       <c r="W200" s="36" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="X200" s="36">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="Y200" s="3"/>
     </row>
@@ -13163,10 +13157,10 @@
       </c>
       <c r="V202" s="3"/>
       <c r="W202" s="36" t="s">
-        <v>267</v>
+        <v>38</v>
       </c>
       <c r="X202" s="36">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="Y202" s="3"/>
     </row>
@@ -13195,10 +13189,10 @@
       </c>
       <c r="V203" s="3"/>
       <c r="W203" s="36" t="s">
-        <v>206</v>
+        <v>286</v>
       </c>
       <c r="X203" s="36">
-        <v>2004</v>
+        <v>2014</v>
       </c>
       <c r="Y203" s="3"/>
     </row>
@@ -13227,10 +13221,10 @@
       </c>
       <c r="V204" s="3"/>
       <c r="W204" s="36" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="X204" s="36">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="Y204" s="3"/>
     </row>
@@ -13291,10 +13285,10 @@
       </c>
       <c r="V206" s="3"/>
       <c r="W206" s="36" t="s">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="X206" s="36">
-        <v>2019</v>
+        <v>2006</v>
       </c>
       <c r="Y206" s="3"/>
     </row>
@@ -13323,10 +13317,10 @@
       </c>
       <c r="V207" s="3"/>
       <c r="W207" s="36" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="X207" s="36">
-        <v>2006</v>
+        <v>2013</v>
       </c>
       <c r="Y207" s="3"/>
     </row>
@@ -13419,10 +13413,10 @@
       </c>
       <c r="V210" s="3"/>
       <c r="W210" s="36" t="s">
-        <v>248</v>
+        <v>310</v>
       </c>
       <c r="X210" s="36">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="Y210" s="3"/>
     </row>
@@ -13483,10 +13477,10 @@
       </c>
       <c r="V212" s="3"/>
       <c r="W212" s="36" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="X212" s="36">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="Y212" s="3"/>
     </row>
@@ -13515,10 +13509,10 @@
       </c>
       <c r="V213" s="3"/>
       <c r="W213" s="36" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="X213" s="36">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="Y213" s="3"/>
     </row>
@@ -14340,10 +14334,10 @@
       </c>
       <c r="S239" s="4"/>
       <c r="T239" s="13" t="s">
-        <v>54</v>
+        <v>1279</v>
       </c>
       <c r="U239" s="12">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="V239" s="3"/>
       <c r="W239" s="36" t="s">
@@ -14653,10 +14647,10 @@
       <c r="G249" s="2"/>
       <c r="P249" s="3"/>
       <c r="Q249" s="18" t="s">
-        <v>1279</v>
+        <v>562</v>
       </c>
       <c r="R249" s="19">
-        <v>1992</v>
+        <v>1978</v>
       </c>
       <c r="S249" s="4"/>
       <c r="T249" s="13" t="s">
@@ -14717,7 +14711,7 @@
       <c r="G251" s="2"/>
       <c r="P251" s="3"/>
       <c r="Q251" s="18" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="R251" s="19">
         <v>2015</v>
@@ -22955,290 +22949,290 @@
     <row r="958" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V958" s="3"/>
       <c r="W958" s="36" t="s">
-        <v>667</v>
+        <v>1265</v>
       </c>
       <c r="X958" s="36">
-        <v>2023</v>
+        <v>2004</v>
       </c>
       <c r="Y958" s="3"/>
     </row>
     <row r="959" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V959" s="3"/>
       <c r="W959" s="36" t="s">
-        <v>1238</v>
+        <v>667</v>
       </c>
       <c r="X959" s="36">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="Y959" s="3"/>
     </row>
     <row r="960" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V960" s="3"/>
       <c r="W960" s="36" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="X960" s="36">
-        <v>1991</v>
+        <v>2018</v>
       </c>
       <c r="Y960" s="3"/>
     </row>
     <row r="961" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V961" s="3"/>
       <c r="W961" s="36" t="s">
-        <v>1240</v>
+        <v>77</v>
       </c>
       <c r="X961" s="36">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="Y961" s="3"/>
     </row>
     <row r="962" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V962" s="3"/>
       <c r="W962" s="36" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="X962" s="36">
-        <v>2024</v>
+        <v>1991</v>
       </c>
       <c r="Y962" s="3"/>
     </row>
     <row r="963" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V963" s="3"/>
       <c r="W963" s="36" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="X963" s="36">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="Y963" s="3"/>
     </row>
     <row r="964" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V964" s="3"/>
       <c r="W964" s="36" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="X964" s="36">
-        <v>2004</v>
+        <v>2024</v>
       </c>
       <c r="Y964" s="3"/>
     </row>
     <row r="965" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V965" s="3"/>
       <c r="W965" s="36" t="s">
-        <v>1244</v>
+        <v>1266</v>
       </c>
       <c r="X965" s="36">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="Y965" s="3"/>
     </row>
     <row r="966" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V966" s="3"/>
       <c r="W966" s="36" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="X966" s="36">
-        <v>1977</v>
+        <v>2006</v>
       </c>
       <c r="Y966" s="3"/>
     </row>
     <row r="967" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V967" s="3"/>
       <c r="W967" s="36" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="X967" s="36">
-        <v>2022</v>
+        <v>2004</v>
       </c>
       <c r="Y967" s="3"/>
     </row>
     <row r="968" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V968" s="3"/>
       <c r="W968" s="36" t="s">
-        <v>33</v>
+        <v>1244</v>
       </c>
       <c r="X968" s="36">
-        <v>2011</v>
+        <v>2001</v>
       </c>
       <c r="Y968" s="3"/>
     </row>
     <row r="969" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V969" s="3"/>
       <c r="W969" s="36" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="X969" s="36">
-        <v>2016</v>
+        <v>1977</v>
       </c>
       <c r="Y969" s="3"/>
     </row>
     <row r="970" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V970" s="3"/>
       <c r="W970" s="36" t="s">
-        <v>1248</v>
+        <v>1280</v>
       </c>
       <c r="X970" s="36">
-        <v>1996</v>
+        <v>2024</v>
       </c>
       <c r="Y970" s="3"/>
     </row>
     <row r="971" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V971" s="3"/>
       <c r="W971" s="36" t="s">
-        <v>506</v>
+        <v>1246</v>
       </c>
       <c r="X971" s="36">
-        <v>2004</v>
+        <v>2022</v>
       </c>
       <c r="Y971" s="3"/>
     </row>
     <row r="972" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V972" s="3"/>
       <c r="W972" s="36" t="s">
-        <v>1249</v>
+        <v>1261</v>
       </c>
       <c r="X972" s="36">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="Y972" s="3"/>
     </row>
     <row r="973" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V973" s="3"/>
       <c r="W973" s="36" t="s">
-        <v>1250</v>
+        <v>33</v>
       </c>
       <c r="X973" s="36">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="Y973" s="3"/>
     </row>
     <row r="974" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V974" s="3"/>
       <c r="W974" s="36" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="X974" s="36">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="Y974" s="3"/>
     </row>
     <row r="975" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V975" s="3"/>
       <c r="W975" s="36" t="s">
-        <v>556</v>
+        <v>1271</v>
       </c>
       <c r="X975" s="36">
-        <v>1984</v>
+        <v>2024</v>
       </c>
       <c r="Y975" s="3"/>
     </row>
     <row r="976" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V976" s="3"/>
       <c r="W976" s="36" t="s">
-        <v>1252</v>
+        <v>1268</v>
       </c>
       <c r="X976" s="36">
-        <v>2004</v>
+        <v>2024</v>
       </c>
       <c r="Y976" s="3"/>
     </row>
     <row r="977" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V977" s="3"/>
       <c r="W977" s="36" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
       <c r="X977" s="36">
-        <v>2007</v>
+        <v>1996</v>
       </c>
       <c r="Y977" s="3"/>
     </row>
     <row r="978" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V978" s="3"/>
       <c r="W978" s="36" t="s">
-        <v>1254</v>
+        <v>506</v>
       </c>
       <c r="X978" s="36">
-        <v>2019</v>
+        <v>2004</v>
       </c>
       <c r="Y978" s="3"/>
     </row>
     <row r="979" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V979" s="3"/>
       <c r="W979" s="36" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
       <c r="X979" s="36">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="Y979" s="3"/>
     </row>
     <row r="980" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V980" s="3"/>
       <c r="W980" s="36" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="X980" s="36">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="Y980" s="3"/>
     </row>
     <row r="981" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V981" s="3"/>
       <c r="W981" s="36" t="s">
-        <v>1257</v>
+        <v>1250</v>
       </c>
       <c r="X981" s="36">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="Y981" s="3"/>
     </row>
     <row r="982" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V982" s="3"/>
       <c r="W982" s="36" t="s">
-        <v>1258</v>
+        <v>1251</v>
       </c>
       <c r="X982" s="36">
-        <v>2007</v>
+        <v>2024</v>
       </c>
       <c r="Y982" s="3"/>
     </row>
     <row r="983" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V983" s="3"/>
       <c r="W983" s="36" t="s">
-        <v>1259</v>
+        <v>556</v>
       </c>
       <c r="X983" s="36">
-        <v>2024</v>
+        <v>1984</v>
       </c>
       <c r="Y983" s="3"/>
     </row>
     <row r="984" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V984" s="3"/>
       <c r="W984" s="36" t="s">
-        <v>1260</v>
+        <v>1281</v>
       </c>
       <c r="X984" s="36">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Y984" s="3"/>
     </row>
     <row r="985" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V985" s="3"/>
       <c r="W985" s="36" t="s">
-        <v>1261</v>
+        <v>1252</v>
       </c>
       <c r="X985" s="36">
-        <v>2023</v>
+        <v>2004</v>
       </c>
       <c r="Y985" s="3"/>
     </row>
     <row r="986" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V986" s="3"/>
       <c r="W986" s="36" t="s">
-        <v>77</v>
+        <v>1269</v>
       </c>
       <c r="X986" s="36">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="Y986" s="3"/>
     </row>
@@ -23255,100 +23249,100 @@
     <row r="988" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V988" s="3"/>
       <c r="W988" s="36" t="s">
-        <v>1263</v>
+        <v>454</v>
       </c>
       <c r="X988" s="36">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="Y988" s="3"/>
     </row>
     <row r="989" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V989" s="3"/>
       <c r="W989" s="36" t="s">
-        <v>454</v>
+        <v>1264</v>
       </c>
       <c r="X989" s="36">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="Y989" s="3"/>
     </row>
     <row r="990" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V990" s="3"/>
       <c r="W990" s="36" t="s">
-        <v>1264</v>
+        <v>1253</v>
       </c>
       <c r="X990" s="36">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="Y990" s="3"/>
     </row>
     <row r="991" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V991" s="3"/>
       <c r="W991" s="36" t="s">
-        <v>1265</v>
+        <v>1254</v>
       </c>
       <c r="X991" s="36">
-        <v>2004</v>
+        <v>2019</v>
       </c>
       <c r="Y991" s="3"/>
     </row>
     <row r="992" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V992" s="3"/>
       <c r="W992" s="36" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="X992" s="36">
-        <v>2003</v>
+        <v>1982</v>
       </c>
       <c r="Y992" s="3"/>
     </row>
     <row r="993" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V993" s="3"/>
       <c r="W993" s="36" t="s">
-        <v>1267</v>
+        <v>1255</v>
       </c>
       <c r="X993" s="36">
-        <v>1982</v>
+        <v>2014</v>
       </c>
       <c r="Y993" s="3"/>
     </row>
     <row r="994" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V994" s="3"/>
       <c r="W994" s="36" t="s">
-        <v>1268</v>
+        <v>1256</v>
       </c>
       <c r="X994" s="36">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="Y994" s="3"/>
     </row>
     <row r="995" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V995" s="3"/>
       <c r="W995" s="36" t="s">
-        <v>1269</v>
+        <v>1257</v>
       </c>
       <c r="X995" s="36">
-        <v>2021</v>
+        <v>2007</v>
       </c>
       <c r="Y995" s="3"/>
     </row>
     <row r="996" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V996" s="3"/>
       <c r="W996" s="36" t="s">
-        <v>1270</v>
+        <v>1258</v>
       </c>
       <c r="X996" s="36">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="Y996" s="3"/>
     </row>
     <row r="997" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V997" s="3"/>
       <c r="W997" s="36" t="s">
-        <v>1271</v>
+        <v>1259</v>
       </c>
       <c r="X997" s="36">
-        <v>2011</v>
+        <v>2024</v>
       </c>
       <c r="Y997" s="3"/>
     </row>
@@ -23358,24 +23352,24 @@
         <v>1272</v>
       </c>
       <c r="X998" s="36">
-        <v>2024</v>
+        <v>1993</v>
       </c>
       <c r="Y998" s="3"/>
     </row>
     <row r="999" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V999" s="3"/>
       <c r="W999" s="36" t="s">
-        <v>1273</v>
+        <v>1260</v>
       </c>
       <c r="X999" s="36">
-        <v>1993</v>
+        <v>2023</v>
       </c>
       <c r="Y999" s="3"/>
     </row>
     <row r="1000" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V1000" s="3"/>
       <c r="W1000" s="36" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="X1000" s="36">
         <v>1988</v>
@@ -23385,10 +23379,10 @@
     <row r="1001" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V1001" s="3"/>
       <c r="W1001" s="36" t="s">
-        <v>1275</v>
+        <v>1270</v>
       </c>
       <c r="X1001" s="36">
-        <v>2003</v>
+        <v>2011</v>
       </c>
       <c r="Y1001" s="3"/>
     </row>

--- a/lists.xlsx
+++ b/lists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/StatsAutomator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2936E4F1-1A5F-9B47-A06D-0BAC3590D57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66F737C-C767-604A-B85D-F3949C62C567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" xr2:uid="{98AF27AA-E156-FB4B-94CA-68D339A0B8C2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="1282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2271" uniqueCount="1282">
   <si>
     <t>Avatar</t>
   </si>
@@ -4689,10 +4689,10 @@
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="25" t="s">
-        <v>1276</v>
+        <v>767</v>
       </c>
       <c r="F2" s="19">
-        <v>1991</v>
+        <v>2010</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="10" t="s">
@@ -4750,10 +4750,10 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="25" t="s">
-        <v>487</v>
+        <v>1276</v>
       </c>
       <c r="F3" s="19">
-        <v>1982</v>
+        <v>1991</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="10" t="s">
@@ -4811,10 +4811,10 @@
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="25" t="s">
-        <v>764</v>
+        <v>487</v>
       </c>
       <c r="F4" s="19">
-        <v>2014</v>
+        <v>1982</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="10" t="s">
@@ -4872,10 +4872,10 @@
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="25" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="F5" s="19">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="10" t="s">
@@ -4933,10 +4933,10 @@
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="25" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="F6" s="19">
-        <v>2003</v>
+        <v>2022</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="10" t="s">
@@ -4990,10 +4990,10 @@
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="25" t="s">
-        <v>59</v>
+        <v>758</v>
       </c>
       <c r="F7" s="19">
-        <v>2013</v>
+        <v>2003</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="10" t="s">
@@ -5045,10 +5045,10 @@
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="25" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="F8" s="19">
-        <v>1987</v>
+        <v>2013</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="10" t="s">
@@ -5100,10 +5100,10 @@
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F9" s="19">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="10" t="s">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F10" s="19">
         <v>1989</v>
@@ -5210,10 +5210,10 @@
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F11" s="19">
-        <v>2015</v>
+        <v>1989</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="10" t="s">
@@ -5265,10 +5265,10 @@
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F12" s="19">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="10" t="s">
@@ -5320,10 +5320,10 @@
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F13" s="19">
-        <v>1990</v>
+        <v>2007</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="10" t="s">
@@ -5375,10 +5375,10 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F14" s="19">
-        <v>1957</v>
+        <v>1990</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="10" t="s">
@@ -5430,10 +5430,10 @@
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F15" s="19">
-        <v>1993</v>
+        <v>1957</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="10" t="s">
@@ -5485,10 +5485,10 @@
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F16" s="19">
-        <v>2009</v>
+        <v>1993</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="10" t="s">
@@ -5540,10 +5540,10 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F17" s="19">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="10" t="s">
@@ -5595,10 +5595,10 @@
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F18" s="19">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="10" t="s">
@@ -5650,10 +5650,10 @@
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F19" s="19">
-        <v>1999</v>
+        <v>2011</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="10" t="s">
@@ -5705,10 +5705,10 @@
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="25" t="s">
-        <v>25</v>
+        <v>111</v>
       </c>
       <c r="F20" s="19">
-        <v>2024</v>
+        <v>1999</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="10" t="s">
@@ -5760,10 +5760,10 @@
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="25" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="F21" s="19">
-        <v>2009</v>
+        <v>2024</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="10" t="s">
@@ -5815,10 +5815,10 @@
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F22" s="19">
-        <v>1994</v>
+        <v>2009</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="10" t="s">
@@ -5870,10 +5870,10 @@
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F23" s="19">
-        <v>2011</v>
+        <v>1994</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="10" t="s">
@@ -5925,10 +5925,10 @@
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F24" s="19">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="10" t="s">
@@ -5980,10 +5980,10 @@
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F25" s="19">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="10" t="s">
@@ -6035,10 +6035,10 @@
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F26" s="19">
-        <v>1973</v>
+        <v>2013</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="10" t="s">
@@ -6090,10 +6090,10 @@
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F27" s="19">
-        <v>2004</v>
+        <v>1973</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="10" t="s">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F28" s="19">
         <v>2004</v>
@@ -6200,10 +6200,10 @@
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F29" s="19">
-        <v>2020</v>
+        <v>2004</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="10" t="s">
@@ -6255,10 +6255,10 @@
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F30" s="19">
-        <v>1984</v>
+        <v>2020</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="10" t="s">
@@ -6310,10 +6310,10 @@
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F31" s="19">
-        <v>2008</v>
+        <v>1984</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="10" t="s">
@@ -6365,10 +6365,10 @@
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F32" s="19">
-        <v>2022</v>
+        <v>2008</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="10" t="s">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F33" s="19">
         <v>2022</v>
@@ -6471,10 +6471,10 @@
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="25" t="s">
-        <v>9</v>
+        <v>124</v>
       </c>
       <c r="F34" s="19">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="10" t="s">
@@ -6519,10 +6519,10 @@
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="25" t="s">
-        <v>125</v>
+        <v>9</v>
       </c>
       <c r="F35" s="19">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="10" t="s">
@@ -6567,10 +6567,10 @@
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F36" s="19">
-        <v>2023</v>
+        <v>2002</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="10" t="s">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F37" s="19">
         <v>2023</v>
@@ -6663,10 +6663,10 @@
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F38" s="19">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="10" t="s">
@@ -6711,10 +6711,10 @@
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F39" s="19">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="10" t="s">
@@ -6759,10 +6759,10 @@
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F40" s="19">
-        <v>2003</v>
+        <v>2017</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="10" t="s">
@@ -6807,10 +6807,10 @@
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F41" s="19">
-        <v>1995</v>
+        <v>2003</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="10" t="s">
@@ -6855,10 +6855,10 @@
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F42" s="19">
-        <v>2015</v>
+        <v>1995</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="10" t="s">
@@ -6903,10 +6903,10 @@
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F43" s="19">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="10" t="s">
@@ -6951,10 +6951,10 @@
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F44" s="19">
-        <v>1995</v>
+        <v>2007</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="10" t="s">
@@ -6999,10 +6999,10 @@
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F45" s="19">
-        <v>2022</v>
+        <v>1995</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="10" t="s">
@@ -7047,10 +7047,10 @@
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F46" s="19">
-        <v>1999</v>
+        <v>2022</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="10" t="s">
@@ -7095,10 +7095,10 @@
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F47" s="19">
-        <v>2023</v>
+        <v>1999</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="10" t="s">
@@ -7143,10 +7143,10 @@
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F48" s="19">
-        <v>1986</v>
+        <v>2023</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="10" t="s">
@@ -7191,10 +7191,10 @@
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F49" s="19">
-        <v>2005</v>
+        <v>1986</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="10" t="s">
@@ -7239,10 +7239,10 @@
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F50" s="19">
-        <v>2021</v>
+        <v>2005</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="10" t="s">
@@ -7287,10 +7287,10 @@
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F51" s="19">
-        <v>1997</v>
+        <v>2021</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="10" t="s">
@@ -7335,10 +7335,10 @@
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F52" s="19">
-        <v>2024</v>
+        <v>1997</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="10" t="s">
@@ -7383,10 +7383,10 @@
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="25" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="F53" s="19">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="10" t="s">
@@ -7431,10 +7431,10 @@
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="25" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="F54" s="19">
-        <v>2005</v>
+        <v>2016</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="10" t="s">
@@ -7479,10 +7479,10 @@
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="25" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F55" s="19">
-        <v>2012</v>
+        <v>2005</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="10" t="s">
@@ -7527,10 +7527,10 @@
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F56" s="19">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="10" t="s">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F57" s="19">
         <v>2023</v>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F58" s="19">
         <v>2023</v>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F59" s="19">
         <v>2023</v>
@@ -7719,10 +7719,10 @@
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F60" s="19">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="10" t="s">
@@ -7767,10 +7767,10 @@
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F61" s="19">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="10" t="s">
@@ -7815,10 +7815,10 @@
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F62" s="19">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="10" t="s">
@@ -7863,10 +7863,10 @@
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F63" s="19">
-        <v>2007</v>
+        <v>2020</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="10" t="s">
@@ -7911,10 +7911,10 @@
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F64" s="19">
-        <v>2021</v>
+        <v>2007</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="10" t="s">
@@ -7959,10 +7959,10 @@
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F65" s="19">
-        <v>2009</v>
+        <v>2021</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="10" t="s">
@@ -8007,10 +8007,10 @@
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F66" s="19">
-        <v>1996</v>
+        <v>2009</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="10" t="s">
@@ -8055,10 +8055,10 @@
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F67" s="19">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="10" t="s">
@@ -8103,10 +8103,10 @@
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F68" s="19">
-        <v>2014</v>
+        <v>1998</v>
       </c>
       <c r="G68" s="4"/>
       <c r="H68" s="10" t="s">
@@ -8151,10 +8151,10 @@
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F69" s="19">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="10" t="s">
@@ -8199,10 +8199,10 @@
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F70" s="19">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="10" t="s">
@@ -8247,10 +8247,10 @@
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F71" s="19">
-        <v>1978</v>
+        <v>2023</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="10" t="s">
@@ -8295,10 +8295,10 @@
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F72" s="19">
-        <v>2000</v>
+        <v>1978</v>
       </c>
       <c r="G72" s="4"/>
       <c r="H72" s="10" t="s">
@@ -8343,10 +8343,10 @@
       </c>
       <c r="D73" s="3"/>
       <c r="E73" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F73" s="19">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="G73" s="4"/>
       <c r="H73" s="10" t="s">
@@ -8391,10 +8391,10 @@
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F74" s="19">
-        <v>1989</v>
+        <v>2003</v>
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="10" t="s">
@@ -8439,10 +8439,10 @@
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F75" s="19">
-        <v>2015</v>
+        <v>1989</v>
       </c>
       <c r="G75" s="4"/>
       <c r="H75" s="10" t="s">
@@ -8487,10 +8487,10 @@
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="25" t="s">
-        <v>87</v>
+        <v>164</v>
       </c>
       <c r="F76" s="19">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="10" t="s">
@@ -8535,10 +8535,10 @@
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="25" t="s">
-        <v>165</v>
+        <v>87</v>
       </c>
       <c r="F77" s="19">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="10" t="s">
@@ -8583,10 +8583,10 @@
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F78" s="19">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="10" t="s">
@@ -8631,10 +8631,10 @@
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F79" s="19">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="10" t="s">
@@ -8679,10 +8679,10 @@
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F80" s="19">
-        <v>2021</v>
+        <v>2006</v>
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="10" t="s">
@@ -8727,10 +8727,10 @@
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F81" s="19">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="10" t="s">
@@ -8775,10 +8775,10 @@
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F82" s="19">
-        <v>1996</v>
+        <v>2016</v>
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="10" t="s">
@@ -8823,10 +8823,10 @@
       </c>
       <c r="D83" s="2"/>
       <c r="E83" s="25" t="s">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="F83" s="19">
-        <v>2007</v>
+        <v>1996</v>
       </c>
       <c r="G83" s="4"/>
       <c r="H83" s="10" t="s">
@@ -8871,10 +8871,10 @@
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="25" t="s">
-        <v>171</v>
+        <v>58</v>
       </c>
       <c r="F84" s="19">
-        <v>2021</v>
+        <v>2007</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="10" t="s">
@@ -8919,10 +8919,10 @@
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F85" s="19">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="10" t="s">
@@ -8967,10 +8967,10 @@
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F86" s="19">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="10" t="s">
@@ -9015,10 +9015,10 @@
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F87" s="19">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="10" t="s">
@@ -9063,10 +9063,10 @@
       </c>
       <c r="D88" s="2"/>
       <c r="E88" s="25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F88" s="19">
-        <v>2005</v>
+        <v>2001</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="10" t="s">
@@ -9111,10 +9111,10 @@
       </c>
       <c r="D89" s="2"/>
       <c r="E89" s="25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F89" s="19">
-        <v>2023</v>
+        <v>2005</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="10" t="s">
@@ -9159,10 +9159,10 @@
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F90" s="19">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="10" t="s">
@@ -9207,10 +9207,10 @@
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F91" s="19">
-        <v>1988</v>
+        <v>2017</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="10" t="s">
@@ -9255,10 +9255,10 @@
       </c>
       <c r="D92" s="2"/>
       <c r="E92" s="25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F92" s="19">
-        <v>2002</v>
+        <v>1988</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="10" t="s">
@@ -9303,10 +9303,10 @@
       </c>
       <c r="D93" s="2"/>
       <c r="E93" s="25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F93" s="19">
-        <v>2016</v>
+        <v>2002</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="10" t="s">
@@ -9351,10 +9351,10 @@
       </c>
       <c r="D94" s="2"/>
       <c r="E94" s="25" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F94" s="19">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="10" t="s">
@@ -9399,10 +9399,10 @@
       </c>
       <c r="D95" s="2"/>
       <c r="E95" s="25" t="s">
-        <v>57</v>
+        <v>181</v>
       </c>
       <c r="F95" s="19">
-        <v>2017</v>
+        <v>2008</v>
       </c>
       <c r="G95" s="4"/>
       <c r="H95" s="10" t="s">
@@ -9447,10 +9447,10 @@
       </c>
       <c r="D96" s="2"/>
       <c r="E96" s="25" t="s">
-        <v>182</v>
+        <v>57</v>
       </c>
       <c r="F96" s="19">
-        <v>1998</v>
+        <v>2017</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="10" t="s">
@@ -9495,10 +9495,10 @@
       </c>
       <c r="D97" s="2"/>
       <c r="E97" s="25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F97" s="19">
-        <v>2004</v>
+        <v>1998</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="10" t="s">
@@ -9543,10 +9543,10 @@
       </c>
       <c r="D98" s="2"/>
       <c r="E98" s="25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F98" s="19">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="10" t="s">
@@ -9591,10 +9591,10 @@
       </c>
       <c r="D99" s="2"/>
       <c r="E99" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F99" s="19">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="10" t="s">
@@ -9639,10 +9639,10 @@
       </c>
       <c r="D100" s="2"/>
       <c r="E100" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F100" s="19">
-        <v>2014</v>
+        <v>2000</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="10" t="s">
@@ -9687,10 +9687,10 @@
       </c>
       <c r="D101" s="2"/>
       <c r="E101" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F101" s="19">
-        <v>1978</v>
+        <v>2014</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="10" t="s">
@@ -9729,10 +9729,10 @@
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="25" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F102" s="19">
-        <v>2005</v>
+        <v>1978</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="10" t="s">
@@ -9768,10 +9768,10 @@
     <row r="103" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D103" s="3"/>
       <c r="E103" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F103" s="19">
-        <v>1974</v>
+        <v>2005</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="10" t="s">
@@ -9807,10 +9807,10 @@
     <row r="104" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D104" s="3"/>
       <c r="E104" s="25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F104" s="19">
-        <v>2003</v>
+        <v>1974</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="10" t="s">
@@ -9846,10 +9846,10 @@
     <row r="105" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D105" s="3"/>
       <c r="E105" s="25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F105" s="19">
-        <v>1983</v>
+        <v>2003</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="10" t="s">
@@ -9884,11 +9884,11 @@
     </row>
     <row r="106" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D106" s="3"/>
-      <c r="E106" s="18" t="s">
-        <v>192</v>
+      <c r="E106" s="25" t="s">
+        <v>191</v>
       </c>
       <c r="F106" s="19">
-        <v>1992</v>
+        <v>1983</v>
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="10" t="s">
@@ -9924,10 +9924,10 @@
     <row r="107" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D107" s="3"/>
       <c r="E107" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F107" s="19">
-        <v>2012</v>
+        <v>1992</v>
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="10" t="s">
@@ -9963,10 +9963,10 @@
     <row r="108" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D108" s="3"/>
       <c r="E108" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F108" s="19">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="10" t="s">
@@ -10002,10 +10002,10 @@
     <row r="109" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D109" s="3"/>
       <c r="E109" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F109" s="19">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="10" t="s">
@@ -10041,10 +10041,10 @@
     <row r="110" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D110" s="3"/>
       <c r="E110" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F110" s="19">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="10" t="s">
@@ -10080,10 +10080,10 @@
     <row r="111" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D111" s="3"/>
       <c r="E111" s="18" t="s">
-        <v>16</v>
+        <v>196</v>
       </c>
       <c r="F111" s="19">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="10" t="s">
@@ -10119,10 +10119,10 @@
     <row r="112" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D112" s="3"/>
       <c r="E112" s="18" t="s">
-        <v>197</v>
+        <v>16</v>
       </c>
       <c r="F112" s="19">
-        <v>1988</v>
+        <v>2023</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="10" t="s">
@@ -10158,10 +10158,10 @@
     <row r="113" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D113" s="3"/>
       <c r="E113" s="18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F113" s="19">
-        <v>2013</v>
+        <v>1988</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="10" t="s">
@@ -10197,10 +10197,10 @@
     <row r="114" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D114" s="3"/>
       <c r="E114" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F114" s="19">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="10" t="s">
@@ -10236,10 +10236,10 @@
     <row r="115" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D115" s="3"/>
       <c r="E115" s="18" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F115" s="19">
-        <v>1996</v>
+        <v>2012</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="10" t="s">
@@ -10275,10 +10275,10 @@
     <row r="116" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D116" s="3"/>
       <c r="E116" s="18" t="s">
-        <v>22</v>
+        <v>200</v>
       </c>
       <c r="F116" s="19">
-        <v>1991</v>
+        <v>1996</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="10" t="s">
@@ -10314,10 +10314,10 @@
     <row r="117" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D117" s="3"/>
       <c r="E117" s="18" t="s">
-        <v>201</v>
+        <v>22</v>
       </c>
       <c r="F117" s="19">
-        <v>2018</v>
+        <v>1991</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="10" t="s">
@@ -10353,10 +10353,10 @@
     <row r="118" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D118" s="3"/>
       <c r="E118" s="18" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F118" s="19">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="10" t="s">
@@ -10392,10 +10392,10 @@
     <row r="119" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D119" s="3"/>
       <c r="E119" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F119" s="19">
-        <v>1999</v>
+        <v>2023</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="10" t="s">
@@ -10431,10 +10431,10 @@
     <row r="120" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D120" s="3"/>
       <c r="E120" s="18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F120" s="19">
-        <v>2012</v>
+        <v>1999</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="10" t="s">
@@ -10470,10 +10470,10 @@
     <row r="121" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D121" s="3"/>
       <c r="E121" s="18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F121" s="19">
-        <v>1984</v>
+        <v>2012</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="10" t="s">
@@ -10509,10 +10509,10 @@
     <row r="122" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D122" s="3"/>
       <c r="E122" s="18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F122" s="19">
-        <v>2004</v>
+        <v>1984</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="10" t="s">
@@ -10548,10 +10548,10 @@
     <row r="123" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D123" s="3"/>
       <c r="E123" s="18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F123" s="19">
-        <v>2021</v>
+        <v>2004</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="10" t="s">
@@ -10587,10 +10587,10 @@
     <row r="124" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D124" s="3"/>
       <c r="E124" s="18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F124" s="19">
-        <v>2001</v>
+        <v>2021</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="10" t="s">
@@ -10626,10 +10626,10 @@
     <row r="125" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D125" s="3"/>
       <c r="E125" s="18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F125" s="19">
-        <v>2019</v>
+        <v>2001</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="10" t="s">
@@ -10665,10 +10665,10 @@
     <row r="126" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D126" s="3"/>
       <c r="E126" s="18" t="s">
-        <v>34</v>
+        <v>209</v>
       </c>
       <c r="F126" s="19">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="10" t="s">
@@ -10704,7 +10704,7 @@
     <row r="127" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D127" s="3"/>
       <c r="E127" s="18" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="F127" s="19">
         <v>2012</v>
@@ -10743,10 +10743,10 @@
     <row r="128" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D128" s="3"/>
       <c r="E128" s="18" t="s">
-        <v>210</v>
+        <v>50</v>
       </c>
       <c r="F128" s="19">
-        <v>2005</v>
+        <v>2012</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="1" t="s">
@@ -10782,10 +10782,10 @@
     <row r="129" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D129" s="3"/>
       <c r="E129" s="18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F129" s="19">
-        <v>1997</v>
+        <v>2005</v>
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="1" t="s">
@@ -10821,7 +10821,7 @@
     <row r="130" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D130" s="3"/>
       <c r="E130" s="18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F130" s="19">
         <v>1997</v>
@@ -10860,14 +10860,18 @@
     <row r="131" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D131" s="3"/>
       <c r="E131" s="18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F131" s="19">
-        <v>2022</v>
+        <v>1997</v>
       </c>
       <c r="G131" s="2"/>
-      <c r="H131" s="3"/>
-      <c r="I131" s="3"/>
+      <c r="H131" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="I131" s="1">
+        <v>1976</v>
+      </c>
       <c r="J131" s="3"/>
       <c r="P131" s="3"/>
       <c r="Q131" s="18" t="s">
@@ -10895,12 +10899,15 @@
     <row r="132" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D132" s="3"/>
       <c r="E132" s="18" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F132" s="19">
-        <v>1989</v>
+        <v>2022</v>
       </c>
       <c r="G132" s="2"/>
+      <c r="H132" s="3"/>
+      <c r="I132" s="3"/>
+      <c r="J132" s="3"/>
       <c r="P132" s="3"/>
       <c r="Q132" s="18" t="s">
         <v>407</v>
@@ -10927,10 +10934,10 @@
     <row r="133" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D133" s="3"/>
       <c r="E133" s="18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F133" s="19">
-        <v>2018</v>
+        <v>1989</v>
       </c>
       <c r="G133" s="2"/>
       <c r="P133" s="3"/>
@@ -10959,10 +10966,10 @@
     <row r="134" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D134" s="3"/>
       <c r="E134" s="18" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F134" s="19">
-        <v>2001</v>
+        <v>2018</v>
       </c>
       <c r="G134" s="2"/>
       <c r="P134" s="3"/>
@@ -10991,7 +10998,7 @@
     <row r="135" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D135" s="3"/>
       <c r="E135" s="18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F135" s="19">
         <v>2001</v>
@@ -11023,10 +11030,10 @@
     <row r="136" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D136" s="3"/>
       <c r="E136" s="18" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F136" s="19">
-        <v>2013</v>
+        <v>2001</v>
       </c>
       <c r="G136" s="2"/>
       <c r="P136" s="3"/>
@@ -11055,10 +11062,10 @@
     <row r="137" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D137" s="3"/>
       <c r="E137" s="18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F137" s="19">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="G137" s="2"/>
       <c r="P137" s="3"/>
@@ -11087,10 +11094,10 @@
     <row r="138" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D138" s="3"/>
       <c r="E138" s="18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F138" s="19">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="G138" s="2"/>
       <c r="P138" s="3"/>
@@ -11119,10 +11126,10 @@
     <row r="139" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D139" s="3"/>
       <c r="E139" s="18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F139" s="19">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="G139" s="2"/>
       <c r="P139" s="3"/>
@@ -11151,10 +11158,10 @@
     <row r="140" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D140" s="3"/>
       <c r="E140" s="18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F140" s="19">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="G140" s="2"/>
       <c r="P140" s="3"/>
@@ -11183,10 +11190,10 @@
     <row r="141" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D141" s="3"/>
       <c r="E141" s="18" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F141" s="19">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="G141" s="2"/>
       <c r="P141" s="3"/>
@@ -11215,10 +11222,10 @@
     <row r="142" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D142" s="3"/>
       <c r="E142" s="18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F142" s="19">
-        <v>2006</v>
+        <v>2000</v>
       </c>
       <c r="G142" s="2"/>
       <c r="P142" s="3"/>
@@ -11247,10 +11254,10 @@
     <row r="143" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D143" s="3"/>
       <c r="E143" s="18" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F143" s="19">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="G143" s="2"/>
       <c r="P143" s="3"/>
@@ -11279,10 +11286,10 @@
     <row r="144" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D144" s="3"/>
       <c r="E144" s="18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F144" s="19">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="G144" s="2"/>
       <c r="P144" s="3"/>
@@ -11311,10 +11318,10 @@
     <row r="145" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D145" s="3"/>
       <c r="E145" s="18" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F145" s="19">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="G145" s="2"/>
       <c r="P145" s="3"/>
@@ -11343,10 +11350,10 @@
     <row r="146" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D146" s="3"/>
       <c r="E146" s="18" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F146" s="19">
-        <v>2000</v>
+        <v>2012</v>
       </c>
       <c r="G146" s="2"/>
       <c r="P146" s="3"/>
@@ -11375,10 +11382,10 @@
     <row r="147" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D147" s="3"/>
       <c r="E147" s="18" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F147" s="19">
-        <v>1993</v>
+        <v>2000</v>
       </c>
       <c r="G147" s="2"/>
       <c r="P147" s="3"/>
@@ -11407,10 +11414,10 @@
     <row r="148" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D148" s="3"/>
       <c r="E148" s="18" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F148" s="19">
-        <v>2004</v>
+        <v>1993</v>
       </c>
       <c r="G148" s="2"/>
       <c r="P148" s="3"/>
@@ -11439,10 +11446,10 @@
     <row r="149" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D149" s="3"/>
       <c r="E149" s="18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F149" s="19">
-        <v>2015</v>
+        <v>2004</v>
       </c>
       <c r="G149" s="2"/>
       <c r="P149" s="3"/>
@@ -11471,10 +11478,10 @@
     <row r="150" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D150" s="3"/>
       <c r="E150" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F150" s="19">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="G150" s="2"/>
       <c r="P150" s="3"/>
@@ -11503,10 +11510,10 @@
     <row r="151" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D151" s="3"/>
       <c r="E151" s="18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F151" s="19">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="G151" s="2"/>
       <c r="P151" s="3"/>
@@ -11535,10 +11542,10 @@
     <row r="152" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D152" s="3"/>
       <c r="E152" s="18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F152" s="19">
-        <v>2022</v>
+        <v>2005</v>
       </c>
       <c r="G152" s="2"/>
       <c r="P152" s="3"/>
@@ -11567,7 +11574,7 @@
     <row r="153" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D153" s="3"/>
       <c r="E153" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F153" s="19">
         <v>2022</v>
@@ -11599,10 +11606,10 @@
     <row r="154" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D154" s="3"/>
       <c r="E154" s="18" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F154" s="19">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="G154" s="2"/>
       <c r="P154" s="3"/>
@@ -11631,10 +11638,10 @@
     <row r="155" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D155" s="3"/>
       <c r="E155" s="18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F155" s="19">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="G155" s="2"/>
       <c r="P155" s="3"/>
@@ -11663,10 +11670,10 @@
     <row r="156" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D156" s="3"/>
       <c r="E156" s="18" t="s">
-        <v>91</v>
+        <v>237</v>
       </c>
       <c r="F156" s="19">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="G156" s="2"/>
       <c r="P156" s="3"/>
@@ -11695,10 +11702,10 @@
     <row r="157" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D157" s="3"/>
       <c r="E157" s="18" t="s">
-        <v>238</v>
+        <v>91</v>
       </c>
       <c r="F157" s="19">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="G157" s="2"/>
       <c r="P157" s="3"/>
@@ -11727,10 +11734,10 @@
     <row r="158" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D158" s="3"/>
       <c r="E158" s="18" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F158" s="19">
-        <v>1960</v>
+        <v>2015</v>
       </c>
       <c r="G158" s="2"/>
       <c r="P158" s="3"/>
@@ -11759,10 +11766,10 @@
     <row r="159" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D159" s="3"/>
       <c r="E159" s="18" t="s">
-        <v>86</v>
+        <v>239</v>
       </c>
       <c r="F159" s="19">
-        <v>2018</v>
+        <v>1960</v>
       </c>
       <c r="G159" s="2"/>
       <c r="P159" s="3"/>
@@ -11791,10 +11798,10 @@
     <row r="160" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D160" s="3"/>
       <c r="E160" s="18" t="s">
-        <v>240</v>
+        <v>86</v>
       </c>
       <c r="F160" s="19">
-        <v>2008</v>
+        <v>2018</v>
       </c>
       <c r="G160" s="2"/>
       <c r="P160" s="3"/>
@@ -11823,10 +11830,10 @@
     <row r="161" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D161" s="3"/>
       <c r="E161" s="18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F161" s="19">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="G161" s="2"/>
       <c r="P161" s="3"/>
@@ -11855,10 +11862,10 @@
     <row r="162" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D162" s="3"/>
       <c r="E162" s="18" t="s">
-        <v>40</v>
+        <v>241</v>
       </c>
       <c r="F162" s="19">
-        <v>2006</v>
+        <v>1998</v>
       </c>
       <c r="G162" s="2"/>
       <c r="P162" s="3"/>
@@ -11887,10 +11894,10 @@
     <row r="163" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D163" s="3"/>
       <c r="E163" s="18" t="s">
-        <v>242</v>
+        <v>40</v>
       </c>
       <c r="F163" s="19">
-        <v>1994</v>
+        <v>2006</v>
       </c>
       <c r="G163" s="2"/>
       <c r="P163" s="3"/>
@@ -11919,10 +11926,10 @@
     <row r="164" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D164" s="3"/>
       <c r="E164" s="18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F164" s="19">
-        <v>2014</v>
+        <v>1994</v>
       </c>
       <c r="G164" s="2"/>
       <c r="P164" s="3"/>
@@ -11951,10 +11958,10 @@
     <row r="165" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D165" s="3"/>
       <c r="E165" s="18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F165" s="19">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="G165" s="2"/>
       <c r="P165" s="3"/>
@@ -11983,10 +11990,10 @@
     <row r="166" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D166" s="3"/>
       <c r="E166" s="18" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F166" s="19">
-        <v>1999</v>
+        <v>2006</v>
       </c>
       <c r="G166" s="2"/>
       <c r="P166" s="3"/>
@@ -12015,10 +12022,10 @@
     <row r="167" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D167" s="3"/>
       <c r="E167" s="18" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F167" s="19">
-        <v>2021</v>
+        <v>1999</v>
       </c>
       <c r="G167" s="2"/>
       <c r="P167" s="3"/>
@@ -12047,10 +12054,10 @@
     <row r="168" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D168" s="3"/>
       <c r="E168" s="18" t="s">
-        <v>44</v>
+        <v>246</v>
       </c>
       <c r="F168" s="19">
-        <v>1992</v>
+        <v>2021</v>
       </c>
       <c r="G168" s="2"/>
       <c r="P168" s="3"/>
@@ -12079,10 +12086,10 @@
     <row r="169" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D169" s="3"/>
       <c r="E169" s="18" t="s">
-        <v>247</v>
+        <v>44</v>
       </c>
       <c r="F169" s="19">
-        <v>2014</v>
+        <v>1992</v>
       </c>
       <c r="G169" s="2"/>
       <c r="P169" s="3"/>
@@ -12111,10 +12118,10 @@
     <row r="170" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D170" s="3"/>
       <c r="E170" s="18" t="s">
-        <v>48</v>
+        <v>247</v>
       </c>
       <c r="F170" s="19">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="G170" s="2"/>
       <c r="P170" s="3"/>
@@ -12143,10 +12150,10 @@
     <row r="171" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D171" s="3"/>
       <c r="E171" s="18" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F171" s="19">
-        <v>2023</v>
+        <v>2010</v>
       </c>
       <c r="G171" s="2"/>
       <c r="P171" s="3"/>
@@ -12175,10 +12182,10 @@
     <row r="172" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D172" s="3"/>
       <c r="E172" s="18" t="s">
-        <v>248</v>
+        <v>54</v>
       </c>
       <c r="F172" s="19">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="G172" s="2"/>
       <c r="P172" s="3"/>
@@ -12207,10 +12214,10 @@
     <row r="173" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D173" s="3"/>
       <c r="E173" s="18" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F173" s="19">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="G173" s="2"/>
       <c r="P173" s="3"/>
@@ -12239,10 +12246,10 @@
     <row r="174" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D174" s="3"/>
       <c r="E174" s="18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F174" s="19">
-        <v>2010</v>
+        <v>2021</v>
       </c>
       <c r="G174" s="2"/>
       <c r="P174" s="3"/>
@@ -12271,10 +12278,10 @@
     <row r="175" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D175" s="3"/>
       <c r="E175" s="18" t="s">
-        <v>37</v>
+        <v>250</v>
       </c>
       <c r="F175" s="19">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="G175" s="2"/>
       <c r="P175" s="3"/>
@@ -12303,10 +12310,10 @@
     <row r="176" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D176" s="3"/>
       <c r="E176" s="18" t="s">
-        <v>251</v>
+        <v>37</v>
       </c>
       <c r="F176" s="19">
-        <v>1968</v>
+        <v>2019</v>
       </c>
       <c r="G176" s="2"/>
       <c r="P176" s="3"/>
@@ -12335,10 +12342,10 @@
     <row r="177" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D177" s="3"/>
       <c r="E177" s="18" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F177" s="19">
-        <v>2009</v>
+        <v>1968</v>
       </c>
       <c r="G177" s="2"/>
       <c r="P177" s="3"/>
@@ -12367,10 +12374,10 @@
     <row r="178" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D178" s="3"/>
       <c r="E178" s="18" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F178" s="19">
-        <v>1998</v>
+        <v>2009</v>
       </c>
       <c r="G178" s="2"/>
       <c r="P178" s="3"/>
@@ -12399,10 +12406,10 @@
     <row r="179" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D179" s="3"/>
       <c r="E179" s="18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F179" s="19">
-        <v>2002</v>
+        <v>1998</v>
       </c>
       <c r="G179" s="2"/>
       <c r="P179" s="3"/>
@@ -12431,10 +12438,10 @@
     <row r="180" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D180" s="3"/>
       <c r="E180" s="18" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F180" s="19">
-        <v>2021</v>
+        <v>2002</v>
       </c>
       <c r="G180" s="2"/>
       <c r="P180" s="3"/>
@@ -12463,10 +12470,10 @@
     <row r="181" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D181" s="3"/>
       <c r="E181" s="18" t="s">
-        <v>14</v>
+        <v>255</v>
       </c>
       <c r="F181" s="19">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="G181" s="2"/>
       <c r="P181" s="3"/>
@@ -12495,10 +12502,10 @@
     <row r="182" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D182" s="3"/>
       <c r="E182" s="18" t="s">
-        <v>256</v>
+        <v>14</v>
       </c>
       <c r="F182" s="19">
-        <v>1998</v>
+        <v>2023</v>
       </c>
       <c r="G182" s="2"/>
       <c r="P182" s="3"/>
@@ -12527,10 +12534,10 @@
     <row r="183" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D183" s="3"/>
       <c r="E183" s="18" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F183" s="19">
-        <v>2023</v>
+        <v>1998</v>
       </c>
       <c r="G183" s="2"/>
       <c r="P183" s="3"/>
@@ -12559,10 +12566,10 @@
     <row r="184" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D184" s="3"/>
       <c r="E184" s="18" t="s">
-        <v>49</v>
+        <v>257</v>
       </c>
       <c r="F184" s="19">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="G184" s="2"/>
       <c r="P184" s="3"/>
@@ -12591,10 +12598,10 @@
     <row r="185" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D185" s="3"/>
       <c r="E185" s="18" t="s">
-        <v>258</v>
+        <v>49</v>
       </c>
       <c r="F185" s="19">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="G185" s="2"/>
       <c r="P185" s="3"/>
@@ -12623,10 +12630,10 @@
     <row r="186" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D186" s="3"/>
       <c r="E186" s="18" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F186" s="19">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="G186" s="2"/>
       <c r="P186" s="3"/>
@@ -12655,10 +12662,10 @@
     <row r="187" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D187" s="3"/>
       <c r="E187" s="18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F187" s="19">
-        <v>2006</v>
+        <v>2013</v>
       </c>
       <c r="G187" s="2"/>
       <c r="P187" s="3"/>
@@ -12687,10 +12694,10 @@
     <row r="188" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D188" s="3"/>
       <c r="E188" s="18" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F188" s="19">
-        <v>2019</v>
+        <v>2006</v>
       </c>
       <c r="G188" s="2"/>
       <c r="P188" s="3"/>
@@ -12719,10 +12726,10 @@
     <row r="189" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D189" s="3"/>
       <c r="E189" s="18" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F189" s="19">
-        <v>2003</v>
+        <v>2019</v>
       </c>
       <c r="G189" s="2"/>
       <c r="P189" s="3"/>
@@ -12751,10 +12758,10 @@
     <row r="190" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D190" s="3"/>
       <c r="E190" s="18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F190" s="19">
-        <v>2014</v>
+        <v>2003</v>
       </c>
       <c r="G190" s="2"/>
       <c r="P190" s="3"/>
@@ -12783,10 +12790,10 @@
     <row r="191" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D191" s="3"/>
       <c r="E191" s="18" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F191" s="19">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="G191" s="2"/>
       <c r="P191" s="3"/>
@@ -12815,10 +12822,10 @@
     <row r="192" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D192" s="3"/>
       <c r="E192" s="18" t="s">
-        <v>12</v>
+        <v>264</v>
       </c>
       <c r="F192" s="19">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="G192" s="2"/>
       <c r="P192" s="3"/>
@@ -12847,7 +12854,7 @@
     <row r="193" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D193" s="3"/>
       <c r="E193" s="18" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F193" s="19">
         <v>2022</v>
@@ -12879,10 +12886,10 @@
     <row r="194" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D194" s="3"/>
       <c r="E194" s="18" t="s">
-        <v>265</v>
+        <v>2</v>
       </c>
       <c r="F194" s="19">
-        <v>1981</v>
+        <v>2022</v>
       </c>
       <c r="G194" s="2"/>
       <c r="P194" s="3"/>
@@ -12911,10 +12918,10 @@
     <row r="195" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D195" s="3"/>
       <c r="E195" s="18" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F195" s="19">
-        <v>1996</v>
+        <v>1981</v>
       </c>
       <c r="G195" s="2"/>
       <c r="P195" s="3"/>
@@ -12943,10 +12950,10 @@
     <row r="196" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D196" s="3"/>
       <c r="E196" s="18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F196" s="19">
-        <v>2021</v>
+        <v>1996</v>
       </c>
       <c r="G196" s="2"/>
       <c r="P196" s="3"/>
@@ -12975,10 +12982,10 @@
     <row r="197" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D197" s="3"/>
       <c r="E197" s="18" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F197" s="19">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="G197" s="2"/>
       <c r="P197" s="3"/>
@@ -13007,10 +13014,10 @@
     <row r="198" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D198" s="3"/>
       <c r="E198" s="18" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F198" s="19">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="G198" s="2"/>
       <c r="P198" s="3"/>
@@ -13039,10 +13046,10 @@
     <row r="199" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D199" s="3"/>
       <c r="E199" s="18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F199" s="19">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="G199" s="2"/>
       <c r="P199" s="3"/>
@@ -13071,10 +13078,10 @@
     <row r="200" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D200" s="3"/>
       <c r="E200" s="18" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F200" s="19">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="G200" s="2"/>
       <c r="P200" s="3"/>
@@ -13103,10 +13110,10 @@
     <row r="201" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D201" s="3"/>
       <c r="E201" s="18" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F201" s="19">
-        <v>2008</v>
+        <v>2020</v>
       </c>
       <c r="G201" s="2"/>
       <c r="P201" s="3"/>
@@ -13135,10 +13142,10 @@
     <row r="202" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D202" s="3"/>
       <c r="E202" s="18" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F202" s="19">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="G202" s="2"/>
       <c r="P202" s="3"/>
@@ -13167,10 +13174,10 @@
     <row r="203" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D203" s="3"/>
       <c r="E203" s="18" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F203" s="19">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="G203" s="2"/>
       <c r="P203" s="3"/>
@@ -13199,10 +13206,10 @@
     <row r="204" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D204" s="3"/>
       <c r="E204" s="18" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F204" s="19">
-        <v>2015</v>
+        <v>2004</v>
       </c>
       <c r="G204" s="2"/>
       <c r="P204" s="3"/>
@@ -13231,10 +13238,10 @@
     <row r="205" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D205" s="3"/>
       <c r="E205" s="18" t="s">
-        <v>275</v>
+        <v>7</v>
       </c>
       <c r="F205" s="19">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="G205" s="2"/>
       <c r="P205" s="3"/>
@@ -13263,10 +13270,10 @@
     <row r="206" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D206" s="3"/>
       <c r="E206" s="18" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F206" s="19">
-        <v>1995</v>
+        <v>2009</v>
       </c>
       <c r="G206" s="2"/>
       <c r="P206" s="3"/>
@@ -13295,10 +13302,10 @@
     <row r="207" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D207" s="3"/>
       <c r="E207" s="18" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F207" s="19">
-        <v>1971</v>
+        <v>1995</v>
       </c>
       <c r="G207" s="2"/>
       <c r="P207" s="3"/>
@@ -13327,10 +13334,10 @@
     <row r="208" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D208" s="3"/>
       <c r="E208" s="18" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F208" s="19">
-        <v>2010</v>
+        <v>1971</v>
       </c>
       <c r="G208" s="2"/>
       <c r="P208" s="3"/>
@@ -13359,10 +13366,10 @@
     <row r="209" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D209" s="3"/>
       <c r="E209" s="18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F209" s="19">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="G209" s="2"/>
       <c r="P209" s="3"/>
@@ -13391,10 +13398,10 @@
     <row r="210" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D210" s="3"/>
       <c r="E210" s="18" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F210" s="19">
-        <v>1988</v>
+        <v>2013</v>
       </c>
       <c r="G210" s="2"/>
       <c r="P210" s="3"/>
@@ -13423,10 +13430,10 @@
     <row r="211" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D211" s="3"/>
       <c r="E211" s="18" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F211" s="19">
-        <v>2004</v>
+        <v>1988</v>
       </c>
       <c r="G211" s="2"/>
       <c r="P211" s="3"/>
@@ -13455,10 +13462,10 @@
     <row r="212" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D212" s="3"/>
       <c r="E212" s="18" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F212" s="19">
-        <v>1982</v>
+        <v>2004</v>
       </c>
       <c r="G212" s="2"/>
       <c r="P212" s="3"/>
@@ -13487,10 +13494,10 @@
     <row r="213" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D213" s="3"/>
       <c r="E213" s="18" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F213" s="19">
-        <v>2006</v>
+        <v>1982</v>
       </c>
       <c r="G213" s="2"/>
       <c r="P213" s="3"/>
@@ -13519,10 +13526,10 @@
     <row r="214" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D214" s="3"/>
       <c r="E214" s="18" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F214" s="19">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="G214" s="2"/>
       <c r="P214" s="3"/>
@@ -13551,10 +13558,10 @@
     <row r="215" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D215" s="3"/>
       <c r="E215" s="18" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F215" s="19">
-        <v>2015</v>
+        <v>2008</v>
       </c>
       <c r="G215" s="2"/>
       <c r="P215" s="3"/>
@@ -13583,10 +13590,10 @@
     <row r="216" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D216" s="3"/>
       <c r="E216" s="18" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F216" s="19">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="G216" s="2"/>
       <c r="P216" s="3"/>
@@ -13615,10 +13622,10 @@
     <row r="217" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D217" s="3"/>
       <c r="E217" s="18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F217" s="19">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="G217" s="2"/>
       <c r="P217" s="3"/>
@@ -13647,10 +13654,10 @@
     <row r="218" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D218" s="3"/>
       <c r="E218" s="18" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F218" s="19">
-        <v>2015</v>
+        <v>2006</v>
       </c>
       <c r="G218" s="2"/>
       <c r="P218" s="3"/>
@@ -13679,10 +13686,10 @@
     <row r="219" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D219" s="3"/>
       <c r="E219" s="18" t="s">
-        <v>38</v>
+        <v>288</v>
       </c>
       <c r="F219" s="19">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="G219" s="2"/>
       <c r="P219" s="3"/>
@@ -13711,10 +13718,10 @@
     <row r="220" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D220" s="3"/>
       <c r="E220" s="18" t="s">
-        <v>289</v>
+        <v>38</v>
       </c>
       <c r="F220" s="19">
-        <v>1990</v>
+        <v>2019</v>
       </c>
       <c r="G220" s="2"/>
       <c r="P220" s="3"/>
@@ -13743,10 +13750,10 @@
     <row r="221" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D221" s="3"/>
       <c r="E221" s="18" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F221" s="19">
-        <v>2022</v>
+        <v>1990</v>
       </c>
       <c r="G221" s="2"/>
       <c r="P221" s="3"/>
@@ -13775,10 +13782,10 @@
     <row r="222" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D222" s="3"/>
       <c r="E222" s="18" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F222" s="19">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="G222" s="2"/>
       <c r="P222" s="3"/>
@@ -13807,10 +13814,10 @@
     <row r="223" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D223" s="3"/>
       <c r="E223" s="18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F223" s="19">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="G223" s="2"/>
       <c r="P223" s="3"/>
@@ -13839,10 +13846,10 @@
     <row r="224" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D224" s="3"/>
       <c r="E224" s="18" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F224" s="19">
-        <v>1979</v>
+        <v>2016</v>
       </c>
       <c r="G224" s="2"/>
       <c r="P224" s="3"/>
@@ -13871,10 +13878,10 @@
     <row r="225" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D225" s="3"/>
       <c r="E225" s="18" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F225" s="19">
-        <v>2000</v>
+        <v>1979</v>
       </c>
       <c r="G225" s="2"/>
       <c r="P225" s="3"/>
@@ -13903,10 +13910,10 @@
     <row r="226" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D226" s="3"/>
       <c r="E226" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F226" s="19">
-        <v>2013</v>
+        <v>2000</v>
       </c>
       <c r="G226" s="2"/>
       <c r="P226" s="3"/>
@@ -13935,10 +13942,10 @@
     <row r="227" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D227" s="3"/>
       <c r="E227" s="18" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F227" s="19">
-        <v>1986</v>
+        <v>2013</v>
       </c>
       <c r="G227" s="2"/>
       <c r="P227" s="3"/>
@@ -13967,10 +13974,10 @@
     <row r="228" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D228" s="3"/>
       <c r="E228" s="18" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F228" s="19">
-        <v>2022</v>
+        <v>1986</v>
       </c>
       <c r="G228" s="2"/>
       <c r="P228" s="3"/>
@@ -13999,10 +14006,10 @@
     <row r="229" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D229" s="3"/>
       <c r="E229" s="18" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F229" s="19">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="G229" s="2"/>
       <c r="P229" s="3"/>
@@ -14031,10 +14038,10 @@
     <row r="230" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D230" s="3"/>
       <c r="E230" s="18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F230" s="19">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="G230" s="2"/>
       <c r="P230" s="3"/>
@@ -14063,10 +14070,10 @@
     <row r="231" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D231" s="3"/>
       <c r="E231" s="18" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F231" s="19">
-        <v>1992</v>
+        <v>2007</v>
       </c>
       <c r="G231" s="2"/>
       <c r="P231" s="3"/>
@@ -14095,10 +14102,10 @@
     <row r="232" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D232" s="3"/>
       <c r="E232" s="18" t="s">
-        <v>71</v>
+        <v>300</v>
       </c>
       <c r="F232" s="19">
-        <v>2007</v>
+        <v>1992</v>
       </c>
       <c r="G232" s="2"/>
       <c r="P232" s="3"/>
@@ -14127,10 +14134,10 @@
     <row r="233" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D233" s="3"/>
       <c r="E233" s="18" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F233" s="19">
-        <v>2022</v>
+        <v>2007</v>
       </c>
       <c r="G233" s="2"/>
       <c r="P233" s="3"/>
@@ -14159,10 +14166,10 @@
     <row r="234" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D234" s="3"/>
       <c r="E234" s="18" t="s">
-        <v>301</v>
+        <v>60</v>
       </c>
       <c r="F234" s="19">
-        <v>1990</v>
+        <v>2022</v>
       </c>
       <c r="G234" s="2"/>
       <c r="P234" s="3"/>
@@ -14191,10 +14198,10 @@
     <row r="235" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D235" s="3"/>
       <c r="E235" s="18" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F235" s="19">
-        <v>2002</v>
+        <v>1990</v>
       </c>
       <c r="G235" s="2"/>
       <c r="P235" s="3"/>
@@ -14223,10 +14230,10 @@
     <row r="236" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D236" s="3"/>
       <c r="E236" s="18" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F236" s="19">
-        <v>1982</v>
+        <v>2002</v>
       </c>
       <c r="G236" s="2"/>
       <c r="P236" s="3"/>
@@ -14255,10 +14262,10 @@
     <row r="237" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D237" s="3"/>
       <c r="E237" s="18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F237" s="19">
-        <v>2009</v>
+        <v>1982</v>
       </c>
       <c r="G237" s="2"/>
       <c r="P237" s="3"/>
@@ -14287,10 +14294,10 @@
     <row r="238" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D238" s="3"/>
       <c r="E238" s="18" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F238" s="19">
-        <v>1975</v>
+        <v>2009</v>
       </c>
       <c r="G238" s="2"/>
       <c r="P238" s="3"/>
@@ -14319,10 +14326,10 @@
     <row r="239" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D239" s="3"/>
       <c r="E239" s="18" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F239" s="19">
-        <v>2019</v>
+        <v>1975</v>
       </c>
       <c r="G239" s="2"/>
       <c r="P239" s="3"/>
@@ -14351,10 +14358,10 @@
     <row r="240" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D240" s="3"/>
       <c r="E240" s="18" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F240" s="19">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="G240" s="2"/>
       <c r="P240" s="3"/>
@@ -14383,10 +14390,10 @@
     <row r="241" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D241" s="3"/>
       <c r="E241" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F241" s="19">
-        <v>1989</v>
+        <v>2009</v>
       </c>
       <c r="G241" s="2"/>
       <c r="P241" s="3"/>
@@ -14415,10 +14422,10 @@
     <row r="242" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D242" s="3"/>
       <c r="E242" s="18" t="s">
-        <v>85</v>
+        <v>308</v>
       </c>
       <c r="F242" s="19">
-        <v>2013</v>
+        <v>1989</v>
       </c>
       <c r="G242" s="2"/>
       <c r="P242" s="3"/>
@@ -14447,10 +14454,10 @@
     <row r="243" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D243" s="3"/>
       <c r="E243" s="18" t="s">
-        <v>309</v>
+        <v>85</v>
       </c>
       <c r="F243" s="19">
-        <v>1993</v>
+        <v>2013</v>
       </c>
       <c r="G243" s="2"/>
       <c r="P243" s="3"/>
@@ -14479,10 +14486,10 @@
     <row r="244" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D244" s="3"/>
       <c r="E244" s="18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F244" s="19">
-        <v>2019</v>
+        <v>1993</v>
       </c>
       <c r="G244" s="2"/>
       <c r="P244" s="3"/>
@@ -14511,10 +14518,10 @@
     <row r="245" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D245" s="3"/>
       <c r="E245" s="18" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F245" s="19">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="G245" s="2"/>
       <c r="P245" s="3"/>
@@ -14543,10 +14550,10 @@
     <row r="246" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D246" s="3"/>
       <c r="E246" s="18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F246" s="19">
-        <v>2009</v>
+        <v>2017</v>
       </c>
       <c r="G246" s="2"/>
       <c r="P246" s="3"/>
@@ -14575,10 +14582,10 @@
     <row r="247" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D247" s="3"/>
       <c r="E247" s="18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F247" s="19">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="G247" s="2"/>
       <c r="P247" s="3"/>
@@ -14607,10 +14614,10 @@
     <row r="248" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D248" s="3"/>
       <c r="E248" s="18" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F248" s="19">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="G248" s="2"/>
       <c r="P248" s="3"/>
@@ -14639,10 +14646,10 @@
     <row r="249" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D249" s="3"/>
       <c r="E249" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F249" s="19">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="G249" s="2"/>
       <c r="P249" s="3"/>
@@ -14671,10 +14678,10 @@
     <row r="250" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D250" s="3"/>
       <c r="E250" s="18" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F250" s="19">
-        <v>2007</v>
+        <v>2016</v>
       </c>
       <c r="G250" s="2"/>
       <c r="P250" s="3"/>
@@ -14703,10 +14710,10 @@
     <row r="251" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D251" s="3"/>
       <c r="E251" s="18" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F251" s="19">
-        <v>2018</v>
+        <v>2007</v>
       </c>
       <c r="G251" s="2"/>
       <c r="P251" s="3"/>
@@ -14735,10 +14742,10 @@
     <row r="252" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D252" s="3"/>
       <c r="E252" s="18" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F252" s="19">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="G252" s="2"/>
       <c r="P252" s="3"/>
@@ -14759,10 +14766,10 @@
     <row r="253" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D253" s="3"/>
       <c r="E253" s="18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F253" s="19">
-        <v>2007</v>
+        <v>2016</v>
       </c>
       <c r="G253" s="2"/>
       <c r="V253" s="3"/>
@@ -14777,10 +14784,10 @@
     <row r="254" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D254" s="3"/>
       <c r="E254" s="18" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F254" s="19">
-        <v>1997</v>
+        <v>2007</v>
       </c>
       <c r="G254" s="2"/>
       <c r="V254" s="3"/>
@@ -14795,10 +14802,10 @@
     <row r="255" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D255" s="3"/>
       <c r="E255" s="18" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F255" s="19">
-        <v>2014</v>
+        <v>1997</v>
       </c>
       <c r="G255" s="2"/>
       <c r="V255" s="3"/>
@@ -14813,10 +14820,10 @@
     <row r="256" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D256" s="3"/>
       <c r="E256" s="18" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F256" s="19">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="G256" s="2"/>
       <c r="V256" s="3"/>
@@ -14831,10 +14838,10 @@
     <row r="257" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D257" s="3"/>
       <c r="E257" s="18" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F257" s="19">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="G257" s="2"/>
       <c r="V257" s="3"/>
@@ -14849,10 +14856,10 @@
     <row r="258" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D258" s="3"/>
       <c r="E258" s="18" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F258" s="19">
-        <v>2002</v>
+        <v>2017</v>
       </c>
       <c r="G258" s="2"/>
       <c r="V258" s="3"/>
@@ -14867,10 +14874,10 @@
     <row r="259" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D259" s="3"/>
       <c r="E259" s="18" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F259" s="19">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="G259" s="2"/>
       <c r="V259" s="3"/>
@@ -14885,10 +14892,10 @@
     <row r="260" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D260" s="3"/>
       <c r="E260" s="18" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F260" s="19">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="G260" s="2"/>
       <c r="V260" s="3"/>
@@ -14903,10 +14910,10 @@
     <row r="261" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D261" s="3"/>
       <c r="E261" s="18" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F261" s="19">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="G261" s="2"/>
       <c r="V261" s="3"/>
@@ -14921,10 +14928,10 @@
     <row r="262" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D262" s="3"/>
       <c r="E262" s="18" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F262" s="19">
-        <v>2022</v>
+        <v>2001</v>
       </c>
       <c r="G262" s="2"/>
       <c r="V262" s="3"/>
@@ -14939,10 +14946,10 @@
     <row r="263" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D263" s="3"/>
       <c r="E263" s="18" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F263" s="19">
-        <v>1999</v>
+        <v>2022</v>
       </c>
       <c r="G263" s="2"/>
       <c r="V263" s="3"/>
@@ -14957,7 +14964,7 @@
     <row r="264" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D264" s="3"/>
       <c r="E264" s="18" t="s">
-        <v>46</v>
+        <v>329</v>
       </c>
       <c r="F264" s="19">
         <v>1999</v>
@@ -14974,11 +14981,11 @@
     </row>
     <row r="265" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D265" s="3"/>
-      <c r="E265" s="26">
-        <v>1917</v>
+      <c r="E265" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="F265" s="19">
-        <v>2019</v>
+        <v>1999</v>
       </c>
       <c r="G265" s="2"/>
       <c r="V265" s="3"/>
@@ -14992,11 +14999,11 @@
     </row>
     <row r="266" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D266" s="3"/>
-      <c r="E266" s="18" t="s">
-        <v>97</v>
+      <c r="E266" s="26">
+        <v>1917</v>
       </c>
       <c r="F266" s="19">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="G266" s="2"/>
       <c r="V266" s="3"/>
@@ -15011,10 +15018,10 @@
     <row r="267" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D267" s="3"/>
       <c r="E267" s="18" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F267" s="19">
-        <v>2005</v>
+        <v>2017</v>
       </c>
       <c r="G267" s="2"/>
       <c r="V267" s="3"/>
@@ -15029,10 +15036,10 @@
     <row r="268" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D268" s="3"/>
       <c r="E268" s="18" t="s">
-        <v>330</v>
+        <v>90</v>
       </c>
       <c r="F268" s="19">
-        <v>2019</v>
+        <v>2005</v>
       </c>
       <c r="G268" s="2"/>
       <c r="V268" s="3"/>
@@ -15047,10 +15054,10 @@
     <row r="269" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D269" s="3"/>
       <c r="E269" s="18" t="s">
-        <v>23</v>
+        <v>330</v>
       </c>
       <c r="F269" s="19">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G269" s="2"/>
       <c r="V269" s="3"/>
@@ -15065,10 +15072,10 @@
     <row r="270" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D270" s="3"/>
       <c r="E270" s="18" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F270" s="19">
-        <v>2004</v>
+        <v>2018</v>
       </c>
       <c r="G270" s="2"/>
       <c r="V270" s="3"/>
@@ -15083,10 +15090,10 @@
     <row r="271" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D271" s="3"/>
       <c r="E271" s="18" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="F271" s="19">
-        <v>2016</v>
+        <v>2004</v>
       </c>
       <c r="G271" s="2"/>
       <c r="V271" s="3"/>
@@ -15101,10 +15108,10 @@
     <row r="272" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D272" s="3"/>
       <c r="E272" s="18" t="s">
-        <v>331</v>
+        <v>43</v>
       </c>
       <c r="F272" s="19">
-        <v>2005</v>
+        <v>2016</v>
       </c>
       <c r="G272" s="2"/>
       <c r="V272" s="3"/>
@@ -15119,10 +15126,10 @@
     <row r="273" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D273" s="3"/>
       <c r="E273" s="18" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F273" s="19">
-        <v>2020</v>
+        <v>2005</v>
       </c>
       <c r="G273" s="2"/>
       <c r="V273" s="3"/>
@@ -15137,10 +15144,10 @@
     <row r="274" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D274" s="3"/>
       <c r="E274" s="18" t="s">
-        <v>53</v>
+        <v>332</v>
       </c>
       <c r="F274" s="19">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="G274" s="2"/>
       <c r="V274" s="3"/>
@@ -15155,10 +15162,10 @@
     <row r="275" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D275" s="3"/>
       <c r="E275" s="18" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="F275" s="19">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="G275" s="2"/>
       <c r="V275" s="3"/>
@@ -15173,10 +15180,10 @@
     <row r="276" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D276" s="3"/>
       <c r="E276" s="18" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="F276" s="19">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="G276" s="2"/>
       <c r="V276" s="3"/>
@@ -15191,10 +15198,10 @@
     <row r="277" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D277" s="3"/>
       <c r="E277" s="18" t="s">
-        <v>333</v>
+        <v>78</v>
       </c>
       <c r="F277" s="19">
-        <v>2003</v>
+        <v>2018</v>
       </c>
       <c r="G277" s="2"/>
       <c r="V277" s="3"/>
@@ -15209,10 +15216,10 @@
     <row r="278" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D278" s="3"/>
       <c r="E278" s="18" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F278" s="19">
-        <v>1976</v>
+        <v>2003</v>
       </c>
       <c r="G278" s="2"/>
       <c r="V278" s="3"/>
@@ -15227,10 +15234,10 @@
     <row r="279" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D279" s="3"/>
       <c r="E279" s="18" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F279" s="19">
-        <v>2021</v>
+        <v>1976</v>
       </c>
       <c r="G279" s="2"/>
       <c r="V279" s="3"/>
@@ -15245,10 +15252,10 @@
     <row r="280" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D280" s="3"/>
       <c r="E280" s="18" t="s">
-        <v>31</v>
+        <v>335</v>
       </c>
       <c r="F280" s="19">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="G280" s="2"/>
       <c r="V280" s="3"/>
@@ -15263,10 +15270,10 @@
     <row r="281" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D281" s="3"/>
       <c r="E281" s="18" t="s">
-        <v>336</v>
+        <v>31</v>
       </c>
       <c r="F281" s="19">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="G281" s="2"/>
       <c r="V281" s="3"/>
@@ -15281,10 +15288,10 @@
     <row r="282" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D282" s="3"/>
       <c r="E282" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F282" s="19">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="G282" s="2"/>
       <c r="V282" s="3"/>
@@ -15299,10 +15306,10 @@
     <row r="283" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D283" s="3"/>
       <c r="E283" s="18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F283" s="19">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G283" s="2"/>
       <c r="V283" s="3"/>
@@ -15317,10 +15324,10 @@
     <row r="284" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D284" s="3"/>
       <c r="E284" s="18" t="s">
-        <v>26</v>
+        <v>338</v>
       </c>
       <c r="F284" s="19">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="G284" s="2"/>
       <c r="V284" s="3"/>
@@ -15335,10 +15342,10 @@
     <row r="285" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D285" s="3"/>
       <c r="E285" s="18" t="s">
-        <v>339</v>
+        <v>26</v>
       </c>
       <c r="F285" s="19">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="G285" s="2"/>
       <c r="V285" s="3"/>
@@ -15353,10 +15360,10 @@
     <row r="286" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D286" s="3"/>
       <c r="E286" s="18" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F286" s="19">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="G286" s="2"/>
       <c r="V286" s="3"/>
@@ -15371,10 +15378,10 @@
     <row r="287" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D287" s="3"/>
       <c r="E287" s="18" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F287" s="19">
-        <v>2012</v>
+        <v>2004</v>
       </c>
       <c r="G287" s="2"/>
       <c r="V287" s="3"/>
@@ -15389,10 +15396,10 @@
     <row r="288" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D288" s="3"/>
       <c r="E288" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F288" s="19">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="G288" s="2"/>
       <c r="V288" s="3"/>
@@ -15407,10 +15414,10 @@
     <row r="289" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D289" s="3"/>
       <c r="E289" s="18" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F289" s="19">
-        <v>1983</v>
+        <v>2011</v>
       </c>
       <c r="G289" s="2"/>
       <c r="V289" s="3"/>
@@ -15425,10 +15432,10 @@
     <row r="290" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D290" s="3"/>
       <c r="E290" s="18" t="s">
-        <v>68</v>
+        <v>343</v>
       </c>
       <c r="F290" s="19">
-        <v>2009</v>
+        <v>1983</v>
       </c>
       <c r="G290" s="2"/>
       <c r="V290" s="3"/>
@@ -15443,10 +15450,10 @@
     <row r="291" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D291" s="3"/>
       <c r="E291" s="18" t="s">
-        <v>344</v>
+        <v>68</v>
       </c>
       <c r="F291" s="19">
-        <v>2021</v>
+        <v>2009</v>
       </c>
       <c r="G291" s="2"/>
       <c r="V291" s="3"/>
@@ -15461,10 +15468,10 @@
     <row r="292" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D292" s="3"/>
       <c r="E292" s="18" t="s">
-        <v>69</v>
+        <v>344</v>
       </c>
       <c r="F292" s="19">
-        <v>2002</v>
+        <v>2021</v>
       </c>
       <c r="G292" s="2"/>
       <c r="V292" s="3"/>
@@ -15479,10 +15486,10 @@
     <row r="293" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D293" s="3"/>
       <c r="E293" s="18" t="s">
-        <v>345</v>
+        <v>69</v>
       </c>
       <c r="F293" s="19">
-        <v>2015</v>
+        <v>2002</v>
       </c>
       <c r="G293" s="2"/>
       <c r="V293" s="3"/>
@@ -15497,10 +15504,10 @@
     <row r="294" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D294" s="3"/>
       <c r="E294" s="18" t="s">
-        <v>62</v>
+        <v>345</v>
       </c>
       <c r="F294" s="19">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="G294" s="2"/>
       <c r="V294" s="3"/>
@@ -15515,10 +15522,10 @@
     <row r="295" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D295" s="3"/>
       <c r="E295" s="18" t="s">
-        <v>346</v>
+        <v>62</v>
       </c>
       <c r="F295" s="19">
-        <v>1999</v>
+        <v>2010</v>
       </c>
       <c r="G295" s="2"/>
       <c r="V295" s="3"/>
@@ -15533,10 +15540,10 @@
     <row r="296" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D296" s="3"/>
       <c r="E296" s="18" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F296" s="19">
-        <v>2019</v>
+        <v>1999</v>
       </c>
       <c r="G296" s="2"/>
       <c r="V296" s="3"/>
@@ -15551,10 +15558,10 @@
     <row r="297" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D297" s="3"/>
       <c r="E297" s="18" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F297" s="19">
-        <v>1985</v>
+        <v>2019</v>
       </c>
       <c r="G297" s="2"/>
       <c r="V297" s="3"/>
@@ -15569,10 +15576,10 @@
     <row r="298" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D298" s="3"/>
       <c r="E298" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F298" s="19">
-        <v>2005</v>
+        <v>1985</v>
       </c>
       <c r="G298" s="2"/>
       <c r="V298" s="3"/>
@@ -15587,10 +15594,10 @@
     <row r="299" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D299" s="3"/>
       <c r="E299" s="18" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F299" s="19">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="G299" s="2"/>
       <c r="V299" s="3"/>
@@ -15605,10 +15612,10 @@
     <row r="300" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D300" s="3"/>
       <c r="E300" s="18" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F300" s="19">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="G300" s="2"/>
       <c r="V300" s="3"/>
@@ -15623,10 +15630,10 @@
     <row r="301" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D301" s="3"/>
       <c r="E301" s="18" t="s">
-        <v>32</v>
+        <v>351</v>
       </c>
       <c r="F301" s="19">
-        <v>2003</v>
+        <v>2017</v>
       </c>
       <c r="G301" s="2"/>
       <c r="V301" s="3"/>
@@ -15641,10 +15648,10 @@
     <row r="302" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D302" s="3"/>
       <c r="E302" s="18" t="s">
-        <v>352</v>
+        <v>32</v>
       </c>
       <c r="F302" s="19">
-        <v>1972</v>
+        <v>2003</v>
       </c>
       <c r="G302" s="2"/>
       <c r="V302" s="3"/>
@@ -15659,10 +15666,10 @@
     <row r="303" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D303" s="3"/>
       <c r="E303" s="18" t="s">
-        <v>65</v>
+        <v>352</v>
       </c>
       <c r="F303" s="19">
-        <v>2007</v>
+        <v>1972</v>
       </c>
       <c r="G303" s="2"/>
       <c r="V303" s="3"/>
@@ -15677,10 +15684,10 @@
     <row r="304" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D304" s="3"/>
       <c r="E304" s="18" t="s">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F304" s="19">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="G304" s="2"/>
       <c r="V304" s="3"/>
@@ -15695,10 +15702,10 @@
     <row r="305" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D305" s="3"/>
       <c r="E305" s="18" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F305" s="19">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="G305" s="2"/>
       <c r="V305" s="3"/>
@@ -15713,10 +15720,10 @@
     <row r="306" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D306" s="3"/>
       <c r="E306" s="18" t="s">
-        <v>18</v>
+        <v>354</v>
       </c>
       <c r="F306" s="19">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="G306" s="2"/>
       <c r="V306" s="3"/>
@@ -15731,7 +15738,7 @@
     <row r="307" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D307" s="3"/>
       <c r="E307" s="18" t="s">
-        <v>355</v>
+        <v>18</v>
       </c>
       <c r="F307" s="19">
         <v>2017</v>
@@ -15749,10 +15756,10 @@
     <row r="308" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D308" s="3"/>
       <c r="E308" s="18" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F308" s="19">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="G308" s="2"/>
       <c r="V308" s="3"/>
@@ -15767,10 +15774,10 @@
     <row r="309" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D309" s="3"/>
       <c r="E309" s="18" t="s">
-        <v>39</v>
+        <v>356</v>
       </c>
       <c r="F309" s="19">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="G309" s="2"/>
       <c r="V309" s="3"/>
@@ -15785,10 +15792,10 @@
     <row r="310" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D310" s="3"/>
       <c r="E310" s="18" t="s">
-        <v>357</v>
+        <v>39</v>
       </c>
       <c r="F310" s="19">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="G310" s="2"/>
       <c r="V310" s="3"/>
@@ -15803,10 +15810,10 @@
     <row r="311" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D311" s="3"/>
       <c r="E311" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F311" s="19">
-        <v>1994</v>
+        <v>2004</v>
       </c>
       <c r="G311" s="2"/>
       <c r="V311" s="3"/>
@@ -15821,10 +15828,10 @@
     <row r="312" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D312" s="3"/>
       <c r="E312" s="18" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F312" s="19">
-        <v>2012</v>
+        <v>1994</v>
       </c>
       <c r="G312" s="2"/>
       <c r="V312" s="3"/>
@@ -15839,10 +15846,10 @@
     <row r="313" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D313" s="3"/>
       <c r="E313" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F313" s="19">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="G313" s="2"/>
       <c r="V313" s="3"/>
@@ -15857,10 +15864,10 @@
     <row r="314" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D314" s="3"/>
       <c r="E314" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F314" s="19">
-        <v>1990</v>
+        <v>2010</v>
       </c>
       <c r="G314" s="2"/>
       <c r="V314" s="3"/>
@@ -15875,10 +15882,10 @@
     <row r="315" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D315" s="3"/>
       <c r="E315" s="18" t="s">
-        <v>6</v>
+        <v>361</v>
       </c>
       <c r="F315" s="19">
-        <v>2021</v>
+        <v>1990</v>
       </c>
       <c r="G315" s="2"/>
       <c r="V315" s="3"/>
@@ -15893,10 +15900,10 @@
     <row r="316" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D316" s="3"/>
       <c r="E316" s="18" t="s">
-        <v>362</v>
+        <v>6</v>
       </c>
       <c r="F316" s="19">
-        <v>2000</v>
+        <v>2021</v>
       </c>
       <c r="G316" s="2"/>
       <c r="V316" s="3"/>
@@ -15911,10 +15918,10 @@
     <row r="317" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D317" s="3"/>
       <c r="E317" s="18" t="s">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="F317" s="19">
-        <v>2011</v>
+        <v>2000</v>
       </c>
       <c r="G317" s="2"/>
       <c r="V317" s="3"/>
@@ -15929,10 +15936,10 @@
     <row r="318" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D318" s="3"/>
       <c r="E318" s="18" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F318" s="19">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="G318" s="2"/>
       <c r="V318" s="3"/>
@@ -15947,10 +15954,10 @@
     <row r="319" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D319" s="3"/>
       <c r="E319" s="18" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="F319" s="19">
-        <v>2005</v>
+        <v>2019</v>
       </c>
       <c r="G319" s="2"/>
       <c r="V319" s="3"/>
@@ -15965,10 +15972,10 @@
     <row r="320" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D320" s="3"/>
       <c r="E320" s="18" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="F320" s="19">
-        <v>2012</v>
+        <v>2005</v>
       </c>
       <c r="G320" s="2"/>
       <c r="V320" s="3"/>
@@ -15983,10 +15990,10 @@
     <row r="321" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D321" s="3"/>
       <c r="E321" s="18" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F321" s="19">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="G321" s="2"/>
       <c r="V321" s="3"/>
@@ -16001,10 +16008,10 @@
     <row r="322" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D322" s="3"/>
       <c r="E322" s="18" t="s">
-        <v>363</v>
+        <v>81</v>
       </c>
       <c r="F322" s="19">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="G322" s="2"/>
       <c r="V322" s="3"/>
@@ -16019,10 +16026,10 @@
     <row r="323" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D323" s="3"/>
       <c r="E323" s="18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F323" s="19">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="G323" s="2"/>
       <c r="V323" s="3"/>
@@ -16037,10 +16044,10 @@
     <row r="324" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D324" s="3"/>
       <c r="E324" s="18" t="s">
-        <v>15</v>
+        <v>364</v>
       </c>
       <c r="F324" s="19">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="G324" s="2"/>
       <c r="V324" s="3"/>
@@ -16055,10 +16062,10 @@
     <row r="325" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D325" s="3"/>
       <c r="E325" s="18" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F325" s="19">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="G325" s="2"/>
       <c r="V325" s="3"/>
@@ -16073,10 +16080,10 @@
     <row r="326" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D326" s="3"/>
       <c r="E326" s="18" t="s">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="F326" s="19">
-        <v>2002</v>
+        <v>2009</v>
       </c>
       <c r="G326" s="2"/>
       <c r="V326" s="3"/>
@@ -16091,10 +16098,10 @@
     <row r="327" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D327" s="3"/>
       <c r="E327" s="18" t="s">
-        <v>365</v>
+        <v>96</v>
       </c>
       <c r="F327" s="19">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="G327" s="2"/>
       <c r="V327" s="3"/>
@@ -16109,10 +16116,10 @@
     <row r="328" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D328" s="3"/>
       <c r="E328" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F328" s="19">
-        <v>2013</v>
+        <v>2001</v>
       </c>
       <c r="G328" s="2"/>
       <c r="V328" s="3"/>
@@ -16127,10 +16134,10 @@
     <row r="329" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D329" s="3"/>
       <c r="E329" s="18" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F329" s="19">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="G329" s="2"/>
       <c r="V329" s="3"/>
@@ -16145,10 +16152,10 @@
     <row r="330" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D330" s="3"/>
       <c r="E330" s="18" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F330" s="19">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="G330" s="2"/>
       <c r="V330" s="3"/>
@@ -16163,10 +16170,10 @@
     <row r="331" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D331" s="3"/>
       <c r="E331" s="18" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F331" s="19">
-        <v>1980</v>
+        <v>2014</v>
       </c>
       <c r="G331" s="2"/>
       <c r="V331" s="3"/>
@@ -16181,10 +16188,10 @@
     <row r="332" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D332" s="3"/>
       <c r="E332" s="18" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F332" s="19">
-        <v>1995</v>
+        <v>1980</v>
       </c>
       <c r="G332" s="2"/>
       <c r="V332" s="3"/>
@@ -16199,10 +16206,10 @@
     <row r="333" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D333" s="3"/>
       <c r="E333" s="18" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F333" s="19">
-        <v>2016</v>
+        <v>1995</v>
       </c>
       <c r="G333" s="2"/>
       <c r="V333" s="3"/>
@@ -16217,10 +16224,10 @@
     <row r="334" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D334" s="3"/>
       <c r="E334" s="18" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F334" s="19">
-        <v>2004</v>
+        <v>2016</v>
       </c>
       <c r="G334" s="2"/>
       <c r="V334" s="3"/>
@@ -16235,10 +16242,10 @@
     <row r="335" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D335" s="3"/>
       <c r="E335" s="18" t="s">
-        <v>42</v>
+        <v>372</v>
       </c>
       <c r="F335" s="19">
-        <v>1993</v>
+        <v>2004</v>
       </c>
       <c r="G335" s="2"/>
       <c r="V335" s="3"/>
@@ -16253,10 +16260,10 @@
     <row r="336" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D336" s="3"/>
       <c r="E336" s="18" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F336" s="19">
-        <v>2017</v>
+        <v>1993</v>
       </c>
       <c r="G336" s="2"/>
       <c r="V336" s="3"/>
@@ -16271,10 +16278,10 @@
     <row r="337" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D337" s="3"/>
       <c r="E337" s="18" t="s">
-        <v>373</v>
+        <v>84</v>
       </c>
       <c r="F337" s="19">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="G337" s="2"/>
       <c r="V337" s="3"/>
@@ -16289,10 +16296,10 @@
     <row r="338" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D338" s="3"/>
       <c r="E338" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F338" s="19">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="G338" s="2"/>
       <c r="V338" s="3"/>
@@ -16307,10 +16314,10 @@
     <row r="339" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D339" s="3"/>
       <c r="E339" s="18" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F339" s="19">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="G339" s="2"/>
       <c r="V339" s="3"/>
@@ -16325,7 +16332,7 @@
     <row r="340" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D340" s="3"/>
       <c r="E340" s="18" t="s">
-        <v>28</v>
+        <v>375</v>
       </c>
       <c r="F340" s="19">
         <v>2016</v>
@@ -16343,10 +16350,10 @@
     <row r="341" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D341" s="3"/>
       <c r="E341" s="18" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F341" s="19">
-        <v>1994</v>
+        <v>2016</v>
       </c>
       <c r="G341" s="2"/>
       <c r="V341" s="3"/>
@@ -16361,10 +16368,10 @@
     <row r="342" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D342" s="3"/>
       <c r="E342" s="18" t="s">
-        <v>376</v>
+        <v>8</v>
       </c>
       <c r="F342" s="19">
-        <v>2015</v>
+        <v>1994</v>
       </c>
       <c r="G342" s="2"/>
       <c r="V342" s="3"/>
@@ -16379,10 +16386,10 @@
     <row r="343" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D343" s="3"/>
       <c r="E343" s="18" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F343" s="19">
-        <v>1991</v>
+        <v>2015</v>
       </c>
       <c r="G343" s="2"/>
       <c r="V343" s="3"/>
@@ -16397,10 +16404,10 @@
     <row r="344" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D344" s="3"/>
       <c r="E344" s="18" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F344" s="19">
-        <v>2019</v>
+        <v>1991</v>
       </c>
       <c r="G344" s="2"/>
       <c r="V344" s="3"/>
@@ -16415,10 +16422,10 @@
     <row r="345" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D345" s="3"/>
       <c r="E345" s="18" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F345" s="19">
-        <v>2001</v>
+        <v>2019</v>
       </c>
       <c r="G345" s="2"/>
       <c r="V345" s="3"/>
@@ -16433,10 +16440,10 @@
     <row r="346" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D346" s="3"/>
       <c r="E346" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F346" s="19">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="G346" s="2"/>
       <c r="V346" s="3"/>
@@ -16451,10 +16458,10 @@
     <row r="347" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D347" s="3"/>
       <c r="E347" s="18" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F347" s="19">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="G347" s="2"/>
       <c r="V347" s="3"/>
@@ -16469,7 +16476,7 @@
     <row r="348" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D348" s="3"/>
       <c r="E348" s="18" t="s">
-        <v>56</v>
+        <v>381</v>
       </c>
       <c r="F348" s="19">
         <v>2001</v>
@@ -16487,10 +16494,10 @@
     <row r="349" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D349" s="3"/>
       <c r="E349" s="18" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="F349" s="19">
-        <v>2017</v>
+        <v>2001</v>
       </c>
       <c r="G349" s="2"/>
       <c r="V349" s="3"/>
@@ -16505,10 +16512,10 @@
     <row r="350" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D350" s="3"/>
       <c r="E350" s="18" t="s">
-        <v>382</v>
+        <v>88</v>
       </c>
       <c r="F350" s="19">
-        <v>1985</v>
+        <v>2017</v>
       </c>
       <c r="G350" s="2"/>
       <c r="V350" s="3"/>
@@ -16523,10 +16530,10 @@
     <row r="351" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D351" s="3"/>
       <c r="E351" s="18" t="s">
-        <v>72</v>
+        <v>382</v>
       </c>
       <c r="F351" s="19">
-        <v>2001</v>
+        <v>1985</v>
       </c>
       <c r="G351" s="2"/>
       <c r="V351" s="3"/>
@@ -16541,10 +16548,10 @@
     <row r="352" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D352" s="3"/>
       <c r="E352" s="18" t="s">
-        <v>383</v>
+        <v>72</v>
       </c>
       <c r="F352" s="19">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="G352" s="2"/>
       <c r="V352" s="3"/>
@@ -16559,10 +16566,10 @@
     <row r="353" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D353" s="3"/>
       <c r="E353" s="18" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F353" s="19">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="G353" s="2"/>
       <c r="V353" s="3"/>
@@ -16577,10 +16584,10 @@
     <row r="354" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D354" s="3"/>
       <c r="E354" s="18" t="s">
-        <v>3</v>
+        <v>384</v>
       </c>
       <c r="F354" s="19">
-        <v>1997</v>
+        <v>2008</v>
       </c>
       <c r="G354" s="2"/>
       <c r="V354" s="3"/>
@@ -16595,10 +16602,10 @@
     <row r="355" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D355" s="3"/>
       <c r="E355" s="18" t="s">
-        <v>385</v>
+        <v>3</v>
       </c>
       <c r="F355" s="19">
-        <v>2019</v>
+        <v>1997</v>
       </c>
       <c r="G355" s="2"/>
       <c r="V355" s="3"/>
@@ -16613,10 +16620,10 @@
     <row r="356" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D356" s="3"/>
       <c r="E356" s="18" t="s">
-        <v>80</v>
+        <v>385</v>
       </c>
       <c r="F356" s="19">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="G356" s="2"/>
       <c r="V356" s="3"/>
@@ -16631,10 +16638,10 @@
     <row r="357" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D357" s="3"/>
       <c r="E357" s="18" t="s">
-        <v>386</v>
+        <v>80</v>
       </c>
       <c r="F357" s="19">
-        <v>1977</v>
+        <v>2017</v>
       </c>
       <c r="G357" s="2"/>
       <c r="V357" s="3"/>
@@ -16649,10 +16656,10 @@
     <row r="358" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D358" s="3"/>
       <c r="E358" s="18" t="s">
-        <v>4</v>
+        <v>386</v>
       </c>
       <c r="F358" s="19">
-        <v>2015</v>
+        <v>1977</v>
       </c>
       <c r="G358" s="2"/>
       <c r="V358" s="3"/>
@@ -16667,10 +16674,10 @@
     <row r="359" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D359" s="3"/>
       <c r="E359" s="18" t="s">
-        <v>387</v>
+        <v>4</v>
       </c>
       <c r="F359" s="19">
-        <v>1999</v>
+        <v>2015</v>
       </c>
       <c r="G359" s="2"/>
       <c r="V359" s="3"/>
@@ -16685,10 +16692,10 @@
     <row r="360" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D360" s="3"/>
       <c r="E360" s="18" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F360" s="19">
-        <v>2014</v>
+        <v>1999</v>
       </c>
       <c r="G360" s="2"/>
       <c r="V360" s="3"/>
@@ -16703,10 +16710,10 @@
     <row r="361" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D361" s="3"/>
       <c r="E361" s="18" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F361" s="19">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="G361" s="2"/>
       <c r="V361" s="3"/>
@@ -16721,10 +16728,10 @@
     <row r="362" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D362" s="3"/>
       <c r="E362" s="18" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F362" s="19">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="G362" s="2"/>
       <c r="V362" s="3"/>
@@ -16739,10 +16746,10 @@
     <row r="363" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D363" s="3"/>
       <c r="E363" s="18" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F363" s="19">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="G363" s="2"/>
       <c r="V363" s="3"/>
@@ -16757,10 +16764,10 @@
     <row r="364" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D364" s="3"/>
       <c r="E364" s="18" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F364" s="19">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="G364" s="2"/>
       <c r="V364" s="3"/>
@@ -16775,10 +16782,10 @@
     <row r="365" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D365" s="3"/>
       <c r="E365" s="18" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F365" s="19">
-        <v>2017</v>
+        <v>1998</v>
       </c>
       <c r="G365" s="2"/>
       <c r="V365" s="3"/>
@@ -16793,10 +16800,10 @@
     <row r="366" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D366" s="3"/>
       <c r="E366" s="18" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F366" s="19">
-        <v>2004</v>
+        <v>2017</v>
       </c>
       <c r="G366" s="2"/>
       <c r="V366" s="3"/>
@@ -16811,10 +16818,10 @@
     <row r="367" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D367" s="3"/>
       <c r="E367" s="18" t="s">
-        <v>66</v>
+        <v>394</v>
       </c>
       <c r="F367" s="19">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="G367" s="2"/>
       <c r="V367" s="3"/>
@@ -16829,10 +16836,10 @@
     <row r="368" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D368" s="3"/>
       <c r="E368" s="18" t="s">
-        <v>395</v>
+        <v>66</v>
       </c>
       <c r="F368" s="19">
-        <v>2012</v>
+        <v>2003</v>
       </c>
       <c r="G368" s="2"/>
       <c r="V368" s="3"/>
@@ -16847,10 +16854,10 @@
     <row r="369" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D369" s="3"/>
       <c r="E369" s="18" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F369" s="19">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="G369" s="2"/>
       <c r="V369" s="3"/>
@@ -16865,10 +16872,10 @@
     <row r="370" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D370" s="3"/>
       <c r="E370" s="18" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F370" s="19">
-        <v>2017</v>
+        <v>2007</v>
       </c>
       <c r="G370" s="2"/>
       <c r="V370" s="3"/>
@@ -16883,10 +16890,10 @@
     <row r="371" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D371" s="3"/>
       <c r="E371" s="18" t="s">
-        <v>1</v>
+        <v>397</v>
       </c>
       <c r="F371" s="19">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="G371" s="2"/>
       <c r="V371" s="3"/>
@@ -16901,10 +16908,10 @@
     <row r="372" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D372" s="3"/>
       <c r="E372" s="18" t="s">
-        <v>398</v>
+        <v>1</v>
       </c>
       <c r="F372" s="19">
-        <v>1995</v>
+        <v>2019</v>
       </c>
       <c r="G372" s="2"/>
       <c r="V372" s="3"/>
@@ -16919,10 +16926,10 @@
     <row r="373" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D373" s="3"/>
       <c r="E373" s="18" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F373" s="19">
-        <v>1980</v>
+        <v>1995</v>
       </c>
       <c r="G373" s="2"/>
       <c r="V373" s="3"/>
@@ -16937,10 +16944,10 @@
     <row r="374" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D374" s="3"/>
       <c r="E374" s="18" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F374" s="19">
-        <v>2018</v>
+        <v>1980</v>
       </c>
       <c r="G374" s="2"/>
       <c r="V374" s="3"/>
@@ -16955,10 +16962,10 @@
     <row r="375" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D375" s="3"/>
       <c r="E375" s="18" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F375" s="19">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="G375" s="2"/>
       <c r="V375" s="3"/>
@@ -16973,10 +16980,10 @@
     <row r="376" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D376" s="3"/>
       <c r="E376" s="18" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F376" s="19">
-        <v>2009</v>
+        <v>2016</v>
       </c>
       <c r="G376" s="2"/>
       <c r="V376" s="3"/>
@@ -16991,10 +16998,10 @@
     <row r="377" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D377" s="3"/>
       <c r="E377" s="18" t="s">
-        <v>89</v>
+        <v>402</v>
       </c>
       <c r="F377" s="19">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="G377" s="2"/>
       <c r="V377" s="3"/>
@@ -17009,10 +17016,10 @@
     <row r="378" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D378" s="3"/>
       <c r="E378" s="18" t="s">
-        <v>403</v>
+        <v>89</v>
       </c>
       <c r="F378" s="19">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="G378" s="2"/>
       <c r="V378" s="3"/>
@@ -17027,10 +17034,10 @@
     <row r="379" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D379" s="3"/>
       <c r="E379" s="18" t="s">
-        <v>10</v>
+        <v>403</v>
       </c>
       <c r="F379" s="19">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="G379" s="2"/>
       <c r="V379" s="3"/>
@@ -17045,10 +17052,10 @@
     <row r="380" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D380" s="3"/>
       <c r="E380" s="18" t="s">
-        <v>404</v>
+        <v>10</v>
       </c>
       <c r="F380" s="19">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="G380" s="2"/>
       <c r="V380" s="3"/>
@@ -17063,10 +17070,10 @@
     <row r="381" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D381" s="3"/>
       <c r="E381" s="18" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F381" s="19">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="G381" s="2"/>
       <c r="V381" s="3"/>
@@ -17081,10 +17088,10 @@
     <row r="382" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D382" s="3"/>
       <c r="E382" s="18" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F382" s="19">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="G382" s="2"/>
       <c r="V382" s="3"/>
@@ -17099,10 +17106,10 @@
     <row r="383" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D383" s="3"/>
       <c r="E383" s="18" t="s">
-        <v>17</v>
+        <v>406</v>
       </c>
       <c r="F383" s="19">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="G383" s="2"/>
       <c r="V383" s="3"/>
@@ -17117,7 +17124,7 @@
     <row r="384" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D384" s="3"/>
       <c r="E384" s="18" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F384" s="19">
         <v>2018</v>
@@ -17135,10 +17142,10 @@
     <row r="385" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D385" s="3"/>
       <c r="E385" s="18" t="s">
-        <v>407</v>
+        <v>5</v>
       </c>
       <c r="F385" s="19">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="G385" s="2"/>
       <c r="V385" s="3"/>
@@ -17153,10 +17160,10 @@
     <row r="386" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D386" s="3"/>
       <c r="E386" s="18" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F386" s="19">
-        <v>1994</v>
+        <v>2013</v>
       </c>
       <c r="G386" s="2"/>
       <c r="V386" s="3"/>
@@ -17171,10 +17178,10 @@
     <row r="387" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D387" s="3"/>
       <c r="E387" s="18" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F387" s="19">
-        <v>2014</v>
+        <v>1994</v>
       </c>
       <c r="G387" s="2"/>
       <c r="V387" s="3"/>
@@ -17189,10 +17196,10 @@
     <row r="388" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D388" s="3"/>
       <c r="E388" s="18" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F388" s="19">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="G388" s="2"/>
       <c r="V388" s="3"/>
@@ -17207,10 +17214,10 @@
     <row r="389" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D389" s="3"/>
       <c r="E389" s="18" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F389" s="19">
-        <v>1999</v>
+        <v>2017</v>
       </c>
       <c r="G389" s="2"/>
       <c r="V389" s="3"/>
@@ -17225,10 +17232,10 @@
     <row r="390" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D390" s="3"/>
       <c r="E390" s="18" t="s">
-        <v>41</v>
+        <v>411</v>
       </c>
       <c r="F390" s="19">
-        <v>2019</v>
+        <v>1999</v>
       </c>
       <c r="G390" s="2"/>
       <c r="V390" s="3"/>
@@ -17243,7 +17250,7 @@
     <row r="391" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D391" s="3"/>
       <c r="E391" s="18" t="s">
-        <v>412</v>
+        <v>41</v>
       </c>
       <c r="F391" s="19">
         <v>2019</v>
@@ -17261,10 +17268,10 @@
     <row r="392" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D392" s="3"/>
       <c r="E392" s="18" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F392" s="19">
-        <v>1994</v>
+        <v>2019</v>
       </c>
       <c r="G392" s="3"/>
       <c r="V392" s="3"/>
@@ -17279,10 +17286,10 @@
     <row r="393" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D393" s="3"/>
       <c r="E393" s="18" t="s">
-        <v>51</v>
+        <v>413</v>
       </c>
       <c r="F393" s="19">
-        <v>2008</v>
+        <v>1994</v>
       </c>
       <c r="G393" s="3"/>
       <c r="V393" s="3"/>
@@ -17297,10 +17304,10 @@
     <row r="394" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D394" s="3"/>
       <c r="E394" s="18" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="F394" s="19">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="G394" s="3"/>
       <c r="V394" s="3"/>
@@ -17314,8 +17321,12 @@
     </row>
     <row r="395" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D395" s="3"/>
-      <c r="E395" s="3"/>
-      <c r="F395" s="3"/>
+      <c r="E395" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F395" s="19">
+        <v>2010</v>
+      </c>
       <c r="G395" s="3"/>
       <c r="V395" s="3"/>
       <c r="W395" s="36" t="s">
@@ -17327,6 +17338,10 @@
       <c r="Y395" s="3"/>
     </row>
     <row r="396" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D396" s="3"/>
+      <c r="E396" s="3"/>
+      <c r="F396" s="3"/>
+      <c r="G396" s="3"/>
       <c r="V396" s="3"/>
       <c r="W396" s="36" t="s">
         <v>767</v>

--- a/lists.xlsx
+++ b/lists.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/StatsAutomator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800D88E0-7169-1042-BBF6-3FD3FEF696AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF89E56-2E72-1A48-88BE-B9235F6E2279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17500" xr2:uid="{98AF27AA-E156-FB4B-94CA-68D339A0B8C2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2281" uniqueCount="1285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2312" uniqueCount="1283">
   <si>
     <t>Avatar</t>
   </si>
@@ -3860,9 +3860,6 @@
     <t>Terminator 2: Judgement Day</t>
   </si>
   <si>
-    <t>Drishyam</t>
-  </si>
-  <si>
     <t>The Wild Robot</t>
   </si>
   <si>
@@ -3881,16 +3878,13 @@
     <t>An Autumn Afternoon</t>
   </si>
   <si>
-    <t>Gangs of Wasseypur - Part 1</t>
-  </si>
-  <si>
-    <t>Laapataa Ladies</t>
-  </si>
-  <si>
     <t>Anora</t>
   </si>
   <si>
     <t>John Wick: Chapter 3 - Parabellum</t>
+  </si>
+  <si>
+    <t>The Substance</t>
   </si>
 </sst>
 </file>
@@ -4039,7 +4033,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4149,35 +4143,17 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color theme="1"/>
@@ -4607,7 +4583,7 @@
     <col min="8" max="8" width="41.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="2.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="2.6640625" style="1" customWidth="1"/>
     <col min="14" max="14" width="17.5" style="1" bestFit="1" customWidth="1"/>
@@ -4698,10 +4674,10 @@
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="25" t="s">
-        <v>1284</v>
+        <v>784</v>
       </c>
       <c r="F2" s="19">
-        <v>2019</v>
+        <v>2006</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="10" t="s">
@@ -4759,10 +4735,10 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="25" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="F3" s="19">
-        <v>2007</v>
+        <v>2018</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="10" t="s">
@@ -4820,10 +4796,10 @@
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="25" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="F4" s="19">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="10" t="s">
@@ -4881,10 +4857,10 @@
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="25" t="s">
-        <v>779</v>
+        <v>679</v>
       </c>
       <c r="F5" s="19">
-        <v>1999</v>
+        <v>2023</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="10" t="s">
@@ -4942,10 +4918,10 @@
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="25" t="s">
-        <v>770</v>
+        <v>1282</v>
       </c>
       <c r="F6" s="19">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="10" t="s">
@@ -4962,8 +4938,12 @@
         <v>2010</v>
       </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
+      <c r="N6" s="37" t="s">
+        <v>406</v>
+      </c>
+      <c r="O6" s="38">
+        <v>2014</v>
+      </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="18" t="s">
         <v>106</v>
@@ -4999,10 +4979,10 @@
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="25" t="s">
-        <v>30</v>
+        <v>781</v>
       </c>
       <c r="F7" s="19">
-        <v>2018</v>
+        <v>2007</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="10" t="s">
@@ -5019,6 +4999,8 @@
         <v>2014</v>
       </c>
       <c r="M7" s="2"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="18" t="s">
         <v>229</v>
@@ -5054,10 +5036,10 @@
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="25" t="s">
-        <v>767</v>
+        <v>778</v>
       </c>
       <c r="F8" s="19">
-        <v>2018</v>
+        <v>2000</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="10" t="s">
@@ -5109,10 +5091,10 @@
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="25" t="s">
-        <v>763</v>
+        <v>464</v>
       </c>
       <c r="F9" s="19">
-        <v>2021</v>
+        <v>1987</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="10" t="s">
@@ -5164,10 +5146,10 @@
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="25" t="s">
-        <v>849</v>
+        <v>55</v>
       </c>
       <c r="F10" s="19">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="10" t="s">
@@ -5219,10 +5201,10 @@
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="25" t="s">
-        <v>764</v>
+        <v>812</v>
       </c>
       <c r="F11" s="19">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="10" t="s">
@@ -5274,10 +5256,10 @@
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="25" t="s">
-        <v>765</v>
+        <v>22</v>
       </c>
       <c r="F12" s="19">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="10" t="s">
@@ -5329,10 +5311,10 @@
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="25" t="s">
-        <v>1273</v>
+        <v>775</v>
       </c>
       <c r="F13" s="19">
-        <v>1991</v>
+        <v>2009</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="10" t="s">
@@ -5384,10 +5366,10 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="25" t="s">
-        <v>487</v>
+        <v>780</v>
       </c>
       <c r="F14" s="19">
-        <v>1982</v>
+        <v>2011</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="10" t="s">
@@ -5439,10 +5421,10 @@
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="25" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="F15" s="19">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="10" t="s">
@@ -5494,10 +5476,10 @@
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="25" t="s">
-        <v>1279</v>
+        <v>774</v>
       </c>
       <c r="F16" s="19">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="10" t="s">
@@ -5549,10 +5531,10 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="25" t="s">
-        <v>756</v>
+        <v>785</v>
       </c>
       <c r="F17" s="19">
-        <v>2003</v>
+        <v>2022</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="10" t="s">
@@ -5604,10 +5586,10 @@
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="25" t="s">
-        <v>59</v>
+        <v>771</v>
       </c>
       <c r="F18" s="19">
-        <v>2013</v>
+        <v>2006</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="10" t="s">
@@ -5659,10 +5641,10 @@
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="25" t="s">
-        <v>100</v>
+        <v>769</v>
       </c>
       <c r="F19" s="19">
-        <v>1987</v>
+        <v>2018</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="10" t="s">
@@ -5714,10 +5696,10 @@
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="25" t="s">
-        <v>101</v>
+        <v>1281</v>
       </c>
       <c r="F20" s="19">
-        <v>1989</v>
+        <v>2019</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="10" t="s">
@@ -5769,10 +5751,10 @@
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="25" t="s">
-        <v>102</v>
+        <v>766</v>
       </c>
       <c r="F21" s="19">
-        <v>1989</v>
+        <v>2007</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="10" t="s">
@@ -5824,10 +5806,10 @@
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="25" t="s">
-        <v>103</v>
+        <v>772</v>
       </c>
       <c r="F22" s="19">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="10" t="s">
@@ -5879,10 +5861,10 @@
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="25" t="s">
-        <v>104</v>
+        <v>779</v>
       </c>
       <c r="F23" s="19">
-        <v>2007</v>
+        <v>1999</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="10" t="s">
@@ -5934,10 +5916,10 @@
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="25" t="s">
-        <v>105</v>
+        <v>770</v>
       </c>
       <c r="F24" s="19">
-        <v>1990</v>
+        <v>2018</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="10" t="s">
@@ -5963,7 +5945,7 @@
       </c>
       <c r="S24" s="4"/>
       <c r="T24" s="13" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="U24" s="12">
         <v>2024</v>
@@ -5989,10 +5971,10 @@
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="25" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="F25" s="19">
-        <v>1957</v>
+        <v>2018</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="10" t="s">
@@ -6044,10 +6026,10 @@
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="25" t="s">
-        <v>107</v>
+        <v>767</v>
       </c>
       <c r="F26" s="19">
-        <v>1993</v>
+        <v>2018</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="10" t="s">
@@ -6099,10 +6081,10 @@
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="25" t="s">
-        <v>108</v>
+        <v>763</v>
       </c>
       <c r="F27" s="19">
-        <v>2009</v>
+        <v>2021</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="10" t="s">
@@ -6154,10 +6136,10 @@
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="25" t="s">
-        <v>109</v>
+        <v>849</v>
       </c>
       <c r="F28" s="19">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="10" t="s">
@@ -6209,10 +6191,10 @@
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="25" t="s">
-        <v>110</v>
+        <v>764</v>
       </c>
       <c r="F29" s="19">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="10" t="s">
@@ -6264,10 +6246,10 @@
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="25" t="s">
-        <v>111</v>
+        <v>765</v>
       </c>
       <c r="F30" s="19">
-        <v>1999</v>
+        <v>2010</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="10" t="s">
@@ -6319,10 +6301,10 @@
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="25" t="s">
-        <v>25</v>
+        <v>1273</v>
       </c>
       <c r="F31" s="19">
-        <v>2024</v>
+        <v>1991</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="10" t="s">
@@ -6374,10 +6356,10 @@
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="25" t="s">
-        <v>112</v>
+        <v>487</v>
       </c>
       <c r="F32" s="19">
-        <v>2009</v>
+        <v>1982</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="10" t="s">
@@ -6429,10 +6411,10 @@
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="25" t="s">
-        <v>113</v>
+        <v>762</v>
       </c>
       <c r="F33" s="19">
-        <v>1994</v>
+        <v>2014</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="10" t="s">
@@ -6442,8 +6424,12 @@
         <v>1995</v>
       </c>
       <c r="J33" s="2"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
+      <c r="K33" s="33" t="s">
+        <v>403</v>
+      </c>
+      <c r="L33" s="34">
+        <v>2016</v>
+      </c>
       <c r="M33" s="3"/>
       <c r="P33" s="3"/>
       <c r="Q33" s="18" t="s">
@@ -6480,10 +6466,10 @@
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="25" t="s">
-        <v>114</v>
+        <v>1278</v>
       </c>
       <c r="F34" s="19">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="10" t="s">
@@ -6493,6 +6479,13 @@
         <v>2001</v>
       </c>
       <c r="J34" s="2"/>
+      <c r="K34" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="L34" s="34">
+        <v>2023</v>
+      </c>
+      <c r="M34" s="3"/>
       <c r="P34" s="3"/>
       <c r="Q34" s="18" t="s">
         <v>412</v>
@@ -6528,10 +6521,10 @@
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="25" t="s">
-        <v>115</v>
+        <v>756</v>
       </c>
       <c r="F35" s="19">
-        <v>2018</v>
+        <v>2003</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="10" t="s">
@@ -6541,6 +6534,13 @@
         <v>2008</v>
       </c>
       <c r="J35" s="2"/>
+      <c r="K35" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="L35" s="34">
+        <v>2001</v>
+      </c>
+      <c r="M35" s="3"/>
       <c r="P35" s="3"/>
       <c r="Q35" s="18" t="s">
         <v>239</v>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="25" t="s">
-        <v>116</v>
+        <v>59</v>
       </c>
       <c r="F36" s="19">
         <v>2013</v>
@@ -6589,6 +6589,9 @@
         <v>1997</v>
       </c>
       <c r="J36" s="2"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
       <c r="P36" s="3"/>
       <c r="Q36" s="18" t="s">
         <v>228</v>
@@ -6624,10 +6627,10 @@
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="25" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="F37" s="19">
-        <v>1973</v>
+        <v>1987</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="10" t="s">
@@ -6672,10 +6675,10 @@
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="25" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F38" s="19">
-        <v>2004</v>
+        <v>1989</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="10" t="s">
@@ -6720,10 +6723,10 @@
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="25" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="F39" s="19">
-        <v>2004</v>
+        <v>1989</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="10" t="s">
@@ -6768,10 +6771,10 @@
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="25" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="F40" s="19">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="10" t="s">
@@ -6816,10 +6819,10 @@
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="25" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="F41" s="19">
-        <v>1984</v>
+        <v>2007</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="10" t="s">
@@ -6864,10 +6867,10 @@
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="25" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="F42" s="19">
-        <v>2008</v>
+        <v>1990</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="10" t="s">
@@ -6912,10 +6915,10 @@
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="25" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="F43" s="19">
-        <v>2022</v>
+        <v>1957</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="10" t="s">
@@ -6960,10 +6963,10 @@
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="25" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="F44" s="19">
-        <v>2022</v>
+        <v>1993</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="10" t="s">
@@ -7008,10 +7011,10 @@
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="25" t="s">
-        <v>9</v>
+        <v>108</v>
       </c>
       <c r="F45" s="19">
-        <v>2024</v>
+        <v>2009</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="10" t="s">
@@ -7056,10 +7059,10 @@
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="25" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="F46" s="19">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="10" t="s">
@@ -7104,10 +7107,10 @@
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="25" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="F47" s="19">
-        <v>2023</v>
+        <v>2011</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="10" t="s">
@@ -7152,10 +7155,10 @@
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="25" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="F48" s="19">
-        <v>2023</v>
+        <v>1999</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="10" t="s">
@@ -7200,10 +7203,10 @@
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="25" t="s">
-        <v>128</v>
+        <v>25</v>
       </c>
       <c r="F49" s="19">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="10" t="s">
@@ -7248,10 +7251,10 @@
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="25" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="F50" s="19">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="10" t="s">
@@ -7296,10 +7299,10 @@
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="25" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="F51" s="19">
-        <v>2003</v>
+        <v>1994</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="10" t="s">
@@ -7344,10 +7347,10 @@
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="25" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="F52" s="19">
-        <v>1995</v>
+        <v>2011</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="10" t="s">
@@ -7392,10 +7395,10 @@
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="25" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="F53" s="19">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="10" t="s">
@@ -7440,10 +7443,10 @@
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="25" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="F54" s="19">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="10" t="s">
@@ -7488,10 +7491,10 @@
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="25" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="F55" s="19">
-        <v>1995</v>
+        <v>1973</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="10" t="s">
@@ -7536,10 +7539,10 @@
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="25" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="F56" s="19">
-        <v>2022</v>
+        <v>2004</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="10" t="s">
@@ -7584,10 +7587,10 @@
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="25" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="F57" s="19">
-        <v>1999</v>
+        <v>2004</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="10" t="s">
@@ -7632,10 +7635,10 @@
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="25" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="F58" s="19">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="10" t="s">
@@ -7680,10 +7683,10 @@
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="25" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="F59" s="19">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="10" t="s">
@@ -7728,10 +7731,10 @@
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="25" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="F60" s="19">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="10" t="s">
@@ -7776,10 +7779,10 @@
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="25" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="F61" s="19">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="10" t="s">
@@ -7824,10 +7827,10 @@
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="25" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="F62" s="19">
-        <v>1997</v>
+        <v>2022</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="10" t="s">
@@ -7872,7 +7875,7 @@
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="25" t="s">
-        <v>142</v>
+        <v>9</v>
       </c>
       <c r="F63" s="19">
         <v>2024</v>
@@ -7920,10 +7923,10 @@
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="25" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="F64" s="19">
-        <v>2016</v>
+        <v>2002</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="10" t="s">
@@ -7968,10 +7971,10 @@
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="25" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="F65" s="19">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="10" t="s">
@@ -8016,10 +8019,10 @@
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="25" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="F66" s="19">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="10" t="s">
@@ -8064,10 +8067,10 @@
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="25" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="F67" s="19">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="10" t="s">
@@ -8112,10 +8115,10 @@
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="25" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="F68" s="19">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="G68" s="4"/>
       <c r="H68" s="10" t="s">
@@ -8160,10 +8163,10 @@
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="25" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="F69" s="19">
-        <v>2023</v>
+        <v>2003</v>
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="10" t="s">
@@ -8208,10 +8211,10 @@
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="25" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="F70" s="19">
-        <v>2023</v>
+        <v>1995</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="10" t="s">
@@ -8256,10 +8259,10 @@
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="25" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="F71" s="19">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="10" t="s">
@@ -8304,10 +8307,10 @@
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="25" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="F72" s="19">
-        <v>2013</v>
+        <v>2007</v>
       </c>
       <c r="G72" s="4"/>
       <c r="H72" s="10" t="s">
@@ -8352,10 +8355,10 @@
       </c>
       <c r="D73" s="3"/>
       <c r="E73" s="25" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="F73" s="19">
-        <v>2020</v>
+        <v>1995</v>
       </c>
       <c r="G73" s="4"/>
       <c r="H73" s="10" t="s">
@@ -8400,10 +8403,10 @@
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="25" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="F74" s="19">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="10" t="s">
@@ -8448,10 +8451,10 @@
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="25" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="F75" s="19">
-        <v>2021</v>
+        <v>1999</v>
       </c>
       <c r="G75" s="4"/>
       <c r="H75" s="10" t="s">
@@ -8496,10 +8499,10 @@
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="25" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="F76" s="19">
-        <v>2009</v>
+        <v>2023</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="10" t="s">
@@ -8544,10 +8547,10 @@
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="25" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="F77" s="19">
-        <v>1996</v>
+        <v>1986</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="10" t="s">
@@ -8592,10 +8595,10 @@
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="25" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="F78" s="19">
-        <v>1998</v>
+        <v>2005</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="10" t="s">
@@ -8640,10 +8643,10 @@
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="25" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="F79" s="19">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="10" t="s">
@@ -8688,10 +8691,10 @@
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="25" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="F80" s="19">
-        <v>2022</v>
+        <v>1997</v>
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="10" t="s">
@@ -8736,10 +8739,10 @@
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="25" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="F81" s="19">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="10" t="s">
@@ -8784,10 +8787,10 @@
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="25" t="s">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="F82" s="19">
-        <v>1978</v>
+        <v>2016</v>
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="10" t="s">
@@ -8832,10 +8835,10 @@
       </c>
       <c r="D83" s="2"/>
       <c r="E83" s="25" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="F83" s="19">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="G83" s="4"/>
       <c r="H83" s="10" t="s">
@@ -8880,10 +8883,10 @@
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="25" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="F84" s="19">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="10" t="s">
@@ -8928,10 +8931,10 @@
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="25" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="F85" s="19">
-        <v>1989</v>
+        <v>2023</v>
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="10" t="s">
@@ -8976,10 +8979,10 @@
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="25" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="F86" s="19">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="10" t="s">
@@ -9024,10 +9027,10 @@
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="25" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="F87" s="19">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="10" t="s">
@@ -9072,10 +9075,10 @@
       </c>
       <c r="D88" s="2"/>
       <c r="E88" s="25" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="F88" s="19">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="10" t="s">
@@ -9120,7 +9123,7 @@
       </c>
       <c r="D89" s="2"/>
       <c r="E89" s="25" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="F89" s="19">
         <v>2022</v>
@@ -9168,10 +9171,10 @@
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="25" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="F90" s="19">
-        <v>2006</v>
+        <v>2013</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="10" t="s">
@@ -9216,10 +9219,10 @@
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="25" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="F91" s="19">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="10" t="s">
@@ -9264,10 +9267,10 @@
       </c>
       <c r="D92" s="2"/>
       <c r="E92" s="25" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="F92" s="19">
-        <v>2016</v>
+        <v>2007</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="10" t="s">
@@ -9312,10 +9315,10 @@
       </c>
       <c r="D93" s="2"/>
       <c r="E93" s="25" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="F93" s="19">
-        <v>1996</v>
+        <v>2021</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="10" t="s">
@@ -9360,10 +9363,10 @@
       </c>
       <c r="D94" s="2"/>
       <c r="E94" s="25" t="s">
-        <v>58</v>
+        <v>154</v>
       </c>
       <c r="F94" s="19">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="10" t="s">
@@ -9408,10 +9411,10 @@
       </c>
       <c r="D95" s="2"/>
       <c r="E95" s="25" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="F95" s="19">
-        <v>2021</v>
+        <v>1996</v>
       </c>
       <c r="G95" s="4"/>
       <c r="H95" s="10" t="s">
@@ -9456,10 +9459,10 @@
       </c>
       <c r="D96" s="2"/>
       <c r="E96" s="25" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="F96" s="19">
-        <v>2022</v>
+        <v>1998</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="10" t="s">
@@ -9504,10 +9507,10 @@
       </c>
       <c r="D97" s="2"/>
       <c r="E97" s="25" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="F97" s="19">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="10" t="s">
@@ -9552,10 +9555,10 @@
       </c>
       <c r="D98" s="2"/>
       <c r="E98" s="25" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="F98" s="19">
-        <v>2001</v>
+        <v>2022</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="10" t="s">
@@ -9600,10 +9603,10 @@
       </c>
       <c r="D99" s="2"/>
       <c r="E99" s="25" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="F99" s="19">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="10" t="s">
@@ -9648,10 +9651,10 @@
       </c>
       <c r="D100" s="2"/>
       <c r="E100" s="25" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="F100" s="19">
-        <v>2023</v>
+        <v>1978</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="10" t="s">
@@ -9696,10 +9699,10 @@
       </c>
       <c r="D101" s="2"/>
       <c r="E101" s="25" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="F101" s="19">
-        <v>2017</v>
+        <v>2000</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="10" t="s">
@@ -9738,10 +9741,10 @@
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="25" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="F102" s="19">
-        <v>1988</v>
+        <v>2003</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="10" t="s">
@@ -9777,10 +9780,10 @@
     <row r="103" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D103" s="3"/>
       <c r="E103" s="25" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="F103" s="19">
-        <v>2002</v>
+        <v>1989</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="10" t="s">
@@ -9816,10 +9819,10 @@
     <row r="104" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D104" s="3"/>
       <c r="E104" s="25" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="F104" s="19">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="10" t="s">
@@ -9855,10 +9858,10 @@
     <row r="105" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D105" s="3"/>
       <c r="E105" s="25" t="s">
-        <v>181</v>
+        <v>87</v>
       </c>
       <c r="F105" s="19">
-        <v>2008</v>
+        <v>2022</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="10" t="s">
@@ -9894,10 +9897,10 @@
     <row r="106" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D106" s="3"/>
       <c r="E106" s="25" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="F106" s="19">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="10" t="s">
@@ -9933,10 +9936,10 @@
     <row r="107" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D107" s="3"/>
       <c r="E107" s="25" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="F107" s="19">
-        <v>1998</v>
+        <v>2022</v>
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="10" t="s">
@@ -9972,10 +9975,10 @@
     <row r="108" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D108" s="3"/>
       <c r="E108" s="25" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="F108" s="19">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="10" t="s">
@@ -10011,10 +10014,10 @@
     <row r="109" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D109" s="3"/>
       <c r="E109" s="25" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="F109" s="19">
-        <v>2010</v>
+        <v>2021</v>
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="10" t="s">
@@ -10050,10 +10053,10 @@
     <row r="110" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D110" s="3"/>
       <c r="E110" s="25" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F110" s="19">
-        <v>2000</v>
+        <v>2016</v>
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="10" t="s">
@@ -10089,10 +10092,10 @@
     <row r="111" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D111" s="3"/>
       <c r="E111" s="25" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="F111" s="19">
-        <v>2014</v>
+        <v>1996</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="10" t="s">
@@ -10128,10 +10131,10 @@
     <row r="112" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D112" s="3"/>
       <c r="E112" s="25" t="s">
-        <v>187</v>
+        <v>58</v>
       </c>
       <c r="F112" s="19">
-        <v>1978</v>
+        <v>2007</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="10" t="s">
@@ -10167,10 +10170,10 @@
     <row r="113" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D113" s="3"/>
       <c r="E113" s="25" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="F113" s="19">
-        <v>2005</v>
+        <v>2021</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="10" t="s">
@@ -10206,10 +10209,10 @@
     <row r="114" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D114" s="3"/>
       <c r="E114" s="25" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="F114" s="19">
-        <v>1974</v>
+        <v>2022</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="10" t="s">
@@ -10245,10 +10248,10 @@
     <row r="115" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D115" s="3"/>
       <c r="E115" s="25" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="F115" s="19">
-        <v>2003</v>
+        <v>2011</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="10" t="s">
@@ -10284,10 +10287,10 @@
     <row r="116" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D116" s="3"/>
       <c r="E116" s="25" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="F116" s="19">
-        <v>1983</v>
+        <v>2001</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="10" t="s">
@@ -10322,11 +10325,11 @@
     </row>
     <row r="117" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D117" s="3"/>
-      <c r="E117" s="18" t="s">
-        <v>192</v>
+      <c r="E117" s="25" t="s">
+        <v>175</v>
       </c>
       <c r="F117" s="19">
-        <v>1992</v>
+        <v>2005</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="10" t="s">
@@ -10361,11 +10364,11 @@
     </row>
     <row r="118" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D118" s="3"/>
-      <c r="E118" s="18" t="s">
-        <v>193</v>
+      <c r="E118" s="25" t="s">
+        <v>176</v>
       </c>
       <c r="F118" s="19">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="10" t="s">
@@ -10400,8 +10403,8 @@
     </row>
     <row r="119" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D119" s="3"/>
-      <c r="E119" s="18" t="s">
-        <v>194</v>
+      <c r="E119" s="25" t="s">
+        <v>177</v>
       </c>
       <c r="F119" s="19">
         <v>2017</v>
@@ -10439,11 +10442,11 @@
     </row>
     <row r="120" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D120" s="3"/>
-      <c r="E120" s="18" t="s">
-        <v>195</v>
+      <c r="E120" s="25" t="s">
+        <v>178</v>
       </c>
       <c r="F120" s="19">
-        <v>2022</v>
+        <v>1988</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="10" t="s">
@@ -10478,11 +10481,11 @@
     </row>
     <row r="121" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D121" s="3"/>
-      <c r="E121" s="18" t="s">
-        <v>196</v>
+      <c r="E121" s="25" t="s">
+        <v>179</v>
       </c>
       <c r="F121" s="19">
-        <v>2018</v>
+        <v>2002</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="10" t="s">
@@ -10517,11 +10520,11 @@
     </row>
     <row r="122" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D122" s="3"/>
-      <c r="E122" s="18" t="s">
-        <v>16</v>
+      <c r="E122" s="25" t="s">
+        <v>180</v>
       </c>
       <c r="F122" s="19">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="10" t="s">
@@ -10556,11 +10559,11 @@
     </row>
     <row r="123" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D123" s="3"/>
-      <c r="E123" s="18" t="s">
-        <v>197</v>
+      <c r="E123" s="25" t="s">
+        <v>181</v>
       </c>
       <c r="F123" s="19">
-        <v>1988</v>
+        <v>2008</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="10" t="s">
@@ -10595,11 +10598,11 @@
     </row>
     <row r="124" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D124" s="3"/>
-      <c r="E124" s="18" t="s">
-        <v>198</v>
+      <c r="E124" s="25" t="s">
+        <v>57</v>
       </c>
       <c r="F124" s="19">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="10" t="s">
@@ -10634,11 +10637,11 @@
     </row>
     <row r="125" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D125" s="3"/>
-      <c r="E125" s="18" t="s">
-        <v>199</v>
+      <c r="E125" s="25" t="s">
+        <v>182</v>
       </c>
       <c r="F125" s="19">
-        <v>2012</v>
+        <v>1998</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="10" t="s">
@@ -10673,11 +10676,11 @@
     </row>
     <row r="126" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D126" s="3"/>
-      <c r="E126" s="18" t="s">
-        <v>200</v>
+      <c r="E126" s="25" t="s">
+        <v>183</v>
       </c>
       <c r="F126" s="19">
-        <v>1996</v>
+        <v>2004</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="10" t="s">
@@ -10712,11 +10715,11 @@
     </row>
     <row r="127" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D127" s="3"/>
-      <c r="E127" s="18" t="s">
-        <v>22</v>
+      <c r="E127" s="25" t="s">
+        <v>184</v>
       </c>
       <c r="F127" s="19">
-        <v>1991</v>
+        <v>2010</v>
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="1" t="s">
@@ -10751,11 +10754,11 @@
     </row>
     <row r="128" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D128" s="3"/>
-      <c r="E128" s="18" t="s">
-        <v>201</v>
+      <c r="E128" s="25" t="s">
+        <v>185</v>
       </c>
       <c r="F128" s="19">
-        <v>2018</v>
+        <v>2000</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="1" t="s">
@@ -10790,11 +10793,11 @@
     </row>
     <row r="129" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D129" s="3"/>
-      <c r="E129" s="18" t="s">
-        <v>202</v>
+      <c r="E129" s="25" t="s">
+        <v>186</v>
       </c>
       <c r="F129" s="19">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="1" t="s">
@@ -10829,11 +10832,11 @@
     </row>
     <row r="130" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D130" s="3"/>
-      <c r="E130" s="18" t="s">
-        <v>203</v>
+      <c r="E130" s="25" t="s">
+        <v>187</v>
       </c>
       <c r="F130" s="19">
-        <v>1999</v>
+        <v>1978</v>
       </c>
       <c r="G130" s="2"/>
       <c r="H130" s="1" t="s">
@@ -10868,11 +10871,11 @@
     </row>
     <row r="131" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D131" s="3"/>
-      <c r="E131" s="18" t="s">
-        <v>204</v>
+      <c r="E131" s="25" t="s">
+        <v>188</v>
       </c>
       <c r="F131" s="19">
-        <v>2012</v>
+        <v>2005</v>
       </c>
       <c r="G131" s="2"/>
       <c r="H131" s="1" t="s">
@@ -10907,15 +10910,19 @@
     </row>
     <row r="132" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D132" s="3"/>
-      <c r="E132" s="18" t="s">
-        <v>205</v>
+      <c r="E132" s="25" t="s">
+        <v>189</v>
       </c>
       <c r="F132" s="19">
-        <v>1984</v>
+        <v>1974</v>
       </c>
       <c r="G132" s="2"/>
-      <c r="H132" s="3"/>
-      <c r="I132" s="3"/>
+      <c r="H132" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="I132" s="1">
+        <v>2011</v>
+      </c>
       <c r="J132" s="3"/>
       <c r="P132" s="3"/>
       <c r="Q132" s="18" t="s">
@@ -10942,13 +10949,20 @@
     </row>
     <row r="133" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D133" s="3"/>
-      <c r="E133" s="18" t="s">
-        <v>206</v>
+      <c r="E133" s="25" t="s">
+        <v>190</v>
       </c>
       <c r="F133" s="19">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="G133" s="2"/>
+      <c r="H133" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I133" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J133" s="3"/>
       <c r="P133" s="3"/>
       <c r="Q133" s="18" t="s">
         <v>478</v>
@@ -10974,13 +10988,20 @@
     </row>
     <row r="134" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D134" s="3"/>
-      <c r="E134" s="18" t="s">
-        <v>207</v>
+      <c r="E134" s="25" t="s">
+        <v>191</v>
       </c>
       <c r="F134" s="19">
-        <v>2021</v>
+        <v>1983</v>
       </c>
       <c r="G134" s="2"/>
+      <c r="H134" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I134" s="1">
+        <v>2004</v>
+      </c>
+      <c r="J134" s="3"/>
       <c r="P134" s="3"/>
       <c r="Q134" s="18" t="s">
         <v>479</v>
@@ -11007,12 +11028,19 @@
     <row r="135" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D135" s="3"/>
       <c r="E135" s="18" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="F135" s="19">
-        <v>2001</v>
+        <v>1992</v>
       </c>
       <c r="G135" s="2"/>
+      <c r="H135" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="I135" s="1">
+        <v>2015</v>
+      </c>
+      <c r="J135" s="3"/>
       <c r="P135" s="3"/>
       <c r="Q135" s="18" t="s">
         <v>480</v>
@@ -11039,12 +11067,19 @@
     <row r="136" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D136" s="3"/>
       <c r="E136" s="18" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="F136" s="19">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="G136" s="2"/>
+      <c r="H136" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I136" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J136" s="3"/>
       <c r="P136" s="3"/>
       <c r="Q136" s="18" t="s">
         <v>481</v>
@@ -11071,12 +11106,19 @@
     <row r="137" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D137" s="3"/>
       <c r="E137" s="18" t="s">
-        <v>34</v>
+        <v>194</v>
       </c>
       <c r="F137" s="19">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="G137" s="2"/>
+      <c r="H137" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="I137" s="1">
+        <v>2007</v>
+      </c>
+      <c r="J137" s="3"/>
       <c r="P137" s="3"/>
       <c r="Q137" s="18" t="s">
         <v>392</v>
@@ -11103,12 +11145,19 @@
     <row r="138" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D138" s="3"/>
       <c r="E138" s="18" t="s">
-        <v>50</v>
+        <v>195</v>
       </c>
       <c r="F138" s="19">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="G138" s="2"/>
+      <c r="H138" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="I138" s="1">
+        <v>2017</v>
+      </c>
+      <c r="J138" s="3"/>
       <c r="P138" s="3"/>
       <c r="Q138" s="18" t="s">
         <v>482</v>
@@ -11135,12 +11184,19 @@
     <row r="139" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D139" s="3"/>
       <c r="E139" s="18" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="F139" s="19">
-        <v>2005</v>
+        <v>2018</v>
       </c>
       <c r="G139" s="2"/>
+      <c r="H139" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I139" s="1">
+        <v>2017</v>
+      </c>
+      <c r="J139" s="3"/>
       <c r="P139" s="3"/>
       <c r="Q139" s="18" t="s">
         <v>483</v>
@@ -11167,12 +11223,19 @@
     <row r="140" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D140" s="3"/>
       <c r="E140" s="18" t="s">
-        <v>211</v>
+        <v>16</v>
       </c>
       <c r="F140" s="19">
-        <v>1997</v>
+        <v>2023</v>
       </c>
       <c r="G140" s="2"/>
+      <c r="H140" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I140" s="1">
+        <v>2016</v>
+      </c>
+      <c r="J140" s="3"/>
       <c r="P140" s="3"/>
       <c r="Q140" s="18" t="s">
         <v>363</v>
@@ -11199,12 +11262,15 @@
     <row r="141" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D141" s="3"/>
       <c r="E141" s="18" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F141" s="19">
-        <v>1997</v>
+        <v>1988</v>
       </c>
       <c r="G141" s="2"/>
+      <c r="H141" s="3"/>
+      <c r="I141" s="3"/>
+      <c r="J141" s="3"/>
       <c r="P141" s="3"/>
       <c r="Q141" s="18" t="s">
         <v>133</v>
@@ -11231,10 +11297,10 @@
     <row r="142" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D142" s="3"/>
       <c r="E142" s="18" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="F142" s="19">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="G142" s="2"/>
       <c r="P142" s="3"/>
@@ -11263,10 +11329,10 @@
     <row r="143" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D143" s="3"/>
       <c r="E143" s="18" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="F143" s="19">
-        <v>1989</v>
+        <v>2012</v>
       </c>
       <c r="G143" s="2"/>
       <c r="P143" s="3"/>
@@ -11295,10 +11361,10 @@
     <row r="144" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D144" s="3"/>
       <c r="E144" s="18" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="F144" s="19">
-        <v>2018</v>
+        <v>1996</v>
       </c>
       <c r="G144" s="2"/>
       <c r="P144" s="3"/>
@@ -11327,10 +11393,10 @@
     <row r="145" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D145" s="3"/>
       <c r="E145" s="18" t="s">
-        <v>216</v>
+        <v>22</v>
       </c>
       <c r="F145" s="19">
-        <v>2001</v>
+        <v>1991</v>
       </c>
       <c r="G145" s="2"/>
       <c r="P145" s="3"/>
@@ -11359,10 +11425,10 @@
     <row r="146" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D146" s="3"/>
       <c r="E146" s="18" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="F146" s="19">
-        <v>2001</v>
+        <v>2018</v>
       </c>
       <c r="G146" s="2"/>
       <c r="P146" s="3"/>
@@ -11391,10 +11457,10 @@
     <row r="147" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D147" s="3"/>
       <c r="E147" s="18" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="F147" s="19">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="G147" s="2"/>
       <c r="P147" s="3"/>
@@ -11423,10 +11489,10 @@
     <row r="148" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D148" s="3"/>
       <c r="E148" s="18" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="F148" s="19">
-        <v>2012</v>
+        <v>1999</v>
       </c>
       <c r="G148" s="2"/>
       <c r="P148" s="3"/>
@@ -11455,10 +11521,10 @@
     <row r="149" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D149" s="3"/>
       <c r="E149" s="18" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="F149" s="19">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="G149" s="2"/>
       <c r="P149" s="3"/>
@@ -11487,10 +11553,10 @@
     <row r="150" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D150" s="3"/>
       <c r="E150" s="18" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="F150" s="19">
-        <v>2005</v>
+        <v>1984</v>
       </c>
       <c r="G150" s="2"/>
       <c r="P150" s="3"/>
@@ -11519,10 +11585,10 @@
     <row r="151" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D151" s="3"/>
       <c r="E151" s="18" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="F151" s="19">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="G151" s="2"/>
       <c r="P151" s="3"/>
@@ -11551,10 +11617,10 @@
     <row r="152" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D152" s="3"/>
       <c r="E152" s="18" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="F152" s="19">
-        <v>2000</v>
+        <v>2021</v>
       </c>
       <c r="G152" s="2"/>
       <c r="P152" s="3"/>
@@ -11583,10 +11649,10 @@
     <row r="153" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D153" s="3"/>
       <c r="E153" s="18" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="F153" s="19">
-        <v>2006</v>
+        <v>2001</v>
       </c>
       <c r="G153" s="2"/>
       <c r="P153" s="3"/>
@@ -11615,10 +11681,10 @@
     <row r="154" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D154" s="3"/>
       <c r="E154" s="18" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="F154" s="19">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="G154" s="2"/>
       <c r="P154" s="3"/>
@@ -11647,10 +11713,10 @@
     <row r="155" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D155" s="3"/>
       <c r="E155" s="18" t="s">
-        <v>226</v>
+        <v>34</v>
       </c>
       <c r="F155" s="19">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="G155" s="2"/>
       <c r="P155" s="3"/>
@@ -11679,7 +11745,7 @@
     <row r="156" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D156" s="3"/>
       <c r="E156" s="18" t="s">
-        <v>227</v>
+        <v>50</v>
       </c>
       <c r="F156" s="19">
         <v>2012</v>
@@ -11711,10 +11777,10 @@
     <row r="157" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D157" s="3"/>
       <c r="E157" s="18" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="F157" s="19">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="G157" s="2"/>
       <c r="P157" s="3"/>
@@ -11743,10 +11809,10 @@
     <row r="158" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D158" s="3"/>
       <c r="E158" s="18" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="F158" s="19">
-        <v>1993</v>
+        <v>1997</v>
       </c>
       <c r="G158" s="2"/>
       <c r="P158" s="3"/>
@@ -11775,10 +11841,10 @@
     <row r="159" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D159" s="3"/>
       <c r="E159" s="18" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="F159" s="19">
-        <v>2004</v>
+        <v>1997</v>
       </c>
       <c r="G159" s="2"/>
       <c r="P159" s="3"/>
@@ -11807,10 +11873,10 @@
     <row r="160" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D160" s="3"/>
       <c r="E160" s="18" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="F160" s="19">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="G160" s="2"/>
       <c r="P160" s="3"/>
@@ -11839,10 +11905,10 @@
     <row r="161" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D161" s="3"/>
       <c r="E161" s="18" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="F161" s="19">
-        <v>2013</v>
+        <v>1989</v>
       </c>
       <c r="G161" s="2"/>
       <c r="P161" s="3"/>
@@ -11871,10 +11937,10 @@
     <row r="162" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D162" s="3"/>
       <c r="E162" s="18" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="F162" s="19">
-        <v>2005</v>
+        <v>2018</v>
       </c>
       <c r="G162" s="2"/>
       <c r="P162" s="3"/>
@@ -11903,10 +11969,10 @@
     <row r="163" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D163" s="3"/>
       <c r="E163" s="18" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="F163" s="19">
-        <v>2022</v>
+        <v>2001</v>
       </c>
       <c r="G163" s="2"/>
       <c r="P163" s="3"/>
@@ -11935,10 +12001,10 @@
     <row r="164" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D164" s="3"/>
       <c r="E164" s="18" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="F164" s="19">
-        <v>2022</v>
+        <v>2001</v>
       </c>
       <c r="G164" s="2"/>
       <c r="P164" s="3"/>
@@ -11967,10 +12033,10 @@
     <row r="165" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D165" s="3"/>
       <c r="E165" s="18" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="F165" s="19">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="G165" s="2"/>
       <c r="P165" s="3"/>
@@ -11999,10 +12065,10 @@
     <row r="166" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D166" s="3"/>
       <c r="E166" s="18" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="F166" s="19">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G166" s="2"/>
       <c r="P166" s="3"/>
@@ -12031,10 +12097,10 @@
     <row r="167" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D167" s="3"/>
       <c r="E167" s="18" t="s">
-        <v>91</v>
+        <v>220</v>
       </c>
       <c r="F167" s="19">
-        <v>2023</v>
+        <v>2003</v>
       </c>
       <c r="G167" s="2"/>
       <c r="P167" s="3"/>
@@ -12063,10 +12129,10 @@
     <row r="168" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D168" s="3"/>
       <c r="E168" s="18" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="F168" s="19">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="G168" s="2"/>
       <c r="P168" s="3"/>
@@ -12095,10 +12161,10 @@
     <row r="169" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D169" s="3"/>
       <c r="E169" s="18" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="F169" s="19">
-        <v>1960</v>
+        <v>2010</v>
       </c>
       <c r="G169" s="2"/>
       <c r="P169" s="3"/>
@@ -12127,10 +12193,10 @@
     <row r="170" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D170" s="3"/>
       <c r="E170" s="18" t="s">
-        <v>86</v>
+        <v>223</v>
       </c>
       <c r="F170" s="19">
-        <v>2018</v>
+        <v>2000</v>
       </c>
       <c r="G170" s="2"/>
       <c r="P170" s="3"/>
@@ -12159,10 +12225,10 @@
     <row r="171" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D171" s="3"/>
       <c r="E171" s="18" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="F171" s="19">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="G171" s="2"/>
       <c r="P171" s="3"/>
@@ -12191,10 +12257,10 @@
     <row r="172" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D172" s="3"/>
       <c r="E172" s="18" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="F172" s="19">
-        <v>1998</v>
+        <v>2014</v>
       </c>
       <c r="G172" s="2"/>
       <c r="P172" s="3"/>
@@ -12223,10 +12289,10 @@
     <row r="173" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D173" s="3"/>
       <c r="E173" s="18" t="s">
-        <v>40</v>
+        <v>226</v>
       </c>
       <c r="F173" s="19">
-        <v>2006</v>
+        <v>2015</v>
       </c>
       <c r="G173" s="2"/>
       <c r="P173" s="3"/>
@@ -12255,10 +12321,10 @@
     <row r="174" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D174" s="3"/>
       <c r="E174" s="18" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="F174" s="19">
-        <v>1994</v>
+        <v>2012</v>
       </c>
       <c r="G174" s="2"/>
       <c r="P174" s="3"/>
@@ -12287,10 +12353,10 @@
     <row r="175" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D175" s="3"/>
       <c r="E175" s="18" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F175" s="19">
-        <v>2014</v>
+        <v>2000</v>
       </c>
       <c r="G175" s="2"/>
       <c r="P175" s="3"/>
@@ -12319,10 +12385,10 @@
     <row r="176" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D176" s="3"/>
       <c r="E176" s="18" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="F176" s="19">
-        <v>2006</v>
+        <v>1993</v>
       </c>
       <c r="G176" s="2"/>
       <c r="P176" s="3"/>
@@ -12351,10 +12417,10 @@
     <row r="177" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D177" s="3"/>
       <c r="E177" s="18" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="F177" s="19">
-        <v>1999</v>
+        <v>2004</v>
       </c>
       <c r="G177" s="2"/>
       <c r="P177" s="3"/>
@@ -12383,10 +12449,10 @@
     <row r="178" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D178" s="3"/>
       <c r="E178" s="18" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="F178" s="19">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="G178" s="2"/>
       <c r="P178" s="3"/>
@@ -12415,10 +12481,10 @@
     <row r="179" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D179" s="3"/>
       <c r="E179" s="18" t="s">
-        <v>44</v>
+        <v>232</v>
       </c>
       <c r="F179" s="19">
-        <v>1992</v>
+        <v>2013</v>
       </c>
       <c r="G179" s="2"/>
       <c r="P179" s="3"/>
@@ -12447,10 +12513,10 @@
     <row r="180" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D180" s="3"/>
       <c r="E180" s="18" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="F180" s="19">
-        <v>2014</v>
+        <v>2005</v>
       </c>
       <c r="G180" s="2"/>
       <c r="P180" s="3"/>
@@ -12479,10 +12545,10 @@
     <row r="181" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D181" s="3"/>
       <c r="E181" s="18" t="s">
-        <v>48</v>
+        <v>234</v>
       </c>
       <c r="F181" s="19">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="G181" s="2"/>
       <c r="P181" s="3"/>
@@ -12511,10 +12577,10 @@
     <row r="182" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D182" s="3"/>
       <c r="E182" s="18" t="s">
-        <v>54</v>
+        <v>235</v>
       </c>
       <c r="F182" s="19">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="G182" s="2"/>
       <c r="P182" s="3"/>
@@ -12543,10 +12609,10 @@
     <row r="183" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D183" s="3"/>
       <c r="E183" s="18" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="F183" s="19">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="G183" s="2"/>
       <c r="P183" s="3"/>
@@ -12575,10 +12641,10 @@
     <row r="184" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D184" s="3"/>
       <c r="E184" s="18" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F184" s="19">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="G184" s="2"/>
       <c r="P184" s="3"/>
@@ -12607,10 +12673,10 @@
     <row r="185" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D185" s="3"/>
       <c r="E185" s="18" t="s">
-        <v>250</v>
+        <v>91</v>
       </c>
       <c r="F185" s="19">
-        <v>2010</v>
+        <v>2023</v>
       </c>
       <c r="G185" s="2"/>
       <c r="P185" s="3"/>
@@ -12639,10 +12705,10 @@
     <row r="186" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D186" s="3"/>
       <c r="E186" s="18" t="s">
-        <v>37</v>
+        <v>238</v>
       </c>
       <c r="F186" s="19">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="G186" s="2"/>
       <c r="P186" s="3"/>
@@ -12671,10 +12737,10 @@
     <row r="187" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D187" s="3"/>
       <c r="E187" s="18" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="F187" s="19">
-        <v>1968</v>
+        <v>1960</v>
       </c>
       <c r="G187" s="2"/>
       <c r="P187" s="3"/>
@@ -12703,10 +12769,10 @@
     <row r="188" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D188" s="3"/>
       <c r="E188" s="18" t="s">
-        <v>252</v>
+        <v>86</v>
       </c>
       <c r="F188" s="19">
-        <v>2009</v>
+        <v>2018</v>
       </c>
       <c r="G188" s="2"/>
       <c r="P188" s="3"/>
@@ -12735,10 +12801,10 @@
     <row r="189" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D189" s="3"/>
       <c r="E189" s="18" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F189" s="19">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="G189" s="2"/>
       <c r="P189" s="3"/>
@@ -12767,10 +12833,10 @@
     <row r="190" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D190" s="3"/>
       <c r="E190" s="18" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F190" s="19">
-        <v>2002</v>
+        <v>1998</v>
       </c>
       <c r="G190" s="2"/>
       <c r="P190" s="3"/>
@@ -12799,10 +12865,10 @@
     <row r="191" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D191" s="3"/>
       <c r="E191" s="18" t="s">
-        <v>255</v>
+        <v>40</v>
       </c>
       <c r="F191" s="19">
-        <v>2021</v>
+        <v>2006</v>
       </c>
       <c r="G191" s="2"/>
       <c r="P191" s="3"/>
@@ -12831,10 +12897,10 @@
     <row r="192" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D192" s="3"/>
       <c r="E192" s="18" t="s">
-        <v>14</v>
+        <v>242</v>
       </c>
       <c r="F192" s="19">
-        <v>2023</v>
+        <v>1994</v>
       </c>
       <c r="G192" s="2"/>
       <c r="P192" s="3"/>
@@ -12863,10 +12929,10 @@
     <row r="193" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D193" s="3"/>
       <c r="E193" s="18" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F193" s="19">
-        <v>1998</v>
+        <v>2014</v>
       </c>
       <c r="G193" s="2"/>
       <c r="P193" s="3"/>
@@ -12895,10 +12961,10 @@
     <row r="194" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D194" s="3"/>
       <c r="E194" s="18" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="F194" s="19">
-        <v>2023</v>
+        <v>2006</v>
       </c>
       <c r="G194" s="2"/>
       <c r="P194" s="3"/>
@@ -12927,10 +12993,10 @@
     <row r="195" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D195" s="3"/>
       <c r="E195" s="18" t="s">
-        <v>49</v>
+        <v>245</v>
       </c>
       <c r="F195" s="19">
-        <v>2016</v>
+        <v>1999</v>
       </c>
       <c r="G195" s="2"/>
       <c r="P195" s="3"/>
@@ -12959,10 +13025,10 @@
     <row r="196" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D196" s="3"/>
       <c r="E196" s="18" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="F196" s="19">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="G196" s="2"/>
       <c r="P196" s="3"/>
@@ -12991,10 +13057,10 @@
     <row r="197" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D197" s="3"/>
       <c r="E197" s="18" t="s">
-        <v>259</v>
+        <v>44</v>
       </c>
       <c r="F197" s="19">
-        <v>2013</v>
+        <v>1992</v>
       </c>
       <c r="G197" s="2"/>
       <c r="P197" s="3"/>
@@ -13023,10 +13089,10 @@
     <row r="198" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D198" s="3"/>
       <c r="E198" s="18" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="F198" s="19">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="G198" s="2"/>
       <c r="P198" s="3"/>
@@ -13055,10 +13121,10 @@
     <row r="199" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D199" s="3"/>
       <c r="E199" s="18" t="s">
-        <v>261</v>
+        <v>48</v>
       </c>
       <c r="F199" s="19">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="G199" s="2"/>
       <c r="P199" s="3"/>
@@ -13087,10 +13153,10 @@
     <row r="200" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D200" s="3"/>
       <c r="E200" s="18" t="s">
-        <v>262</v>
+        <v>54</v>
       </c>
       <c r="F200" s="19">
-        <v>2003</v>
+        <v>2023</v>
       </c>
       <c r="G200" s="2"/>
       <c r="P200" s="3"/>
@@ -13119,10 +13185,10 @@
     <row r="201" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D201" s="3"/>
       <c r="E201" s="18" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="F201" s="19">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="G201" s="2"/>
       <c r="P201" s="3"/>
@@ -13151,10 +13217,10 @@
     <row r="202" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D202" s="3"/>
       <c r="E202" s="18" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="F202" s="19">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="G202" s="2"/>
       <c r="P202" s="3"/>
@@ -13183,10 +13249,10 @@
     <row r="203" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D203" s="3"/>
       <c r="E203" s="18" t="s">
-        <v>12</v>
+        <v>250</v>
       </c>
       <c r="F203" s="19">
-        <v>2022</v>
+        <v>2010</v>
       </c>
       <c r="G203" s="2"/>
       <c r="P203" s="3"/>
@@ -13215,10 +13281,10 @@
     <row r="204" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D204" s="3"/>
       <c r="E204" s="18" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="F204" s="19">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="G204" s="2"/>
       <c r="P204" s="3"/>
@@ -13247,10 +13313,10 @@
     <row r="205" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D205" s="3"/>
       <c r="E205" s="18" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="F205" s="19">
-        <v>1981</v>
+        <v>1968</v>
       </c>
       <c r="G205" s="2"/>
       <c r="P205" s="3"/>
@@ -13279,10 +13345,10 @@
     <row r="206" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D206" s="3"/>
       <c r="E206" s="18" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="F206" s="19">
-        <v>1996</v>
+        <v>2009</v>
       </c>
       <c r="G206" s="2"/>
       <c r="P206" s="3"/>
@@ -13311,10 +13377,10 @@
     <row r="207" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D207" s="3"/>
       <c r="E207" s="18" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="F207" s="19">
-        <v>2021</v>
+        <v>1998</v>
       </c>
       <c r="G207" s="2"/>
       <c r="P207" s="3"/>
@@ -13343,10 +13409,10 @@
     <row r="208" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D208" s="3"/>
       <c r="E208" s="18" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="F208" s="19">
-        <v>2018</v>
+        <v>2002</v>
       </c>
       <c r="G208" s="2"/>
       <c r="P208" s="3"/>
@@ -13375,10 +13441,10 @@
     <row r="209" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D209" s="3"/>
       <c r="E209" s="18" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="F209" s="19">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="G209" s="2"/>
       <c r="P209" s="3"/>
@@ -13407,10 +13473,10 @@
     <row r="210" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D210" s="3"/>
       <c r="E210" s="18" t="s">
-        <v>270</v>
+        <v>14</v>
       </c>
       <c r="F210" s="19">
-        <v>2014</v>
+        <v>2023</v>
       </c>
       <c r="G210" s="2"/>
       <c r="P210" s="3"/>
@@ -13439,10 +13505,10 @@
     <row r="211" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D211" s="3"/>
       <c r="E211" s="18" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="F211" s="19">
-        <v>2020</v>
+        <v>1998</v>
       </c>
       <c r="G211" s="2"/>
       <c r="P211" s="3"/>
@@ -13471,10 +13537,10 @@
     <row r="212" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D212" s="3"/>
       <c r="E212" s="18" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="F212" s="19">
-        <v>2008</v>
+        <v>2023</v>
       </c>
       <c r="G212" s="2"/>
       <c r="P212" s="3"/>
@@ -13503,10 +13569,10 @@
     <row r="213" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D213" s="3"/>
       <c r="E213" s="18" t="s">
-        <v>273</v>
+        <v>49</v>
       </c>
       <c r="F213" s="19">
-        <v>2007</v>
+        <v>2016</v>
       </c>
       <c r="G213" s="2"/>
       <c r="P213" s="3"/>
@@ -13535,10 +13601,10 @@
     <row r="214" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D214" s="3"/>
       <c r="E214" s="18" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="F214" s="19">
-        <v>2004</v>
+        <v>2012</v>
       </c>
       <c r="G214" s="2"/>
       <c r="P214" s="3"/>
@@ -13567,10 +13633,10 @@
     <row r="215" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D215" s="3"/>
       <c r="E215" s="18" t="s">
-        <v>7</v>
+        <v>259</v>
       </c>
       <c r="F215" s="19">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="G215" s="2"/>
       <c r="P215" s="3"/>
@@ -13599,10 +13665,10 @@
     <row r="216" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D216" s="3"/>
       <c r="E216" s="18" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="F216" s="19">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="G216" s="2"/>
       <c r="P216" s="3"/>
@@ -13631,10 +13697,10 @@
     <row r="217" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D217" s="3"/>
       <c r="E217" s="18" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="F217" s="19">
-        <v>1995</v>
+        <v>2019</v>
       </c>
       <c r="G217" s="2"/>
       <c r="P217" s="3"/>
@@ -13663,10 +13729,10 @@
     <row r="218" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D218" s="3"/>
       <c r="E218" s="18" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="F218" s="19">
-        <v>1971</v>
+        <v>2003</v>
       </c>
       <c r="G218" s="2"/>
       <c r="P218" s="3"/>
@@ -13695,10 +13761,10 @@
     <row r="219" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D219" s="3"/>
       <c r="E219" s="18" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="F219" s="19">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="G219" s="2"/>
       <c r="P219" s="3"/>
@@ -13727,10 +13793,10 @@
     <row r="220" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D220" s="3"/>
       <c r="E220" s="18" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="F220" s="19">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="G220" s="2"/>
       <c r="P220" s="3"/>
@@ -13759,10 +13825,10 @@
     <row r="221" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D221" s="3"/>
       <c r="E221" s="18" t="s">
-        <v>280</v>
+        <v>12</v>
       </c>
       <c r="F221" s="19">
-        <v>1988</v>
+        <v>2022</v>
       </c>
       <c r="G221" s="2"/>
       <c r="P221" s="3"/>
@@ -13791,10 +13857,10 @@
     <row r="222" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D222" s="3"/>
       <c r="E222" s="18" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
       <c r="F222" s="19">
-        <v>2004</v>
+        <v>2022</v>
       </c>
       <c r="G222" s="2"/>
       <c r="P222" s="3"/>
@@ -13823,10 +13889,10 @@
     <row r="223" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D223" s="3"/>
       <c r="E223" s="18" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="F223" s="19">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="G223" s="2"/>
       <c r="P223" s="3"/>
@@ -13855,10 +13921,10 @@
     <row r="224" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D224" s="3"/>
       <c r="E224" s="18" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="F224" s="19">
-        <v>2006</v>
+        <v>1996</v>
       </c>
       <c r="G224" s="2"/>
       <c r="P224" s="3"/>
@@ -13887,10 +13953,10 @@
     <row r="225" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D225" s="3"/>
       <c r="E225" s="18" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="F225" s="19">
-        <v>2008</v>
+        <v>2021</v>
       </c>
       <c r="G225" s="2"/>
       <c r="P225" s="3"/>
@@ -13919,10 +13985,10 @@
     <row r="226" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D226" s="3"/>
       <c r="E226" s="18" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="F226" s="19">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="G226" s="2"/>
       <c r="P226" s="3"/>
@@ -13951,10 +14017,10 @@
     <row r="227" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D227" s="3"/>
       <c r="E227" s="18" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="F227" s="19">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="G227" s="2"/>
       <c r="P227" s="3"/>
@@ -13983,10 +14049,10 @@
     <row r="228" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D228" s="3"/>
       <c r="E228" s="18" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="F228" s="19">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="G228" s="2"/>
       <c r="P228" s="3"/>
@@ -14015,10 +14081,10 @@
     <row r="229" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D229" s="3"/>
       <c r="E229" s="18" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="F229" s="19">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="G229" s="2"/>
       <c r="P229" s="3"/>
@@ -14047,10 +14113,10 @@
     <row r="230" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D230" s="3"/>
       <c r="E230" s="18" t="s">
-        <v>38</v>
+        <v>272</v>
       </c>
       <c r="F230" s="19">
-        <v>2019</v>
+        <v>2008</v>
       </c>
       <c r="G230" s="2"/>
       <c r="P230" s="3"/>
@@ -14079,10 +14145,10 @@
     <row r="231" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D231" s="3"/>
       <c r="E231" s="18" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="F231" s="19">
-        <v>1990</v>
+        <v>2007</v>
       </c>
       <c r="G231" s="2"/>
       <c r="P231" s="3"/>
@@ -14111,10 +14177,10 @@
     <row r="232" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D232" s="3"/>
       <c r="E232" s="18" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="F232" s="19">
-        <v>2022</v>
+        <v>2004</v>
       </c>
       <c r="G232" s="2"/>
       <c r="P232" s="3"/>
@@ -14143,10 +14209,10 @@
     <row r="233" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D233" s="3"/>
       <c r="E233" s="18" t="s">
-        <v>291</v>
+        <v>7</v>
       </c>
       <c r="F233" s="19">
-        <v>2006</v>
+        <v>2015</v>
       </c>
       <c r="G233" s="2"/>
       <c r="P233" s="3"/>
@@ -14175,10 +14241,10 @@
     <row r="234" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D234" s="3"/>
       <c r="E234" s="18" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="F234" s="19">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="G234" s="2"/>
       <c r="P234" s="3"/>
@@ -14207,10 +14273,10 @@
     <row r="235" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D235" s="3"/>
       <c r="E235" s="18" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="F235" s="19">
-        <v>1979</v>
+        <v>1995</v>
       </c>
       <c r="G235" s="2"/>
       <c r="P235" s="3"/>
@@ -14239,10 +14305,10 @@
     <row r="236" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D236" s="3"/>
       <c r="E236" s="18" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="F236" s="19">
-        <v>2000</v>
+        <v>1971</v>
       </c>
       <c r="G236" s="2"/>
       <c r="P236" s="3"/>
@@ -14271,10 +14337,10 @@
     <row r="237" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D237" s="3"/>
       <c r="E237" s="18" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="F237" s="19">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="G237" s="2"/>
       <c r="P237" s="3"/>
@@ -14303,10 +14369,10 @@
     <row r="238" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D238" s="3"/>
       <c r="E238" s="18" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="F238" s="19">
-        <v>1986</v>
+        <v>2013</v>
       </c>
       <c r="G238" s="2"/>
       <c r="P238" s="3"/>
@@ -14335,10 +14401,10 @@
     <row r="239" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D239" s="3"/>
       <c r="E239" s="18" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="F239" s="19">
-        <v>2022</v>
+        <v>1988</v>
       </c>
       <c r="G239" s="2"/>
       <c r="P239" s="3"/>
@@ -14350,7 +14416,7 @@
       </c>
       <c r="S239" s="4"/>
       <c r="T239" s="13" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="U239" s="12">
         <v>2024</v>
@@ -14367,10 +14433,10 @@
     <row r="240" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D240" s="3"/>
       <c r="E240" s="18" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="F240" s="19">
-        <v>2014</v>
+        <v>2004</v>
       </c>
       <c r="G240" s="2"/>
       <c r="P240" s="3"/>
@@ -14399,10 +14465,10 @@
     <row r="241" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D241" s="3"/>
       <c r="E241" s="18" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="F241" s="19">
-        <v>2007</v>
+        <v>1982</v>
       </c>
       <c r="G241" s="2"/>
       <c r="P241" s="3"/>
@@ -14431,10 +14497,10 @@
     <row r="242" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D242" s="3"/>
       <c r="E242" s="18" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="F242" s="19">
-        <v>1992</v>
+        <v>2006</v>
       </c>
       <c r="G242" s="2"/>
       <c r="P242" s="3"/>
@@ -14463,10 +14529,10 @@
     <row r="243" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D243" s="3"/>
       <c r="E243" s="18" t="s">
-        <v>71</v>
+        <v>284</v>
       </c>
       <c r="F243" s="19">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="G243" s="2"/>
       <c r="P243" s="3"/>
@@ -14495,10 +14561,10 @@
     <row r="244" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D244" s="3"/>
       <c r="E244" s="18" t="s">
-        <v>60</v>
+        <v>285</v>
       </c>
       <c r="F244" s="19">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="G244" s="2"/>
       <c r="P244" s="3"/>
@@ -14527,10 +14593,10 @@
     <row r="245" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D245" s="3"/>
       <c r="E245" s="18" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="F245" s="19">
-        <v>1990</v>
+        <v>2014</v>
       </c>
       <c r="G245" s="2"/>
       <c r="P245" s="3"/>
@@ -14559,10 +14625,10 @@
     <row r="246" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D246" s="3"/>
       <c r="E246" s="18" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="F246" s="19">
-        <v>2002</v>
+        <v>2006</v>
       </c>
       <c r="G246" s="2"/>
       <c r="P246" s="3"/>
@@ -14574,7 +14640,7 @@
       </c>
       <c r="S246" s="4"/>
       <c r="T246" s="13" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="U246" s="12">
         <v>1962</v>
@@ -14591,10 +14657,10 @@
     <row r="247" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D247" s="3"/>
       <c r="E247" s="18" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="F247" s="19">
-        <v>1982</v>
+        <v>2015</v>
       </c>
       <c r="G247" s="2"/>
       <c r="P247" s="3"/>
@@ -14623,10 +14689,10 @@
     <row r="248" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D248" s="3"/>
       <c r="E248" s="18" t="s">
-        <v>304</v>
+        <v>38</v>
       </c>
       <c r="F248" s="19">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="G248" s="2"/>
       <c r="P248" s="3"/>
@@ -14638,7 +14704,7 @@
       </c>
       <c r="S248" s="4"/>
       <c r="T248" s="13" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="U248" s="12">
         <v>2024</v>
@@ -14655,18 +14721,18 @@
     <row r="249" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D249" s="3"/>
       <c r="E249" s="18" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="F249" s="19">
-        <v>1975</v>
+        <v>1990</v>
       </c>
       <c r="G249" s="2"/>
       <c r="P249" s="3"/>
       <c r="Q249" s="18" t="s">
-        <v>1282</v>
+        <v>590</v>
       </c>
       <c r="R249" s="19">
-        <v>2023</v>
+        <v>1956</v>
       </c>
       <c r="S249" s="4"/>
       <c r="T249" s="13" t="s">
@@ -14687,18 +14753,18 @@
     <row r="250" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D250" s="3"/>
       <c r="E250" s="18" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="F250" s="19">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="G250" s="2"/>
       <c r="P250" s="3"/>
       <c r="Q250" s="18" t="s">
-        <v>1281</v>
+        <v>1274</v>
       </c>
       <c r="R250" s="19">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="S250" s="4"/>
       <c r="T250" s="13" t="s">
@@ -14719,18 +14785,18 @@
     <row r="251" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D251" s="3"/>
       <c r="E251" s="18" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="F251" s="19">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="G251" s="2"/>
       <c r="P251" s="3"/>
       <c r="Q251" s="18" t="s">
-        <v>1274</v>
+        <v>562</v>
       </c>
       <c r="R251" s="19">
-        <v>2015</v>
+        <v>1978</v>
       </c>
       <c r="S251" s="4"/>
       <c r="T251" s="13" t="s">
@@ -14751,10 +14817,10 @@
     <row r="252" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D252" s="3"/>
       <c r="E252" s="18" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="F252" s="19">
-        <v>1989</v>
+        <v>2016</v>
       </c>
       <c r="G252" s="2"/>
       <c r="P252" s="3"/>
@@ -14775,10 +14841,10 @@
     <row r="253" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D253" s="3"/>
       <c r="E253" s="18" t="s">
-        <v>85</v>
+        <v>293</v>
       </c>
       <c r="F253" s="19">
-        <v>2013</v>
+        <v>1979</v>
       </c>
       <c r="G253" s="2"/>
       <c r="V253" s="3"/>
@@ -14793,10 +14859,10 @@
     <row r="254" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D254" s="3"/>
       <c r="E254" s="18" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="F254" s="19">
-        <v>1993</v>
+        <v>2000</v>
       </c>
       <c r="G254" s="2"/>
       <c r="V254" s="3"/>
@@ -14811,10 +14877,10 @@
     <row r="255" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D255" s="3"/>
       <c r="E255" s="18" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="F255" s="19">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="G255" s="2"/>
       <c r="V255" s="3"/>
@@ -14829,10 +14895,10 @@
     <row r="256" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D256" s="3"/>
       <c r="E256" s="18" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="F256" s="19">
-        <v>2017</v>
+        <v>1986</v>
       </c>
       <c r="G256" s="2"/>
       <c r="V256" s="3"/>
@@ -14847,10 +14913,10 @@
     <row r="257" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D257" s="3"/>
       <c r="E257" s="18" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="F257" s="19">
-        <v>2009</v>
+        <v>2022</v>
       </c>
       <c r="G257" s="2"/>
       <c r="V257" s="3"/>
@@ -14865,7 +14931,7 @@
     <row r="258" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D258" s="3"/>
       <c r="E258" s="18" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="F258" s="19">
         <v>2014</v>
@@ -14883,10 +14949,10 @@
     <row r="259" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D259" s="3"/>
       <c r="E259" s="18" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="F259" s="19">
-        <v>2022</v>
+        <v>2007</v>
       </c>
       <c r="G259" s="2"/>
       <c r="V259" s="3"/>
@@ -14901,10 +14967,10 @@
     <row r="260" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D260" s="3"/>
       <c r="E260" s="18" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="F260" s="19">
-        <v>2016</v>
+        <v>1992</v>
       </c>
       <c r="G260" s="2"/>
       <c r="V260" s="3"/>
@@ -14919,7 +14985,7 @@
     <row r="261" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D261" s="3"/>
       <c r="E261" s="18" t="s">
-        <v>316</v>
+        <v>71</v>
       </c>
       <c r="F261" s="19">
         <v>2007</v>
@@ -14937,10 +15003,10 @@
     <row r="262" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D262" s="3"/>
       <c r="E262" s="18" t="s">
-        <v>317</v>
+        <v>60</v>
       </c>
       <c r="F262" s="19">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="G262" s="2"/>
       <c r="V262" s="3"/>
@@ -14955,10 +15021,10 @@
     <row r="263" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D263" s="3"/>
       <c r="E263" s="18" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="F263" s="19">
-        <v>2016</v>
+        <v>1990</v>
       </c>
       <c r="G263" s="2"/>
       <c r="V263" s="3"/>
@@ -14973,10 +15039,10 @@
     <row r="264" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D264" s="3"/>
       <c r="E264" s="18" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="F264" s="19">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="G264" s="2"/>
       <c r="V264" s="3"/>
@@ -14991,10 +15057,10 @@
     <row r="265" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D265" s="3"/>
       <c r="E265" s="18" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="F265" s="19">
-        <v>1997</v>
+        <v>1982</v>
       </c>
       <c r="G265" s="2"/>
       <c r="V265" s="3"/>
@@ -15009,10 +15075,10 @@
     <row r="266" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D266" s="3"/>
       <c r="E266" s="18" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="F266" s="19">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="G266" s="2"/>
       <c r="V266" s="3"/>
@@ -15027,10 +15093,10 @@
     <row r="267" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D267" s="3"/>
       <c r="E267" s="18" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="F267" s="19">
-        <v>2011</v>
+        <v>1975</v>
       </c>
       <c r="G267" s="2"/>
       <c r="V267" s="3"/>
@@ -15045,10 +15111,10 @@
     <row r="268" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D268" s="3"/>
       <c r="E268" s="18" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="F268" s="19">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="G268" s="2"/>
       <c r="V268" s="3"/>
@@ -15063,10 +15129,10 @@
     <row r="269" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D269" s="3"/>
       <c r="E269" s="18" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F269" s="19">
-        <v>2002</v>
+        <v>2009</v>
       </c>
       <c r="G269" s="2"/>
       <c r="V269" s="3"/>
@@ -15081,10 +15147,10 @@
     <row r="270" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D270" s="3"/>
       <c r="E270" s="18" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="F270" s="19">
-        <v>2012</v>
+        <v>1989</v>
       </c>
       <c r="G270" s="2"/>
       <c r="V270" s="3"/>
@@ -15099,10 +15165,10 @@
     <row r="271" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D271" s="3"/>
       <c r="E271" s="18" t="s">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="F271" s="19">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="G271" s="2"/>
       <c r="V271" s="3"/>
@@ -15117,10 +15183,10 @@
     <row r="272" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D272" s="3"/>
       <c r="E272" s="18" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="F272" s="19">
-        <v>2001</v>
+        <v>1993</v>
       </c>
       <c r="G272" s="2"/>
       <c r="V272" s="3"/>
@@ -15135,10 +15201,10 @@
     <row r="273" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D273" s="3"/>
       <c r="E273" s="18" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="F273" s="19">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="G273" s="2"/>
       <c r="V273" s="3"/>
@@ -15153,10 +15219,10 @@
     <row r="274" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D274" s="3"/>
       <c r="E274" s="18" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="F274" s="19">
-        <v>1999</v>
+        <v>2017</v>
       </c>
       <c r="G274" s="2"/>
       <c r="V274" s="3"/>
@@ -15171,10 +15237,10 @@
     <row r="275" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D275" s="3"/>
       <c r="E275" s="18" t="s">
-        <v>46</v>
+        <v>312</v>
       </c>
       <c r="F275" s="19">
-        <v>1999</v>
+        <v>2009</v>
       </c>
       <c r="G275" s="2"/>
       <c r="V275" s="3"/>
@@ -15188,11 +15254,11 @@
     </row>
     <row r="276" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D276" s="3"/>
-      <c r="E276" s="26">
-        <v>1917</v>
+      <c r="E276" s="18" t="s">
+        <v>313</v>
       </c>
       <c r="F276" s="19">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="G276" s="2"/>
       <c r="V276" s="3"/>
@@ -15207,10 +15273,10 @@
     <row r="277" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D277" s="3"/>
       <c r="E277" s="18" t="s">
-        <v>97</v>
+        <v>314</v>
       </c>
       <c r="F277" s="19">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="G277" s="2"/>
       <c r="V277" s="3"/>
@@ -15225,10 +15291,10 @@
     <row r="278" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D278" s="3"/>
       <c r="E278" s="18" t="s">
-        <v>90</v>
+        <v>315</v>
       </c>
       <c r="F278" s="19">
-        <v>2005</v>
+        <v>2016</v>
       </c>
       <c r="G278" s="2"/>
       <c r="V278" s="3"/>
@@ -15243,10 +15309,10 @@
     <row r="279" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D279" s="3"/>
       <c r="E279" s="18" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="F279" s="19">
-        <v>2019</v>
+        <v>2007</v>
       </c>
       <c r="G279" s="2"/>
       <c r="V279" s="3"/>
@@ -15261,7 +15327,7 @@
     <row r="280" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D280" s="3"/>
       <c r="E280" s="18" t="s">
-        <v>23</v>
+        <v>317</v>
       </c>
       <c r="F280" s="19">
         <v>2018</v>
@@ -15279,10 +15345,10 @@
     <row r="281" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D281" s="3"/>
       <c r="E281" s="18" t="s">
-        <v>67</v>
+        <v>318</v>
       </c>
       <c r="F281" s="19">
-        <v>2004</v>
+        <v>2016</v>
       </c>
       <c r="G281" s="2"/>
       <c r="V281" s="3"/>
@@ -15297,10 +15363,10 @@
     <row r="282" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D282" s="3"/>
       <c r="E282" s="18" t="s">
-        <v>43</v>
+        <v>319</v>
       </c>
       <c r="F282" s="19">
-        <v>2016</v>
+        <v>2007</v>
       </c>
       <c r="G282" s="2"/>
       <c r="V282" s="3"/>
@@ -15315,10 +15381,10 @@
     <row r="283" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D283" s="3"/>
       <c r="E283" s="18" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="F283" s="19">
-        <v>2005</v>
+        <v>1997</v>
       </c>
       <c r="G283" s="2"/>
       <c r="V283" s="3"/>
@@ -15333,10 +15399,10 @@
     <row r="284" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D284" s="3"/>
       <c r="E284" s="18" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="F284" s="19">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="G284" s="2"/>
       <c r="V284" s="3"/>
@@ -15351,10 +15417,10 @@
     <row r="285" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D285" s="3"/>
       <c r="E285" s="18" t="s">
-        <v>53</v>
+        <v>322</v>
       </c>
       <c r="F285" s="19">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="G285" s="2"/>
       <c r="V285" s="3"/>
@@ -15369,10 +15435,10 @@
     <row r="286" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D286" s="3"/>
       <c r="E286" s="18" t="s">
-        <v>21</v>
+        <v>323</v>
       </c>
       <c r="F286" s="19">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="G286" s="2"/>
       <c r="V286" s="3"/>
@@ -15387,10 +15453,10 @@
     <row r="287" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D287" s="3"/>
       <c r="E287" s="18" t="s">
-        <v>78</v>
+        <v>324</v>
       </c>
       <c r="F287" s="19">
-        <v>2018</v>
+        <v>2002</v>
       </c>
       <c r="G287" s="2"/>
       <c r="V287" s="3"/>
@@ -15405,10 +15471,10 @@
     <row r="288" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D288" s="3"/>
       <c r="E288" s="18" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F288" s="19">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="G288" s="2"/>
       <c r="V288" s="3"/>
@@ -15423,10 +15489,10 @@
     <row r="289" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D289" s="3"/>
       <c r="E289" s="18" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="F289" s="19">
-        <v>1976</v>
+        <v>2010</v>
       </c>
       <c r="G289" s="2"/>
       <c r="V289" s="3"/>
@@ -15441,10 +15507,10 @@
     <row r="290" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D290" s="3"/>
       <c r="E290" s="18" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F290" s="19">
-        <v>2021</v>
+        <v>2001</v>
       </c>
       <c r="G290" s="2"/>
       <c r="V290" s="3"/>
@@ -15459,10 +15525,10 @@
     <row r="291" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D291" s="3"/>
       <c r="E291" s="18" t="s">
-        <v>31</v>
+        <v>328</v>
       </c>
       <c r="F291" s="19">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="G291" s="2"/>
       <c r="V291" s="3"/>
@@ -15477,10 +15543,10 @@
     <row r="292" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D292" s="3"/>
       <c r="E292" s="18" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="F292" s="19">
-        <v>2016</v>
+        <v>1999</v>
       </c>
       <c r="G292" s="2"/>
       <c r="V292" s="3"/>
@@ -15495,10 +15561,10 @@
     <row r="293" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D293" s="3"/>
       <c r="E293" s="18" t="s">
-        <v>337</v>
+        <v>46</v>
       </c>
       <c r="F293" s="19">
-        <v>2019</v>
+        <v>1999</v>
       </c>
       <c r="G293" s="2"/>
       <c r="V293" s="3"/>
@@ -15512,11 +15578,11 @@
     </row>
     <row r="294" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D294" s="3"/>
-      <c r="E294" s="18" t="s">
-        <v>338</v>
+      <c r="E294" s="26">
+        <v>1917</v>
       </c>
       <c r="F294" s="19">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G294" s="2"/>
       <c r="V294" s="3"/>
@@ -15531,10 +15597,10 @@
     <row r="295" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D295" s="3"/>
       <c r="E295" s="18" t="s">
-        <v>26</v>
+        <v>97</v>
       </c>
       <c r="F295" s="19">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="G295" s="2"/>
       <c r="V295" s="3"/>
@@ -15549,10 +15615,10 @@
     <row r="296" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D296" s="3"/>
       <c r="E296" s="18" t="s">
-        <v>339</v>
+        <v>90</v>
       </c>
       <c r="F296" s="19">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="G296" s="2"/>
       <c r="V296" s="3"/>
@@ -15567,10 +15633,10 @@
     <row r="297" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D297" s="3"/>
       <c r="E297" s="18" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="F297" s="19">
-        <v>2004</v>
+        <v>2019</v>
       </c>
       <c r="G297" s="2"/>
       <c r="V297" s="3"/>
@@ -15585,10 +15651,10 @@
     <row r="298" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D298" s="3"/>
       <c r="E298" s="18" t="s">
-        <v>341</v>
+        <v>23</v>
       </c>
       <c r="F298" s="19">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="G298" s="2"/>
       <c r="V298" s="3"/>
@@ -15603,10 +15669,10 @@
     <row r="299" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D299" s="3"/>
       <c r="E299" s="18" t="s">
-        <v>342</v>
+        <v>67</v>
       </c>
       <c r="F299" s="19">
-        <v>2011</v>
+        <v>2004</v>
       </c>
       <c r="G299" s="2"/>
       <c r="V299" s="3"/>
@@ -15621,10 +15687,10 @@
     <row r="300" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D300" s="3"/>
       <c r="E300" s="18" t="s">
-        <v>343</v>
+        <v>43</v>
       </c>
       <c r="F300" s="19">
-        <v>1983</v>
+        <v>2016</v>
       </c>
       <c r="G300" s="2"/>
       <c r="V300" s="3"/>
@@ -15639,10 +15705,10 @@
     <row r="301" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D301" s="3"/>
       <c r="E301" s="18" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="F301" s="19">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="G301" s="2"/>
       <c r="V301" s="3"/>
@@ -15657,10 +15723,10 @@
     <row r="302" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D302" s="3"/>
       <c r="E302" s="18" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="F302" s="19">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="G302" s="2"/>
       <c r="V302" s="3"/>
@@ -15675,10 +15741,10 @@
     <row r="303" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D303" s="3"/>
       <c r="E303" s="18" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="F303" s="19">
-        <v>2002</v>
+        <v>2016</v>
       </c>
       <c r="G303" s="2"/>
       <c r="V303" s="3"/>
@@ -15693,10 +15759,10 @@
     <row r="304" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D304" s="3"/>
       <c r="E304" s="18" t="s">
-        <v>345</v>
+        <v>21</v>
       </c>
       <c r="F304" s="19">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="G304" s="2"/>
       <c r="V304" s="3"/>
@@ -15711,10 +15777,10 @@
     <row r="305" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D305" s="3"/>
       <c r="E305" s="18" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="F305" s="19">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="G305" s="2"/>
       <c r="V305" s="3"/>
@@ -15729,10 +15795,10 @@
     <row r="306" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D306" s="3"/>
       <c r="E306" s="18" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="F306" s="19">
-        <v>1999</v>
+        <v>2003</v>
       </c>
       <c r="G306" s="2"/>
       <c r="V306" s="3"/>
@@ -15747,10 +15813,10 @@
     <row r="307" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D307" s="3"/>
       <c r="E307" s="18" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="F307" s="19">
-        <v>2019</v>
+        <v>1976</v>
       </c>
       <c r="G307" s="2"/>
       <c r="V307" s="3"/>
@@ -15765,10 +15831,10 @@
     <row r="308" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D308" s="3"/>
       <c r="E308" s="18" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="F308" s="19">
-        <v>1985</v>
+        <v>2021</v>
       </c>
       <c r="G308" s="2"/>
       <c r="V308" s="3"/>
@@ -15783,10 +15849,10 @@
     <row r="309" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D309" s="3"/>
       <c r="E309" s="18" t="s">
-        <v>349</v>
+        <v>31</v>
       </c>
       <c r="F309" s="19">
-        <v>2005</v>
+        <v>2019</v>
       </c>
       <c r="G309" s="2"/>
       <c r="V309" s="3"/>
@@ -15801,10 +15867,10 @@
     <row r="310" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D310" s="3"/>
       <c r="E310" s="18" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="F310" s="19">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="G310" s="2"/>
       <c r="V310" s="3"/>
@@ -15819,10 +15885,10 @@
     <row r="311" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D311" s="3"/>
       <c r="E311" s="18" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="F311" s="19">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="G311" s="2"/>
       <c r="V311" s="3"/>
@@ -15837,10 +15903,10 @@
     <row r="312" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D312" s="3"/>
       <c r="E312" s="18" t="s">
-        <v>32</v>
+        <v>338</v>
       </c>
       <c r="F312" s="19">
-        <v>2003</v>
+        <v>2018</v>
       </c>
       <c r="G312" s="2"/>
       <c r="V312" s="3"/>
@@ -15855,10 +15921,10 @@
     <row r="313" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D313" s="3"/>
       <c r="E313" s="18" t="s">
-        <v>352</v>
+        <v>26</v>
       </c>
       <c r="F313" s="19">
-        <v>1972</v>
+        <v>2013</v>
       </c>
       <c r="G313" s="2"/>
       <c r="V313" s="3"/>
@@ -15873,10 +15939,10 @@
     <row r="314" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D314" s="3"/>
       <c r="E314" s="18" t="s">
-        <v>65</v>
+        <v>339</v>
       </c>
       <c r="F314" s="19">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="G314" s="2"/>
       <c r="V314" s="3"/>
@@ -15891,10 +15957,10 @@
     <row r="315" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D315" s="3"/>
       <c r="E315" s="18" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="F315" s="19">
-        <v>2011</v>
+        <v>2004</v>
       </c>
       <c r="G315" s="2"/>
       <c r="V315" s="3"/>
@@ -15909,10 +15975,10 @@
     <row r="316" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D316" s="3"/>
       <c r="E316" s="18" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="F316" s="19">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="G316" s="2"/>
       <c r="V316" s="3"/>
@@ -15927,10 +15993,10 @@
     <row r="317" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D317" s="3"/>
       <c r="E317" s="18" t="s">
-        <v>18</v>
+        <v>342</v>
       </c>
       <c r="F317" s="19">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="G317" s="2"/>
       <c r="V317" s="3"/>
@@ -15945,10 +16011,10 @@
     <row r="318" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D318" s="3"/>
       <c r="E318" s="18" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="F318" s="19">
-        <v>2017</v>
+        <v>1983</v>
       </c>
       <c r="G318" s="2"/>
       <c r="V318" s="3"/>
@@ -15963,10 +16029,10 @@
     <row r="319" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D319" s="3"/>
       <c r="E319" s="18" t="s">
-        <v>356</v>
+        <v>68</v>
       </c>
       <c r="F319" s="19">
-        <v>2018</v>
+        <v>2009</v>
       </c>
       <c r="G319" s="2"/>
       <c r="V319" s="3"/>
@@ -15981,10 +16047,10 @@
     <row r="320" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D320" s="3"/>
       <c r="E320" s="18" t="s">
-        <v>39</v>
+        <v>344</v>
       </c>
       <c r="F320" s="19">
-        <v>2010</v>
+        <v>2021</v>
       </c>
       <c r="G320" s="2"/>
       <c r="V320" s="3"/>
@@ -15999,10 +16065,10 @@
     <row r="321" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D321" s="3"/>
       <c r="E321" s="18" t="s">
-        <v>357</v>
+        <v>69</v>
       </c>
       <c r="F321" s="19">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="G321" s="2"/>
       <c r="V321" s="3"/>
@@ -16017,10 +16083,10 @@
     <row r="322" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D322" s="3"/>
       <c r="E322" s="18" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="F322" s="19">
-        <v>1994</v>
+        <v>2015</v>
       </c>
       <c r="G322" s="2"/>
       <c r="V322" s="3"/>
@@ -16035,10 +16101,10 @@
     <row r="323" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D323" s="3"/>
       <c r="E323" s="18" t="s">
-        <v>359</v>
+        <v>62</v>
       </c>
       <c r="F323" s="19">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="G323" s="2"/>
       <c r="V323" s="3"/>
@@ -16053,10 +16119,10 @@
     <row r="324" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D324" s="3"/>
       <c r="E324" s="18" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="F324" s="19">
-        <v>2010</v>
+        <v>1999</v>
       </c>
       <c r="G324" s="2"/>
       <c r="V324" s="3"/>
@@ -16071,10 +16137,10 @@
     <row r="325" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D325" s="3"/>
       <c r="E325" s="18" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="F325" s="19">
-        <v>1990</v>
+        <v>2019</v>
       </c>
       <c r="G325" s="2"/>
       <c r="V325" s="3"/>
@@ -16089,10 +16155,10 @@
     <row r="326" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D326" s="3"/>
       <c r="E326" s="18" t="s">
-        <v>6</v>
+        <v>348</v>
       </c>
       <c r="F326" s="19">
-        <v>2021</v>
+        <v>1985</v>
       </c>
       <c r="G326" s="2"/>
       <c r="V326" s="3"/>
@@ -16107,10 +16173,10 @@
     <row r="327" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D327" s="3"/>
       <c r="E327" s="18" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="F327" s="19">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="G327" s="2"/>
       <c r="V327" s="3"/>
@@ -16125,10 +16191,10 @@
     <row r="328" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D328" s="3"/>
       <c r="E328" s="18" t="s">
-        <v>19</v>
+        <v>350</v>
       </c>
       <c r="F328" s="19">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G328" s="2"/>
       <c r="V328" s="3"/>
@@ -16143,10 +16209,10 @@
     <row r="329" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D329" s="3"/>
       <c r="E329" s="18" t="s">
-        <v>29</v>
+        <v>351</v>
       </c>
       <c r="F329" s="19">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="G329" s="2"/>
       <c r="V329" s="3"/>
@@ -16161,10 +16227,10 @@
     <row r="330" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D330" s="3"/>
       <c r="E330" s="18" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="F330" s="19">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="G330" s="2"/>
       <c r="V330" s="3"/>
@@ -16179,10 +16245,10 @@
     <row r="331" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D331" s="3"/>
       <c r="E331" s="18" t="s">
-        <v>36</v>
+        <v>352</v>
       </c>
       <c r="F331" s="19">
-        <v>2012</v>
+        <v>1972</v>
       </c>
       <c r="G331" s="2"/>
       <c r="V331" s="3"/>
@@ -16197,10 +16263,10 @@
     <row r="332" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D332" s="3"/>
       <c r="E332" s="18" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F332" s="19">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="G332" s="2"/>
       <c r="V332" s="3"/>
@@ -16215,10 +16281,10 @@
     <row r="333" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D333" s="3"/>
       <c r="E333" s="18" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="F333" s="19">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="G333" s="2"/>
       <c r="V333" s="3"/>
@@ -16233,10 +16299,10 @@
     <row r="334" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D334" s="3"/>
       <c r="E334" s="18" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="F334" s="19">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="G334" s="2"/>
       <c r="V334" s="3"/>
@@ -16251,10 +16317,10 @@
     <row r="335" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D335" s="3"/>
       <c r="E335" s="18" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F335" s="19">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="G335" s="2"/>
       <c r="V335" s="3"/>
@@ -16269,10 +16335,10 @@
     <row r="336" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D336" s="3"/>
       <c r="E336" s="18" t="s">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="F336" s="19">
-        <v>2009</v>
+        <v>2017</v>
       </c>
       <c r="G336" s="2"/>
       <c r="V336" s="3"/>
@@ -16287,10 +16353,10 @@
     <row r="337" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D337" s="3"/>
       <c r="E337" s="18" t="s">
-        <v>96</v>
+        <v>356</v>
       </c>
       <c r="F337" s="19">
-        <v>2002</v>
+        <v>2018</v>
       </c>
       <c r="G337" s="2"/>
       <c r="V337" s="3"/>
@@ -16305,10 +16371,10 @@
     <row r="338" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D338" s="3"/>
       <c r="E338" s="18" t="s">
-        <v>365</v>
+        <v>39</v>
       </c>
       <c r="F338" s="19">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="G338" s="2"/>
       <c r="V338" s="3"/>
@@ -16323,10 +16389,10 @@
     <row r="339" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D339" s="3"/>
       <c r="E339" s="18" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="F339" s="19">
-        <v>2013</v>
+        <v>2004</v>
       </c>
       <c r="G339" s="2"/>
       <c r="V339" s="3"/>
@@ -16341,10 +16407,10 @@
     <row r="340" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D340" s="3"/>
       <c r="E340" s="18" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="F340" s="19">
-        <v>2017</v>
+        <v>1994</v>
       </c>
       <c r="G340" s="2"/>
       <c r="V340" s="3"/>
@@ -16359,10 +16425,10 @@
     <row r="341" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D341" s="3"/>
       <c r="E341" s="18" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="F341" s="19">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="G341" s="2"/>
       <c r="V341" s="3"/>
@@ -16377,10 +16443,10 @@
     <row r="342" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D342" s="3"/>
       <c r="E342" s="18" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="F342" s="19">
-        <v>1980</v>
+        <v>2010</v>
       </c>
       <c r="G342" s="2"/>
       <c r="V342" s="3"/>
@@ -16395,10 +16461,10 @@
     <row r="343" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D343" s="3"/>
       <c r="E343" s="18" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="F343" s="19">
-        <v>1995</v>
+        <v>1990</v>
       </c>
       <c r="G343" s="2"/>
       <c r="V343" s="3"/>
@@ -16413,10 +16479,10 @@
     <row r="344" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D344" s="3"/>
       <c r="E344" s="18" t="s">
-        <v>371</v>
+        <v>6</v>
       </c>
       <c r="F344" s="19">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="G344" s="2"/>
       <c r="V344" s="3"/>
@@ -16431,10 +16497,10 @@
     <row r="345" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D345" s="3"/>
       <c r="E345" s="18" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="F345" s="19">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="G345" s="2"/>
       <c r="V345" s="3"/>
@@ -16449,10 +16515,10 @@
     <row r="346" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D346" s="3"/>
       <c r="E346" s="18" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F346" s="19">
-        <v>1993</v>
+        <v>2011</v>
       </c>
       <c r="G346" s="2"/>
       <c r="V346" s="3"/>
@@ -16467,10 +16533,10 @@
     <row r="347" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D347" s="3"/>
       <c r="E347" s="18" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="F347" s="19">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="G347" s="2"/>
       <c r="V347" s="3"/>
@@ -16485,10 +16551,10 @@
     <row r="348" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D348" s="3"/>
       <c r="E348" s="18" t="s">
-        <v>373</v>
+        <v>76</v>
       </c>
       <c r="F348" s="19">
-        <v>2014</v>
+        <v>2005</v>
       </c>
       <c r="G348" s="2"/>
       <c r="V348" s="3"/>
@@ -16503,10 +16569,10 @@
     <row r="349" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D349" s="3"/>
       <c r="E349" s="18" t="s">
-        <v>374</v>
+        <v>36</v>
       </c>
       <c r="F349" s="19">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="G349" s="2"/>
       <c r="V349" s="3"/>
@@ -16521,10 +16587,10 @@
     <row r="350" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D350" s="3"/>
       <c r="E350" s="18" t="s">
-        <v>375</v>
+        <v>81</v>
       </c>
       <c r="F350" s="19">
-        <v>2016</v>
+        <v>2002</v>
       </c>
       <c r="G350" s="2"/>
       <c r="V350" s="3"/>
@@ -16539,10 +16605,10 @@
     <row r="351" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D351" s="3"/>
       <c r="E351" s="18" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="F351" s="19">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="G351" s="2"/>
       <c r="V351" s="3"/>
@@ -16557,10 +16623,10 @@
     <row r="352" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D352" s="3"/>
       <c r="E352" s="18" t="s">
-        <v>8</v>
+        <v>364</v>
       </c>
       <c r="F352" s="19">
-        <v>1994</v>
+        <v>2017</v>
       </c>
       <c r="G352" s="2"/>
       <c r="V352" s="3"/>
@@ -16575,7 +16641,7 @@
     <row r="353" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D353" s="3"/>
       <c r="E353" s="18" t="s">
-        <v>376</v>
+        <v>15</v>
       </c>
       <c r="F353" s="19">
         <v>2015</v>
@@ -16593,10 +16659,10 @@
     <row r="354" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D354" s="3"/>
       <c r="E354" s="18" t="s">
-        <v>377</v>
+        <v>0</v>
       </c>
       <c r="F354" s="19">
-        <v>1991</v>
+        <v>2009</v>
       </c>
       <c r="G354" s="2"/>
       <c r="V354" s="3"/>
@@ -16611,10 +16677,10 @@
     <row r="355" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D355" s="3"/>
       <c r="E355" s="18" t="s">
-        <v>378</v>
+        <v>96</v>
       </c>
       <c r="F355" s="19">
-        <v>2019</v>
+        <v>2002</v>
       </c>
       <c r="G355" s="2"/>
       <c r="V355" s="3"/>
@@ -16629,7 +16695,7 @@
     <row r="356" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D356" s="3"/>
       <c r="E356" s="18" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="F356" s="19">
         <v>2001</v>
@@ -16647,10 +16713,10 @@
     <row r="357" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D357" s="3"/>
       <c r="E357" s="18" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="F357" s="19">
-        <v>2004</v>
+        <v>2013</v>
       </c>
       <c r="G357" s="2"/>
       <c r="V357" s="3"/>
@@ -16665,10 +16731,10 @@
     <row r="358" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D358" s="3"/>
       <c r="E358" s="18" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="F358" s="19">
-        <v>2001</v>
+        <v>2017</v>
       </c>
       <c r="G358" s="2"/>
       <c r="V358" s="3"/>
@@ -16683,10 +16749,10 @@
     <row r="359" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D359" s="3"/>
       <c r="E359" s="18" t="s">
-        <v>56</v>
+        <v>368</v>
       </c>
       <c r="F359" s="19">
-        <v>2001</v>
+        <v>2014</v>
       </c>
       <c r="G359" s="2"/>
       <c r="V359" s="3"/>
@@ -16701,10 +16767,10 @@
     <row r="360" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D360" s="3"/>
       <c r="E360" s="18" t="s">
-        <v>88</v>
+        <v>369</v>
       </c>
       <c r="F360" s="19">
-        <v>2017</v>
+        <v>1980</v>
       </c>
       <c r="G360" s="2"/>
       <c r="V360" s="3"/>
@@ -16719,10 +16785,10 @@
     <row r="361" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D361" s="3"/>
       <c r="E361" s="18" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="F361" s="19">
-        <v>1985</v>
+        <v>1995</v>
       </c>
       <c r="G361" s="2"/>
       <c r="V361" s="3"/>
@@ -16737,10 +16803,10 @@
     <row r="362" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D362" s="3"/>
       <c r="E362" s="18" t="s">
-        <v>72</v>
+        <v>371</v>
       </c>
       <c r="F362" s="19">
-        <v>2001</v>
+        <v>2016</v>
       </c>
       <c r="G362" s="2"/>
       <c r="V362" s="3"/>
@@ -16755,10 +16821,10 @@
     <row r="363" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D363" s="3"/>
       <c r="E363" s="18" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="F363" s="19">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="G363" s="2"/>
       <c r="V363" s="3"/>
@@ -16773,10 +16839,10 @@
     <row r="364" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D364" s="3"/>
       <c r="E364" s="18" t="s">
-        <v>384</v>
+        <v>42</v>
       </c>
       <c r="F364" s="19">
-        <v>2008</v>
+        <v>1993</v>
       </c>
       <c r="G364" s="2"/>
       <c r="V364" s="3"/>
@@ -16791,10 +16857,10 @@
     <row r="365" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D365" s="3"/>
       <c r="E365" s="18" t="s">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="F365" s="19">
-        <v>1997</v>
+        <v>2017</v>
       </c>
       <c r="G365" s="2"/>
       <c r="V365" s="3"/>
@@ -16809,10 +16875,10 @@
     <row r="366" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D366" s="3"/>
       <c r="E366" s="18" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="F366" s="19">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="G366" s="2"/>
       <c r="V366" s="3"/>
@@ -16827,10 +16893,10 @@
     <row r="367" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D367" s="3"/>
       <c r="E367" s="18" t="s">
-        <v>80</v>
+        <v>374</v>
       </c>
       <c r="F367" s="19">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="G367" s="2"/>
       <c r="V367" s="3"/>
@@ -16845,10 +16911,10 @@
     <row r="368" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D368" s="3"/>
       <c r="E368" s="18" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="F368" s="19">
-        <v>1977</v>
+        <v>2016</v>
       </c>
       <c r="G368" s="2"/>
       <c r="V368" s="3"/>
@@ -16863,10 +16929,10 @@
     <row r="369" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D369" s="3"/>
       <c r="E369" s="18" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F369" s="19">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="G369" s="2"/>
       <c r="V369" s="3"/>
@@ -16881,10 +16947,10 @@
     <row r="370" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D370" s="3"/>
       <c r="E370" s="18" t="s">
-        <v>387</v>
+        <v>8</v>
       </c>
       <c r="F370" s="19">
-        <v>1999</v>
+        <v>1994</v>
       </c>
       <c r="G370" s="2"/>
       <c r="V370" s="3"/>
@@ -16899,10 +16965,10 @@
     <row r="371" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D371" s="3"/>
       <c r="E371" s="18" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="F371" s="19">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="G371" s="2"/>
       <c r="V371" s="3"/>
@@ -16917,10 +16983,10 @@
     <row r="372" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D372" s="3"/>
       <c r="E372" s="18" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="F372" s="19">
-        <v>2010</v>
+        <v>1991</v>
       </c>
       <c r="G372" s="2"/>
       <c r="V372" s="3"/>
@@ -16935,10 +17001,10 @@
     <row r="373" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D373" s="3"/>
       <c r="E373" s="18" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="F373" s="19">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="G373" s="2"/>
       <c r="V373" s="3"/>
@@ -16953,10 +17019,10 @@
     <row r="374" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D374" s="3"/>
       <c r="E374" s="18" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="F374" s="19">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="G374" s="2"/>
       <c r="V374" s="3"/>
@@ -16971,10 +17037,10 @@
     <row r="375" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D375" s="3"/>
       <c r="E375" s="18" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="F375" s="19">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="G375" s="2"/>
       <c r="V375" s="3"/>
@@ -16989,10 +17055,10 @@
     <row r="376" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D376" s="3"/>
       <c r="E376" s="18" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="F376" s="19">
-        <v>2017</v>
+        <v>2001</v>
       </c>
       <c r="G376" s="2"/>
       <c r="V376" s="3"/>
@@ -17007,10 +17073,10 @@
     <row r="377" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D377" s="3"/>
       <c r="E377" s="18" t="s">
-        <v>394</v>
+        <v>56</v>
       </c>
       <c r="F377" s="19">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="G377" s="2"/>
       <c r="V377" s="3"/>
@@ -17025,10 +17091,10 @@
     <row r="378" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D378" s="3"/>
       <c r="E378" s="18" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="F378" s="19">
-        <v>2003</v>
+        <v>2017</v>
       </c>
       <c r="G378" s="2"/>
       <c r="V378" s="3"/>
@@ -17043,10 +17109,10 @@
     <row r="379" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D379" s="3"/>
       <c r="E379" s="18" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="F379" s="19">
-        <v>2012</v>
+        <v>1985</v>
       </c>
       <c r="G379" s="2"/>
       <c r="V379" s="3"/>
@@ -17061,10 +17127,10 @@
     <row r="380" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D380" s="3"/>
       <c r="E380" s="18" t="s">
-        <v>396</v>
+        <v>72</v>
       </c>
       <c r="F380" s="19">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="G380" s="2"/>
       <c r="V380" s="3"/>
@@ -17079,10 +17145,10 @@
     <row r="381" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D381" s="3"/>
       <c r="E381" s="18" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="F381" s="19">
-        <v>2017</v>
+        <v>2003</v>
       </c>
       <c r="G381" s="2"/>
       <c r="V381" s="3"/>
@@ -17097,10 +17163,10 @@
     <row r="382" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D382" s="3"/>
       <c r="E382" s="18" t="s">
-        <v>1</v>
+        <v>384</v>
       </c>
       <c r="F382" s="19">
-        <v>2019</v>
+        <v>2008</v>
       </c>
       <c r="G382" s="2"/>
       <c r="V382" s="3"/>
@@ -17115,10 +17181,10 @@
     <row r="383" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D383" s="3"/>
       <c r="E383" s="18" t="s">
-        <v>398</v>
+        <v>3</v>
       </c>
       <c r="F383" s="19">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="G383" s="2"/>
       <c r="V383" s="3"/>
@@ -17133,10 +17199,10 @@
     <row r="384" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D384" s="3"/>
       <c r="E384" s="18" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="F384" s="19">
-        <v>1980</v>
+        <v>2019</v>
       </c>
       <c r="G384" s="2"/>
       <c r="V384" s="3"/>
@@ -17151,10 +17217,10 @@
     <row r="385" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D385" s="3"/>
       <c r="E385" s="18" t="s">
-        <v>400</v>
+        <v>80</v>
       </c>
       <c r="F385" s="19">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="G385" s="2"/>
       <c r="V385" s="3"/>
@@ -17169,10 +17235,10 @@
     <row r="386" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D386" s="3"/>
       <c r="E386" s="18" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="F386" s="19">
-        <v>2016</v>
+        <v>1977</v>
       </c>
       <c r="G386" s="2"/>
       <c r="V386" s="3"/>
@@ -17187,10 +17253,10 @@
     <row r="387" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D387" s="3"/>
       <c r="E387" s="18" t="s">
-        <v>402</v>
+        <v>4</v>
       </c>
       <c r="F387" s="19">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="G387" s="2"/>
       <c r="V387" s="3"/>
@@ -17205,10 +17271,10 @@
     <row r="388" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D388" s="3"/>
       <c r="E388" s="18" t="s">
-        <v>89</v>
+        <v>387</v>
       </c>
       <c r="F388" s="19">
-        <v>2015</v>
+        <v>1999</v>
       </c>
       <c r="G388" s="2"/>
       <c r="V388" s="3"/>
@@ -17223,10 +17289,10 @@
     <row r="389" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D389" s="3"/>
       <c r="E389" s="18" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="F389" s="19">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="G389" s="2"/>
       <c r="V389" s="3"/>
@@ -17241,10 +17307,10 @@
     <row r="390" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D390" s="3"/>
       <c r="E390" s="18" t="s">
-        <v>10</v>
+        <v>389</v>
       </c>
       <c r="F390" s="19">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="G390" s="2"/>
       <c r="V390" s="3"/>
@@ -17259,10 +17325,10 @@
     <row r="391" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D391" s="3"/>
       <c r="E391" s="18" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="F391" s="19">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="G391" s="3"/>
       <c r="V391" s="3"/>
@@ -17277,10 +17343,10 @@
     <row r="392" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D392" s="3"/>
       <c r="E392" s="18" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F392" s="19">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="G392" s="3"/>
       <c r="V392" s="3"/>
@@ -17295,10 +17361,10 @@
     <row r="393" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D393" s="3"/>
       <c r="E393" s="18" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="F393" s="19">
-        <v>2014</v>
+        <v>1998</v>
       </c>
       <c r="G393" s="3"/>
       <c r="V393" s="3"/>
@@ -17313,10 +17379,10 @@
     <row r="394" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D394" s="3"/>
       <c r="E394" s="18" t="s">
-        <v>17</v>
+        <v>393</v>
       </c>
       <c r="F394" s="19">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="G394" s="3"/>
       <c r="V394" s="3"/>
@@ -17331,10 +17397,10 @@
     <row r="395" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D395" s="3"/>
       <c r="E395" s="18" t="s">
-        <v>5</v>
+        <v>394</v>
       </c>
       <c r="F395" s="19">
-        <v>2018</v>
+        <v>2004</v>
       </c>
       <c r="G395" s="3"/>
       <c r="V395" s="3"/>
@@ -17349,10 +17415,10 @@
     <row r="396" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D396" s="3"/>
       <c r="E396" s="18" t="s">
-        <v>407</v>
+        <v>66</v>
       </c>
       <c r="F396" s="19">
-        <v>2013</v>
+        <v>2003</v>
       </c>
       <c r="G396" s="3"/>
       <c r="V396" s="3"/>
@@ -17367,10 +17433,10 @@
     <row r="397" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D397" s="3"/>
       <c r="E397" s="18" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="F397" s="19">
-        <v>1994</v>
+        <v>2012</v>
       </c>
       <c r="G397" s="3"/>
       <c r="V397" s="3"/>
@@ -17385,10 +17451,10 @@
     <row r="398" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D398" s="3"/>
       <c r="E398" s="18" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="F398" s="19">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="G398" s="3"/>
       <c r="V398" s="3"/>
@@ -17403,7 +17469,7 @@
     <row r="399" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D399" s="3"/>
       <c r="E399" s="18" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="F399" s="19">
         <v>2017</v>
@@ -17421,10 +17487,10 @@
     <row r="400" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D400" s="3"/>
       <c r="E400" s="18" t="s">
-        <v>411</v>
+        <v>1</v>
       </c>
       <c r="F400" s="19">
-        <v>1999</v>
+        <v>2019</v>
       </c>
       <c r="G400" s="3"/>
       <c r="V400" s="3"/>
@@ -17439,10 +17505,10 @@
     <row r="401" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D401" s="3"/>
       <c r="E401" s="18" t="s">
-        <v>41</v>
+        <v>398</v>
       </c>
       <c r="F401" s="19">
-        <v>2019</v>
+        <v>1995</v>
       </c>
       <c r="G401" s="3"/>
       <c r="V401" s="3"/>
@@ -17457,10 +17523,10 @@
     <row r="402" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D402" s="3"/>
       <c r="E402" s="18" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="F402" s="19">
-        <v>2019</v>
+        <v>1980</v>
       </c>
       <c r="G402" s="3"/>
       <c r="V402" s="3"/>
@@ -17475,10 +17541,10 @@
     <row r="403" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D403" s="3"/>
       <c r="E403" s="18" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="F403" s="19">
-        <v>1994</v>
+        <v>2018</v>
       </c>
       <c r="G403" s="3"/>
       <c r="V403" s="3"/>
@@ -17493,10 +17559,10 @@
     <row r="404" spans="4:25" x14ac:dyDescent="0.2">
       <c r="D404" s="3"/>
       <c r="E404" s="18" t="s">
-        <v>51</v>
+        <v>401</v>
       </c>
       <c r="F404" s="19">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="G404" s="3"/>
       <c r="V404" s="3"/>
@@ -17509,12 +17575,14 @@
       <c r="Y404" s="3"/>
     </row>
     <row r="405" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D405" s="3"/>
       <c r="E405" s="18" t="s">
-        <v>95</v>
+        <v>402</v>
       </c>
       <c r="F405" s="19">
-        <v>2010</v>
-      </c>
+        <v>2009</v>
+      </c>
+      <c r="G405" s="3"/>
       <c r="V405" s="3"/>
       <c r="W405" s="36" t="s">
         <v>772</v>
@@ -17525,8 +17593,14 @@
       <c r="Y405" s="3"/>
     </row>
     <row r="406" spans="4:25" x14ac:dyDescent="0.2">
-      <c r="E406" s="3"/>
-      <c r="F406" s="3"/>
+      <c r="D406" s="3"/>
+      <c r="E406" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F406" s="19">
+        <v>2015</v>
+      </c>
+      <c r="G406" s="3"/>
       <c r="V406" s="3"/>
       <c r="W406" s="36" t="s">
         <v>22</v>
@@ -17537,6 +17611,14 @@
       <c r="Y406" s="3"/>
     </row>
     <row r="407" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D407" s="3"/>
+      <c r="E407" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="F407" s="19">
+        <v>2016</v>
+      </c>
+      <c r="G407" s="3"/>
       <c r="V407" s="3"/>
       <c r="W407" s="36" t="s">
         <v>773</v>
@@ -17547,6 +17629,14 @@
       <c r="Y407" s="3"/>
     </row>
     <row r="408" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D408" s="3"/>
+      <c r="E408" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F408" s="19">
+        <v>2012</v>
+      </c>
+      <c r="G408" s="3"/>
       <c r="V408" s="3"/>
       <c r="W408" s="36" t="s">
         <v>774</v>
@@ -17557,6 +17647,14 @@
       <c r="Y408" s="3"/>
     </row>
     <row r="409" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D409" s="3"/>
+      <c r="E409" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="F409" s="19">
+        <v>2019</v>
+      </c>
+      <c r="G409" s="3"/>
       <c r="V409" s="3"/>
       <c r="W409" s="36" t="s">
         <v>775</v>
@@ -17567,6 +17665,14 @@
       <c r="Y409" s="3"/>
     </row>
     <row r="410" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D410" s="3"/>
+      <c r="E410" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="F410" s="19">
+        <v>2009</v>
+      </c>
+      <c r="G410" s="3"/>
       <c r="V410" s="3"/>
       <c r="W410" s="36" t="s">
         <v>776</v>
@@ -17577,6 +17683,14 @@
       <c r="Y410" s="3"/>
     </row>
     <row r="411" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D411" s="3"/>
+      <c r="E411" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="F411" s="19">
+        <v>2014</v>
+      </c>
+      <c r="G411" s="3"/>
       <c r="V411" s="3"/>
       <c r="W411" s="36" t="s">
         <v>777</v>
@@ -17587,6 +17701,14 @@
       <c r="Y411" s="3"/>
     </row>
     <row r="412" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D412" s="3"/>
+      <c r="E412" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F412" s="19">
+        <v>2018</v>
+      </c>
+      <c r="G412" s="3"/>
       <c r="V412" s="3"/>
       <c r="W412" s="36" t="s">
         <v>55</v>
@@ -17597,6 +17719,14 @@
       <c r="Y412" s="3"/>
     </row>
     <row r="413" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D413" s="3"/>
+      <c r="E413" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F413" s="19">
+        <v>2018</v>
+      </c>
+      <c r="G413" s="3"/>
       <c r="V413" s="3"/>
       <c r="W413" s="36" t="s">
         <v>778</v>
@@ -17607,6 +17737,14 @@
       <c r="Y413" s="3"/>
     </row>
     <row r="414" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D414" s="3"/>
+      <c r="E414" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="F414" s="19">
+        <v>2013</v>
+      </c>
+      <c r="G414" s="3"/>
       <c r="V414" s="3"/>
       <c r="W414" s="36" t="s">
         <v>464</v>
@@ -17617,6 +17755,14 @@
       <c r="Y414" s="3"/>
     </row>
     <row r="415" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D415" s="3"/>
+      <c r="E415" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="F415" s="19">
+        <v>1994</v>
+      </c>
+      <c r="G415" s="3"/>
       <c r="V415" s="3"/>
       <c r="W415" s="36" t="s">
         <v>779</v>
@@ -17627,6 +17773,14 @@
       <c r="Y415" s="3"/>
     </row>
     <row r="416" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D416" s="3"/>
+      <c r="E416" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="F416" s="19">
+        <v>2014</v>
+      </c>
+      <c r="G416" s="3"/>
       <c r="V416" s="3"/>
       <c r="W416" s="36" t="s">
         <v>780</v>
@@ -17636,7 +17790,15 @@
       </c>
       <c r="Y416" s="3"/>
     </row>
-    <row r="417" spans="22:25" x14ac:dyDescent="0.2">
+    <row r="417" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D417" s="3"/>
+      <c r="E417" s="18" t="s">
+        <v>410</v>
+      </c>
+      <c r="F417" s="19">
+        <v>2017</v>
+      </c>
+      <c r="G417" s="3"/>
       <c r="V417" s="3"/>
       <c r="W417" s="36" t="s">
         <v>781</v>
@@ -17646,7 +17808,15 @@
       </c>
       <c r="Y417" s="3"/>
     </row>
-    <row r="418" spans="22:25" x14ac:dyDescent="0.2">
+    <row r="418" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D418" s="3"/>
+      <c r="E418" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="F418" s="19">
+        <v>1999</v>
+      </c>
+      <c r="G418" s="3"/>
       <c r="V418" s="3"/>
       <c r="W418" s="36" t="s">
         <v>782</v>
@@ -17656,7 +17826,15 @@
       </c>
       <c r="Y418" s="3"/>
     </row>
-    <row r="419" spans="22:25" x14ac:dyDescent="0.2">
+    <row r="419" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D419" s="3"/>
+      <c r="E419" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F419" s="19">
+        <v>2019</v>
+      </c>
+      <c r="G419" s="3"/>
       <c r="V419" s="3"/>
       <c r="W419" s="36" t="s">
         <v>783</v>
@@ -17666,7 +17844,15 @@
       </c>
       <c r="Y419" s="3"/>
     </row>
-    <row r="420" spans="22:25" x14ac:dyDescent="0.2">
+    <row r="420" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="D420" s="3"/>
+      <c r="E420" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="F420" s="19">
+        <v>2019</v>
+      </c>
+      <c r="G420" s="3"/>
       <c r="V420" s="3"/>
       <c r="W420" s="36" t="s">
         <v>679</v>
@@ -17676,7 +17862,13 @@
       </c>
       <c r="Y420" s="3"/>
     </row>
-    <row r="421" spans="22:25" x14ac:dyDescent="0.2">
+    <row r="421" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="E421" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="F421" s="19">
+        <v>1994</v>
+      </c>
       <c r="V421" s="3"/>
       <c r="W421" s="36" t="s">
         <v>784</v>
@@ -17686,7 +17878,13 @@
       </c>
       <c r="Y421" s="3"/>
     </row>
-    <row r="422" spans="22:25" x14ac:dyDescent="0.2">
+    <row r="422" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="E422" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F422" s="19">
+        <v>2008</v>
+      </c>
       <c r="V422" s="3"/>
       <c r="W422" s="36" t="s">
         <v>419</v>
@@ -17696,7 +17894,13 @@
       </c>
       <c r="Y422" s="3"/>
     </row>
-    <row r="423" spans="22:25" x14ac:dyDescent="0.2">
+    <row r="423" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="E423" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F423" s="19">
+        <v>2010</v>
+      </c>
       <c r="V423" s="3"/>
       <c r="W423" s="36" t="s">
         <v>785</v>
@@ -17706,7 +17910,9 @@
       </c>
       <c r="Y423" s="3"/>
     </row>
-    <row r="424" spans="22:25" x14ac:dyDescent="0.2">
+    <row r="424" spans="4:25" x14ac:dyDescent="0.2">
+      <c r="E424" s="3"/>
+      <c r="F424" s="3"/>
       <c r="V424" s="3"/>
       <c r="W424" s="36" t="s">
         <v>786</v>
@@ -17716,7 +17922,7 @@
       </c>
       <c r="Y424" s="3"/>
     </row>
-    <row r="425" spans="22:25" x14ac:dyDescent="0.2">
+    <row r="425" spans="4:25" x14ac:dyDescent="0.2">
       <c r="V425" s="3"/>
       <c r="W425" s="36" t="s">
         <v>787</v>
@@ -17726,7 +17932,7 @@
       </c>
       <c r="Y425" s="3"/>
     </row>
-    <row r="426" spans="22:25" x14ac:dyDescent="0.2">
+    <row r="426" spans="4:25" x14ac:dyDescent="0.2">
       <c r="V426" s="3"/>
       <c r="W426" s="36" t="s">
         <v>788</v>
@@ -17736,7 +17942,7 @@
       </c>
       <c r="Y426" s="3"/>
     </row>
-    <row r="427" spans="22:25" x14ac:dyDescent="0.2">
+    <row r="427" spans="4:25" x14ac:dyDescent="0.2">
       <c r="V427" s="3"/>
       <c r="W427" s="36" t="s">
         <v>13</v>
@@ -17746,7 +17952,7 @@
       </c>
       <c r="Y427" s="3"/>
     </row>
-    <row r="428" spans="22:25" x14ac:dyDescent="0.2">
+    <row r="428" spans="4:25" x14ac:dyDescent="0.2">
       <c r="V428" s="3"/>
       <c r="W428" s="36" t="s">
         <v>789</v>
@@ -17756,7 +17962,7 @@
       </c>
       <c r="Y428" s="3"/>
     </row>
-    <row r="429" spans="22:25" x14ac:dyDescent="0.2">
+    <row r="429" spans="4:25" x14ac:dyDescent="0.2">
       <c r="V429" s="3"/>
       <c r="W429" s="36" t="s">
         <v>790</v>
@@ -17766,7 +17972,7 @@
       </c>
       <c r="Y429" s="3"/>
     </row>
-    <row r="430" spans="22:25" x14ac:dyDescent="0.2">
+    <row r="430" spans="4:25" x14ac:dyDescent="0.2">
       <c r="V430" s="3"/>
       <c r="W430" s="36" t="s">
         <v>528</v>
@@ -17776,7 +17982,7 @@
       </c>
       <c r="Y430" s="3"/>
     </row>
-    <row r="431" spans="22:25" x14ac:dyDescent="0.2">
+    <row r="431" spans="4:25" x14ac:dyDescent="0.2">
       <c r="V431" s="3"/>
       <c r="W431" s="36" t="s">
         <v>791</v>
@@ -17786,7 +17992,7 @@
       </c>
       <c r="Y431" s="3"/>
     </row>
-    <row r="432" spans="22:25" x14ac:dyDescent="0.2">
+    <row r="432" spans="4:25" x14ac:dyDescent="0.2">
       <c r="V432" s="3"/>
       <c r="W432" s="36" t="s">
         <v>792</v>
@@ -23169,7 +23375,7 @@
     <row r="970" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V970" s="3"/>
       <c r="W970" s="36" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="X970" s="36">
         <v>2024</v>
@@ -23309,7 +23515,7 @@
     <row r="984" spans="22:25" x14ac:dyDescent="0.2">
       <c r="V984" s="3"/>
       <c r="W984" s="36" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="X984" s="36">
         <v>2024</v>
@@ -23493,24 +23699,19 @@
       <c r="Y1002" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:F1 E411:E1048576 E2:E409 F2:F1048576">
-    <cfRule type="notContainsBlanks" dxfId="3" priority="2">
+  <conditionalFormatting sqref="E1:F1 E2:E427 F2:F1048576 E429:E1048576">
+    <cfRule type="notContainsBlanks" dxfId="2" priority="2">
       <formula>LEN(TRIM(E1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:I1048576">
-    <cfRule type="notContainsBlanks" dxfId="2" priority="3">
+  <conditionalFormatting sqref="H1:I1048576 N1:O1048576">
+    <cfRule type="notContainsBlanks" dxfId="1" priority="3">
       <formula>LEN(TRIM(H1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1048576">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="4">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="4">
       <formula>LEN(TRIM(K1))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N1:O1048576">
-    <cfRule type="notContainsBlanks" dxfId="0" priority="6">
-      <formula>LEN(TRIM(N1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lists.xlsx
+++ b/lists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/StatsAutomator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6623FF98-12AC-2349-B257-731B283CAC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F8CF71-EDE5-5841-AF7E-5DF54B0E8C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30220" windowHeight="17500" xr2:uid="{98AF27AA-E156-FB4B-94CA-68D339A0B8C2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2483" uniqueCount="1315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2489" uniqueCount="1321">
   <si>
     <t>Avatar</t>
   </si>
@@ -3981,6 +3981,24 @@
   </si>
   <si>
     <t>Blink Twice</t>
+  </si>
+  <si>
+    <t>2025 Box Office Title</t>
+  </si>
+  <si>
+    <t>2025 Box Office Year</t>
+  </si>
+  <si>
+    <t>Den of Thieves 2: Pantera</t>
+  </si>
+  <si>
+    <t>Wolf Man</t>
+  </si>
+  <si>
+    <t>One of Them Days</t>
+  </si>
+  <si>
+    <t>Flight Risk</t>
   </si>
 </sst>
 </file>
@@ -4135,7 +4153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4274,6 +4292,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4696,7 +4720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69789896-8E18-4F4E-96F8-276B9180E2A2}">
-  <dimension ref="A1:AB1002"/>
+  <dimension ref="A1:AE1002"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="27.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.5" style="1" bestFit="1" customWidth="1"/>
@@ -4727,10 +4751,12 @@
     <col min="26" max="26" width="28.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="2.83203125" style="1" customWidth="1"/>
-    <col min="29" max="16384" width="27.83203125" style="1"/>
+    <col min="29" max="30" width="27.83203125" style="1"/>
+    <col min="31" max="31" width="2.83203125" style="1" customWidth="1"/>
+    <col min="32" max="16384" width="27.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
         <v>674</v>
       </c>
@@ -4797,8 +4823,15 @@
         <v>1290</v>
       </c>
       <c r="AB1" s="7"/>
-    </row>
-    <row r="2" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC1" s="47" t="s">
+        <v>1315</v>
+      </c>
+      <c r="AD1" s="47" t="s">
+        <v>1316</v>
+      </c>
+      <c r="AE1" s="7"/>
+    </row>
+    <row r="2" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
@@ -4865,8 +4898,15 @@
         <v>2024</v>
       </c>
       <c r="AB2" s="3"/>
-    </row>
-    <row r="3" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC2" s="48" t="s">
+        <v>1317</v>
+      </c>
+      <c r="AD2" s="48">
+        <v>2025</v>
+      </c>
+      <c r="AE2" s="3"/>
+    </row>
+    <row r="3" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
@@ -4933,8 +4973,15 @@
         <v>2024</v>
       </c>
       <c r="AB3" s="3"/>
-    </row>
-    <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC3" s="48" t="s">
+        <v>1318</v>
+      </c>
+      <c r="AD3" s="48">
+        <v>2025</v>
+      </c>
+      <c r="AE3" s="3"/>
+    </row>
+    <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>2</v>
       </c>
@@ -5001,8 +5048,15 @@
         <v>2024</v>
       </c>
       <c r="AB4" s="3"/>
-    </row>
-    <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC4" s="48" t="s">
+        <v>1319</v>
+      </c>
+      <c r="AD4" s="48">
+        <v>2025</v>
+      </c>
+      <c r="AE4" s="3"/>
+    </row>
+    <row r="5" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>3</v>
       </c>
@@ -5069,8 +5123,15 @@
         <v>2024</v>
       </c>
       <c r="AB5" s="3"/>
-    </row>
-    <row r="6" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC5" s="48" t="s">
+        <v>1320</v>
+      </c>
+      <c r="AD5" s="48">
+        <v>2025</v>
+      </c>
+      <c r="AE5" s="3"/>
+    </row>
+    <row r="6" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>4</v>
       </c>
@@ -5137,8 +5198,11 @@
         <v>2024</v>
       </c>
       <c r="AB6" s="3"/>
-    </row>
-    <row r="7" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+    </row>
+    <row r="7" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>5</v>
       </c>
@@ -5206,7 +5270,7 @@
       </c>
       <c r="AB7" s="3"/>
     </row>
-    <row r="8" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>6</v>
       </c>
@@ -5274,7 +5338,7 @@
       </c>
       <c r="AB8" s="3"/>
     </row>
-    <row r="9" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
         <v>9</v>
       </c>
@@ -5342,7 +5406,7 @@
       </c>
       <c r="AB9" s="3"/>
     </row>
-    <row r="10" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>7</v>
       </c>
@@ -5410,7 +5474,7 @@
       </c>
       <c r="AB10" s="3"/>
     </row>
-    <row r="11" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>8</v>
       </c>
@@ -5478,7 +5542,7 @@
       </c>
       <c r="AB11" s="3"/>
     </row>
-    <row r="12" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
         <v>10</v>
       </c>
@@ -5546,7 +5610,7 @@
       </c>
       <c r="AB12" s="3"/>
     </row>
-    <row r="13" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
         <v>11</v>
       </c>
@@ -5614,7 +5678,7 @@
       </c>
       <c r="AB13" s="3"/>
     </row>
-    <row r="14" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
         <v>12</v>
       </c>
@@ -5682,7 +5746,7 @@
       </c>
       <c r="AB14" s="3"/>
     </row>
-    <row r="15" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
         <v>13</v>
       </c>
@@ -5746,7 +5810,7 @@
       </c>
       <c r="AB15" s="3"/>
     </row>
-    <row r="16" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
         <v>14</v>
       </c>
